--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -621,7 +621,7 @@
         <v>0.7436042439436601</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>1.010209847897446</v>
+        <v>1.010209708942419</v>
       </c>
       <c r="N2" s="6" t="n">
         <v>2.355134926155393</v>
@@ -836,10 +836,10 @@
         <v>0.5448876757882486</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.954614224715592</v>
+        <v>0.954614348687318</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.2503176205595681</v>
+        <v>0.2503176469934338</v>
       </c>
     </row>
     <row r="7">
@@ -883,10 +883,10 @@
         <v>0.1333081154126903</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.2972673844512854</v>
+        <v>0.2972673038617362</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.3227731372002025</v>
+        <v>0.3227732209898797</v>
       </c>
       <c r="N7" s="6" t="n">
         <v>1.165684511259543</v>
@@ -942,10 +942,10 @@
         <v>0.3204008684166899</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.3929283585845491</v>
+        <v>0.3929282291430767</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.1168021981659741</v>
+        <v>0.1168021635720615</v>
       </c>
     </row>
     <row r="9">
@@ -995,10 +995,10 @@
         <v>0.1963425037673241</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.955240422732913</v>
+        <v>0.9552406255062227</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.2504511273507257</v>
+        <v>0.2504511705778232</v>
       </c>
     </row>
     <row r="10">
@@ -1042,16 +1042,16 @@
         <v>0.09918275117008202</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.2509784211419124</v>
+        <v>0.2509785183066207</v>
       </c>
       <c r="M10" s="6" t="n">
         <v>0.290569732444071</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>1.279185901479832</v>
+        <v>1.279185740215488</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.3160122036496986</v>
+        <v>0.3160121726114453</v>
       </c>
     </row>
     <row r="11">
@@ -1101,10 +1101,10 @@
         <v>0.06558974900891346</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.3945423491046378</v>
+        <v>0.394542504761942</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.1172333790918061</v>
+        <v>0.1172334206599304</v>
       </c>
     </row>
     <row r="12">
@@ -1148,16 +1148,16 @@
         <v>0.1069176134689611</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.2743589950717296</v>
+        <v>0.2743588951276641</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.2839433165238308</v>
+        <v>0.2839434179769031</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.4779026710489265</v>
+        <v>0.4779025366285532</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.13906527232931</v>
+        <v>0.1390652377953301</v>
       </c>
     </row>
     <row r="13">
@@ -1260,10 +1260,10 @@
         <v>0.2809499867168403</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.8040486205741388</v>
+        <v>0.8040484128217973</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.2173517357467096</v>
+        <v>0.2173516890170593</v>
       </c>
     </row>
     <row r="15">
@@ -1366,10 +1366,10 @@
         <v>0.2858148366906854</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.05164832892848925</v>
+        <v>0.05164825669291973</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.01692793764124301</v>
+        <v>0.01692791435767682</v>
       </c>
     </row>
     <row r="17">
@@ -1419,10 +1419,10 @@
         <v>0.1086386057209463</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.5945028261378276</v>
+        <v>0.5945030250842338</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.1682660721541926</v>
+        <v>0.1682661207424472</v>
       </c>
     </row>
     <row r="18">
@@ -1466,16 +1466,16 @@
         <v>-0.1030739944664463</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.2251965228529125</v>
+        <v>0.2251966145171875</v>
       </c>
       <c r="M18" s="6" t="n">
         <v>0.5727283335086024</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>2.128750968890241</v>
+        <v>2.128750670007718</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.4625935898638278</v>
+        <v>0.4625935432910708</v>
       </c>
     </row>
     <row r="19">
@@ -1519,16 +1519,16 @@
         <v>0.1037840135498129</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>-0.0207747908867556</v>
+        <v>-0.02077471984685031</v>
       </c>
       <c r="M19" s="6" t="n">
         <v>0.04504573209089346</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1261862555799129</v>
+        <v>0.1261863495430817</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.04040734030535509</v>
+        <v>0.04040736924076072</v>
       </c>
     </row>
     <row r="20">
@@ -1625,16 +1625,16 @@
         <v>0.0697280224698984</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.1610200043155849</v>
+        <v>0.1610198868090169</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.1769572518877205</v>
+        <v>0.1769573726424654</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.371062441170092</v>
+        <v>0.3710626869738884</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.1109275695395773</v>
+        <v>0.1109276359285298</v>
       </c>
     </row>
     <row r="22">
@@ -1737,10 +1737,10 @@
         <v>0.2205932014710026</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.7771622924682438</v>
+        <v>0.7771621800384252</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.2112739110392707</v>
+        <v>0.211273885496057</v>
       </c>
     </row>
     <row r="24">
@@ -1882,16 +1882,16 @@
         <v>0.01441086506525235</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.1530451251392011</v>
+        <v>0.1530450189146859</v>
       </c>
       <c r="M26" s="6" t="n">
         <v>0.103769490809156</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.1581011791733111</v>
+        <v>0.1581010720151732</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.05014394978003933</v>
+        <v>0.0501439173903897</v>
       </c>
     </row>
     <row r="27">
@@ -1941,10 +1941,10 @@
         <v>0.1708439543224261</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.2206642493248834</v>
+        <v>0.2206643606772303</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.06872362123505815</v>
+        <v>0.06872365373235878</v>
       </c>
     </row>
     <row r="28">
@@ -1994,10 +1994,10 @@
         <v>0.1043722863254177</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.08155100976358765</v>
+        <v>0.08155093053326623</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.02647647926155727</v>
+        <v>0.02647645419629985</v>
       </c>
     </row>
     <row r="29">
@@ -2047,10 +2047,10 @@
         <v>0.06992864917324559</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.4555015236136077</v>
+        <v>0.4555016355440606</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.1332808620225299</v>
+        <v>0.1332808910729144</v>
       </c>
     </row>
     <row r="30">
@@ -2147,16 +2147,16 @@
         <v>0.01324972665635937</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.04479351445310042</v>
+        <v>0.04479357756462998</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.04746248547164411</v>
+        <v>0.04746254890602808</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.4362772085956768</v>
+        <v>0.4362773278637815</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.1282692612792513</v>
+        <v>0.1282692925096507</v>
       </c>
     </row>
     <row r="32">
@@ -2256,7 +2256,7 @@
         <v>-0.003774464122493382</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.04051677120261798</v>
+        <v>0.04051684587407212</v>
       </c>
       <c r="N33" s="6" t="n">
         <v>0.2438158503473316</v>
@@ -2309,13 +2309,13 @@
         <v>0.003112539173837359</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.05763040998071811</v>
+        <v>0.05763047437933166</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.5608312338381856</v>
+        <v>0.5608310935824961</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.1599839558418512</v>
+        <v>0.1599839210966141</v>
       </c>
     </row>
   </sheetData>
@@ -2332,7 +2332,7 @@
   <dimension ref="A1:K68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
@@ -2347,7 +2347,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="9">
-        <f>== IBD RS RATING LEADERS &amp; LAGGARDS ===</f>
+        <f>== IBD RELATIVE STRENGTH LEADERS &amp; LAGGARDS ===</f>
         <v/>
       </c>
     </row>
@@ -3957,7 +3957,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>1.010209847897446</v>
+        <v>1.010209708942419</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>0.04051677120261798</v>
+        <v>0.04051684587407212</v>
       </c>
     </row>
     <row r="50">
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.3227731372002025</v>
+        <v>0.3227732209898797</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>0.04746248547164411</v>
+        <v>0.04746254890602808</v>
       </c>
     </row>
     <row r="53">
@@ -4339,7 +4339,7 @@
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.05763040998071811</v>
+        <v>0.05763047437933166</v>
       </c>
     </row>
     <row r="54">
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>0.05164832892848925</v>
+        <v>0.05164825669291973</v>
       </c>
     </row>
     <row r="60">
@@ -4535,7 +4535,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>0.08155100976358765</v>
+        <v>0.08155093053326623</v>
       </c>
     </row>
     <row r="61">
@@ -4558,7 +4558,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>2.128750968890241</v>
+        <v>2.128750670007718</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4580,7 +4580,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>0.1261862555799129</v>
+        <v>0.1261863495430817</v>
       </c>
     </row>
     <row r="62">
@@ -4625,7 +4625,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>0.1581011791733111</v>
+        <v>0.1581010720151732</v>
       </c>
     </row>
     <row r="63">
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>1.279185901479832</v>
+        <v>1.279185740215488</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4715,7 +4715,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>0.2206642493248834</v>
+        <v>0.2206643606772303</v>
       </c>
     </row>
     <row r="65">
@@ -4738,7 +4738,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.955240422732913</v>
+        <v>0.9552406255062227</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.954614224715592</v>
+        <v>0.954614348687318</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4828,7 +4828,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.8040486205741388</v>
+        <v>0.8040484128217973</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.7771622924682438</v>
+        <v>0.7771621800384252</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.371062441170092</v>
+        <v>0.3710626869738884</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -624,10 +624,10 @@
         <v>1.010209708942419</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>2.355134926155393</v>
+        <v>2.355135313245017</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>0.4970512330780694</v>
+        <v>0.497051290650814</v>
       </c>
     </row>
     <row r="3">
@@ -783,10 +783,10 @@
         <v>0.5072741660579498</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>1.578203601226092</v>
+        <v>1.578203373729222</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.3712155729166799</v>
+        <v>0.3712155325853346</v>
       </c>
     </row>
     <row r="6">
@@ -836,10 +836,10 @@
         <v>0.5448876757882486</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.954614348687318</v>
+        <v>0.9546139767721875</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.2503176469934338</v>
+        <v>0.2503175676918432</v>
       </c>
     </row>
     <row r="7">
@@ -889,10 +889,10 @@
         <v>0.3227732209898797</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>1.165684511259543</v>
+        <v>1.165684735859766</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.2937937936916526</v>
+        <v>0.2937938384175214</v>
       </c>
     </row>
     <row r="8">
@@ -1101,10 +1101,10 @@
         <v>0.06558974900891346</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.394542504761942</v>
+        <v>0.3945421934473683</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.1172334206599304</v>
+        <v>0.1172333375236878</v>
       </c>
     </row>
     <row r="12">
@@ -1148,10 +1148,10 @@
         <v>0.1069176134689611</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.2743588951276641</v>
+        <v>0.2743589950717296</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.2839434179769031</v>
+        <v>0.2839433165238308</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>0.4779025366285532</v>
@@ -1207,10 +1207,10 @@
         <v>0.4547730613970824</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.6408962356626946</v>
+        <v>0.6408963873346893</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.1794884874013067</v>
+        <v>0.1794885237422936</v>
       </c>
     </row>
     <row r="14">
@@ -1260,10 +1260,10 @@
         <v>0.2809499867168403</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.8040484128217973</v>
+        <v>0.8040486205741388</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.2173516890170593</v>
+        <v>0.2173517357467096</v>
       </c>
     </row>
     <row r="15">
@@ -1416,7 +1416,7 @@
         <v>0.1269935770417672</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.1086386057209463</v>
+        <v>0.1086387018966761</v>
       </c>
       <c r="N17" s="6" t="n">
         <v>0.5945030250842338</v>
@@ -1472,10 +1472,10 @@
         <v>0.5727283335086024</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>2.128750670007718</v>
+        <v>2.128750968890241</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.4625935432910708</v>
+        <v>0.4625935898638278</v>
       </c>
     </row>
     <row r="19">
@@ -1525,10 +1525,10 @@
         <v>0.04504573209089346</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1261863495430817</v>
+        <v>0.1261861616167599</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.04040736924076072</v>
+        <v>0.04040731136995301</v>
       </c>
     </row>
     <row r="20">
@@ -1578,10 +1578,10 @@
         <v>-0.01807299664187034</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.3374907422050768</v>
+        <v>0.3374908396357126</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.1017851845177644</v>
+        <v>0.1017852112712527</v>
       </c>
     </row>
     <row r="21">
@@ -1631,10 +1631,10 @@
         <v>0.1769573726424654</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.3710626869738884</v>
+        <v>0.3710625231046811</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.1109276359285298</v>
+        <v>0.1109275916692265</v>
       </c>
     </row>
     <row r="22">
@@ -1681,13 +1681,13 @@
         <v>0.2118612911830753</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.1908527879363535</v>
+        <v>0.1908527102660371</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.7606480008694114</v>
+        <v>0.7606478310904075</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.2075103056402838</v>
+        <v>0.2075102668269408</v>
       </c>
     </row>
     <row r="23">
@@ -1737,10 +1737,10 @@
         <v>0.2205932014710026</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.7771621800384252</v>
+        <v>0.7771622924682438</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.211273885496057</v>
+        <v>0.2112739110392707</v>
       </c>
     </row>
     <row r="24">
@@ -1888,10 +1888,10 @@
         <v>0.103769490809156</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.1581010720151732</v>
+        <v>0.1581012863314686</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.0501439173903897</v>
+        <v>0.05014398216969251</v>
       </c>
     </row>
     <row r="27">
@@ -2094,16 +2094,16 @@
         <v>0.1041879207185539</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.01945113565396261</v>
+        <v>0.01945122145725464</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>-0.0756123616951746</v>
+        <v>-0.0756124322422983</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.6507225407825037</v>
+        <v>0.6507226532661234</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.1818382104874459</v>
+        <v>0.1818382373317387</v>
       </c>
     </row>
     <row r="31">
@@ -2147,16 +2147,16 @@
         <v>0.01324972665635937</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.04479357756462998</v>
+        <v>0.04479351445310042</v>
       </c>
       <c r="M31" s="6" t="n">
         <v>0.04746254890602808</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.4362773278637815</v>
+        <v>0.4362772085956768</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.1282692925096507</v>
+        <v>0.1282692612792513</v>
       </c>
     </row>
     <row r="32">
@@ -2259,10 +2259,10 @@
         <v>0.04051684587407212</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.2438158503473316</v>
+        <v>0.2438159570483636</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.07543796118293367</v>
+        <v>0.07543799193516465</v>
       </c>
     </row>
     <row r="34">
@@ -4024,7 +4024,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.0756123616951746</v>
+        <v>-0.0756124322422983</v>
       </c>
     </row>
     <row r="47">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>2.355134926155393</v>
+        <v>2.355135313245017</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4558,7 +4558,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>2.128750670007718</v>
+        <v>2.128750968890241</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4580,7 +4580,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>0.1261863495430817</v>
+        <v>0.1261861616167599</v>
       </c>
     </row>
     <row r="62">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>1.578203601226092</v>
+        <v>1.578203373729222</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4625,7 +4625,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>0.1581010720151732</v>
+        <v>0.1581012863314686</v>
       </c>
     </row>
     <row r="63">
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>1.165684511259543</v>
+        <v>1.165684735859766</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4760,7 +4760,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.2438158503473316</v>
+        <v>0.2438159570483636</v>
       </c>
     </row>
     <row r="66">
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.954614348687318</v>
+        <v>0.9546139767721875</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4828,7 +4828,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.8040484128217973</v>
+        <v>0.8040486205741388</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4850,7 +4850,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.3374907422050768</v>
+        <v>0.3374908396357126</v>
       </c>
     </row>
     <row r="68">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.7771621800384252</v>
+        <v>0.7771622924682438</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.3710626869738884</v>
+        <v>0.3710625231046811</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -624,10 +624,10 @@
         <v>1.010209708942419</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>2.355135313245017</v>
+        <v>2.355134926155393</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>0.497051290650814</v>
+        <v>0.4970512330780694</v>
       </c>
     </row>
     <row r="3">
@@ -836,10 +836,10 @@
         <v>0.5448876757882486</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.9546139767721875</v>
+        <v>0.954614224715592</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.2503175676918432</v>
+        <v>0.2503176205595681</v>
       </c>
     </row>
     <row r="7">
@@ -883,16 +883,16 @@
         <v>0.1333081154126903</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.2972673038617362</v>
+        <v>0.2972673844512854</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.3227732209898797</v>
+        <v>0.3227731372002025</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>1.165684735859766</v>
+        <v>1.165684511259543</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.2937938384175214</v>
+        <v>0.2937937936916526</v>
       </c>
     </row>
     <row r="8">
@@ -1042,16 +1042,16 @@
         <v>0.09918275117008202</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.2509785183066207</v>
+        <v>0.2509784211419124</v>
       </c>
       <c r="M10" s="6" t="n">
         <v>0.290569732444071</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>1.279185740215488</v>
+        <v>1.279185901479832</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.3160121726114453</v>
+        <v>0.3160122036496986</v>
       </c>
     </row>
     <row r="11">
@@ -1101,10 +1101,10 @@
         <v>0.06558974900891346</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.3945421934473683</v>
+        <v>0.3945423491046378</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.1172333375236878</v>
+        <v>0.1172333790918061</v>
       </c>
     </row>
     <row r="12">
@@ -1148,16 +1148,16 @@
         <v>0.1069176134689611</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.2743589950717296</v>
+        <v>0.2743588951276641</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.2839433165238308</v>
+        <v>0.2839434179769031</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.4779025366285532</v>
+        <v>0.4779026710489265</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.1390652377953301</v>
+        <v>0.13906527232931</v>
       </c>
     </row>
     <row r="13">
@@ -1307,16 +1307,16 @@
         <v>0.2219137641347035</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.06348971952186466</v>
+        <v>0.0634898149323575</v>
       </c>
       <c r="M15" s="6" t="n">
         <v>0.04188666432932187</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.2968041964544554</v>
+        <v>0.2968043383204706</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.09049782171493925</v>
+        <v>0.09049786148053518</v>
       </c>
     </row>
     <row r="16">
@@ -1416,13 +1416,13 @@
         <v>0.1269935770417672</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.1086387018966761</v>
+        <v>0.1086386057209463</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.5945030250842338</v>
+        <v>0.5945029256110246</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.1682661207424472</v>
+        <v>0.1682660964483189</v>
       </c>
     </row>
     <row r="18">
@@ -1472,10 +1472,10 @@
         <v>0.5727283335086024</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>2.128750968890241</v>
+        <v>2.128750371125252</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.4625935898638278</v>
+        <v>0.4625934967183196</v>
       </c>
     </row>
     <row r="19">
@@ -1519,16 +1519,16 @@
         <v>0.1037840135498129</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>-0.02077471984685031</v>
+        <v>-0.0207747908867556</v>
       </c>
       <c r="M19" s="6" t="n">
         <v>0.04504573209089346</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1261861616167599</v>
+        <v>0.1261862555799129</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.04040731136995301</v>
+        <v>0.04040734030535509</v>
       </c>
     </row>
     <row r="20">
@@ -1572,10 +1572,10 @@
         <v>0.1143574030956209</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.09456440928460075</v>
+        <v>0.09456434403219105</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>-0.01807299664187034</v>
+        <v>-0.01807310166919218</v>
       </c>
       <c r="N20" s="6" t="n">
         <v>0.3374908396357126</v>
@@ -1681,7 +1681,7 @@
         <v>0.2118612911830753</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.1908527102660371</v>
+        <v>0.1908526325957307</v>
       </c>
       <c r="N22" s="6" t="n">
         <v>0.7606478310904075</v>
@@ -1737,10 +1737,10 @@
         <v>0.2205932014710026</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.7771622924682438</v>
+        <v>0.7771621800384252</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.2112739110392707</v>
+        <v>0.211273885496057</v>
       </c>
     </row>
     <row r="24">
@@ -1882,10 +1882,10 @@
         <v>0.01441086506525235</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.1530450189146859</v>
+        <v>0.1530451251392011</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.103769490809156</v>
+        <v>0.1037693934696982</v>
       </c>
       <c r="N26" s="6" t="n">
         <v>0.1581012863314686</v>
@@ -1935,10 +1935,10 @@
         <v>-0.01811792323657113</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.216795918243009</v>
+        <v>0.2167958075953236</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.1708439543224261</v>
+        <v>0.1708440567707739</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>0.2206643606772303</v>
@@ -1994,10 +1994,10 @@
         <v>0.1043722863254177</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.08155093053326623</v>
+        <v>0.08155100976358765</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.02647645419629985</v>
+        <v>0.02647647926155727</v>
       </c>
     </row>
     <row r="29">
@@ -2147,16 +2147,16 @@
         <v>0.01324972665635937</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.04479351445310042</v>
+        <v>0.04479357756462998</v>
       </c>
       <c r="M31" s="6" t="n">
         <v>0.04746254890602808</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.4362772085956768</v>
+        <v>0.4362773278637815</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.1282692612792513</v>
+        <v>0.1282692925096507</v>
       </c>
     </row>
     <row r="32">
@@ -2259,10 +2259,10 @@
         <v>0.04051684587407212</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.2438159570483636</v>
+        <v>0.2438158503473316</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.07543799193516465</v>
+        <v>0.07543796118293367</v>
       </c>
     </row>
     <row r="34">
@@ -2309,13 +2309,13 @@
         <v>0.003112539173837359</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.05763047437933166</v>
+        <v>0.05763040998071811</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.5608310935824961</v>
+        <v>0.5608309533268316</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.1599839210966141</v>
+        <v>0.1599838863513809</v>
       </c>
     </row>
   </sheetData>
@@ -4069,7 +4069,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.01807299664187034</v>
+        <v>-0.01807310166919218</v>
       </c>
     </row>
     <row r="48">
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.3227732209898797</v>
+        <v>0.3227731372002025</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4339,7 +4339,7 @@
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.05763047437933166</v>
+        <v>0.05763040998071811</v>
       </c>
     </row>
     <row r="54">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>2.355135313245017</v>
+        <v>2.355134926155393</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4535,7 +4535,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>0.08155093053326623</v>
+        <v>0.08155100976358765</v>
       </c>
     </row>
     <row r="61">
@@ -4558,7 +4558,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>2.128750968890241</v>
+        <v>2.128750371125252</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4580,7 +4580,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>0.1261861616167599</v>
+        <v>0.1261862555799129</v>
       </c>
     </row>
     <row r="62">
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>1.279185740215488</v>
+        <v>1.279185901479832</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>1.165684735859766</v>
+        <v>1.165684511259543</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4760,7 +4760,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.2438159570483636</v>
+        <v>0.2438158503473316</v>
       </c>
     </row>
     <row r="66">
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.9546139767721875</v>
+        <v>0.954614224715592</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4805,7 +4805,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>0.2968041964544554</v>
+        <v>0.2968043383204706</v>
       </c>
     </row>
     <row r="67">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.7771622924682438</v>
+        <v>0.7771621800384252</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -480,24 +480,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="25" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="23" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -543,35 +544,40 @@
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>9M</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>1Y</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>3Y</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>3Y (Ann.)</t>
         </is>
@@ -591,7 +597,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Select Tech Hardware</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -609,25 +615,28 @@
         <v>0.0596016799461152</v>
       </c>
       <c r="I2" s="6" t="n">
+        <v>0.07489942919814063</v>
+      </c>
+      <c r="J2" s="6" t="n">
         <v>0.01315123773588533</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="K2" s="6" t="n">
         <v>0.09365603813922641</v>
       </c>
-      <c r="K2" s="6" t="n">
+      <c r="L2" s="6" t="n">
         <v>0.5325686619065126</v>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="M2" s="6" t="n">
         <v>0.7436042439436601</v>
       </c>
-      <c r="M2" s="6" t="n">
-        <v>1.010209708942419</v>
-      </c>
       <c r="N2" s="6" t="n">
-        <v>2.355134926155393</v>
+        <v>1.010209847897446</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>0.4970512330780694</v>
+        <v>2.355135313245017</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v>0.497051290650814</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +653,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Select Semiconductors</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -662,24 +671,27 @@
         <v>0.005319983623840674</v>
       </c>
       <c r="I3" s="6" t="n">
+        <v>0.08548743859925922</v>
+      </c>
+      <c r="J3" s="6" t="n">
         <v>-0.01547658754472736</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="K3" s="6" t="n">
         <v>-0.02028060070021043</v>
       </c>
-      <c r="K3" s="6" t="n">
+      <c r="L3" s="6" t="n">
         <v>0.4356763539097035</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="M3" s="6" t="n">
         <v>0.6811412165441184</v>
       </c>
-      <c r="M3" s="6" t="n">
+      <c r="N3" s="6" t="n">
         <v>0.8958286315873361</v>
       </c>
-      <c r="N3" s="6" t="n">
+      <c r="O3" s="6" t="n">
         <v>2.657534783520286</v>
       </c>
-      <c r="O3" s="6" t="n">
+      <c r="P3" s="6" t="n">
         <v>0.5407404635452537</v>
       </c>
     </row>
@@ -697,7 +709,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Select Energy</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -715,25 +727,28 @@
         <v>0.08032504538787344</v>
       </c>
       <c r="I4" s="6" t="n">
+        <v>0.05166388975889191</v>
+      </c>
+      <c r="J4" s="6" t="n">
         <v>0.0933945469306503</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="6" t="n">
         <v>0.08097113495569364</v>
       </c>
-      <c r="K4" s="6" t="n">
+      <c r="L4" s="6" t="n">
         <v>0.2055451494520224</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="6" t="n">
         <v>0.4424043077238904</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="N4" s="6" t="n">
         <v>0.592432619827618</v>
       </c>
-      <c r="N4" s="6" t="n">
-        <v>0.6060983892427367</v>
-      </c>
       <c r="O4" s="6" t="n">
-        <v>0.1710911945277593</v>
+        <v>0.6060982803667716</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v>0.1710911680653526</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +765,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Select Technology</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -768,25 +783,28 @@
         <v>0.008140390247403317</v>
       </c>
       <c r="I5" s="6" t="n">
+        <v>0.06680700137129025</v>
+      </c>
+      <c r="J5" s="6" t="n">
         <v>0.01327271894975146</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="6" t="n">
         <v>0.05250233690728567</v>
       </c>
-      <c r="K5" s="6" t="n">
+      <c r="L5" s="6" t="n">
         <v>0.3874473461230392</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="M5" s="6" t="n">
         <v>0.3765759197103189</v>
       </c>
-      <c r="M5" s="6" t="n">
+      <c r="N5" s="6" t="n">
         <v>0.5072741660579498</v>
       </c>
-      <c r="N5" s="6" t="n">
-        <v>1.578203373729222</v>
-      </c>
       <c r="O5" s="6" t="n">
-        <v>0.3712155325853346</v>
+        <v>1.578203601226092</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v>0.3712155729166799</v>
       </c>
     </row>
     <row r="6">
@@ -803,7 +821,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Select Biotechnology</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -821,25 +839,28 @@
         <v>-0.0006800563708752039</v>
       </c>
       <c r="I6" s="6" t="n">
+        <v>0.04702528354738855</v>
+      </c>
+      <c r="J6" s="6" t="n">
         <v>0.03413086948453592</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="K6" s="6" t="n">
         <v>0.1493938107319355</v>
       </c>
-      <c r="K6" s="6" t="n">
+      <c r="L6" s="6" t="n">
         <v>0.1909553141258775</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="M6" s="6" t="n">
         <v>0.2676963680730038</v>
       </c>
-      <c r="M6" s="6" t="n">
+      <c r="N6" s="6" t="n">
         <v>0.5448876757882486</v>
       </c>
-      <c r="N6" s="6" t="n">
-        <v>0.954614224715592</v>
-      </c>
       <c r="O6" s="6" t="n">
-        <v>0.2503176205595681</v>
+        <v>0.954614100743882</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v>0.2503175941257045</v>
       </c>
     </row>
     <row r="7">
@@ -856,7 +877,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Select Banking</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -874,25 +895,28 @@
         <v>0.02469778558142544</v>
       </c>
       <c r="I7" s="6" t="n">
+        <v>0.03427690384456317</v>
+      </c>
+      <c r="J7" s="6" t="n">
         <v>0.04103511705168761</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="6" t="n">
         <v>0.1818991373690566</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="L7" s="6" t="n">
         <v>0.1333081154126903</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="M7" s="6" t="n">
         <v>0.2972673844512854</v>
       </c>
-      <c r="M7" s="6" t="n">
+      <c r="N7" s="6" t="n">
         <v>0.3227731372002025</v>
       </c>
-      <c r="N7" s="6" t="n">
-        <v>1.165684511259543</v>
-      </c>
       <c r="O7" s="6" t="n">
-        <v>0.2937937936916526</v>
+        <v>1.165684286659368</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v>0.29379374896579</v>
       </c>
     </row>
     <row r="8">
@@ -909,7 +933,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Select Health Care</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -927,24 +951,27 @@
         <v>0.003862381043526097</v>
       </c>
       <c r="I8" s="6" t="n">
+        <v>0.04495612261685999</v>
+      </c>
+      <c r="J8" s="6" t="n">
         <v>0.02989913245182585</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="K8" s="6" t="n">
         <v>0.1853233481685301</v>
       </c>
-      <c r="K8" s="6" t="n">
+      <c r="L8" s="6" t="n">
         <v>0.1712164156328317</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="M8" s="6" t="n">
         <v>0.1458675776083378</v>
       </c>
-      <c r="M8" s="6" t="n">
+      <c r="N8" s="6" t="n">
         <v>0.3204008684166899</v>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="O8" s="6" t="n">
         <v>0.3929282291430767</v>
       </c>
-      <c r="O8" s="6" t="n">
+      <c r="P8" s="6" t="n">
         <v>0.1168021635720615</v>
       </c>
     </row>
@@ -962,7 +989,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Select Financials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -980,24 +1007,27 @@
         <v>0.02450144295549284</v>
       </c>
       <c r="I9" s="6" t="n">
+        <v>0.03930637775515411</v>
+      </c>
+      <c r="J9" s="6" t="n">
         <v>0.06014153967127922</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="6" t="n">
         <v>0.1813402908531168</v>
       </c>
-      <c r="K9" s="6" t="n">
+      <c r="L9" s="6" t="n">
         <v>0.1674809179118946</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="M9" s="6" t="n">
         <v>0.2129478059313981</v>
       </c>
-      <c r="M9" s="6" t="n">
+      <c r="N9" s="6" t="n">
         <v>0.1963425037673241</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="O9" s="6" t="n">
         <v>0.9552406255062227</v>
       </c>
-      <c r="O9" s="6" t="n">
+      <c r="P9" s="6" t="n">
         <v>0.2504511705778232</v>
       </c>
     </row>
@@ -1015,7 +1045,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Select Defense and Aerospace</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1033,24 +1063,27 @@
         <v>0.005564650754155132</v>
       </c>
       <c r="I10" s="6" t="n">
+        <v>0.05061557981605036</v>
+      </c>
+      <c r="J10" s="6" t="n">
         <v>0.07001045952554263</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="K10" s="6" t="n">
         <v>0.1424321312993577</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="L10" s="6" t="n">
         <v>0.09918275117008202</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="M10" s="6" t="n">
         <v>0.2509784211419124</v>
       </c>
-      <c r="M10" s="6" t="n">
+      <c r="N10" s="6" t="n">
         <v>0.290569732444071</v>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="O10" s="6" t="n">
         <v>1.279185901479832</v>
       </c>
-      <c r="O10" s="6" t="n">
+      <c r="P10" s="6" t="n">
         <v>0.3160122036496986</v>
       </c>
     </row>
@@ -1068,7 +1101,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Select Software &amp; IT Services</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1086,25 +1119,28 @@
         <v>0.01968331484611729</v>
       </c>
       <c r="I11" s="6" t="n">
+        <v>0.1058004996457023</v>
+      </c>
+      <c r="J11" s="6" t="n">
         <v>0.1489874728393643</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="6" t="n">
         <v>0.2302529112667384</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="L11" s="6" t="n">
         <v>0.3253472015954513</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="6" t="n">
         <v>0.02850940270176516</v>
       </c>
-      <c r="M11" s="6" t="n">
+      <c r="N11" s="6" t="n">
         <v>0.06558974900891346</v>
       </c>
-      <c r="N11" s="6" t="n">
-        <v>0.3945423491046378</v>
-      </c>
       <c r="O11" s="6" t="n">
-        <v>0.1172333790918061</v>
+        <v>0.394542504761942</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v>0.1172334206599304</v>
       </c>
     </row>
     <row r="12">
@@ -1121,7 +1157,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Select Transportation</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1139,25 +1175,28 @@
         <v>-0.0008865297286289042</v>
       </c>
       <c r="I12" s="6" t="n">
+        <v>0.02828470248145165</v>
+      </c>
+      <c r="J12" s="6" t="n">
         <v>-0.001128026661509463</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="K12" s="6" t="n">
         <v>0.101759730885508</v>
       </c>
-      <c r="K12" s="6" t="n">
+      <c r="L12" s="6" t="n">
         <v>0.1069176134689611</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="M12" s="6" t="n">
         <v>0.2743588951276641</v>
       </c>
-      <c r="M12" s="6" t="n">
+      <c r="N12" s="6" t="n">
         <v>0.2839434179769031</v>
       </c>
-      <c r="N12" s="6" t="n">
-        <v>0.4779026710489265</v>
-      </c>
       <c r="O12" s="6" t="n">
-        <v>0.13906527232931</v>
+        <v>0.4779025366285532</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v>0.1390652377953301</v>
       </c>
     </row>
     <row r="13">
@@ -1174,7 +1213,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Select Pharmaceuticals</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1192,25 +1231,28 @@
         <v>-0.007038060836033977</v>
       </c>
       <c r="I13" s="6" t="n">
+        <v>0.003854167503099193</v>
+      </c>
+      <c r="J13" s="6" t="n">
         <v>0.003259277343750089</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="K13" s="6" t="n">
         <v>0.06578533592929658</v>
       </c>
-      <c r="K13" s="6" t="n">
+      <c r="L13" s="6" t="n">
         <v>0.0588211296236365</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="M13" s="6" t="n">
         <v>0.1640082333798087</v>
       </c>
-      <c r="M13" s="6" t="n">
+      <c r="N13" s="6" t="n">
         <v>0.4547730613970824</v>
       </c>
-      <c r="N13" s="6" t="n">
-        <v>0.6408963873346893</v>
-      </c>
       <c r="O13" s="6" t="n">
-        <v>0.1794885237422936</v>
+        <v>0.6408960839907278</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v>0.1794884510603243</v>
       </c>
     </row>
     <row r="14">
@@ -1227,7 +1269,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Select Wireless</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1245,24 +1287,27 @@
         <v>0.0087777958867854</v>
       </c>
       <c r="I14" s="6" t="n">
+        <v>0.0573248025040396</v>
+      </c>
+      <c r="J14" s="6" t="n">
         <v>0.004707444207326272</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="K14" s="6" t="n">
         <v>0.01563559086606925</v>
       </c>
-      <c r="K14" s="6" t="n">
+      <c r="L14" s="6" t="n">
         <v>0.1988263906526939</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="M14" s="6" t="n">
         <v>0.2737881013938817</v>
       </c>
-      <c r="M14" s="6" t="n">
+      <c r="N14" s="6" t="n">
         <v>0.2809499867168403</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="O14" s="6" t="n">
         <v>0.8040486205741388</v>
       </c>
-      <c r="O14" s="6" t="n">
+      <c r="P14" s="6" t="n">
         <v>0.2173517357467096</v>
       </c>
     </row>
@@ -1280,7 +1325,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Select Enterprise Tech Services</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1298,25 +1343,28 @@
         <v>0.01823916631556166</v>
       </c>
       <c r="I15" s="6" t="n">
+        <v>0.0470016823000956</v>
+      </c>
+      <c r="J15" s="6" t="n">
         <v>0.09042681190295898</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="K15" s="6" t="n">
         <v>0.2110337717170336</v>
       </c>
-      <c r="K15" s="6" t="n">
+      <c r="L15" s="6" t="n">
         <v>0.2219137641347035</v>
       </c>
-      <c r="L15" s="6" t="n">
-        <v>0.0634898149323575</v>
-      </c>
       <c r="M15" s="6" t="n">
+        <v>0.06348971952186466</v>
+      </c>
+      <c r="N15" s="6" t="n">
         <v>0.04188666432932187</v>
       </c>
-      <c r="N15" s="6" t="n">
-        <v>0.2968043383204706</v>
-      </c>
       <c r="O15" s="6" t="n">
-        <v>0.09049786148053518</v>
+        <v>0.2968041964544554</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v>0.09049782171493925</v>
       </c>
     </row>
     <row r="16">
@@ -1333,7 +1381,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Select Health Care Services</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1351,25 +1399,28 @@
         <v>-0.002902295884392725</v>
       </c>
       <c r="I16" s="6" t="n">
+        <v>-0.005449122233102122</v>
+      </c>
+      <c r="J16" s="6" t="n">
         <v>-0.04167693704563358</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="K16" s="6" t="n">
         <v>0.0644250030294411</v>
       </c>
-      <c r="K16" s="6" t="n">
+      <c r="L16" s="6" t="n">
         <v>0.161826103987569</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="M16" s="6" t="n">
         <v>0.1628359321567898</v>
       </c>
-      <c r="M16" s="6" t="n">
+      <c r="N16" s="6" t="n">
         <v>0.2858148366906854</v>
       </c>
-      <c r="N16" s="6" t="n">
-        <v>0.05164825669291973</v>
-      </c>
       <c r="O16" s="6" t="n">
-        <v>0.01692791435767682</v>
+        <v>0.05164832892848925</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v>0.01692793764124301</v>
       </c>
     </row>
     <row r="17">
@@ -1386,7 +1437,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Select Insurance</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1404,25 +1455,28 @@
         <v>-0.01175758786794856</v>
       </c>
       <c r="I17" s="6" t="n">
+        <v>0.001026678362982647</v>
+      </c>
+      <c r="J17" s="6" t="n">
         <v>0.01806414762006625</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="K17" s="6" t="n">
         <v>0.1488157988062115</v>
       </c>
-      <c r="K17" s="6" t="n">
+      <c r="L17" s="6" t="n">
         <v>0.1317742955370285</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="M17" s="6" t="n">
         <v>0.1269935770417672</v>
       </c>
-      <c r="M17" s="6" t="n">
-        <v>0.1086386057209463</v>
-      </c>
       <c r="N17" s="6" t="n">
-        <v>0.5945029256110246</v>
+        <v>0.1086387018966761</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.1682660964483189</v>
+        <v>0.5945028261378276</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v>0.1682660721541926</v>
       </c>
     </row>
     <row r="18">
@@ -1439,7 +1493,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Select Gold</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1457,25 +1511,28 @@
         <v>0.006282206477857155</v>
       </c>
       <c r="I18" s="6" t="n">
+        <v>0.219402728457962</v>
+      </c>
+      <c r="J18" s="6" t="n">
         <v>0.220832586595942</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="K18" s="6" t="n">
         <v>-0.02237872098636251</v>
       </c>
-      <c r="K18" s="6" t="n">
+      <c r="L18" s="6" t="n">
         <v>-0.1030739944664463</v>
       </c>
-      <c r="L18" s="6" t="n">
-        <v>0.2251966145171875</v>
-      </c>
       <c r="M18" s="6" t="n">
+        <v>0.2251965228529125</v>
+      </c>
+      <c r="N18" s="6" t="n">
         <v>0.5727283335086024</v>
       </c>
-      <c r="N18" s="6" t="n">
-        <v>2.128750371125252</v>
-      </c>
       <c r="O18" s="6" t="n">
-        <v>0.4625934967183196</v>
+        <v>2.128750670007718</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v>0.4625935432910708</v>
       </c>
     </row>
     <row r="19">
@@ -1492,7 +1549,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Select Medical Tech &amp; Devices</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1510,25 +1567,28 @@
         <v>0.01418162722496152</v>
       </c>
       <c r="I19" s="6" t="n">
+        <v>0.06143070418559038</v>
+      </c>
+      <c r="J19" s="6" t="n">
         <v>0.07855047901457124</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="K19" s="6" t="n">
         <v>0.2512758145606664</v>
       </c>
-      <c r="K19" s="6" t="n">
+      <c r="L19" s="6" t="n">
         <v>0.1037840135498129</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="M19" s="6" t="n">
         <v>-0.0207747908867556</v>
       </c>
-      <c r="M19" s="6" t="n">
+      <c r="N19" s="6" t="n">
         <v>0.04504573209089346</v>
       </c>
-      <c r="N19" s="6" t="n">
-        <v>0.1261862555799129</v>
-      </c>
       <c r="O19" s="6" t="n">
-        <v>0.04040734030535509</v>
+        <v>0.1261861616167599</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v>0.04040731136995301</v>
       </c>
     </row>
     <row r="20">
@@ -1545,7 +1605,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Select Leisure</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1563,25 +1623,28 @@
         <v>0.006321874296733698</v>
       </c>
       <c r="I20" s="6" t="n">
+        <v>0.03793712850090891</v>
+      </c>
+      <c r="J20" s="6" t="n">
         <v>0.07225966385111793</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="K20" s="6" t="n">
         <v>0.1626825857238252</v>
       </c>
-      <c r="K20" s="6" t="n">
+      <c r="L20" s="6" t="n">
         <v>0.1143574030956209</v>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="M20" s="6" t="n">
         <v>0.09456434403219105</v>
       </c>
-      <c r="M20" s="6" t="n">
+      <c r="N20" s="6" t="n">
         <v>-0.01807310166919218</v>
       </c>
-      <c r="N20" s="6" t="n">
-        <v>0.3374908396357126</v>
-      </c>
       <c r="O20" s="6" t="n">
-        <v>0.1017852112712527</v>
+        <v>0.3374907422050768</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v>0.1017851845177644</v>
       </c>
     </row>
     <row r="21">
@@ -1598,7 +1661,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Select Real Estate Investment</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1616,25 +1679,28 @@
         <v>0.008062623251586132</v>
       </c>
       <c r="I21" s="6" t="n">
+        <v>0.00505276530500498</v>
+      </c>
+      <c r="J21" s="6" t="n">
         <v>0.0169648980466055</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="K21" s="6" t="n">
         <v>0.05005073396044812</v>
       </c>
-      <c r="K21" s="6" t="n">
+      <c r="L21" s="6" t="n">
         <v>0.0697280224698984</v>
       </c>
-      <c r="L21" s="6" t="n">
-        <v>0.1610198868090169</v>
-      </c>
       <c r="M21" s="6" t="n">
+        <v>0.1610200043155849</v>
+      </c>
+      <c r="N21" s="6" t="n">
         <v>0.1769573726424654</v>
       </c>
-      <c r="N21" s="6" t="n">
-        <v>0.3710625231046811</v>
-      </c>
       <c r="O21" s="6" t="n">
-        <v>0.1109275916692265</v>
+        <v>0.371062441170092</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v>0.1109275695395773</v>
       </c>
     </row>
     <row r="22">
@@ -1651,7 +1717,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Select Telecommunications</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1669,25 +1735,28 @@
         <v>0.02956393133612734</v>
       </c>
       <c r="I22" s="6" t="n">
+        <v>0.06189976238255812</v>
+      </c>
+      <c r="J22" s="6" t="n">
         <v>0.05996047019177753</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="K22" s="6" t="n">
         <v>0.02116956197886077</v>
       </c>
-      <c r="K22" s="6" t="n">
+      <c r="L22" s="6" t="n">
         <v>0.06051555528294839</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="M22" s="6" t="n">
         <v>0.2118612911830753</v>
       </c>
-      <c r="M22" s="6" t="n">
+      <c r="N22" s="6" t="n">
         <v>0.1908526325957307</v>
       </c>
-      <c r="N22" s="6" t="n">
-        <v>0.7606478310904075</v>
-      </c>
       <c r="O22" s="6" t="n">
-        <v>0.2075102668269408</v>
+        <v>0.7606476613114361</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v>0.207510228013603</v>
       </c>
     </row>
     <row r="23">
@@ -1704,7 +1773,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Select Environment &amp; Alt Energy</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1722,25 +1791,28 @@
         <v>0.002807440108967718</v>
       </c>
       <c r="I23" s="6" t="n">
+        <v>0.04464809660071722</v>
+      </c>
+      <c r="J23" s="6" t="n">
         <v>0.01285444774218236</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="K23" s="6" t="n">
         <v>0.00695363189152931</v>
       </c>
-      <c r="K23" s="6" t="n">
+      <c r="L23" s="6" t="n">
         <v>0.06814400336922555</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="M23" s="6" t="n">
         <v>0.1715386119958278</v>
       </c>
-      <c r="M23" s="6" t="n">
+      <c r="N23" s="6" t="n">
         <v>0.2205932014710026</v>
       </c>
-      <c r="N23" s="6" t="n">
-        <v>0.7771621800384252</v>
-      </c>
       <c r="O23" s="6" t="n">
-        <v>0.211273885496057</v>
+        <v>0.7771622924682438</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v>0.2112739110392707</v>
       </c>
     </row>
     <row r="24">
@@ -1757,7 +1829,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Select Industrials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1775,18 +1847,21 @@
         <v>0.005582214384167283</v>
       </c>
       <c r="I24" s="6" t="n">
+        <v>0.04315462478273102</v>
+      </c>
+      <c r="J24" s="6" t="n">
         <v>0.03786011081564511</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="K24" s="6" t="n">
         <v>0.08039418793302788</v>
       </c>
-      <c r="K24" s="6" t="n">
+      <c r="L24" s="6" t="n">
         <v>0.09161746251898828</v>
       </c>
-      <c r="L24" s="6" t="inlineStr"/>
       <c r="M24" s="6" t="inlineStr"/>
       <c r="N24" s="6" t="inlineStr"/>
       <c r="O24" s="6" t="inlineStr"/>
+      <c r="P24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -1802,7 +1877,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Select FinTech</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1820,24 +1895,27 @@
         <v>0.03073425867425694</v>
       </c>
       <c r="I25" s="6" t="n">
+        <v>0.07096397242860419</v>
+      </c>
+      <c r="J25" s="6" t="n">
         <v>0.08313405227755344</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="K25" s="6" t="n">
         <v>0.182887009405122</v>
       </c>
-      <c r="K25" s="6" t="n">
+      <c r="L25" s="6" t="n">
         <v>0.1411468645838347</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="M25" s="6" t="n">
         <v>-0.02634407317573639</v>
       </c>
-      <c r="M25" s="6" t="n">
+      <c r="N25" s="6" t="n">
         <v>-0.08811681501600022</v>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="O25" s="6" t="n">
         <v>0.2170699241309788</v>
       </c>
-      <c r="O25" s="6" t="n">
+      <c r="P25" s="6" t="n">
         <v>0.06767361457465726</v>
       </c>
     </row>
@@ -1855,7 +1933,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Select Consumer Staples</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1873,25 +1951,28 @@
         <v>0.01036922765197335</v>
       </c>
       <c r="I26" s="6" t="n">
+        <v>0.01812556702897683</v>
+      </c>
+      <c r="J26" s="6" t="n">
         <v>0.04703948529693491</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="K26" s="6" t="n">
         <v>0.0505359207808036</v>
       </c>
-      <c r="K26" s="6" t="n">
+      <c r="L26" s="6" t="n">
         <v>0.01441086506525235</v>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="M26" s="6" t="n">
         <v>0.1530451251392011</v>
       </c>
-      <c r="M26" s="6" t="n">
+      <c r="N26" s="6" t="n">
         <v>0.1037693934696982</v>
       </c>
-      <c r="N26" s="6" t="n">
-        <v>0.1581012863314686</v>
-      </c>
       <c r="O26" s="6" t="n">
-        <v>0.05014398216969251</v>
+        <v>0.1581010720151732</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v>0.0501439173903897</v>
       </c>
     </row>
     <row r="27">
@@ -1908,7 +1989,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Select Materials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1926,25 +2007,28 @@
         <v>-0.0007830266466521962</v>
       </c>
       <c r="I27" s="6" t="n">
+        <v>0.0573795247128368</v>
+      </c>
+      <c r="J27" s="6" t="n">
         <v>0.03508059597307511</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="K27" s="6" t="n">
         <v>-0.01562050680631599</v>
       </c>
-      <c r="K27" s="6" t="n">
+      <c r="L27" s="6" t="n">
         <v>-0.01811792323657113</v>
       </c>
-      <c r="L27" s="6" t="n">
-        <v>0.2167958075953236</v>
-      </c>
       <c r="M27" s="6" t="n">
-        <v>0.1708440567707739</v>
+        <v>0.216795918243009</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.2206643606772303</v>
+        <v>0.1708439543224261</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.06872365373235878</v>
+        <v>0.2206642493248834</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v>0.06872362123505815</v>
       </c>
     </row>
     <row r="28">
@@ -1961,7 +2045,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Select Chemicals</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -1979,25 +2063,28 @@
         <v>-0.007751914019033079</v>
       </c>
       <c r="I28" s="6" t="n">
+        <v>0.02399999445134937</v>
+      </c>
+      <c r="J28" s="6" t="n">
         <v>0.002135212282130317</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="K28" s="6" t="n">
         <v>0.0007107483367974066</v>
       </c>
-      <c r="K28" s="6" t="n">
+      <c r="L28" s="6" t="n">
         <v>0.01021688261231857</v>
       </c>
-      <c r="L28" s="6" t="n">
-        <v>0.2113066058440574</v>
-      </c>
       <c r="M28" s="6" t="n">
+        <v>0.2113065064625521</v>
+      </c>
+      <c r="N28" s="6" t="n">
         <v>0.1043722863254177</v>
       </c>
-      <c r="N28" s="6" t="n">
-        <v>0.08155100976358765</v>
-      </c>
       <c r="O28" s="6" t="n">
-        <v>0.02647647926155727</v>
+        <v>0.08155093053326623</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v>0.02647645419629985</v>
       </c>
     </row>
     <row r="29">
@@ -2014,7 +2101,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Select Retailing</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -2032,25 +2119,28 @@
         <v>-0.02326841535861557</v>
       </c>
       <c r="I29" s="6" t="n">
+        <v>-0.001106832213694009</v>
+      </c>
+      <c r="J29" s="6" t="n">
         <v>0.04094573692184733</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="K29" s="6" t="n">
         <v>0.03083946322787656</v>
       </c>
-      <c r="K29" s="6" t="n">
+      <c r="L29" s="6" t="n">
         <v>0.03781066799932487</v>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="M29" s="6" t="n">
         <v>0.1132968022326644</v>
       </c>
-      <c r="M29" s="6" t="n">
+      <c r="N29" s="6" t="n">
         <v>0.06992864917324559</v>
       </c>
-      <c r="N29" s="6" t="n">
-        <v>0.4555016355440606</v>
-      </c>
       <c r="O29" s="6" t="n">
-        <v>0.1332808910729144</v>
+        <v>0.4555015236136077</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v>0.1332808620225299</v>
       </c>
     </row>
     <row r="30">
@@ -2067,7 +2157,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Select Brokerage &amp; Inv Mgmt</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -2085,24 +2175,27 @@
         <v>0.03796478635466949</v>
       </c>
       <c r="I30" s="6" t="n">
+        <v>0.0592011089796165</v>
+      </c>
+      <c r="J30" s="6" t="n">
         <v>0.07497246087100673</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="K30" s="6" t="n">
         <v>0.08800855146147346</v>
       </c>
-      <c r="K30" s="6" t="n">
+      <c r="L30" s="6" t="n">
         <v>0.1041879207185539</v>
       </c>
-      <c r="L30" s="6" t="n">
-        <v>0.01945122145725464</v>
-      </c>
       <c r="M30" s="6" t="n">
-        <v>-0.0756124322422983</v>
+        <v>0.01945113565396261</v>
       </c>
       <c r="N30" s="6" t="n">
+        <v>-0.0756123616951746</v>
+      </c>
+      <c r="O30" s="6" t="n">
         <v>0.6507226532661234</v>
       </c>
-      <c r="O30" s="6" t="n">
+      <c r="P30" s="6" t="n">
         <v>0.1818382373317387</v>
       </c>
     </row>
@@ -2120,7 +2213,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Select Consumer Discretionary</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -2138,25 +2231,28 @@
         <v>-0.01756998571817414</v>
       </c>
       <c r="I31" s="6" t="n">
+        <v>0.01273985896569774</v>
+      </c>
+      <c r="J31" s="6" t="n">
         <v>0.01336204482301473</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="K31" s="6" t="n">
         <v>0.006406434014346374</v>
       </c>
-      <c r="K31" s="6" t="n">
+      <c r="L31" s="6" t="n">
         <v>0.01324972665635937</v>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="M31" s="6" t="n">
         <v>0.04479357756462998</v>
       </c>
-      <c r="M31" s="6" t="n">
-        <v>0.04746254890602808</v>
-      </c>
       <c r="N31" s="6" t="n">
-        <v>0.4362773278637815</v>
+        <v>0.04746248547164411</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.1282692925096507</v>
+        <v>0.4362772085956768</v>
+      </c>
+      <c r="P31" s="6" t="n">
+        <v>0.1282692612792513</v>
       </c>
     </row>
     <row r="32">
@@ -2173,7 +2269,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Select Construction &amp; Housing</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2191,24 +2287,27 @@
         <v>-0.01454973222115585</v>
       </c>
       <c r="I32" s="6" t="n">
+        <v>0.03399903231726653</v>
+      </c>
+      <c r="J32" s="6" t="n">
         <v>0.01416430559914184</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="K32" s="6" t="n">
         <v>0.0144927607850982</v>
       </c>
-      <c r="K32" s="6" t="n">
+      <c r="L32" s="6" t="n">
         <v>-0.06648786116969174</v>
       </c>
-      <c r="L32" s="6" t="n">
+      <c r="M32" s="6" t="n">
         <v>0.08613008717109305</v>
       </c>
-      <c r="M32" s="6" t="n">
+      <c r="N32" s="6" t="n">
         <v>0.03149104341912445</v>
       </c>
-      <c r="N32" s="6" t="n">
+      <c r="O32" s="6" t="n">
         <v>0.3961756775034286</v>
       </c>
-      <c r="O32" s="6" t="n">
+      <c r="P32" s="6" t="n">
         <v>0.1176693876139951</v>
       </c>
     </row>
@@ -2226,7 +2325,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Select Automotive</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -2244,25 +2343,28 @@
         <v>0.003629119229258126</v>
       </c>
       <c r="I33" s="6" t="n">
+        <v>0.02066807113794633</v>
+      </c>
+      <c r="J33" s="6" t="n">
         <v>0.03693290616924649</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="K33" s="6" t="n">
         <v>-0.007536303111343234</v>
       </c>
-      <c r="K33" s="6" t="n">
+      <c r="L33" s="6" t="n">
         <v>-0.06199276024727007</v>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="M33" s="6" t="n">
         <v>-0.003774464122493382</v>
       </c>
-      <c r="M33" s="6" t="n">
-        <v>0.04051684587407212</v>
-      </c>
       <c r="N33" s="6" t="n">
-        <v>0.2438158503473316</v>
+        <v>0.04051677120261798</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.07543796118293367</v>
+        <v>0.2438159570483636</v>
+      </c>
+      <c r="P33" s="6" t="n">
+        <v>0.07543799193516465</v>
       </c>
     </row>
     <row r="34">
@@ -2279,7 +2381,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Select Utilities</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -2297,25 +2399,28 @@
         <v>0.01774055325617097</v>
       </c>
       <c r="I34" s="6" t="n">
+        <v>-0.001281167878645406</v>
+      </c>
+      <c r="J34" s="6" t="n">
         <v>-0.03817676406908432</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="K34" s="6" t="n">
         <v>-0.03900594212390573</v>
       </c>
-      <c r="K34" s="6" t="n">
+      <c r="L34" s="6" t="n">
         <v>-0.05152052900082926</v>
       </c>
-      <c r="L34" s="6" t="n">
+      <c r="M34" s="6" t="n">
         <v>0.003112539173837359</v>
       </c>
-      <c r="M34" s="6" t="n">
-        <v>0.05763040998071811</v>
-      </c>
       <c r="N34" s="6" t="n">
-        <v>0.5608309533268316</v>
+        <v>0.05763053877795321</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.1599838863513809</v>
+        <v>0.5608312338381856</v>
+      </c>
+      <c r="P34" s="6" t="n">
+        <v>0.1599839558418512</v>
       </c>
     </row>
   </sheetData>
@@ -2329,18 +2434,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K68"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="33" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="27" customWidth="1" min="11" max="11"/>
   </cols>
@@ -2415,7 +2520,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Select Tech Hardware</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2437,7 +2542,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Select Utilities</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -2460,7 +2565,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Select Semiconductors</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2482,7 +2587,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Select Automotive</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -2505,7 +2610,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Select Energy</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2527,7 +2632,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Select Construction &amp; Housing</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2550,7 +2655,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Select Technology</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2572,7 +2677,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Select Consumer Discretionary</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2595,7 +2700,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Select Biotechnology</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2617,7 +2722,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Select Brokerage &amp; Inv Mgmt</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2640,7 +2745,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Select Banking</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2662,7 +2767,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Select Retailing</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2685,7 +2790,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Select Health Care</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2707,7 +2812,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Select Chemicals</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2730,7 +2835,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Select Financials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2752,7 +2857,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Select Materials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2775,7 +2880,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Select Defense and Aerospace</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2797,7 +2902,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Select Consumer Staples</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2820,7 +2925,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Select Software &amp; IT Services</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2842,7 +2947,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Select FinTech</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2858,7 +2963,7 @@
     <row r="14"/>
     <row r="15">
       <c r="A15" s="9">
-        <f>== PAST 3 MONTHS LEADERS &amp; LAGGARDS ===</f>
+        <f>== PAST 1 MONTH LEADERS &amp; LAGGARDS ===</f>
         <v/>
       </c>
     </row>
@@ -2885,7 +2990,7 @@
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>Top 10 - 3M</t>
+          <t>Top 10 - 1M</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -2911,7 +3016,7 @@
       </c>
       <c r="K16" s="10" t="inlineStr">
         <is>
-          <t>Bottom 10 - 3M</t>
+          <t>Bottom 10 - 1M</t>
         </is>
       </c>
     </row>
@@ -2921,21 +3026,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Select Medical Tech &amp; Devices</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.2512758145606664</v>
+        <v>0.220832586595942</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -2943,21 +3048,21 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Select Utilities</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.03900594212390573</v>
+        <v>-0.04167693704563358</v>
       </c>
     </row>
     <row r="18">
@@ -2971,7 +3076,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Select Software &amp; IT Services</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2980,7 +3085,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.2302529112667384</v>
+        <v>0.1489874728393643</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -2988,21 +3093,21 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Select Gold</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.02237872098636251</v>
+        <v>-0.03817676406908432</v>
       </c>
     </row>
     <row r="19">
@@ -3011,21 +3116,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Select Enterprise Tech Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.2110337717170336</v>
+        <v>0.0933945469306503</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -3038,7 +3143,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Select Semiconductors</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3047,7 +3152,7 @@
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.02028060070021043</v>
+        <v>-0.01547658754472736</v>
       </c>
     </row>
     <row r="20">
@@ -3056,21 +3161,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Select Health Care</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.1853233481685301</v>
+        <v>0.09042681190295898</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -3078,21 +3183,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Select Materials</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.01562050680631599</v>
+        <v>-0.001128026661509463</v>
       </c>
     </row>
     <row r="21">
@@ -3106,7 +3211,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Select FinTech</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3115,7 +3220,7 @@
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.182887009405122</v>
+        <v>0.08313405227755344</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -3123,21 +3228,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Select Automotive</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.007536303111343234</v>
+        <v>0.002135212282130317</v>
       </c>
     </row>
     <row r="22">
@@ -3146,21 +3251,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Select Banking</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.1818991373690566</v>
+        <v>0.07855047901457124</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -3168,21 +3273,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Select Chemicals</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>0.0007107483367974066</v>
+        <v>0.003259277343750089</v>
       </c>
     </row>
     <row r="23">
@@ -3191,12 +3296,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Select Financials</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3205,7 +3310,7 @@
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.1813402908531168</v>
+        <v>0.07497246087100673</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -3213,21 +3318,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Select Consumer Discretionary</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>0.006406434014346374</v>
+        <v>0.004707444207326272</v>
       </c>
     </row>
     <row r="24">
@@ -3241,7 +3346,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Select Leisure</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3250,7 +3355,7 @@
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.1626825857238252</v>
+        <v>0.07225966385111793</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -3263,7 +3368,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Select Environment &amp; Alt Energy</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3272,7 +3377,7 @@
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>0.00695363189152931</v>
+        <v>0.01285444774218236</v>
       </c>
     </row>
     <row r="25">
@@ -3281,21 +3386,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Select Biotechnology</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.1493938107319355</v>
+        <v>0.07001045952554263</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -3303,21 +3408,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FDCPX</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Select Construction &amp; Housing</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>0.0144927607850982</v>
+        <v>0.01315123773588533</v>
       </c>
     </row>
     <row r="26">
@@ -3326,12 +3431,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Select Insurance</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3340,7 +3445,7 @@
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.1488157988062115</v>
+        <v>0.06014153967127922</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -3348,28 +3453,28 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Select Wireless</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>0.01563559086606925</v>
+        <v>0.01327271894975146</v>
       </c>
     </row>
     <row r="27"/>
     <row r="28"/>
     <row r="29">
       <c r="A29" s="9">
-        <f>== PAST 6 MONTHS LEADERS &amp; LAGGARDS ===</f>
+        <f>== PAST 3 MONTHS LEADERS &amp; LAGGARDS ===</f>
         <v/>
       </c>
     </row>
@@ -3396,7 +3501,7 @@
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>Top 10 - 6M</t>
+          <t>Top 10 - 3M</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -3422,7 +3527,7 @@
       </c>
       <c r="K30" s="10" t="inlineStr">
         <is>
-          <t>Bottom 10 - 6M</t>
+          <t>Bottom 10 - 3M</t>
         </is>
       </c>
     </row>
@@ -3432,21 +3537,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FDCPX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Select Tech Hardware</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.5325686619065126</v>
+        <v>0.2512758145606664</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -3454,21 +3559,21 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Select Gold</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.1030739944664463</v>
+        <v>-0.03900594212390573</v>
       </c>
     </row>
     <row r="32">
@@ -3477,12 +3582,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Select Semiconductors</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3491,7 +3596,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.4356763539097035</v>
+        <v>0.2302529112667384</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -3499,21 +3604,21 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Select Construction &amp; Housing</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.06648786116969174</v>
+        <v>-0.02237872098636251</v>
       </c>
     </row>
     <row r="33">
@@ -3522,12 +3627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Select Technology</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3536,7 +3641,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.3874473461230392</v>
+        <v>0.2110337717170336</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -3544,21 +3649,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Select Automotive</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.06199276024727007</v>
+        <v>-0.02028060070021043</v>
       </c>
     </row>
     <row r="34">
@@ -3567,21 +3672,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Select Software &amp; IT Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.3253472015954513</v>
+        <v>0.1853233481685301</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -3589,21 +3694,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Select Utilities</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.05152052900082926</v>
+        <v>-0.01562050680631599</v>
       </c>
     </row>
     <row r="35">
@@ -3612,21 +3717,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Select Enterprise Tech Services</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.2219137641347035</v>
+        <v>0.182887009405122</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -3634,21 +3739,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Select Materials</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.01811792323657113</v>
+        <v>-0.007536303111343234</v>
       </c>
     </row>
     <row r="36">
@@ -3657,21 +3762,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Select Energy</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.2055451494520224</v>
+        <v>0.1818991373690566</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -3684,7 +3789,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Select Chemicals</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3693,7 +3798,7 @@
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>0.01021688261231857</v>
+        <v>0.0007107483367974066</v>
       </c>
     </row>
     <row r="37">
@@ -3702,21 +3807,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Select Wireless</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1988263906526939</v>
+        <v>0.1813402908531168</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -3729,7 +3834,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Select Consumer Discretionary</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3738,7 +3843,7 @@
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>0.01324972665635937</v>
+        <v>0.006406434014346374</v>
       </c>
     </row>
     <row r="38">
@@ -3747,21 +3852,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Select Biotechnology</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1909553141258775</v>
+        <v>0.1626825857238252</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -3769,21 +3874,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Select Consumer Staples</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>0.01441086506525235</v>
+        <v>0.00695363189152931</v>
       </c>
     </row>
     <row r="39">
@@ -3792,12 +3897,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Select Health Care</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3806,7 +3911,7 @@
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1712164156328317</v>
+        <v>0.1493938107319355</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -3814,12 +3919,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Select Retailing</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3828,7 +3933,7 @@
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0.03781066799932487</v>
+        <v>0.0144927607850982</v>
       </c>
     </row>
     <row r="40">
@@ -3837,12 +3942,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Select Financials</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3851,7 +3956,7 @@
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1674809179118946</v>
+        <v>0.1488157988062115</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -3859,28 +3964,28 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Select Pharmaceuticals</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>0.0588211296236365</v>
+        <v>0.01563559086606925</v>
       </c>
     </row>
     <row r="41"/>
     <row r="42"/>
     <row r="43">
       <c r="A43" s="9">
-        <f>== PAST 1 YEAR LEADERS &amp; LAGGARDS ===</f>
+        <f>== PAST 6 MONTHS LEADERS &amp; LAGGARDS ===</f>
         <v/>
       </c>
     </row>
@@ -3907,7 +4012,7 @@
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>Top 10 - 1Y</t>
+          <t>Top 10 - 6M</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -3933,7 +4038,7 @@
       </c>
       <c r="K44" s="10" t="inlineStr">
         <is>
-          <t>Bottom 10 - 1Y</t>
+          <t>Bottom 10 - 6M</t>
         </is>
       </c>
     </row>
@@ -3948,7 +4053,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Select Tech Hardware</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3957,29 +4062,29 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>1.010209708942419</v>
+        <v>0.5325686619065126</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Select FinTech</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.08811681501600022</v>
+        <v>-0.1030739944664463</v>
       </c>
     </row>
     <row r="46">
@@ -3993,7 +4098,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Select Semiconductors</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4002,29 +4107,29 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.8958286315873361</v>
+        <v>0.4356763539097035</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Select Brokerage &amp; Inv Mgmt</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.0756124322422983</v>
+        <v>-0.06648786116969174</v>
       </c>
     </row>
     <row r="47">
@@ -4033,34 +4138,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Select Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.592432619827618</v>
+        <v>0.3874473461230392</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Select Leisure</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4069,7 +4174,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.01807310166919218</v>
+        <v>-0.06199276024727007</v>
       </c>
     </row>
     <row r="48">
@@ -4078,43 +4183,43 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Select Gold</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.5727283335086024</v>
+        <v>0.3253472015954513</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Select Construction &amp; Housing</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>0.03149104341912445</v>
+        <v>-0.05152052900082926</v>
       </c>
     </row>
     <row r="49">
@@ -4123,43 +4228,43 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Select Biotechnology</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.5448876757882486</v>
+        <v>0.2219137641347035</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Select Automotive</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>0.04051684587407212</v>
+        <v>-0.01811792323657113</v>
       </c>
     </row>
     <row r="50">
@@ -4168,43 +4273,43 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Select Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.5072741660579498</v>
+        <v>0.2055451494520224</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Select Enterprise Tech Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>0.04188666432932187</v>
+        <v>0.01021688261231857</v>
       </c>
     </row>
     <row r="51">
@@ -4213,43 +4318,43 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Select Pharmaceuticals</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.4547730613970824</v>
+        <v>0.1988263906526939</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Select Medical Tech &amp; Devices</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0.04504573209089346</v>
+        <v>0.01324972665635937</v>
       </c>
     </row>
     <row r="52">
@@ -4258,43 +4363,43 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Select Banking</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.3227731372002025</v>
+        <v>0.1909553141258775</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Select Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>0.04746254890602808</v>
+        <v>0.01441086506525235</v>
       </c>
     </row>
     <row r="53">
@@ -4308,7 +4413,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Select Health Care</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4317,29 +4422,29 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.3204008684166899</v>
+        <v>0.1712164156328317</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Select Utilities</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.05763040998071811</v>
+        <v>0.03781066799932487</v>
       </c>
     </row>
     <row r="54">
@@ -4348,50 +4453,50 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Select Defense and Aerospace</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.290569732444071</v>
+        <v>0.1674809179118946</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Select Software &amp; IT Services</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.06558974900891346</v>
+        <v>0.0588211296236365</v>
       </c>
     </row>
     <row r="55"/>
     <row r="56"/>
     <row r="57">
       <c r="A57" s="9">
-        <f>== PAST 3 YEARS LEADERS &amp; LAGGARDS ===</f>
+        <f>== PAST 1 YEAR LEADERS &amp; LAGGARDS ===</f>
         <v/>
       </c>
     </row>
@@ -4418,7 +4523,7 @@
       </c>
       <c r="E58" s="10" t="inlineStr">
         <is>
-          <t>Top 10 - 3Y</t>
+          <t>Top 10 - 1Y</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -4444,7 +4549,7 @@
       </c>
       <c r="K58" s="10" t="inlineStr">
         <is>
-          <t>Bottom 10 - 3Y</t>
+          <t>Bottom 10 - 1Y</t>
         </is>
       </c>
     </row>
@@ -4454,12 +4559,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FDCPX</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Select Semiconductors</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4468,7 +4573,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>2.657534783520286</v>
+        <v>1.010209847897446</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4476,21 +4581,21 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Select Health Care Services</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>0.05164825669291973</v>
+        <v>-0.08811681501600022</v>
       </c>
     </row>
     <row r="60">
@@ -4499,12 +4604,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FDCPX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Select Tech Hardware</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4513,7 +4618,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>2.355134926155393</v>
+        <v>0.8958286315873361</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4521,21 +4626,21 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Select Chemicals</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>0.08155100976358765</v>
+        <v>-0.0756123616951746</v>
       </c>
     </row>
     <row r="61">
@@ -4544,21 +4649,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Select Gold</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>2.128750371125252</v>
+        <v>0.592432619827618</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4566,21 +4671,21 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Select Medical Tech &amp; Devices</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>0.1261862555799129</v>
+        <v>-0.01807310166919218</v>
       </c>
     </row>
     <row r="62">
@@ -4589,21 +4694,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Select Technology</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>1.578203373729222</v>
+        <v>0.5727283335086024</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4611,21 +4716,21 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Select Consumer Staples</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>0.1581012863314686</v>
+        <v>0.03149104341912445</v>
       </c>
     </row>
     <row r="63">
@@ -4634,21 +4739,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Select Defense and Aerospace</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>1.279185901479832</v>
+        <v>0.5448876757882486</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4656,21 +4761,21 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Select FinTech</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>0.2170699241309788</v>
+        <v>0.04051677120261798</v>
       </c>
     </row>
     <row r="64">
@@ -4679,21 +4784,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Select Banking</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>1.165684511259543</v>
+        <v>0.5072741660579498</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4701,21 +4806,21 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Select Materials</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>0.2206643606772303</v>
+        <v>0.04188666432932187</v>
       </c>
     </row>
     <row r="65">
@@ -4724,21 +4829,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Select Financials</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.9552406255062227</v>
+        <v>0.4547730613970824</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4746,21 +4851,21 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Select Automotive</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.2438158503473316</v>
+        <v>0.04504573209089346</v>
       </c>
     </row>
     <row r="66">
@@ -4769,21 +4874,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Select Biotechnology</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.954614224715592</v>
+        <v>0.3227731372002025</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4791,21 +4896,21 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Select Enterprise Tech Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>0.2968043383204706</v>
+        <v>0.04746248547164411</v>
       </c>
     </row>
     <row r="67">
@@ -4814,21 +4919,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Select Wireless</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.8040486205741388</v>
+        <v>0.3204008684166899</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4836,21 +4941,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Select Leisure</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.3374908396357126</v>
+        <v>0.05763053877795321</v>
       </c>
     </row>
     <row r="68">
@@ -4859,21 +4964,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Select Environment &amp; Alt Energy</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.7771621800384252</v>
+        <v>0.290569732444071</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -4881,21 +4986,532 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
+          <t>FSCSX</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Software &amp; IT Services</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="K68" s="11" t="n">
+        <v>0.06558974900891346</v>
+      </c>
+    </row>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71">
+      <c r="A71" s="9">
+        <f>== PAST 3 YEARS LEADERS &amp; LAGGARDS ===</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>Top 10 - Rank</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>Top 10 - Ticker</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>Top 10 - Fund Name</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>Top 10 - Sector</t>
+        </is>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>Top 10 - 3Y</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" s="10" t="inlineStr">
+        <is>
+          <t>Bottom 10 - Rank</t>
+        </is>
+      </c>
+      <c r="H72" s="10" t="inlineStr">
+        <is>
+          <t>Bottom 10 - Ticker</t>
+        </is>
+      </c>
+      <c r="I72" s="10" t="inlineStr">
+        <is>
+          <t>Bottom 10 - Fund Name</t>
+        </is>
+      </c>
+      <c r="J72" s="10" t="inlineStr">
+        <is>
+          <t>Bottom 10 - Sector</t>
+        </is>
+      </c>
+      <c r="K72" s="10" t="inlineStr">
+        <is>
+          <t>Bottom 10 - 3Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>1</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>FSELX</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Semiconductors</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="n">
+        <v>2.657534783520286</v>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="n">
+        <v>23</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>FSHCX</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Health Care Services</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="K73" s="11" t="n">
+        <v>0.05164832892848925</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>FDCPX</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Tech Hardware</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="E74" s="11" t="n">
+        <v>2.355135313245017</v>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="n">
+        <v>24</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>FSCHX</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="K74" s="11" t="n">
+        <v>0.08155093053326623</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>3</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>FSAGX</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="n">
+        <v>2.128750670007718</v>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="n">
+        <v>25</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>FSMEX</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Medical Tech &amp; Devices</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="K75" s="11" t="n">
+        <v>0.1261861616167599</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>4</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>FSPTX</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="E76" s="11" t="n">
+        <v>1.578203601226092</v>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="n">
+        <v>26</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>FDFAX</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="K76" s="11" t="n">
+        <v>0.1581010720151732</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>5</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>FSDAX</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Defense and Aerospace</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="n">
+        <v>1.279185901479832</v>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="n">
+        <v>27</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>FSVLX</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>FinTech</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="K77" s="11" t="n">
+        <v>0.2170699241309788</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>6</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>FSRBX</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="E78" s="11" t="n">
+        <v>1.165684286659368</v>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="n">
+        <v>28</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>FSDPX</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="K78" s="11" t="n">
+        <v>0.2206642493248834</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>7</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>FIDSX</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="n">
+        <v>0.9552406255062227</v>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="n">
+        <v>29</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>FSAVX</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="K79" s="11" t="n">
+        <v>0.2438159570483636</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>8</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>FBIOX</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Biotechnology</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="E80" s="11" t="n">
+        <v>0.954614100743882</v>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="n">
+        <v>30</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>FBSOX</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Enterprise Tech Services</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="K80" s="11" t="n">
+        <v>0.2968041964544554</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>9</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>FWRLX</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Wireless</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="n">
+        <v>0.8040486205741388</v>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="n">
+        <v>31</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>FDLSX</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Leisure</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="K81" s="11" t="n">
+        <v>0.3374907422050768</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>10</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>FSLEX</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Environment &amp; Alt Energy</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="E82" s="11" t="n">
+        <v>0.7771622924682438</v>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="n">
+        <v>32</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
           <t>FRESX</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>Select Real Estate Investment</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Real Estate Investment</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
         <is>
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="K68" s="11" t="n">
-        <v>0.3710625231046811</v>
+      <c r="K82" s="11" t="n">
+        <v>0.371062441170092</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -633,10 +633,10 @@
         <v>1.010209847897446</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.355135313245017</v>
+        <v>2.355134539065858</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.497051290650814</v>
+        <v>0.497051175505334</v>
       </c>
     </row>
     <row r="3">
@@ -745,10 +745,10 @@
         <v>0.592432619827618</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.6060982803667716</v>
+        <v>0.6060983892427367</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1710911680653526</v>
+        <v>0.1710911945277593</v>
       </c>
     </row>
     <row r="5">
@@ -801,10 +801,10 @@
         <v>0.5072741660579498</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1.578203601226092</v>
+        <v>1.578203373729222</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.3712155729166799</v>
+        <v>0.3712155325853346</v>
       </c>
     </row>
     <row r="6">
@@ -907,16 +907,16 @@
         <v>0.1333081154126903</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.2972673844512854</v>
+        <v>0.2972673038617362</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.3227731372002025</v>
+        <v>0.3227732209898797</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>1.165684286659368</v>
+        <v>1.165684511259543</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.29379374896579</v>
+        <v>0.2937937936916526</v>
       </c>
     </row>
     <row r="8">
@@ -969,10 +969,10 @@
         <v>0.3204008684166899</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.3929282291430767</v>
+        <v>0.3929283585845491</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1168021635720615</v>
+        <v>0.1168021981659741</v>
       </c>
     </row>
     <row r="9">
@@ -1075,7 +1075,7 @@
         <v>0.09918275117008202</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.2509784211419124</v>
+        <v>0.2509785183066207</v>
       </c>
       <c r="N10" s="6" t="n">
         <v>0.290569732444071</v>
@@ -1137,10 +1137,10 @@
         <v>0.06558974900891346</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.394542504761942</v>
+        <v>0.3945423491046378</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.1172334206599304</v>
+        <v>0.1172333790918061</v>
       </c>
     </row>
     <row r="12">
@@ -1187,10 +1187,10 @@
         <v>0.1069176134689611</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.2743588951276641</v>
+        <v>0.2743589950717296</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.2839434179769031</v>
+        <v>0.2839433165238308</v>
       </c>
       <c r="O12" s="6" t="n">
         <v>0.4779025366285532</v>
@@ -1249,10 +1249,10 @@
         <v>0.4547730613970824</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.6408960839907278</v>
+        <v>0.6408963873346893</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.1794884510603243</v>
+        <v>0.1794885237422936</v>
       </c>
     </row>
     <row r="14">
@@ -1305,10 +1305,10 @@
         <v>0.2809499867168403</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.8040486205741388</v>
+        <v>0.8040484128217973</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.2173517357467096</v>
+        <v>0.2173516890170593</v>
       </c>
     </row>
     <row r="15">
@@ -1417,10 +1417,10 @@
         <v>0.2858148366906854</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.05164832892848925</v>
+        <v>0.05164825669291973</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.01692793764124301</v>
+        <v>0.01692791435767682</v>
       </c>
     </row>
     <row r="17">
@@ -1523,7 +1523,7 @@
         <v>-0.1030739944664463</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.2251965228529125</v>
+        <v>0.2251966145171875</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>0.5727283335086024</v>
@@ -1585,10 +1585,10 @@
         <v>0.04504573209089346</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.1261861616167599</v>
+        <v>0.1261862555799129</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.04040731136995301</v>
+        <v>0.04040734030535509</v>
       </c>
     </row>
     <row r="20">
@@ -1691,16 +1691,16 @@
         <v>0.0697280224698984</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.1610200043155849</v>
+        <v>0.1610198868090169</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>0.1769573726424654</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.371062441170092</v>
+        <v>0.3710626050392798</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1109275695395773</v>
+        <v>0.1109276137988773</v>
       </c>
     </row>
     <row r="22">
@@ -1750,13 +1750,13 @@
         <v>0.2118612911830753</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1908526325957307</v>
+        <v>0.1908527102660371</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.7606476613114361</v>
+        <v>0.7606480008694114</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.207510228013603</v>
+        <v>0.2075103056402838</v>
       </c>
     </row>
     <row r="23">
@@ -1809,10 +1809,10 @@
         <v>0.2205932014710026</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.7771622924682438</v>
+        <v>0.7771624048980768</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.2112739110392707</v>
+        <v>0.2112739365824865</v>
       </c>
     </row>
     <row r="24">
@@ -1963,16 +1963,16 @@
         <v>0.01441086506525235</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.1530451251392011</v>
+        <v>0.1530450189146859</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.1037693934696982</v>
+        <v>0.103769490809156</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.1581010720151732</v>
+        <v>0.1581009648570555</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.0501439173903897</v>
+        <v>0.05014388500074451</v>
       </c>
     </row>
     <row r="27">
@@ -2019,10 +2019,10 @@
         <v>-0.01811792323657113</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.216795918243009</v>
+        <v>0.2167958075953236</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.1708439543224261</v>
+        <v>0.1708440567707739</v>
       </c>
       <c r="O27" s="6" t="n">
         <v>0.2206642493248834</v>
@@ -2075,16 +2075,16 @@
         <v>0.01021688261231857</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.2113065064625521</v>
+        <v>0.2113066058440574</v>
       </c>
       <c r="N28" s="6" t="n">
         <v>0.1043722863254177</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.08155093053326623</v>
+        <v>0.08155100976358765</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.02647645419629985</v>
+        <v>0.02647647926155727</v>
       </c>
     </row>
     <row r="29">
@@ -2137,10 +2137,10 @@
         <v>0.06992864917324559</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.4555015236136077</v>
+        <v>0.4555016355440606</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1332808620225299</v>
+        <v>0.1332808910729144</v>
       </c>
     </row>
     <row r="30">
@@ -2193,10 +2193,10 @@
         <v>-0.0756123616951746</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.6507226532661234</v>
+        <v>0.6507225407825037</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1818382373317387</v>
+        <v>0.1818382104874459</v>
       </c>
     </row>
     <row r="31">
@@ -2246,13 +2246,13 @@
         <v>0.04479357756462998</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.04746248547164411</v>
+        <v>0.04746242203726792</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.4362772085956768</v>
+        <v>0.4362773278637815</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1282692612792513</v>
+        <v>0.1282692925096507</v>
       </c>
     </row>
     <row r="32">
@@ -2358,13 +2358,13 @@
         <v>-0.003774464122493382</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.04051677120261798</v>
+        <v>0.04051684587407212</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.2438159570483636</v>
+        <v>0.2438158503473316</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.07543799193516465</v>
+        <v>0.07543796118293367</v>
       </c>
     </row>
     <row r="34">
@@ -2414,13 +2414,13 @@
         <v>0.003112539173837359</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.05763053877795321</v>
+        <v>0.05763047437933166</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.5608312338381856</v>
+        <v>0.5608309533268316</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1599839558418512</v>
+        <v>0.1599838863513809</v>
       </c>
     </row>
   </sheetData>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>0.04051677120261798</v>
+        <v>0.04051684587407212</v>
       </c>
     </row>
     <row r="64">
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.3227731372002025</v>
+        <v>0.3227732209898797</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>0.04746248547164411</v>
+        <v>0.04746242203726792</v>
       </c>
     </row>
     <row r="67">
@@ -4955,7 +4955,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.05763053877795321</v>
+        <v>0.05763047437933166</v>
       </c>
     </row>
     <row r="68">
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.05164832892848925</v>
+        <v>0.05164825669291973</v>
       </c>
     </row>
     <row r="74">
@@ -5129,7 +5129,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.355135313245017</v>
+        <v>2.355134539065858</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.08155093053326623</v>
+        <v>0.08155100976358765</v>
       </c>
     </row>
     <row r="75">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1261861616167599</v>
+        <v>0.1261862555799129</v>
       </c>
     </row>
     <row r="76">
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.578203601226092</v>
+        <v>1.578203373729222</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1581010720151732</v>
+        <v>0.1581009648570555</v>
       </c>
     </row>
     <row r="77">
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.165684286659368</v>
+        <v>1.165684511259543</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.2438159570483636</v>
+        <v>0.2438158503473316</v>
       </c>
     </row>
     <row r="80">
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8040486205741388</v>
+        <v>0.8040484128217973</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.7771622924682438</v>
+        <v>0.7771624048980768</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.371062441170092</v>
+        <v>0.3710626050392798</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -490,10 +490,10 @@
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
     <col width="23" customWidth="1" min="12" max="12"/>
     <col width="24" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>221.87</v>
+        <v>217.69</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.006213129783163351</v>
+        <v>-0.04130886766308772</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.0596016799461152</v>
+        <v>0.03430418196810892</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.07489942919814063</v>
+        <v>0.0004596080022003513</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.01315123773588533</v>
+        <v>0.06962459645969421</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.09365603813922641</v>
+        <v>0.1005561126530614</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.5325686619065126</v>
+        <v>0.492088128019023</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7436042439436601</v>
+        <v>0.761104786024366</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>1.010209847897446</v>
+        <v>0.9752973808278689</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.355134539065858</v>
+        <v>2.366741160451116</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.497051175505334</v>
+        <v>0.4987754688359554</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>64.25</v>
+        <v>61.97</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>-0.002948516980256444</v>
+        <v>-0.04895644969494128</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.005319983623840674</v>
+        <v>-0.009272550334641361</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.08548743859925922</v>
+        <v>-0.0189963112715763</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>-0.01547658754472736</v>
+        <v>0.02837708175904274</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>-0.02028060070021043</v>
+        <v>0.006333214973237578</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.4356763539097035</v>
+        <v>0.3712743921488286</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.6811412165441184</v>
+        <v>0.6933948894804889</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.8958286315873361</v>
+        <v>0.8490231061530853</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>2.657534783520286</v>
+        <v>2.656918262177158</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.5407404635452537</v>
+        <v>0.540653888587572</v>
       </c>
     </row>
     <row r="4">
@@ -704,51 +704,51 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>90.38</v>
+        <v>30.1</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.01379692323596893</v>
+        <v>0.009728309987347306</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.08032504538787344</v>
+        <v>0.02380955006877805</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.05166388975889191</v>
+        <v>0.05911331107198436</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.0933945469306503</v>
+        <v>0.04951185708452321</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.08097113495569364</v>
+        <v>0.2402142486091758</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.2055451494520224</v>
+        <v>0.2019677880743778</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.4424043077238904</v>
+        <v>0.2786419279447385</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.592432619827618</v>
+        <v>0.572892760498946</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.6060983892427367</v>
+        <v>1.043069730891051</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1710911945277593</v>
+        <v>0.2689009713884123</v>
       </c>
     </row>
     <row r="5">
@@ -760,51 +760,51 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>55.73</v>
+        <v>92.48999999999999</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.002327265784009769</v>
+        <v>0.01414474735409743</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.008140390247403317</v>
+        <v>0.04143677971331816</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.06680700137129025</v>
+        <v>0.09184274422596417</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.01327271894975146</v>
+        <v>0.1096580630710662</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.05250233690728567</v>
+        <v>0.06999069009124903</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.3874473461230392</v>
+        <v>0.2122412593146648</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.3765759197103189</v>
+        <v>0.4777170103156245</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.5072741660579498</v>
+        <v>0.637525451154147</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1.578203373729222</v>
+        <v>0.6580019043393608</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.3712155325853346</v>
+        <v>0.183572888239022</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>29.39</v>
+        <v>54.52</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.00204566880662993</v>
+        <v>-0.02625470935230334</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>-0.0006800563708752039</v>
+        <v>-0.002196173741310425</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.04702528354738855</v>
+        <v>-0.005653863996689434</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.03413086948453592</v>
+        <v>0.03551754753445935</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.1493938107319355</v>
+        <v>0.05761399155497804</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.1909553141258775</v>
+        <v>0.3427804962468717</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.2676963680730038</v>
+        <v>0.3963432297666591</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.5448876757882486</v>
+        <v>0.4778043309358975</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.954614100743882</v>
+        <v>1.587725312136041</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.2503175941257045</v>
+        <v>0.3729015372782927</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>39.83</v>
+        <v>29.04</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.004793199907461743</v>
+        <v>0.007284113505966694</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.02469778558142544</v>
+        <v>0.009735767886549729</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.03427690384456317</v>
+        <v>0.05217393167227691</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.04103511705168761</v>
+        <v>0.04123347260831189</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.1818991373690566</v>
+        <v>0.237851749736337</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.1333081154126903</v>
+        <v>0.1634119207411262</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.2972673038617362</v>
+        <v>0.163516831890183</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.3227732209898797</v>
+        <v>0.3279700475643019</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>1.165684511259543</v>
+        <v>0.4568932405611115</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.2937937936916526</v>
+        <v>0.133641952621933</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>28.59</v>
+        <v>39.35</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.0006990722592447041</v>
+        <v>-0.006062179276124846</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.003862381043526097</v>
+        <v>0.003826472149547788</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.04495612261685999</v>
+        <v>-0.0005080126570050636</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.02989913245182585</v>
+        <v>0.01156804448819404</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.1853233481685301</v>
+        <v>0.165925880714699</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.1712164156328317</v>
+        <v>0.1088517304460426</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.1458675776083378</v>
+        <v>0.3143860340321525</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.3204008684166899</v>
+        <v>0.3212191929257402</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.3929283585845491</v>
+        <v>1.234632894687103</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1168021981659741</v>
+        <v>0.3073806789709661</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>17.98</v>
+        <v>34.8</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.002788579822060155</v>
+        <v>0.02022863132109087</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.02450144295549284</v>
+        <v>0.01576184886115239</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.03930637775515411</v>
+        <v>0.0357143100427133</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.06014153967127922</v>
+        <v>0.01694909397041533</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.1813402908531168</v>
+        <v>0.1229428684763398</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.1674809179118946</v>
+        <v>0.08194412883594793</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.2129478059313981</v>
+        <v>0.1839695651169497</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.1963425037673241</v>
+        <v>0.4753202424816387</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.9552406255062227</v>
+        <v>0.7042468530196748</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.2504511705778232</v>
+        <v>0.1944761983750516</v>
       </c>
     </row>
     <row r="10">
@@ -1054,37 +1054,37 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>30.72</v>
+        <v>30.58</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.01453099791054613</v>
+        <v>0.001309725179424515</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.005564650754155132</v>
+        <v>0.0003271255800350037</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.05061557981605036</v>
+        <v>-0.002283839990063097</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.07001045952554263</v>
+        <v>0.08209482222343256</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.1424321312993577</v>
+        <v>0.161412837535694</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.09918275117008202</v>
+        <v>0.06937531223716209</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.2509785183066207</v>
+        <v>0.2690404424976294</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.290569732444071</v>
+        <v>0.2868037723664518</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.279185901479832</v>
+        <v>1.314260173290272</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.3160122036496986</v>
+        <v>0.3227285489093292</v>
       </c>
     </row>
     <row r="11">
@@ -1096,51 +1096,51 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>23.83</v>
+        <v>17.78</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.0161023699713071</v>
+        <v>-0.0005621263837658486</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.01968331484611729</v>
+        <v>0.006795064567963971</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.1058004996457023</v>
+        <v>0.009080581145935351</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.1489874728393643</v>
+        <v>0.03794521644622306</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.2302529112667384</v>
+        <v>0.1552956653675255</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.3253472015954513</v>
+        <v>0.1377522004963012</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.02850940270176516</v>
+        <v>0.2273320529644551</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.06558974900891346</v>
+        <v>0.1964363250013894</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.3945423491046378</v>
+        <v>0.9960998088341022</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.1172333790918061</v>
+        <v>0.2591015281237765</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>123.97</v>
+        <v>14.73</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.008398619825283116</v>
+        <v>-0.01207245519905376</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.0008865297286289042</v>
+        <v>0.004089943124086171</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.02828470248145165</v>
+        <v>0</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-0.001128026661509463</v>
+        <v>0.0130673714499161</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.101759730885508</v>
+        <v>0.0130673714499161</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.1069176134689611</v>
+        <v>0.1847829780575205</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.2743589950717296</v>
+        <v>0.282517205657133</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.2839433165238308</v>
+        <v>0.2609190085602435</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.4779025366285532</v>
+        <v>0.8374613842841889</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.1390652377953301</v>
+        <v>0.2248213282178295</v>
       </c>
     </row>
     <row r="13">
@@ -1208,51 +1208,51 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>33.86</v>
+        <v>121.55</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.007038060836033977</v>
+        <v>-0.01379307868756341</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.007038060836033977</v>
+        <v>-0.01618777782759062</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.003854167503099193</v>
+        <v>-0.02791105116935544</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.003259277343750089</v>
+        <v>-0.03286121294867539</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.06578533592929658</v>
+        <v>0.08130948395947168</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.0588211296236365</v>
+        <v>0.06198108460998841</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.1640082333798087</v>
+        <v>0.2715908140389458</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.4547730613970824</v>
+        <v>0.2519666934372304</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.6408963873346893</v>
+        <v>0.4789816659507768</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.1794885237422936</v>
+        <v>0.1393424098035529</v>
       </c>
     </row>
     <row r="14">
@@ -1264,51 +1264,51 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>14.94</v>
+        <v>61.85</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.004032222142535735</v>
+        <v>-0.02827970162775195</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.0087777958867854</v>
+        <v>-0.007541739778637369</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.0573248025040396</v>
+        <v>0.1472824828266093</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.004707444207326272</v>
+        <v>0.2721102392612387</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.01563559086606925</v>
+        <v>0.04072014397641777</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.1988263906526939</v>
+        <v>-0.1078513629065362</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.2737881013938817</v>
+        <v>0.2210397782163138</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.2809499867168403</v>
+        <v>0.5478175948006423</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.8040484128217973</v>
+        <v>2.262549671885854</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.2173516890170593</v>
+        <v>0.4831521676423265</v>
       </c>
     </row>
     <row r="15">
@@ -1320,12 +1320,12 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1334,37 +1334,37 @@
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>45.22</v>
+        <v>23.21</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.009636413232137153</v>
+        <v>-0.0025784861242234</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.01823916631556166</v>
+        <v>-0.02683443550358677</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.0470016823000956</v>
+        <v>0.004327064971010985</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.09042681190295898</v>
+        <v>0.1327476497675948</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.2110337717170336</v>
+        <v>0.1610805077650272</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.2219137641347035</v>
+        <v>0.3007691483782722</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.06348971952186466</v>
+        <v>0.03409972095075431</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.04188666432932187</v>
+        <v>0.0229643858417643</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.2968041964544554</v>
+        <v>0.3933117914132078</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.09049782171493925</v>
+        <v>0.1169046631963788</v>
       </c>
     </row>
     <row r="16">
@@ -1376,51 +1376,51 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>116.81</v>
+        <v>44.59</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.01037969848548492</v>
+        <v>0.005411537468413607</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.002902295884392725</v>
+        <v>-0.00535359510738509</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.005449122233102122</v>
+        <v>-0.0002241776205217372</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-0.04167693704563358</v>
+        <v>0.07627322771265677</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.0644250030294411</v>
+        <v>0.1700340970468579</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.161826103987569</v>
+        <v>0.1955970651055683</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.1628359321567898</v>
+        <v>0.08865967648304363</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.2858148366906854</v>
+        <v>0.02163945630850739</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.05164825669291973</v>
+        <v>0.3058395791463391</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.01692791435767682</v>
+        <v>0.09302461536387829</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>97.5</v>
+        <v>115.09</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.000102575489809742</v>
+        <v>0.000608587174988795</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.01175758786794856</v>
+        <v>-0.005100310907059646</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.001026678362982647</v>
+        <v>-0.01091444023547006</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.01806414762006625</v>
+        <v>-0.05127360766534361</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.1488157988062115</v>
+        <v>0.06269615045982779</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.1317742955370285</v>
+        <v>0.1411997826397948</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.1269935770417672</v>
+        <v>0.1504877707998904</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.1086387018966761</v>
+        <v>0.2206069456676076</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.5945028261378276</v>
+        <v>0.07925405140342745</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.1682660721541926</v>
+        <v>0.02574929986851693</v>
       </c>
     </row>
     <row r="18">
@@ -1488,51 +1488,51 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>62.47</v>
+        <v>51.1</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.01775822961257822</v>
+        <v>-0.006029981992046629</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.006282206477857155</v>
+        <v>-0.0169296090008656</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.219402728457962</v>
+        <v>0.04328295123924319</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.220832586595942</v>
+        <v>0.07060546750901708</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>-0.02237872098636251</v>
+        <v>0.2424020701943232</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>-0.1030739944664463</v>
+        <v>0.05577998319807387</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.2251966145171875</v>
+        <v>-0.01576257258586422</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.5727283335086024</v>
+        <v>0.03139641638745561</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>2.128750670007718</v>
+        <v>0.1588986777166521</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.4625935432910708</v>
+        <v>0.05038494660026349</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>51.49</v>
+        <v>96.55</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.003290711758564324</v>
+        <v>0.004473577745409241</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.01418162722496152</v>
+        <v>-0.01085951799985274</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.06143070418559038</v>
+        <v>-0.008930354481004543</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.07855047901457124</v>
+        <v>-0.001447920013584403</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.2512758145606664</v>
+        <v>0.1019173707515564</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.1037840135498129</v>
+        <v>0.1067531697694377</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>-0.0207747908867556</v>
+        <v>0.1249526639906042</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.04504573209089346</v>
+        <v>0.1080629582798383</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.1261862555799129</v>
+        <v>0.593428803899877</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.04040734030535509</v>
+        <v>0.1680037070773626</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>17.51</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.0005707893048259027</v>
+        <v>-0.002748877804632954</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.006321874296733698</v>
+        <v>0.01174230271552923</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.03793712850090891</v>
+        <v>0.01651677904300541</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.07225966385111793</v>
+        <v>0.05445919242798092</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.1626825857238252</v>
+        <v>0.01547342714342292</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.1143574030956209</v>
+        <v>0.06082948551233014</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.09456434403219105</v>
+        <v>0.2077624208043614</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>-0.01807310166919218</v>
+        <v>0.1602987153779831</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.3374907422050768</v>
+        <v>0.7964279394191252</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.1017851845177644</v>
+        <v>0.2156351998018937</v>
       </c>
     </row>
     <row r="21">
@@ -1670,37 +1670,37 @@
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>43.76</v>
+        <v>43.19</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.003669721399349957</v>
+        <v>-0.00437995474246089</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.008062623251586132</v>
+        <v>0.01313623139954823</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.00505276530500498</v>
+        <v>-0.009857870603051877</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.0169648980466055</v>
+        <v>-0.02019063446859226</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.05005073396044812</v>
+        <v>0.0391037862129584</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.0697280224698984</v>
+        <v>0.06121770102283519</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.1610198868090169</v>
+        <v>0.1485954103251452</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.1769573726424654</v>
+        <v>0.1673285515680476</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.3710626050392798</v>
+        <v>0.3860748192774108</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1109276137988773</v>
+        <v>0.1149675416097462</v>
       </c>
     </row>
     <row r="22">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>69.65000000000001</v>
+        <v>52.27</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.006939473321384337</v>
+        <v>-0.02061080187625641</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.02956393133612734</v>
+        <v>-0.02335575465823214</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.06189976238255812</v>
+        <v>-0.02207671259742916</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.05996047019177753</v>
+        <v>0.007711616235122509</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.02116956197886077</v>
+        <v>0.008878576959656215</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.06051555528294839</v>
+        <v>0.04469916993703804</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.2118612911830753</v>
+        <v>0.1682537368342749</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1908527102660371</v>
+        <v>0.1928870944180205</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.7606480008694114</v>
+        <v>0.7964600122375063</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.2075103056402838</v>
+        <v>0.2156424342724221</v>
       </c>
     </row>
     <row r="23">
@@ -1768,52 +1768,44 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>53.58</v>
+        <v>74.28</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.001495361328125</v>
+        <v>-0.01810975173759077</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.002807440108967718</v>
+        <v>-0.01537650615812669</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.04464809660071722</v>
+        <v>-0.01667993276356283</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.01285444774218236</v>
+        <v>0.02738583186672394</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.00695363189152931</v>
+        <v>0.09331757595031664</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.06814400336922555</v>
-      </c>
-      <c r="M23" s="6" t="n">
-        <v>0.1715386119958278</v>
-      </c>
-      <c r="N23" s="6" t="n">
-        <v>0.2205932014710026</v>
-      </c>
-      <c r="O23" s="6" t="n">
-        <v>0.7771624048980768</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v>0.2112739365824865</v>
-      </c>
+        <v>0.06923848386460518</v>
+      </c>
+      <c r="M23" s="6" t="inlineStr"/>
+      <c r="N23" s="6" t="inlineStr"/>
+      <c r="O23" s="6" t="inlineStr"/>
+      <c r="P23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -1824,44 +1816,52 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>75.66</v>
+        <v>17.22</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.00598330784622525</v>
+        <v>-0.001739170240319332</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.005582214384167283</v>
+        <v>-0.004624273250525723</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.04315462478273102</v>
+        <v>0.01833231630630827</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.03786011081564511</v>
+        <v>0.05773947094978116</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.08039418793302788</v>
+        <v>0.1373843410082278</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.09161746251898828</v>
-      </c>
-      <c r="M24" s="6" t="inlineStr"/>
-      <c r="N24" s="6" t="inlineStr"/>
-      <c r="O24" s="6" t="inlineStr"/>
-      <c r="P24" s="6" t="inlineStr"/>
+        <v>0.06945530297430524</v>
+      </c>
+      <c r="M24" s="6" t="n">
+        <v>0.09920239928541563</v>
+      </c>
+      <c r="N24" s="6" t="n">
+        <v>-0.03982504178054347</v>
+      </c>
+      <c r="O24" s="6" t="n">
+        <v>0.3644016657107947</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v>0.109125644726821</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -1872,51 +1872,51 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>18.11</v>
+        <v>100.61</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.007127147061287031</v>
+        <v>-0.01198076400634085</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.03073425867425694</v>
+        <v>-0.02291930253834995</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.07096397242860419</v>
+        <v>0.00670400392813808</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.08313405227755344</v>
+        <v>0.04075724129548974</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.182887009405122</v>
+        <v>0.003991632866314321</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.1411468645838347</v>
+        <v>-0.03045292178610148</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>-0.02634407317573639</v>
+        <v>0.2234417118520866</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>-0.08811681501600022</v>
+        <v>0.158422101174124</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.2170699241309788</v>
+        <v>0.2451997999696329</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.06767361457465726</v>
+        <v>0.07583668051872117</v>
       </c>
     </row>
     <row r="26">
@@ -1942,37 +1942,37 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>95.48999999999999</v>
+        <v>94.62</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.001468268399463346</v>
+        <v>0.006488677762900297</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.01036922765197335</v>
+        <v>0.006702892830422691</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.01812556702897683</v>
+        <v>0.004032309968446945</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.04703948529693491</v>
+        <v>0.02071203734140203</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.0505359207808036</v>
+        <v>0.03035638505217908</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.01441086506525235</v>
+        <v>0.01749884975843297</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.1530450189146859</v>
+        <v>0.1587684161419505</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.103769490809156</v>
+        <v>0.09654126236125493</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.1581009648570555</v>
+        <v>0.160760394309313</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.05014388500074451</v>
+        <v>0.0509471104617758</v>
       </c>
     </row>
     <row r="27">
@@ -1984,51 +1984,51 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>102.09</v>
+        <v>17.78</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.008196663876655963</v>
+        <v>0.002820143581508061</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.0007830266466521962</v>
+        <v>0.007936581737028048</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.0573795247128368</v>
+        <v>0.01716253731496376</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.03508059597307511</v>
+        <v>0.06149257830719446</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>-0.01562050680631599</v>
+        <v>0.1712780190513719</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>-0.01811792323657113</v>
+        <v>0.1009288610908075</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.2167958075953236</v>
+        <v>-0.01222218407524955</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.1708440567707739</v>
+        <v>-0.105633730521753</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.2206642493248834</v>
+        <v>0.2547636267406239</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.06872362123505815</v>
+        <v>0.07858400011413735</v>
       </c>
     </row>
     <row r="28">
@@ -2054,37 +2054,37 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>14.08</v>
+        <v>13.82</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.004279562338327825</v>
+        <v>-0.005039643395846727</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.007751914019033079</v>
+        <v>-0.02607469319946853</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.02399999445134937</v>
+        <v>-0.01985820418937623</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.002135212282130317</v>
+        <v>-0.0170697523207487</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.0007107483367974066</v>
+        <v>0.00363102653583125</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.01021688261231857</v>
+        <v>-0.01261267301466862</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.2113066058440574</v>
+        <v>0.2215681466301236</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.1043722863254177</v>
+        <v>0.09061902457868798</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.08155100976358765</v>
+        <v>0.08843645736215122</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.02647647926155727</v>
+        <v>0.02865014910000441</v>
       </c>
     </row>
     <row r="29">
@@ -2110,37 +2110,37 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>18.05</v>
+        <v>17.78</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.004412571837243973</v>
+        <v>-0.001123514116416424</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.02326841535861557</v>
+        <v>-0.02788410078475556</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.001106832213694009</v>
+        <v>-0.0368363180688952</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.04094573692184733</v>
+        <v>0.01252854370125789</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.03083946322787656</v>
+        <v>0.01949542099634249</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.03781066799932487</v>
+        <v>0.02063598684603107</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.1132968022326644</v>
+        <v>0.1278936040130563</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.06992864917324559</v>
+        <v>0.05340487688897411</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.4555016355440606</v>
+        <v>0.463987292838417</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1332808910729144</v>
+        <v>0.1354789889235313</v>
       </c>
     </row>
     <row r="30">
@@ -2166,37 +2166,37 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>184.82</v>
+        <v>182</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-0.009167380401376546</v>
+        <v>-0.000768636159644065</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.03796478635466949</v>
+        <v>0.004027118168110411</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.0592011089796165</v>
+        <v>0.01426659342266601</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.07497246087100673</v>
+        <v>0.05238809662711419</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.08800855146147346</v>
+        <v>0.08140223826394699</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.1041879207185539</v>
+        <v>0.07176436400598307</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.01945113565396261</v>
+        <v>0.03553706351358898</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>-0.0756123616951746</v>
+        <v>-0.07651708747572938</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.6507225407825037</v>
+        <v>0.6614212970646633</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1818382104874459</v>
+        <v>0.1843859796890841</v>
       </c>
     </row>
     <row r="31">
@@ -2208,51 +2208,51 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
+          <t>Construction &amp; Housing</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
       <c r="F31" s="5" t="n">
-        <v>65.98</v>
+        <v>122.54</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.001362136193526764</v>
+        <v>-0.02108962600425301</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.01756998571817414</v>
+        <v>-0.03007753310519623</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.01273985896569774</v>
+        <v>-0.0323752249990632</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.01336204482301473</v>
+        <v>0.0005715660498613051</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.006406434014346374</v>
+        <v>0.03018078234039168</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.01324972665635937</v>
+        <v>-0.07460456158270312</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.04479357756462998</v>
+        <v>0.09537451172431122</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.04746242203726792</v>
+        <v>0.01482723015646648</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.4362773278637815</v>
+        <v>0.409914774293382</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1282692925096507</v>
+        <v>0.1213235772046217</v>
       </c>
     </row>
     <row r="32">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2278,37 +2278,37 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>125.3</v>
+        <v>64.8</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.003765130287662899</v>
+        <v>-0.005219471002092968</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.01454973222115585</v>
+        <v>-0.02964953225115807</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.03399903231726653</v>
+        <v>-0.03153490501968748</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.01416430559914184</v>
+        <v>-0.005982503068610479</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.0144927607850982</v>
+        <v>0.01044761932067817</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>-0.06648786116969174</v>
+        <v>-0.01165871525940587</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.08613008717109305</v>
+        <v>0.05518961312085424</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.03149104341912445</v>
+        <v>0.02932687436768888</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.3961756775034286</v>
+        <v>0.4694985907480649</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1176693876139951</v>
+        <v>0.1369020719705425</v>
       </c>
     </row>
     <row r="33">
@@ -2320,51 +2320,51 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>55.31</v>
+        <v>130.77</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.008018998541488243</v>
+        <v>-0.00931814945105347</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0.003629119229258126</v>
+        <v>0.002376188430479376</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>0.02066807113794633</v>
+        <v>-0.006155932112189566</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0.03693290616924649</v>
+        <v>-0.03547719054162168</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.007536303111343234</v>
+        <v>-0.01997771258381364</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.06199276024727007</v>
+        <v>-0.04925709057111738</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>-0.003774464122493382</v>
+        <v>-0.01227797514600926</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.04051684587407212</v>
+        <v>0.04788363134650608</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.2438158503473316</v>
+        <v>0.5586188684852251</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.07543796118293367</v>
+        <v>0.1594356322450534</v>
       </c>
     </row>
     <row r="34">
@@ -2376,51 +2376,51 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>132.52</v>
+        <v>53.97</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.007833285696762893</v>
+        <v>-0.01153841155721957</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.01774055325617097</v>
+        <v>-0.02121868302314411</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.001281167878645406</v>
+        <v>-0.01442653624990031</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.03817676406908432</v>
+        <v>0.01086349199635217</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.03900594212390573</v>
+        <v>0.006715176389721078</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.05152052900082926</v>
+        <v>-0.0767384073925601</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.003112539173837359</v>
+        <v>-0.002916213361189079</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.05763047437933166</v>
+        <v>0.005867239913128541</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.5608309533268316</v>
+        <v>0.2605308393175807</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1599838863513809</v>
+        <v>0.08023395689320201</v>
       </c>
     </row>
   </sheetData>
@@ -2537,17 +2537,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -2582,17 +2582,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2650,17 +2650,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -2672,12 +2672,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2695,17 +2695,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -2740,17 +2740,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2785,17 +2785,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -2830,17 +2830,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2852,17 +2852,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -2920,17 +2920,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -2942,17 +2942,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.220832586595942</v>
+        <v>0.2721102392612387</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.04167693704563358</v>
+        <v>-0.05127360766534361</v>
       </c>
     </row>
     <row r="18">
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.1489874728393643</v>
+        <v>0.1327476497675948</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.03817676406908432</v>
+        <v>-0.03547719054162168</v>
       </c>
     </row>
     <row r="19">
@@ -3130,7 +3130,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.0933945469306503</v>
+        <v>0.1096580630710662</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -3138,21 +3138,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.01547658754472736</v>
+        <v>-0.03286121294867539</v>
       </c>
     </row>
     <row r="20">
@@ -3161,21 +3161,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.09042681190295898</v>
+        <v>0.08209482222343256</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -3183,21 +3183,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.001128026661509463</v>
+        <v>-0.02019063446859226</v>
       </c>
     </row>
     <row r="21">
@@ -3206,21 +3206,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.08313405227755344</v>
+        <v>0.07627322771265677</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>0.002135212282130317</v>
+        <v>-0.0170697523207487</v>
       </c>
     </row>
     <row r="22">
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.07855047901457124</v>
+        <v>0.07060546750901708</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -3273,21 +3273,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>0.003259277343750089</v>
+        <v>-0.005982503068610479</v>
       </c>
     </row>
     <row r="23">
@@ -3296,21 +3296,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FDCPX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.07497246087100673</v>
+        <v>0.06962459645969421</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -3318,21 +3318,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>0.004707444207326272</v>
+        <v>-0.001447920013584403</v>
       </c>
     </row>
     <row r="24">
@@ -3341,21 +3341,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.07225966385111793</v>
+        <v>0.06149257830719446</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -3363,21 +3363,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>0.01285444774218236</v>
+        <v>0.0005715660498613051</v>
       </c>
     </row>
     <row r="25">
@@ -3386,21 +3386,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.07001045952554263</v>
+        <v>0.05773947094978116</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -3408,21 +3408,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>FDCPX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Tech Hardware</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>0.01315123773588533</v>
+        <v>0.007711616235122509</v>
       </c>
     </row>
     <row r="26">
@@ -3431,21 +3431,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.06014153967127922</v>
+        <v>0.05445919242798092</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -3453,21 +3453,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>0.01327271894975146</v>
+        <v>0.01086349199635217</v>
       </c>
     </row>
     <row r="27"/>
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.2512758145606664</v>
+        <v>0.2424020701943232</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.03900594212390573</v>
+        <v>-0.01997771258381364</v>
       </c>
     </row>
     <row r="32">
@@ -3582,21 +3582,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.2302529112667384</v>
+        <v>0.2402142486091758</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3618,7 +3618,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.02237872098636251</v>
+        <v>0.00363102653583125</v>
       </c>
     </row>
     <row r="33">
@@ -3627,21 +3627,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.2110337717170336</v>
+        <v>0.237851749736337</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -3649,21 +3649,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.02028060070021043</v>
+        <v>0.003991632866314321</v>
       </c>
     </row>
     <row r="34">
@@ -3672,21 +3672,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.1853233481685301</v>
+        <v>0.1712780190513719</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -3694,21 +3694,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.01562050680631599</v>
+        <v>0.006333214973237578</v>
       </c>
     </row>
     <row r="35">
@@ -3717,21 +3717,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.182887009405122</v>
+        <v>0.1700340970468579</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.007536303111343234</v>
+        <v>0.006715176389721078</v>
       </c>
     </row>
     <row r="36">
@@ -3776,7 +3776,7 @@
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.1818991373690566</v>
+        <v>0.165925880714699</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -3784,21 +3784,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>0.0007107483367974066</v>
+        <v>0.008878576959656215</v>
       </c>
     </row>
     <row r="37">
@@ -3807,21 +3807,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1813402908531168</v>
+        <v>0.161412837535694</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>0.006406434014346374</v>
+        <v>0.01044761932067817</v>
       </c>
     </row>
     <row r="38">
@@ -3852,21 +3852,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1626825857238252</v>
+        <v>0.1610805077650272</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -3874,21 +3874,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>0.00695363189152931</v>
+        <v>0.0130673714499161</v>
       </c>
     </row>
     <row r="39">
@@ -3897,21 +3897,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1493938107319355</v>
+        <v>0.1552956653675255</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -3919,21 +3919,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0.0144927607850982</v>
+        <v>0.01547342714342292</v>
       </c>
     </row>
     <row r="40">
@@ -3942,21 +3942,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1488157988062115</v>
+        <v>0.1373843410082278</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -3964,21 +3964,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>0.01563559086606925</v>
+        <v>0.01949542099634249</v>
       </c>
     </row>
     <row r="41"/>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.5325686619065126</v>
+        <v>0.492088128019023</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1030739944664463</v>
+        <v>-0.1078513629065362</v>
       </c>
     </row>
     <row r="46">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.4356763539097035</v>
+        <v>0.3712743921488286</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4129,7 +4129,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.06648786116969174</v>
+        <v>-0.0767384073925601</v>
       </c>
     </row>
     <row r="47">
@@ -4152,7 +4152,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.3874473461230392</v>
+        <v>0.3427804962468717</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -4160,12 +4160,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4174,7 +4174,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.06199276024727007</v>
+        <v>-0.07460456158270312</v>
       </c>
     </row>
     <row r="48">
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.3253472015954513</v>
+        <v>0.3007691483782722</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.05152052900082926</v>
+        <v>-0.04925709057111738</v>
       </c>
     </row>
     <row r="49">
@@ -4228,21 +4228,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.2219137641347035</v>
+        <v>0.2122412593146648</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -4264,7 +4264,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.01811792323657113</v>
+        <v>-0.03045292178610148</v>
       </c>
     </row>
     <row r="50">
@@ -4273,21 +4273,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.2055451494520224</v>
+        <v>0.2019677880743778</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>0.01021688261231857</v>
+        <v>-0.01261267301466862</v>
       </c>
     </row>
     <row r="51">
@@ -4318,21 +4318,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.1988263906526939</v>
+        <v>0.1955970651055683</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -4354,7 +4354,7 @@
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0.01324972665635937</v>
+        <v>-0.01165871525940587</v>
       </c>
     </row>
     <row r="52">
@@ -4363,21 +4363,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.1909553141258775</v>
+        <v>0.1847829780575205</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>0.01441086506525235</v>
+        <v>0.01749884975843297</v>
       </c>
     </row>
     <row r="53">
@@ -4422,7 +4422,7 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.1712164156328317</v>
+        <v>0.1634119207411262</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.03781066799932487</v>
+        <v>0.02063598684603107</v>
       </c>
     </row>
     <row r="54">
@@ -4453,21 +4453,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.1674809179118946</v>
+        <v>0.1411997826397948</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -4475,21 +4475,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.0588211296236365</v>
+        <v>0.04469916993703804</v>
       </c>
     </row>
     <row r="55"/>
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>1.010209847897446</v>
+        <v>0.9752973808278689</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.08811681501600022</v>
+        <v>-0.105633730521753</v>
       </c>
     </row>
     <row r="60">
@@ -4618,7 +4618,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.8958286315873361</v>
+        <v>0.8490231061530853</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.0756123616951746</v>
+        <v>-0.07651708747572938</v>
       </c>
     </row>
     <row r="61">
@@ -4663,7 +4663,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.592432619827618</v>
+        <v>0.637525451154147</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4685,7 +4685,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.01807310166919218</v>
+        <v>-0.03982504178054347</v>
       </c>
     </row>
     <row r="62">
@@ -4694,21 +4694,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.5727283335086024</v>
+        <v>0.572892760498946</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4716,12 +4716,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>0.03149104341912445</v>
+        <v>0.005867239913128541</v>
       </c>
     </row>
     <row r="63">
@@ -4739,21 +4739,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.5448876757882486</v>
+        <v>0.5478175948006423</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>0.04051684587407212</v>
+        <v>0.01482723015646648</v>
       </c>
     </row>
     <row r="64">
@@ -4798,7 +4798,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.5072741660579498</v>
+        <v>0.4778043309358975</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4820,7 +4820,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>0.04188666432932187</v>
+        <v>0.02163945630850739</v>
       </c>
     </row>
     <row r="65">
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.4547730613970824</v>
+        <v>0.4753202424816387</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4851,21 +4851,21 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.04504573209089346</v>
+        <v>0.0229643858417643</v>
       </c>
     </row>
     <row r="66">
@@ -4874,21 +4874,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.3227732209898797</v>
+        <v>0.3279700475643019</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>0.04746242203726792</v>
+        <v>0.02932687436768888</v>
       </c>
     </row>
     <row r="67">
@@ -4919,21 +4919,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.3204008684166899</v>
+        <v>0.3212191929257402</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4941,21 +4941,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.05763047437933166</v>
+        <v>0.03139641638745561</v>
       </c>
     </row>
     <row r="68">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.290569732444071</v>
+        <v>0.2868037723664518</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -4986,21 +4986,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.06558974900891346</v>
+        <v>0.04788363134650608</v>
       </c>
     </row>
     <row r="69"/>
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.657534783520286</v>
+        <v>2.656918262177158</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.05164825669291973</v>
+        <v>0.07925405140342745</v>
       </c>
     </row>
     <row r="74">
@@ -5129,7 +5129,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.355134539065858</v>
+        <v>2.366741160451116</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.08155100976358765</v>
+        <v>0.08843645736215122</v>
       </c>
     </row>
     <row r="75">
@@ -5174,7 +5174,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.128750670007718</v>
+        <v>2.262549671885854</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1261862555799129</v>
+        <v>0.1588986777166521</v>
       </c>
     </row>
     <row r="76">
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.578203373729222</v>
+        <v>1.587725312136041</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1581009648570555</v>
+        <v>0.160760394309313</v>
       </c>
     </row>
     <row r="77">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.279185901479832</v>
+        <v>1.314260173290272</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5272,21 +5272,21 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.2170699241309788</v>
+        <v>0.2451997999696329</v>
       </c>
     </row>
     <row r="78">
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.165684511259543</v>
+        <v>1.234632894687103</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5317,21 +5317,21 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.2206642493248834</v>
+        <v>0.2547636267406239</v>
       </c>
     </row>
     <row r="79">
@@ -5340,21 +5340,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>0.9552406255062227</v>
+        <v>1.043069730891051</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.2438158503473316</v>
+        <v>0.2605308393175807</v>
       </c>
     </row>
     <row r="80">
@@ -5385,21 +5385,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.954614100743882</v>
+        <v>0.9960998088341022</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5421,7 +5421,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.2968041964544554</v>
+        <v>0.3058395791463391</v>
       </c>
     </row>
     <row r="81">
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8040484128217973</v>
+        <v>0.8374613842841889</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5466,7 +5466,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.3374907422050768</v>
+        <v>0.3644016657107947</v>
       </c>
     </row>
     <row r="82">
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.7771624048980768</v>
+        <v>0.7964600122375063</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.3710626050392798</v>
+        <v>0.3860748192774108</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -491,11 +491,11 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="23" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>217.69</v>
+        <v>212.71</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>-0.04130886766308772</v>
+        <v>-0.02287654771320735</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.03430418196810892</v>
+        <v>-0.02511570496457871</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.0004596080022003513</v>
+        <v>-0.01088117323731186</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.06962459645969421</v>
+        <v>0.04515527834356381</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.1005561126530614</v>
+        <v>0.08603086924847614</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.492088128019023</v>
+        <v>0.4573918594429942</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.761104786024366</v>
+        <v>0.7246623586077956</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.9752973808278689</v>
+        <v>0.9520774783654862</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.366741160451116</v>
+        <v>2.289722133824756</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4987754688359554</v>
+        <v>0.4872583148160401</v>
       </c>
     </row>
     <row r="3">
@@ -648,51 +648,51 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>61.97</v>
+        <v>31.72</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>-0.04895644969494128</v>
+        <v>0.05382056183899842</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>-0.009272550334641361</v>
+        <v>0.06981449313512078</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>-0.0189963112715763</v>
+        <v>0.1048415299500913</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.02837708175904274</v>
+        <v>0.1059971748895028</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.006333214973237578</v>
+        <v>0.3042763039222052</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.3712743921488286</v>
+        <v>0.2749627333782894</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.6933948894804889</v>
+        <v>0.3485349623899499</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.8490231061530853</v>
+        <v>0.6739742256678367</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>2.656918262177158</v>
+        <v>1.153029031053011</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.540653888587572</v>
+        <v>0.2912687137641736</v>
       </c>
     </row>
     <row r="4">
@@ -704,51 +704,51 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>30.1</v>
+        <v>60.68</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.009728309987347306</v>
+        <v>-0.02081653848824483</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.02380955006877805</v>
+        <v>-0.05261518479333693</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.05911331107198436</v>
+        <v>-0.02631577980871913</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.04951185708452321</v>
+        <v>0.006969830656176734</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.2402142486091758</v>
+        <v>-0.01429501378304132</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.2019677880743778</v>
+        <v>0.3536903041044304</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.2786419279447385</v>
+        <v>0.6244467787300783</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.572892760498946</v>
+        <v>0.8609197216288644</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.043069730891051</v>
+        <v>2.58079428545959</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2689009713884123</v>
+        <v>0.5298885369494299</v>
       </c>
     </row>
     <row r="5">
@@ -760,51 +760,51 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>92.48999999999999</v>
+        <v>30.59</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.01414474735409743</v>
+        <v>0.05337462769265211</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.04143677971331816</v>
+        <v>0.05957739048684285</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.09184274422596417</v>
+        <v>0.09523808873425543</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.1096580630710662</v>
+        <v>0.09680892154990794</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.06999069009124903</v>
+        <v>0.29344611610987</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.2122412593146648</v>
+        <v>0.2207316518087459</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.4777170103156245</v>
+        <v>0.2195457088685426</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.637525451154147</v>
+        <v>0.4063105035579599</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.6580019043393608</v>
+        <v>0.5346545217132779</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.183572888239022</v>
+        <v>0.1534626627801285</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>54.52</v>
+        <v>92.14</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-0.02625470935230334</v>
+        <v>-0.003784176475348344</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>-0.002196173741310425</v>
+        <v>0.03458344841103678</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-0.005653863996689434</v>
+        <v>0.108251143445649</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.03551754753445935</v>
+        <v>0.1054589211331121</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.05761399155497804</v>
+        <v>0.05616691478524061</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.3427804962468717</v>
+        <v>0.1995004934281097</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.3963432297666591</v>
+        <v>0.4855530058926529</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.4778043309358975</v>
+        <v>0.6335960704875836</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>1.587725312136041</v>
+        <v>0.6517278454875504</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.3729015372782927</v>
+        <v>0.1820780784596991</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>29.04</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.007284113505966694</v>
+        <v>0.08391273353996631</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.009735767886549729</v>
+        <v>0.06751595111428954</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.05217393167227691</v>
+        <v>0.158258460234517</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.04123347260831189</v>
+        <v>0.3788564868018298</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.237851749736337</v>
+        <v>0.1817380831391522</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.1634119207411262</v>
+        <v>-0.04733568264973753</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.163516831890183</v>
+        <v>0.3094312906241738</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.3279700475643019</v>
+        <v>0.7268003382435506</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.4568932405611115</v>
+        <v>2.536319133163716</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.133641952621933</v>
+        <v>0.5235281519824204</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>39.35</v>
+        <v>37.06</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.006062179276124846</v>
+        <v>0.06494259154533721</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.003826472149547788</v>
+        <v>0.08362574697515157</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-0.0005080126570050636</v>
+        <v>0.08744129642390064</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.01156804448819404</v>
+        <v>0.08299240360253668</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.165925880714699</v>
+        <v>0.1832695317495601</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.1088517304460426</v>
+        <v>0.1483770035160343</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.3143860340321525</v>
+        <v>0.2592342384234247</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.3212191929257402</v>
+        <v>0.5711313623876917</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>1.234632894687103</v>
+        <v>0.8149250602877578</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.3073806789709661</v>
+        <v>0.2197932688068385</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>34.8</v>
+        <v>54.13</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.02022863132109087</v>
+        <v>-0.007153326969440599</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.01576184886115239</v>
+        <v>-0.02380522410572183</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.0357143100427133</v>
+        <v>-0.01060131650636476</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.01694909397041533</v>
+        <v>0.02811015193435207</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.1229428684763398</v>
+        <v>0.0433693129081838</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.08194412883594793</v>
+        <v>0.3405161105892691</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.1839695651169497</v>
+        <v>0.3731028561315088</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.4753202424816387</v>
+        <v>0.4951105486974809</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.7042468530196748</v>
+        <v>1.569214234280331</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1944761983750516</v>
+        <v>0.3696200545263442</v>
       </c>
     </row>
     <row r="10">
@@ -1040,51 +1040,51 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>30.58</v>
+        <v>38.35</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.001309725179424515</v>
+        <v>-0.025412961595352</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.0003271255800350037</v>
+        <v>-0.03058652318416899</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.002283839990063097</v>
+        <v>-0.02442133975152161</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.08209482222343256</v>
+        <v>-0.01413889537746971</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.161412837535694</v>
+        <v>0.1423890027629</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.06937531223716209</v>
+        <v>0.0884709297088293</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.2690404424976294</v>
+        <v>0.2682509045218524</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.2868037723664518</v>
+        <v>0.2880370610290335</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.314260173290272</v>
+        <v>1.177844254754709</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.3227285489093292</v>
+        <v>0.2962107120754172</v>
       </c>
     </row>
     <row r="11">
@@ -1110,37 +1110,37 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>17.78</v>
+        <v>17.6</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.0005621263837658486</v>
+        <v>-0.01012375130620657</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.006795064567963971</v>
+        <v>-0.01179107752778052</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.009080581145935351</v>
+        <v>-0.0039614994070164</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.03794521644622306</v>
+        <v>0.02743731720545473</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.1552956653675255</v>
+        <v>0.155613979676154</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.1377522004963012</v>
+        <v>0.1377114482822566</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.2273320529644551</v>
+        <v>0.2094413417340255</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.1964363250013894</v>
+        <v>0.1835790884890438</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.9960998088341022</v>
+        <v>0.9758922138878656</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.2591015281237765</v>
+        <v>0.2548382545025529</v>
       </c>
     </row>
     <row r="12">
@@ -1166,37 +1166,37 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>14.73</v>
+        <v>14.94</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.01207245519905376</v>
+        <v>0.01425662217740231</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.004089943124086171</v>
+        <v>0.01356850830194856</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0</v>
+        <v>0.03248094710996163</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.0130673714499161</v>
+        <v>0.02751029020493179</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.0130673714499161</v>
+        <v>0.0204917506847857</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.1847829780575205</v>
+        <v>0.2026261868043044</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.282517205657133</v>
+        <v>0.3039923793434192</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.2609190085602435</v>
+        <v>0.2819796778185963</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.8374613842841889</v>
+        <v>0.8636573770054952</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2248213282178295</v>
+        <v>0.2306144894880284</v>
       </c>
     </row>
     <row r="13">
@@ -1208,12 +1208,12 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1222,37 +1222,37 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>121.55</v>
+        <v>29.81</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.01379307868756341</v>
+        <v>-0.02517987114731013</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.01618777782759062</v>
+        <v>-0.02326346596238926</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-0.02791105116935544</v>
+        <v>-0.03371153655323866</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-0.03286121294867539</v>
+        <v>0.05484781403067518</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.08130948395947168</v>
+        <v>0.1430214552587423</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.06198108460998841</v>
+        <v>0.03130132083429893</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.2715908140389458</v>
+        <v>0.2355811218306019</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.2519666934372304</v>
+        <v>0.2732733116833495</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.4789816659507768</v>
+        <v>1.255987563146873</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.1393424098035529</v>
+        <v>0.3115320271584192</v>
       </c>
     </row>
     <row r="14">
@@ -1264,51 +1264,51 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>61.85</v>
+        <v>121.67</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.02827970162775195</v>
+        <v>0.0009872078500599013</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.007541739778637369</v>
+        <v>-0.01369976031975173</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.1472824828266093</v>
+        <v>-0.01569454277022131</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.2721102392612387</v>
+        <v>-0.03190644594600089</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.04072014397641777</v>
+        <v>0.09140648102947813</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>-0.1078513629065362</v>
+        <v>0.07537496108326658</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.2210397782163138</v>
+        <v>0.2815962402830716</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.5478175948006423</v>
+        <v>0.2380812342794645</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>2.262549671885854</v>
+        <v>0.4804417282614981</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.4831521676423265</v>
+        <v>0.1397172090859535</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>23.21</v>
+        <v>53.32</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.0025784861242234</v>
+        <v>0.04344425219165937</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.02683443550358677</v>
+        <v>0.02597649494730625</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.004327064971010985</v>
+        <v>0.0778249116458456</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.1327476497675948</v>
+        <v>0.1171171214372482</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.1610805077650272</v>
+        <v>0.2817308089084187</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.3007691483782722</v>
+        <v>0.1028389812187414</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.03409972095075431</v>
+        <v>0.02047108724949021</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.0229643858417643</v>
+        <v>0.07261068077136712</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.3933117914132078</v>
+        <v>0.2092461641359549</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.1169046631963788</v>
+        <v>0.06538089900949551</v>
       </c>
     </row>
     <row r="16">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1390,37 +1390,37 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>44.59</v>
+        <v>23.21</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.005411537468413607</v>
+        <v>0</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.00535359510738509</v>
+        <v>-0.01610856573366948</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.0002241776205217372</v>
+        <v>0.007815822512394766</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.07627322771265677</v>
+        <v>0.1327476497675948</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.1700340970468579</v>
+        <v>0.1680925065007757</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.1955970651055683</v>
+        <v>0.3074567986340855</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.08865967648304363</v>
+        <v>0.03900067879388147</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.02163945630850739</v>
+        <v>0.03522657590427203</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.3058395791463391</v>
+        <v>0.3933116318798398</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.09302461536387829</v>
+        <v>0.1169046205680715</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>115.09</v>
+        <v>44.82</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.000608587174988795</v>
+        <v>0.005158096915211186</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.005100310907059646</v>
+        <v>0.005158096915211186</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.01091444023547006</v>
+        <v>0.01196655607001951</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.05127360766534361</v>
+        <v>0.08182474932844563</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.06269615045982779</v>
+        <v>0.1832100958558471</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.1411997826397948</v>
+        <v>0.2122828658025409</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.1504877707998904</v>
+        <v>0.09092045235715185</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.2206069456676076</v>
+        <v>0.02829396131124362</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.07925405140342745</v>
+        <v>0.3125752262512944</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.02574929986851693</v>
+        <v>0.09490070233789649</v>
       </c>
     </row>
     <row r="18">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1502,37 +1502,37 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>51.1</v>
+        <v>114.43</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.006029981992046629</v>
+        <v>-0.005734608165050004</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.0169296090008656</v>
+        <v>-0.01785256023446491</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.04328295123924319</v>
+        <v>-0.02029111887550039</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.07060546750901708</v>
+        <v>-0.05671418178122434</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.2424020701943232</v>
+        <v>0.06258703418116029</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.05577998319807387</v>
+        <v>0.1395140648445365</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>-0.01576257258586422</v>
+        <v>0.1512000717189317</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.03139641638745561</v>
+        <v>0.208012253312444</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.1588986777166521</v>
+        <v>0.07306495230808596</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.05038494660026349</v>
+        <v>0.02378478305439424</v>
       </c>
     </row>
     <row r="19">
@@ -1558,37 +1558,37 @@
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>96.55</v>
+        <v>96.7</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.004473577745409241</v>
+        <v>0.001553535906197334</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.01085951799985274</v>
+        <v>-0.003503750660319271</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.008930354481004543</v>
+        <v>-0.01577611248608457</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-0.001447920013584403</v>
+        <v>0.0001033664968825843</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.1019173707515564</v>
+        <v>0.1111110916302307</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.1067531697694377</v>
+        <v>0.1105962558195044</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.1249526639906042</v>
+        <v>0.1386083041659174</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1080629582798383</v>
+        <v>0.09455062468339226</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.593428803899877</v>
+        <v>0.595904353233228</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.1680037070773626</v>
+        <v>0.1686082638874775</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>68.93000000000001</v>
+        <v>102.42</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.002748877804632954</v>
+        <v>0.01799023504237529</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.01174230271552923</v>
+        <v>0.004610115103208301</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.01651677904300541</v>
+        <v>0.01155553747106475</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.05445919242798092</v>
+        <v>0.05948070868844968</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.01547342714342292</v>
+        <v>0.04606265282554856</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.06082948551233014</v>
+        <v>-0.01060626373099127</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.2077624208043614</v>
+        <v>0.2408564394159272</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.1602987153779831</v>
+        <v>0.1757838036680857</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.7964279394191252</v>
+        <v>0.2676011173523023</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.2156351998018937</v>
+        <v>0.0822498586888647</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>43.19</v>
+        <v>17.31</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.00437995474246089</v>
+        <v>0.005226489905727938</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.01313623139954823</v>
+        <v>-0.008022996611805722</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-0.009857870603051877</v>
+        <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-0.02019063446859226</v>
+        <v>0.06326773561759014</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.0391037862129584</v>
+        <v>0.1594105232497234</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.06121770102283519</v>
+        <v>0.09175201632342445</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.1485954103251452</v>
+        <v>0.1140092407495685</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.1673285515680476</v>
+        <v>-0.03617647074441388</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.3860748192774108</v>
+        <v>0.3715326972439907</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1149675416097462</v>
+        <v>0.1110545661190645</v>
       </c>
     </row>
     <row r="22">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>52.27</v>
+        <v>43.56</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.02061080187625641</v>
+        <v>0.008566861735281872</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.02335575465823214</v>
+        <v>0.01161170422790869</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-0.02207671259742916</v>
+        <v>-0.001146508515495803</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.007711616235122509</v>
+        <v>-0.0117967431071504</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.008878576959656215</v>
+        <v>0.04575125629429255</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.04469916993703804</v>
+        <v>0.07293369699785091</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.1682537368342749</v>
+        <v>0.1679081472765909</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1928870944180205</v>
+        <v>0.1546590912193375</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.7964600122375063</v>
+        <v>0.3979493873209745</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.2156424342724221</v>
+        <v>0.1181424852564401</v>
       </c>
     </row>
     <row r="23">
@@ -1768,44 +1768,52 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>74.28</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.01810975173759077</v>
+        <v>0.004497280679258475</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.01537650615812669</v>
+        <v>0.01584498450167393</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.01667993276356283</v>
+        <v>0.04277102820221712</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.02738583186672394</v>
+        <v>0.05920139138115377</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.09331757595031664</v>
+        <v>0.01163701510718562</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.06923848386460518</v>
-      </c>
-      <c r="M23" s="6" t="inlineStr"/>
-      <c r="N23" s="6" t="inlineStr"/>
-      <c r="O23" s="6" t="inlineStr"/>
-      <c r="P23" s="6" t="inlineStr"/>
+        <v>0.05982641381813458</v>
+      </c>
+      <c r="M23" s="6" t="n">
+        <v>0.2255886331201067</v>
+      </c>
+      <c r="N23" s="6" t="n">
+        <v>0.1683725609192466</v>
+      </c>
+      <c r="O23" s="6" t="n">
+        <v>0.8045071594818334</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v>0.2174548659769173</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -1816,51 +1824,51 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>17.22</v>
+        <v>52.26</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.001739170240319332</v>
+        <v>-0.0001913551969173755</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.004624273250525723</v>
+        <v>-0.02481809716864614</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.01833231630630827</v>
+        <v>-0.02043111872096159</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.05773947094978116</v>
+        <v>0.00751878538036177</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.1373843410082278</v>
+        <v>0.02350170223203119</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.06945530297430524</v>
+        <v>0.0440875486284944</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.09920239928541563</v>
+        <v>0.1659811172550356</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>-0.03982504178054347</v>
+        <v>0.19776379573314</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.3644016657107947</v>
+        <v>0.7961162502781103</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.109125644726821</v>
+        <v>0.2155648894935491</v>
       </c>
     </row>
     <row r="25">
@@ -1872,51 +1880,51 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>100.61</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.01198076400634085</v>
+        <v>0.01268227555917645</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.02291930253834995</v>
+        <v>0.0163343332145387</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.00670400392813808</v>
+        <v>0.01504235324144609</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.04075724129548974</v>
+        <v>0.03365698866553402</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.003991632866314321</v>
+        <v>0.04342364865156756</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>-0.03045292178610148</v>
+        <v>0.0327162683504143</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.2234417118520866</v>
+        <v>0.1850629995155697</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.158422101174124</v>
+        <v>0.09737062382262174</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.2451997999696329</v>
+        <v>0.1754814774881219</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.07583668051872117</v>
+        <v>0.05537126036148621</v>
       </c>
     </row>
     <row r="26">
@@ -1928,51 +1936,51 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>94.62</v>
+        <v>13.94</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.006488677762900297</v>
+        <v>0.008683059928288106</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.006702892830422691</v>
+        <v>-0.006414836372119481</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.004032309968446945</v>
+        <v>-0.01900073589295226</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.02071203734140203</v>
+        <v>-0.008534910074822766</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.03035638505217908</v>
+        <v>0.02650954776876024</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.01749884975843297</v>
+        <v>0.0001720877854347602</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.1587684161419505</v>
+        <v>0.23111935124369</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.09654126236125493</v>
+        <v>0.08924659212441832</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.160760394309313</v>
+        <v>0.09788758127323471</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.0509471104617758</v>
+        <v>0.03161890175818582</v>
       </c>
     </row>
     <row r="27">
@@ -1998,37 +2006,37 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>17.78</v>
+        <v>17.88</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.002820143581508061</v>
+        <v>0.00562421092571741</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.007936581737028048</v>
+        <v>0.0136054296724637</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.01716253731496376</v>
+        <v>0.006756696528056327</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.06149257830719446</v>
+        <v>0.06746263646367767</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.1712780190513719</v>
+        <v>0.1880397962900993</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.1009288610908075</v>
+        <v>0.1030228359416514</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>-0.01222218407524955</v>
+        <v>-0.01650171283681279</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>-0.105633730521753</v>
+        <v>-0.09330629901907916</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.2547636267406239</v>
+        <v>0.2618206820393312</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.07858400011413735</v>
+        <v>0.08060228238741884</v>
       </c>
     </row>
     <row r="28">
@@ -2040,52 +2048,44 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>13.82</v>
+        <v>73.36</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.005039643395846727</v>
+        <v>-0.01238554367345701</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.02607469319946853</v>
+        <v>-0.02666846308854121</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.01985820418937623</v>
+        <v>-0.03103947302256738</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.0170697523207487</v>
+        <v>0.01466109977664765</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.00363102653583125</v>
+        <v>0.09508886325890065</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>-0.01261267301466862</v>
-      </c>
-      <c r="M28" s="6" t="n">
-        <v>0.2215681466301236</v>
-      </c>
-      <c r="N28" s="6" t="n">
-        <v>0.09061902457868798</v>
-      </c>
-      <c r="O28" s="6" t="n">
-        <v>0.08843645736215122</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v>0.02865014910000441</v>
-      </c>
+        <v>0.04605737178716596</v>
+      </c>
+      <c r="M28" s="6" t="inlineStr"/>
+      <c r="N28" s="6" t="inlineStr"/>
+      <c r="O28" s="6" t="inlineStr"/>
+      <c r="P28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
@@ -2110,37 +2110,37 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>17.78</v>
+        <v>18.02</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.001123514116416424</v>
+        <v>0.01349829931662638</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.02788410078475556</v>
+        <v>-0.004969638296778767</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.0368363180688952</v>
+        <v>-0.02118410607717958</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.01252854370125789</v>
+        <v>0.02619595705076527</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.01949542099634249</v>
+        <v>0.03801842305342773</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.02063598684603107</v>
+        <v>0.04001031240147745</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.1278936040130563</v>
+        <v>0.1425154611697756</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.05340487688897411</v>
+        <v>0.06815044669310066</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.463987292838417</v>
+        <v>0.4837483984914488</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1354789889235313</v>
+        <v>0.1405651241616857</v>
       </c>
     </row>
     <row r="30">
@@ -2166,37 +2166,37 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>182</v>
+        <v>183.05</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-0.000768636159644065</v>
+        <v>0.005769247537130928</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.004027118168110411</v>
+        <v>0.00510656687626132</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.01426659342266601</v>
+        <v>0.02045934925323967</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.05238809662711419</v>
+        <v>0.05845958406168594</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.08140223826394699</v>
+        <v>0.1076486090781397</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.07176436400598307</v>
+        <v>0.09735801441688441</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.03553706351358898</v>
+        <v>0.03339746646147512</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>-0.07651708747572938</v>
+        <v>-0.05866114079799034</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.6614212970646633</v>
+        <v>0.6710065641704246</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1843859796890841</v>
+        <v>0.1866593130374576</v>
       </c>
     </row>
     <row r="31">
@@ -2208,12 +2208,12 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -2222,37 +2222,37 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>122.54</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.02108962600425301</v>
+        <v>0.01959871270456603</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.03007753310519623</v>
+        <v>0.002884068751177526</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.0323752249990632</v>
+        <v>-0.01166789524458745</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.0005715660498613051</v>
+        <v>0.01349896027705966</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.03018078234039168</v>
+        <v>0.04277144978483327</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>-0.07460456158270312</v>
+        <v>0.01463179334517783</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.09537451172431122</v>
+        <v>0.07520388228851749</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.01482723015646648</v>
+        <v>0.05087337900504751</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.409914774293382</v>
+        <v>0.4982987418336839</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1213235772046217</v>
+        <v>0.1442813111828851</v>
       </c>
     </row>
     <row r="32">
@@ -2264,51 +2264,51 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
+          <t>Construction &amp; Housing</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
       <c r="F32" s="5" t="n">
-        <v>64.8</v>
+        <v>123.35</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.005219471002092968</v>
+        <v>0.006610066529639802</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.02964953225115807</v>
+        <v>-0.00955518253298715</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.03153490501968748</v>
+        <v>-0.03171364263194765</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.005982503068610479</v>
+        <v>0.00718541066911671</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.01044761932067817</v>
+        <v>0.05059189699973299</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>-0.01165871525940587</v>
+        <v>-0.06841979288244282</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.05518961312085424</v>
+        <v>0.09882306805639374</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.02932687436768888</v>
+        <v>0.00879169602369223</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.4694985907480649</v>
+        <v>0.4192344047525831</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1369020719705425</v>
+        <v>0.1237888278158608</v>
       </c>
     </row>
     <row r="33">
@@ -2320,51 +2320,51 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>130.77</v>
+        <v>55.05</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.00931814945105347</v>
+        <v>0.02001108008022667</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0.002376188430479376</v>
+        <v>0.007319262580298913</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.006155932112189566</v>
+        <v>0.004928814599859388</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.03547719054162168</v>
+        <v>0.03109196228486866</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.01997771258381364</v>
+        <v>0.03966002726842111</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.04925709057111738</v>
+        <v>-0.0473428963705621</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>-0.01227797514600926</v>
+        <v>0.01720096226142864</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.04788363134650608</v>
+        <v>0.02033648203402283</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.5586188684852251</v>
+        <v>0.28575542288676</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1594356322450534</v>
+        <v>0.08739197000060317</v>
       </c>
     </row>
     <row r="34">
@@ -2376,51 +2376,51 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>53.97</v>
+        <v>130.9</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>-0.01153841155721957</v>
+        <v>0.0009940324216293206</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.02121868302314411</v>
+        <v>-0.002286608679390123</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.01442653624990031</v>
+        <v>0.004990356211012514</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.01086349199635217</v>
+        <v>-0.03451842359761903</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>0.006715176389721078</v>
+        <v>-0.02518981934904563</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.0767384073925601</v>
+        <v>-0.05650461164050169</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.002916213361189079</v>
+        <v>-0.01151032631584403</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.005867239913128541</v>
+        <v>0.04422533661435146</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2605308393175807</v>
+        <v>0.5601683280443623</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.08023395689320201</v>
+        <v>0.1598197123805005</v>
       </c>
     </row>
   </sheetData>
@@ -2537,17 +2537,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -2560,17 +2560,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -2582,17 +2582,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2650,17 +2650,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -2672,12 +2672,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2695,17 +2695,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -2740,17 +2740,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2785,17 +2785,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -2807,17 +2807,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -2830,17 +2830,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2875,17 +2875,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -2897,17 +2897,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -2942,17 +2942,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.2721102392612387</v>
+        <v>0.3788564868018298</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.05127360766534361</v>
+        <v>-0.05671418178122434</v>
       </c>
     </row>
     <row r="18">
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.03547719054162168</v>
+        <v>-0.03451842359761903</v>
       </c>
     </row>
     <row r="19">
@@ -3116,21 +3116,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.1096580630710662</v>
+        <v>0.1171171214372482</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -3152,7 +3152,7 @@
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.03286121294867539</v>
+        <v>-0.03190644594600089</v>
       </c>
     </row>
     <row r="20">
@@ -3161,21 +3161,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.08209482222343256</v>
+        <v>0.1059971748895028</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -3183,21 +3183,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.02019063446859226</v>
+        <v>-0.01413889537746971</v>
       </c>
     </row>
     <row r="21">
@@ -3206,21 +3206,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.07627322771265677</v>
+        <v>0.1054589211331121</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -3228,21 +3228,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.0170697523207487</v>
+        <v>-0.0117967431071504</v>
       </c>
     </row>
     <row r="22">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.07060546750901708</v>
+        <v>0.09680892154990794</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -3273,21 +3273,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.005982503068610479</v>
+        <v>-0.008534910074822766</v>
       </c>
     </row>
     <row r="23">
@@ -3296,21 +3296,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FDCPX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tech Hardware</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.06962459645969421</v>
+        <v>0.08299240360253668</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.001447920013584403</v>
+        <v>0.0001033664968825843</v>
       </c>
     </row>
     <row r="24">
@@ -3341,21 +3341,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.06149257830719446</v>
+        <v>0.08182474932844563</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -3363,21 +3363,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>0.0005715660498613051</v>
+        <v>0.006969830656176734</v>
       </c>
     </row>
     <row r="25">
@@ -3386,21 +3386,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.05773947094978116</v>
+        <v>0.06746263646367767</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -3408,21 +3408,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>0.007711616235122509</v>
+        <v>0.00718541066911671</v>
       </c>
     </row>
     <row r="26">
@@ -3431,21 +3431,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.05445919242798092</v>
+        <v>0.06326773561759014</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -3453,21 +3453,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>0.01086349199635217</v>
+        <v>0.00751878538036177</v>
       </c>
     </row>
     <row r="27"/>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.2424020701943232</v>
+        <v>0.3042763039222052</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.01997771258381364</v>
+        <v>-0.02518981934904563</v>
       </c>
     </row>
     <row r="32">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3596,7 +3596,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.2402142486091758</v>
+        <v>0.29344611610987</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -3604,21 +3604,21 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>0.00363102653583125</v>
+        <v>-0.01429501378304132</v>
       </c>
     </row>
     <row r="33">
@@ -3627,21 +3627,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>Medical Tech &amp; Devices</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
       <c r="E33" s="11" t="n">
-        <v>0.237851749736337</v>
+        <v>0.2817308089084187</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -3649,21 +3649,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>0.003991632866314321</v>
+        <v>0.01163701510718562</v>
       </c>
     </row>
     <row r="34">
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.1712780190513719</v>
+        <v>0.1880397962900993</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -3694,21 +3694,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>0.006333214973237578</v>
+        <v>0.0204917506847857</v>
       </c>
     </row>
     <row r="35">
@@ -3717,21 +3717,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.1700340970468579</v>
+        <v>0.1832695317495601</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -3739,21 +3739,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>0.006715176389721078</v>
+        <v>0.02350170223203119</v>
       </c>
     </row>
     <row r="36">
@@ -3762,21 +3762,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.165925880714699</v>
+        <v>0.1832100958558471</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -3784,21 +3784,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>0.008878576959656215</v>
+        <v>0.02650954776876024</v>
       </c>
     </row>
     <row r="37">
@@ -3807,21 +3807,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.161412837535694</v>
+        <v>0.1817380831391522</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -3829,21 +3829,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
+          <t>Retailing</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
       <c r="K37" s="11" t="n">
-        <v>0.01044761932067817</v>
+        <v>0.03801842305342773</v>
       </c>
     </row>
     <row r="38">
@@ -3866,7 +3866,7 @@
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1610805077650272</v>
+        <v>0.1680925065007757</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -3874,21 +3874,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>0.0130673714499161</v>
+        <v>0.03966002726842111</v>
       </c>
     </row>
     <row r="39">
@@ -3897,21 +3897,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1552956653675255</v>
+        <v>0.1594105232497234</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -3919,21 +3919,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0.01547342714342292</v>
+        <v>0.04277144978483327</v>
       </c>
     </row>
     <row r="40">
@@ -3942,21 +3942,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1373843410082278</v>
+        <v>0.155613979676154</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -3964,21 +3964,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>0.01949542099634249</v>
+        <v>0.0433693129081838</v>
       </c>
     </row>
     <row r="41"/>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.492088128019023</v>
+        <v>0.4573918594429942</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -4070,21 +4070,21 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1078513629065362</v>
+        <v>-0.06841979288244282</v>
       </c>
     </row>
     <row r="46">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.3712743921488286</v>
+        <v>0.3536903041044304</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -4115,21 +4115,21 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.0767384073925601</v>
+        <v>-0.05650461164050169</v>
       </c>
     </row>
     <row r="47">
@@ -4152,7 +4152,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.3427804962468717</v>
+        <v>0.3405161105892691</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -4160,12 +4160,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4174,7 +4174,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.07460456158270312</v>
+        <v>-0.0473428963705621</v>
       </c>
     </row>
     <row r="48">
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.3007691483782722</v>
+        <v>0.3074567986340855</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -4205,21 +4205,21 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.04925709057111738</v>
+        <v>-0.04733568264973753</v>
       </c>
     </row>
     <row r="49">
@@ -4228,21 +4228,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.2122412593146648</v>
+        <v>0.2749627333782894</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -4264,7 +4264,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.03045292178610148</v>
+        <v>-0.01060626373099127</v>
       </c>
     </row>
     <row r="50">
@@ -4273,12 +4273,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.2019677880743778</v>
+        <v>0.2207316518087459</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.01261267301466862</v>
+        <v>0.0001720877854347602</v>
       </c>
     </row>
     <row r="51">
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.1955970651055683</v>
+        <v>0.2122828658025409</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -4354,7 +4354,7 @@
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.01165871525940587</v>
+        <v>0.01463179334517783</v>
       </c>
     </row>
     <row r="52">
@@ -4377,7 +4377,7 @@
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.1847829780575205</v>
+        <v>0.2026261868043044</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4385,21 +4385,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>0.01749884975843297</v>
+        <v>0.03130132083429893</v>
       </c>
     </row>
     <row r="53">
@@ -4408,21 +4408,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.1634119207411262</v>
+        <v>0.1995004934281097</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -4430,21 +4430,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.02063598684603107</v>
+        <v>0.0327162683504143</v>
       </c>
     </row>
     <row r="54">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4467,7 +4467,7 @@
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.1411997826397948</v>
+        <v>0.1483770035160343</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -4475,21 +4475,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.04469916993703804</v>
+        <v>0.04001031240147745</v>
       </c>
     </row>
     <row r="55"/>
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.9752973808278689</v>
+        <v>0.9520774783654862</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.105633730521753</v>
+        <v>-0.09330629901907916</v>
       </c>
     </row>
     <row r="60">
@@ -4618,7 +4618,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.8490231061530853</v>
+        <v>0.8609197216288644</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.07651708747572938</v>
+        <v>-0.05866114079799034</v>
       </c>
     </row>
     <row r="61">
@@ -4649,21 +4649,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.637525451154147</v>
+        <v>0.7268003382435506</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4685,7 +4685,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.03982504178054347</v>
+        <v>-0.03617647074441388</v>
       </c>
     </row>
     <row r="62">
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.572892760498946</v>
+        <v>0.6739742256678367</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4716,12 +4716,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>0.005867239913128541</v>
+        <v>0.00879169602369223</v>
       </c>
     </row>
     <row r="63">
@@ -4739,21 +4739,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.5478175948006423</v>
+        <v>0.6335960704875836</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>0.01482723015646648</v>
+        <v>0.02033648203402283</v>
       </c>
     </row>
     <row r="64">
@@ -4784,21 +4784,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.4778043309358975</v>
+        <v>0.5711313623876917</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4820,7 +4820,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>0.02163945630850739</v>
+        <v>0.02829396131124362</v>
       </c>
     </row>
     <row r="65">
@@ -4829,21 +4829,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.4753202424816387</v>
+        <v>0.4951105486974809</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4865,7 +4865,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.0229643858417643</v>
+        <v>0.03522657590427203</v>
       </c>
     </row>
     <row r="66">
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.3279700475643019</v>
+        <v>0.4063105035579599</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4896,21 +4896,21 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>0.02932687436768888</v>
+        <v>0.04422533661435146</v>
       </c>
     </row>
     <row r="67">
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.3212191929257402</v>
+        <v>0.2880370610290335</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4941,21 +4941,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.03139641638745561</v>
+        <v>0.05087337900504751</v>
       </c>
     </row>
     <row r="68">
@@ -4964,21 +4964,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.2868037723664518</v>
+        <v>0.2819796778185963</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -4986,21 +4986,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.04788363134650608</v>
+        <v>0.06815044669310066</v>
       </c>
     </row>
     <row r="69"/>
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.656918262177158</v>
+        <v>2.58079428545959</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.07925405140342745</v>
+        <v>0.07306495230808596</v>
       </c>
     </row>
     <row r="74">
@@ -5115,21 +5115,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FDCPX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tech Hardware</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.366741160451116</v>
+        <v>2.536319133163716</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.08843645736215122</v>
+        <v>0.09788758127323471</v>
       </c>
     </row>
     <row r="75">
@@ -5160,21 +5160,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FDCPX</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.262549671885854</v>
+        <v>2.289722133824756</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5182,21 +5182,21 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1588986777166521</v>
+        <v>0.1754814774881219</v>
       </c>
     </row>
     <row r="76">
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.587725312136041</v>
+        <v>1.569214234280331</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5227,21 +5227,21 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.160760394309313</v>
+        <v>0.2092461641359549</v>
       </c>
     </row>
     <row r="77">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.314260173290272</v>
+        <v>1.255987563146873</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5272,21 +5272,21 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.2451997999696329</v>
+        <v>0.2618206820393312</v>
       </c>
     </row>
     <row r="78">
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.234632894687103</v>
+        <v>1.177844254754709</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5317,21 +5317,21 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.2547636267406239</v>
+        <v>0.2676011173523023</v>
       </c>
     </row>
     <row r="79">
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.043069730891051</v>
+        <v>1.153029031053011</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.2605308393175807</v>
+        <v>0.28575542288676</v>
       </c>
     </row>
     <row r="80">
@@ -5399,7 +5399,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.9960998088341022</v>
+        <v>0.9758922138878656</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5421,7 +5421,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.3058395791463391</v>
+        <v>0.3125752262512944</v>
       </c>
     </row>
     <row r="81">
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8374613842841889</v>
+        <v>0.8636573770054952</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5466,7 +5466,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.3644016657107947</v>
+        <v>0.3715326972439907</v>
       </c>
     </row>
     <row r="82">
@@ -5475,21 +5475,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.7964600122375063</v>
+        <v>0.8149250602877578</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5497,21 +5497,21 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.3860748192774108</v>
+        <v>0.3933116318798398</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -493,9 +493,9 @@
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>212.71</v>
+        <v>213.1</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>-0.02287654771320735</v>
+        <v>0.001833479278542161</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>-0.02511570496457871</v>
+        <v>-0.03356006302260484</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>-0.01088117323731186</v>
+        <v>0.01394113317836654</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.04515527834356381</v>
+        <v>0.05375073236228278</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.08603086924847614</v>
+        <v>0.07230921695222103</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.4573918594429942</v>
+        <v>0.4387855938080918</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7246623586077956</v>
+        <v>0.7891279934797888</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.9520774783654862</v>
+        <v>0.9712792475113445</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.289722133824756</v>
+        <v>2.295753382308867</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4872583148160401</v>
+        <v>0.4881666537682929</v>
       </c>
     </row>
     <row r="3">
@@ -648,51 +648,51 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>31.72</v>
+        <v>60.97</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.05382056183899842</v>
+        <v>0.004779184477073928</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.06981449313512078</v>
+        <v>-0.05384855818182677</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.1048415299500913</v>
+        <v>-0.02432389849474825</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.1059971748895028</v>
+        <v>0.004944833703841578</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.3042763039222052</v>
+        <v>-0.05001556667511864</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.2749627333782894</v>
+        <v>0.3453337400583016</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.3485349623899499</v>
+        <v>0.7042665310042533</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.6739742256678367</v>
+        <v>0.8874913481181854</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1.153029031053011</v>
+        <v>2.597907156962665</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2912687137641736</v>
+        <v>0.5323218136313803</v>
       </c>
     </row>
     <row r="4">
@@ -704,51 +704,51 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>60.68</v>
+        <v>30.59</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.02081653848824483</v>
+        <v>-0.03562418616733254</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>-0.05261518479333693</v>
+        <v>0.04295943512306111</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>-0.02631577980871913</v>
+        <v>0.05192573015280111</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.006969830656176734</v>
+        <v>0.09172018746745358</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>-0.01429501378304132</v>
+        <v>0.2280208887984347</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.3536903041044304</v>
+        <v>0.2352598251978533</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.6244467787300783</v>
+        <v>0.3173226611216025</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.8609197216288644</v>
+        <v>0.6008544693997961</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>2.58079428545959</v>
+        <v>1.076329124027107</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.5298885369494299</v>
+        <v>0.2757494758528483</v>
       </c>
     </row>
     <row r="5">
@@ -760,51 +760,51 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>30.59</v>
+        <v>92.48</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.05337462769265211</v>
+        <v>0.003690079981955696</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.05957739048684285</v>
+        <v>0.03735279611956077</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.09523808873425543</v>
+        <v>0.0937906566404425</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.09680892154990794</v>
+        <v>0.1054267189665317</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.29344611610987</v>
+        <v>0.08176401529805633</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.2207316518087459</v>
+        <v>0.2097381738406576</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.2195457088685426</v>
+        <v>0.5123318937437271</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.4063105035579599</v>
+        <v>0.6215938645180512</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.5346545217132779</v>
+        <v>0.6578226266108977</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.1534626627801285</v>
+        <v>0.18353022726928</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>92.14</v>
+        <v>68.87</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-0.003784176475348344</v>
+        <v>0.02729716297827256</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.03458344841103678</v>
+        <v>0.1220267440229419</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.108251143445649</v>
+        <v>0.1841472305238747</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.1054589211331121</v>
+        <v>0.4238165033570835</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.05616691478524061</v>
+        <v>0.1829268516416958</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.1995004934281097</v>
+        <v>-0.03127045366668679</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.4855530058926529</v>
+        <v>0.4167803707122026</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.6335960704875836</v>
+        <v>0.7338530899927156</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.6517278454875504</v>
+        <v>2.632850612884869</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.1820780784596991</v>
+        <v>0.5372665590116372</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>67.04000000000001</v>
+        <v>30.04</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.08391273353996631</v>
+        <v>-0.01797970690804385</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.06751595111428954</v>
+        <v>0.0499825331935988</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.158258460234517</v>
+        <v>0.07400792466893313</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.3788564868018298</v>
+        <v>0.09715127232627219</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.1817380831391522</v>
+        <v>0.2480266429744433</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>-0.04733568264973753</v>
+        <v>0.2064786204040554</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.3094312906241738</v>
+        <v>0.2055841892043744</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.7268003382435506</v>
+        <v>0.3757843583528722</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>2.536319133163716</v>
+        <v>0.5070618832077689</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.5235281519824204</v>
+        <v>0.1465078392948385</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>37.06</v>
+        <v>53.89</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.06494259154533721</v>
+        <v>-0.004433801472953691</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.08362574697515157</v>
+        <v>-0.03526675974181892</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.08744129642390064</v>
+        <v>-0.008098701022953958</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.08299240360253668</v>
+        <v>0.02199885942504065</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.1832695317495601</v>
+        <v>0.01583412185991273</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.1483770035160343</v>
+        <v>0.3304318049799253</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.2592342384234247</v>
+        <v>0.4137946391265601</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.5711313623876917</v>
+        <v>0.4970897392909994</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.8149250602877578</v>
+        <v>1.557822848424045</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.2197932688068385</v>
+        <v>0.3675928476851704</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>54.13</v>
+        <v>35.95</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.007153326969440599</v>
+        <v>-0.02995144547273376</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.02380522410572183</v>
+        <v>0.05425226896189894</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-0.01060131650636476</v>
+        <v>0.05828670800958369</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.02811015193435207</v>
+        <v>0.0718544955762479</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.0433693129081838</v>
+        <v>0.1365792512423245</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.3405161105892691</v>
+        <v>0.1252063627607496</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.3731028561315088</v>
+        <v>0.2322404501981945</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.4951105486974809</v>
+        <v>0.5191869127888411</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>1.569214234280331</v>
+        <v>0.760565431307451</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.3696200545263442</v>
+        <v>0.2074914290381087</v>
       </c>
     </row>
     <row r="10">
@@ -1054,37 +1054,37 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>38.35</v>
+        <v>37.93</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.025412961595352</v>
+        <v>-0.01095171279416685</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.03058652318416899</v>
+        <v>-0.04313822176594695</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.02442133975152161</v>
+        <v>-0.02443417533027104</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-0.01413889537746971</v>
+        <v>-0.01608298169014544</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.1423890027629</v>
+        <v>0.1042213097549864</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.0884709297088293</v>
+        <v>0.06531467753760722</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.2682509045218524</v>
+        <v>0.2634951713169402</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.2880370610290335</v>
+        <v>0.2696585403600702</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.177844254754709</v>
+        <v>1.153993129966209</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2962107120754172</v>
+        <v>0.2914614228844352</v>
       </c>
     </row>
     <row r="11">
@@ -1096,51 +1096,51 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>17.6</v>
+        <v>14.9</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.01012375130620657</v>
+        <v>-0.002677373693205976</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.01179107752778052</v>
+        <v>0.001344052683840191</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-0.0039614994070164</v>
+        <v>0.01637106232034036</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.02743731720545473</v>
+        <v>0.02971660978343293</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.155613979676154</v>
+        <v>0.002017466926837352</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.1377114482822566</v>
+        <v>0.1899769396860487</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.2094413417340255</v>
+        <v>0.3232219718891018</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.1835790884890438</v>
+        <v>0.2795758209210946</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.9758922138878656</v>
+        <v>0.8586676697711513</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.2548382545025529</v>
+        <v>0.2295152362461075</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>14.94</v>
+        <v>17.41</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.01425662217740231</v>
+        <v>-0.0107954846556515</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.01356850830194856</v>
+        <v>-0.02900169821043252</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.03248094710996163</v>
+        <v>-0.007977173546127481</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.02751029020493179</v>
+        <v>0.02291418208925711</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.0204917506847857</v>
+        <v>0.1275906943373053</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.2026261868043044</v>
+        <v>0.1183062730658953</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.3039923793434192</v>
+        <v>0.2080303807030734</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.2819796778185963</v>
+        <v>0.1649404244302686</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.8636573770054952</v>
+        <v>0.9545610812784293</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2306144894880284</v>
+        <v>0.2503062889495984</v>
       </c>
     </row>
     <row r="13">
@@ -1208,51 +1208,51 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>29.81</v>
+        <v>53.57</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.02517987114731013</v>
+        <v>0.004688672194877563</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.02326346596238926</v>
+        <v>0.0369725097377791</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-0.03371153655323866</v>
+        <v>0.08309746636533699</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.05484781403067518</v>
+        <v>0.1366432947328284</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.1430214552587423</v>
+        <v>0.2634433435604404</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.03130132083429893</v>
+        <v>0.1132267684862671</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.2355811218306019</v>
+        <v>0.02819572296239303</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.2732733116833495</v>
+        <v>0.07298164966225618</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>1.255987563146873</v>
+        <v>0.214916028109327</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.3115320271584192</v>
+        <v>0.06704340814234389</v>
       </c>
     </row>
     <row r="14">
@@ -1278,37 +1278,37 @@
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>121.67</v>
+        <v>120.98</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.0009872078500599013</v>
+        <v>-0.005671034950239906</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.01369976031975173</v>
+        <v>-0.03231477679260419</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.01569454277022131</v>
+        <v>-0.01232749231096664</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-0.03190644594600089</v>
+        <v>-0.0288191085067474</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.09140648102947813</v>
+        <v>0.05346575422187749</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.07537496108326658</v>
+        <v>0.05092576637544632</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.2815962402830716</v>
+        <v>0.3021928154056812</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.2380812342794645</v>
+        <v>0.2501199105424781</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.4804417282614981</v>
+        <v>0.4720460914787337</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.1397172090859535</v>
+        <v>0.1375586648270697</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>53.32</v>
+        <v>22.98</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.04344425219165937</v>
+        <v>-0.009909502426055483</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.02597649494730625</v>
+        <v>-0.05119734955708477</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.0778249116458456</v>
+        <v>0.01188905630332138</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.1171171214372482</v>
+        <v>0.1133721037686402</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.2817308089084187</v>
+        <v>0.1467065115965649</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.1028389812187414</v>
+        <v>0.3154670755398972</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.02047108724949021</v>
+        <v>0.05643469474884832</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.07261068077136712</v>
+        <v>0.0305832865222242</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.2092461641359549</v>
+        <v>0.3795046068834751</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.06538089900949551</v>
+        <v>0.1132030435642668</v>
       </c>
     </row>
     <row r="16">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1390,37 +1390,37 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>23.21</v>
+        <v>44.54</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0</v>
+        <v>-0.006247183873345885</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.01610856573366948</v>
+        <v>-0.02452910502907601</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.007815822512394766</v>
+        <v>0.005190691381358636</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.1327476497675948</v>
+        <v>0.07041577174230729</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.1680925065007757</v>
+        <v>0.1681090917349128</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.3074567986340855</v>
+        <v>0.2103005430749521</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.03900067879388147</v>
+        <v>0.093942356322259</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.03522657590427203</v>
+        <v>0.01775269343861718</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.3933116318798398</v>
+        <v>0.304375327465304</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.1169046205680715</v>
+        <v>0.09261592256211038</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>44.82</v>
+        <v>113.8</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.005158096915211186</v>
+        <v>-0.005505525227106678</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.005158096915211186</v>
+        <v>-0.0156560639134854</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.01196655607001951</v>
+        <v>-0.01446261497610424</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.08182474932844563</v>
+        <v>-0.05802495363379212</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.1832100958558471</v>
+        <v>0.06514420584455638</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.2122828658025409</v>
+        <v>0.1350488791844386</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.09092045235715185</v>
+        <v>0.1481868247587237</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.02829396131124362</v>
+        <v>0.1963475293119699</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.3125752262512944</v>
+        <v>0.06715716614282985</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.09490070233789649</v>
+        <v>0.02190250018117479</v>
       </c>
     </row>
     <row r="18">
@@ -1488,51 +1488,51 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>114.43</v>
+        <v>28.82</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.005734608165050004</v>
+        <v>-0.03321032502027477</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.01785256023446491</v>
+        <v>-0.04821667631154314</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.02029111887550039</v>
+        <v>-0.05539169194950722</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-0.05671418178122434</v>
+        <v>0.02855100728019022</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.06258703418116029</v>
+        <v>0.07377047432860828</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.1395140648445365</v>
+        <v>-0.00705869828574468</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.1512000717189317</v>
+        <v>0.2228116255792785</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.208012253312444</v>
+        <v>0.2268858380810603</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.07306495230808596</v>
+        <v>1.181065325519018</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.02378478305439424</v>
+        <v>0.296849436924191</v>
       </c>
     </row>
     <row r="19">
@@ -1558,37 +1558,37 @@
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>96.7</v>
+        <v>97.05</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.001553535906197334</v>
+        <v>0.003619504804151852</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.003503750660319271</v>
+        <v>-0.004717455382987179</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.01577611248608457</v>
+        <v>-0.02058727784363379</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.0001033664968825843</v>
+        <v>0.003827086733699803</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.1111110916302307</v>
+        <v>0.1113019697343769</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.1105962558195044</v>
+        <v>0.108494639931813</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.1386083041659174</v>
+        <v>0.1395264213826315</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.09455062468339226</v>
+        <v>0.08746378266143107</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.595904353233228</v>
+        <v>0.6016806358705382</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.1686082638874775</v>
+        <v>0.1700164694081565</v>
       </c>
     </row>
     <row r="20">
@@ -1614,37 +1614,37 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>102.42</v>
+        <v>102.32</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.01799023504237529</v>
+        <v>-0.0009763569215861523</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.004610115103208301</v>
+        <v>0.01046807758474744</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.01155553747106475</v>
+        <v>0.01598650208507246</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.05948070868844968</v>
+        <v>0.06906280089416406</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.04606265282554856</v>
+        <v>0.03020539679035394</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>-0.01060626373099127</v>
+        <v>-0.01517086137183443</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.2408564394159272</v>
+        <v>0.2614619533589808</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.1757838036680857</v>
+        <v>0.1743790836624082</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.2676011173523023</v>
+        <v>0.266363486227565</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.0822498586888647</v>
+        <v>0.08189752328212974</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>17.31</v>
+        <v>43.53</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.005226489905727938</v>
+        <v>-0.0006887647623569082</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.008022996611805722</v>
+        <v>-0.00160549764389939</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0</v>
+        <v>0.006939607685340077</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.06326773561759014</v>
+        <v>-0.006164394120245054</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.1594105232497234</v>
+        <v>0.0309855988892116</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.09175201632342445</v>
+        <v>0.06384667951360634</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.1140092407495685</v>
+        <v>0.1711196973329436</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>-0.03617647074441388</v>
+        <v>0.1500760325674175</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.3715326972439907</v>
+        <v>0.3969865290434293</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1110545661190645</v>
+        <v>0.1178857139146836</v>
       </c>
     </row>
     <row r="22">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>43.56</v>
+        <v>68.61</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.008566861735281872</v>
+        <v>-0.009098747441579902</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.01161170422790869</v>
+        <v>-0.00809596029229287</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-0.001146508515495803</v>
+        <v>0.02189456708469617</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.0117967431071504</v>
+        <v>0.0502066231037166</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.04575125629429255</v>
+        <v>-0.004759702952392586</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.07293369699785091</v>
+        <v>0.05510638120633304</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.1679081472765909</v>
+        <v>0.2340972499400129</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1546590912193375</v>
+        <v>0.1558537972866223</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.3979493873209745</v>
+        <v>0.7880882268144138</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.1181424852564401</v>
+        <v>0.213751131830372</v>
       </c>
     </row>
     <row r="23">
@@ -1768,51 +1768,51 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>69.23999999999999</v>
+        <v>17.2</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.004497280679258475</v>
+        <v>-0.006354633529559228</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.01584498450167393</v>
+        <v>-0.018264822286715</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.04277102820221712</v>
+        <v>-0.001741078357160641</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.05920139138115377</v>
+        <v>0.06238419984960331</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.01163701510718562</v>
+        <v>0.1293500512091188</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.05982641381813458</v>
+        <v>0.07708858524890649</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.2255886331201067</v>
+        <v>0.1235156508766133</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.1683725609192466</v>
+        <v>-0.04003068408781374</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.8045071594818334</v>
+        <v>0.3628170066006544</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.2174548659769173</v>
+        <v>0.1086960872195757</v>
       </c>
     </row>
     <row r="24">
@@ -1838,37 +1838,37 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>52.26</v>
+        <v>51.51</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.0001913551969173755</v>
+        <v>-0.01435132078239987</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.02481809716864614</v>
+        <v>-0.03719629305545413</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.02043111872096159</v>
+        <v>-0.02847985898139238</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.00751878538036177</v>
+        <v>0.0003883597283853568</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.02350170223203119</v>
+        <v>-0.006365776043274485</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.0440875486284944</v>
+        <v>0.02405790040721034</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.1659811172550356</v>
+        <v>0.1705537068819492</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.19776379573314</v>
+        <v>0.1899565754724564</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.7961162502781103</v>
+        <v>0.7703397258596525</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.2155648894935491</v>
+        <v>0.2097218871917945</v>
       </c>
     </row>
     <row r="25">
@@ -1894,37 +1894,37 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>95.81999999999999</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.01268227555917645</v>
+        <v>-0.01158422681994142</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.0163343332145387</v>
+        <v>-0.006712106973154719</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.01504235324144609</v>
+        <v>0.005520720135768986</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.03365698866553402</v>
+        <v>0.02422404925055854</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.04342364865156756</v>
+        <v>0.03605390392141028</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.0327162683504143</v>
+        <v>0.01521792892689633</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1850629995155697</v>
+        <v>0.1664140842071615</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.09737062382262174</v>
+        <v>0.08093571974905656</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.1754814774881219</v>
+        <v>0.1618644334302597</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.05537126036148621</v>
+        <v>0.05128020218942697</v>
       </c>
     </row>
     <row r="26">
@@ -1950,37 +1950,37 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>13.94</v>
+        <v>13.89</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.008683059928288106</v>
+        <v>-0.003586745951621673</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.006414836372119481</v>
+        <v>-0.009272475762932664</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.01900073589295226</v>
+        <v>-0.01768033903323463</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.008534910074822766</v>
+        <v>-0.002871497557553226</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.02650954776876024</v>
+        <v>0.01091707239470963</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.0001720877854347602</v>
+        <v>-0.008307363743145224</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.23111935124369</v>
+        <v>0.2373060921990371</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.08924659212441832</v>
+        <v>0.08287671095381444</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.09788758127323471</v>
+        <v>0.09394965526969368</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.03161890175818582</v>
+        <v>0.03038401342952657</v>
       </c>
     </row>
     <row r="27">
@@ -2006,37 +2006,37 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>17.88</v>
+        <v>17.78</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.00562421092571741</v>
+        <v>-0.005592756085834538</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.0136054296724637</v>
+        <v>-0.02521924836868883</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.006756696528056327</v>
+        <v>0.003386082145375502</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.06746263646367767</v>
+        <v>0.0583334222672518</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.1880397962900993</v>
+        <v>0.1697369019575734</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.1030228359416514</v>
+        <v>0.09079763919374617</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>-0.01650171283681279</v>
+        <v>-0.01167310100858354</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>-0.09330629901907916</v>
+        <v>-0.09883420683393462</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.2618206820393312</v>
+        <v>0.2547636267406239</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.08060228238741884</v>
+        <v>0.07858400011413735</v>
       </c>
     </row>
     <row r="28">
@@ -2048,44 +2048,52 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>73.36</v>
+        <v>181</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.01238554367345701</v>
+        <v>-0.01119914240688746</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.02666846308854121</v>
+        <v>-0.02964669927350394</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.03103947302256738</v>
+        <v>0.02098376154285919</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.01466109977664765</v>
+        <v>0.05514752876367246</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.09508886325890065</v>
+        <v>0.09134756309281333</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.04605737178716596</v>
-      </c>
-      <c r="M28" s="6" t="inlineStr"/>
-      <c r="N28" s="6" t="inlineStr"/>
-      <c r="O28" s="6" t="inlineStr"/>
-      <c r="P28" s="6" t="inlineStr"/>
+        <v>0.09002378715030757</v>
+      </c>
+      <c r="M28" s="6" t="n">
+        <v>0.04209149642362453</v>
+      </c>
+      <c r="N28" s="6" t="n">
+        <v>-0.06788985462103081</v>
+      </c>
+      <c r="O28" s="6" t="n">
+        <v>0.6522926086192531</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v>0.1822127895230805</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
@@ -2096,52 +2104,44 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>18.02</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.01349829931662638</v>
+        <v>-0.019083990106747</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.004969638296778767</v>
+        <v>-0.04321233931075763</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.02118410607717958</v>
+        <v>-0.04104480001968347</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.02619595705076527</v>
+        <v>0.003626250310974966</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.03801842305342773</v>
+        <v>0.05358705518565343</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.04001031240147745</v>
-      </c>
-      <c r="M29" s="6" t="n">
-        <v>0.1425154611697756</v>
-      </c>
-      <c r="N29" s="6" t="n">
-        <v>0.06815044669310066</v>
-      </c>
-      <c r="O29" s="6" t="n">
-        <v>0.4837483984914488</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v>0.1405651241616857</v>
-      </c>
+        <v>0.01897474208120853</v>
+      </c>
+      <c r="M29" s="6" t="inlineStr"/>
+      <c r="N29" s="6" t="inlineStr"/>
+      <c r="O29" s="6" t="inlineStr"/>
+      <c r="P29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
@@ -2152,51 +2152,51 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>183.05</v>
+        <v>17.54</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.005769247537130928</v>
+        <v>-0.02663704384255594</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.00510656687626132</v>
+        <v>-0.03254265154716696</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.02045934925323967</v>
+        <v>-0.04362045967309669</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.05845958406168594</v>
+        <v>0.001713345873977978</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.1076486090781397</v>
+        <v>-0.004540290572967676</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.09735801441688441</v>
+        <v>0.003080137010358142</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.03339746646147512</v>
+        <v>0.1209504711435472</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>-0.05866114079799034</v>
+        <v>0.04485033526972004</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.6710065641704246</v>
+        <v>0.44422572734951</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1866593130374576</v>
+        <v>0.1303467563876686</v>
       </c>
     </row>
     <row r="31">
@@ -2222,37 +2222,37 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>66.06999999999999</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.01959871270456603</v>
+        <v>-0.01982741886854245</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.002884068751177526</v>
+        <v>-0.01982741886854245</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.01166789524458745</v>
+        <v>-0.02278549242983741</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.01349896027705966</v>
+        <v>0.001701478851590332</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.04277144978483327</v>
+        <v>-0.007357384170081693</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.01463179334517783</v>
+        <v>-0.01655020948158337</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.07520388228851749</v>
+        <v>0.0697805520315844</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.05087337900504751</v>
+        <v>0.04461546441924358</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.4982987418336839</v>
+        <v>0.4685913450891375</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1442813111828851</v>
+        <v>0.1366680552304733</v>
       </c>
     </row>
     <row r="32">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2278,37 +2278,37 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>123.35</v>
+        <v>54.89</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.006610066529639802</v>
+        <v>-0.002906445951490477</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.00955518253298715</v>
+        <v>0.0003645062539274768</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.03171364263194765</v>
+        <v>0.01123803655250311</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.00718541066911671</v>
+        <v>0.0443302502945031</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.05059189699973299</v>
+        <v>0.01123803655250311</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>-0.06841979288244282</v>
+        <v>-0.04902455034304709</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.09882306805639374</v>
+        <v>0.03825727344076335</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.00879169602369223</v>
+        <v>0.02101501881689405</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.4192344047525831</v>
+        <v>0.282018444243304</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1237888278158608</v>
+        <v>0.08633746572360912</v>
       </c>
     </row>
     <row r="33">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -2334,37 +2334,37 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>55.05</v>
+        <v>121.1</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.02001108008022667</v>
+        <v>-0.01824077849885053</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0.007319262580298913</v>
+        <v>-0.02988066412096824</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>0.004928814599859388</v>
+        <v>-0.0352903716104106</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0.03109196228486866</v>
+        <v>0.002815471446473428</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>0.03966002726842111</v>
+        <v>0.009418998432276116</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.0473428963705621</v>
+        <v>-0.09354128954230656</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.01720096226142864</v>
+        <v>0.08845727713612273</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.02033648203402283</v>
+        <v>0.00376265096530326</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.28575542288676</v>
+        <v>0.3933463420269316</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.08739197000060317</v>
+        <v>0.1169138952583983</v>
       </c>
     </row>
     <row r="34">
@@ -2390,37 +2390,37 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>130.9</v>
+        <v>129.96</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.0009940324216293206</v>
+        <v>-0.007180956657343529</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.002286608679390123</v>
+        <v>-0.01163585607558904</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>0.004990356211012514</v>
+        <v>0.00440534297014894</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.03451842359761903</v>
+        <v>-0.0369765864929128</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.02518981934904563</v>
+        <v>-0.0415054416162467</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.05650461164050169</v>
+        <v>-0.07003859143869284</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.01151032631584403</v>
+        <v>-0.007287070845783949</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.04422533661435146</v>
+        <v>0.03798812799400597</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.5601683280443623</v>
+        <v>0.5489648269025156</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1598197123805005</v>
+        <v>0.1570368354445015</v>
       </c>
     </row>
   </sheetData>
@@ -2560,17 +2560,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2650,17 +2650,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -2695,17 +2695,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -2717,17 +2717,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -2740,17 +2740,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2762,17 +2762,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -2785,17 +2785,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -2807,17 +2807,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -2830,17 +2830,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2920,17 +2920,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.3788564868018298</v>
+        <v>0.4238165033570835</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.05671418178122434</v>
+        <v>-0.05802495363379212</v>
       </c>
     </row>
     <row r="18">
@@ -3071,21 +3071,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.1327476497675948</v>
+        <v>0.1366432947328284</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.03451842359761903</v>
+        <v>-0.0369765864929128</v>
       </c>
     </row>
     <row r="19">
@@ -3116,21 +3116,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.1171171214372482</v>
+        <v>0.1133721037686402</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -3152,7 +3152,7 @@
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.03190644594600089</v>
+        <v>-0.0288191085067474</v>
       </c>
     </row>
     <row r="20">
@@ -3161,21 +3161,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.1059971748895028</v>
+        <v>0.1054267189665317</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.01413889537746971</v>
+        <v>-0.01608298169014544</v>
       </c>
     </row>
     <row r="21">
@@ -3206,21 +3206,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.1054589211331121</v>
+        <v>0.09715127232627219</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.0117967431071504</v>
+        <v>-0.006164394120245054</v>
       </c>
     </row>
     <row r="22">
@@ -3251,21 +3251,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>Biotechnology</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
       <c r="E22" s="11" t="n">
-        <v>0.09680892154990794</v>
+        <v>0.09172018746745358</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.008534910074822766</v>
+        <v>-0.002871497557553226</v>
       </c>
     </row>
     <row r="23">
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.08299240360253668</v>
+        <v>0.0718544955762479</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -3318,21 +3318,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>0.0001033664968825843</v>
+        <v>0.0003883597283853568</v>
       </c>
     </row>
     <row r="24">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.08182474932844563</v>
+        <v>0.07041577174230729</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -3363,21 +3363,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>0.006969830656176734</v>
+        <v>0.001701478851590332</v>
       </c>
     </row>
     <row r="25">
@@ -3386,21 +3386,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.06746263646367767</v>
+        <v>0.06906280089416406</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3422,7 +3422,7 @@
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>0.00718541066911671</v>
+        <v>0.001713345873977978</v>
       </c>
     </row>
     <row r="26">
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.06326773561759014</v>
+        <v>0.06238419984960331</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -3453,21 +3453,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>0.00751878538036177</v>
+        <v>0.002815471446473428</v>
       </c>
     </row>
     <row r="27"/>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.3042763039222052</v>
+        <v>0.2634433435604404</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -3559,21 +3559,21 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.02518981934904563</v>
+        <v>-0.05001556667511864</v>
       </c>
     </row>
     <row r="32">
@@ -3596,7 +3596,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.29344611610987</v>
+        <v>0.2480266429744433</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -3604,21 +3604,21 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.01429501378304132</v>
+        <v>-0.0415054416162467</v>
       </c>
     </row>
     <row r="33">
@@ -3627,12 +3627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3641,7 +3641,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.2817308089084187</v>
+        <v>0.2280208887984347</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -3649,21 +3649,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>0.01163701510718562</v>
+        <v>-0.007357384170081693</v>
       </c>
     </row>
     <row r="34">
@@ -3672,21 +3672,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.1880397962900993</v>
+        <v>0.1829268516416958</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -3694,21 +3694,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>0.0204917506847857</v>
+        <v>-0.006365776043274485</v>
       </c>
     </row>
     <row r="35">
@@ -3717,21 +3717,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.1832695317495601</v>
+        <v>0.1697369019575734</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -3739,21 +3739,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>0.02350170223203119</v>
+        <v>-0.004759702952392586</v>
       </c>
     </row>
     <row r="36">
@@ -3776,7 +3776,7 @@
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.1832100958558471</v>
+        <v>0.1681090917349128</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -3784,21 +3784,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>0.02650954776876024</v>
+        <v>-0.004540290572967676</v>
       </c>
     </row>
     <row r="37">
@@ -3807,21 +3807,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1817380831391522</v>
+        <v>0.1467065115965649</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -3829,21 +3829,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>0.03801842305342773</v>
+        <v>0.002017466926837352</v>
       </c>
     </row>
     <row r="38">
@@ -3852,21 +3852,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1680925065007757</v>
+        <v>0.1365792512423245</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3888,7 +3888,7 @@
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>0.03966002726842111</v>
+        <v>0.009418998432276116</v>
       </c>
     </row>
     <row r="39">
@@ -3911,7 +3911,7 @@
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1594105232497234</v>
+        <v>0.1293500512091188</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -3919,21 +3919,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0.04277144978483327</v>
+        <v>0.01091707239470963</v>
       </c>
     </row>
     <row r="40">
@@ -3956,7 +3956,7 @@
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.155613979676154</v>
+        <v>0.1275906943373053</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -3964,21 +3964,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>0.0433693129081838</v>
+        <v>0.01123803655250311</v>
       </c>
     </row>
     <row r="41"/>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.4573918594429942</v>
+        <v>0.4387855938080918</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.06841979288244282</v>
+        <v>-0.09354128954230656</v>
       </c>
     </row>
     <row r="46">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.3536903041044304</v>
+        <v>0.3453337400583016</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -4129,7 +4129,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.05650461164050169</v>
+        <v>-0.07003859143869284</v>
       </c>
     </row>
     <row r="47">
@@ -4152,7 +4152,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.3405161105892691</v>
+        <v>0.3304318049799253</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -4174,7 +4174,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.0473428963705621</v>
+        <v>-0.04902455034304709</v>
       </c>
     </row>
     <row r="48">
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.3074567986340855</v>
+        <v>0.3154670755398972</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.04733568264973753</v>
+        <v>-0.03127045366668679</v>
       </c>
     </row>
     <row r="49">
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.2749627333782894</v>
+        <v>0.2352598251978533</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -4250,21 +4250,21 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.01060626373099127</v>
+        <v>-0.01655020948158337</v>
       </c>
     </row>
     <row r="50">
@@ -4273,21 +4273,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.2207316518087459</v>
+        <v>0.2103005430749521</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -4295,12 +4295,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>0.0001720877854347602</v>
+        <v>-0.01517086137183443</v>
       </c>
     </row>
     <row r="51">
@@ -4318,21 +4318,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.2122828658025409</v>
+        <v>0.2097381738406576</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -4340,21 +4340,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0.01463179334517783</v>
+        <v>-0.008307363743145224</v>
       </c>
     </row>
     <row r="52">
@@ -4363,21 +4363,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.2026261868043044</v>
+        <v>0.2064786204040554</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>0.03130132083429893</v>
+        <v>-0.00705869828574468</v>
       </c>
     </row>
     <row r="53">
@@ -4408,21 +4408,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.1995004934281097</v>
+        <v>0.1899769396860487</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -4430,21 +4430,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.0327162683504143</v>
+        <v>0.003080137010358142</v>
       </c>
     </row>
     <row r="54">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4467,7 +4467,7 @@
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.1483770035160343</v>
+        <v>0.1350488791844386</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -4475,21 +4475,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.04001031240147745</v>
+        <v>0.01521792892689633</v>
       </c>
     </row>
     <row r="55"/>
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.9520774783654862</v>
+        <v>0.9712792475113445</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.09330629901907916</v>
+        <v>-0.09883420683393462</v>
       </c>
     </row>
     <row r="60">
@@ -4618,7 +4618,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.8609197216288644</v>
+        <v>0.8874913481181854</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.05866114079799034</v>
+        <v>-0.06788985462103081</v>
       </c>
     </row>
     <row r="61">
@@ -4663,7 +4663,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.7268003382435506</v>
+        <v>0.7338530899927156</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4685,7 +4685,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.03617647074441388</v>
+        <v>-0.04003068408781374</v>
       </c>
     </row>
     <row r="62">
@@ -4694,21 +4694,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.6739742256678367</v>
+        <v>0.6215938645180512</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>0.00879169602369223</v>
+        <v>0.00376265096530326</v>
       </c>
     </row>
     <row r="63">
@@ -4739,21 +4739,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.6335960704875836</v>
+        <v>0.6008544693997961</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4761,21 +4761,21 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>0.02033648203402283</v>
+        <v>0.01775269343861718</v>
       </c>
     </row>
     <row r="64">
@@ -4798,7 +4798,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.5711313623876917</v>
+        <v>0.5191869127888411</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4806,21 +4806,21 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>0.02829396131124362</v>
+        <v>0.02101501881689405</v>
       </c>
     </row>
     <row r="65">
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.4951105486974809</v>
+        <v>0.4970897392909994</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4865,7 +4865,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.03522657590427203</v>
+        <v>0.0305832865222242</v>
       </c>
     </row>
     <row r="66">
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.4063105035579599</v>
+        <v>0.3757843583528722</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>0.04422533661435146</v>
+        <v>0.03798812799400597</v>
       </c>
     </row>
     <row r="67">
@@ -4919,21 +4919,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.2880370610290335</v>
+        <v>0.2795758209210946</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4955,7 +4955,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.05087337900504751</v>
+        <v>0.04461546441924358</v>
       </c>
     </row>
     <row r="68">
@@ -4964,21 +4964,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.2819796778185963</v>
+        <v>0.2696585403600702</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -5000,7 +5000,7 @@
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.06815044669310066</v>
+        <v>0.04485033526972004</v>
       </c>
     </row>
     <row r="69"/>
@@ -5070,21 +5070,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.58079428545959</v>
+        <v>2.632850612884869</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.07306495230808596</v>
+        <v>0.06715716614282985</v>
       </c>
     </row>
     <row r="74">
@@ -5115,21 +5115,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.536319133163716</v>
+        <v>2.597907156962665</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.09788758127323471</v>
+        <v>0.09394965526969368</v>
       </c>
     </row>
     <row r="75">
@@ -5174,7 +5174,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.289722133824756</v>
+        <v>2.295753382308867</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1754814774881219</v>
+        <v>0.1618644334302597</v>
       </c>
     </row>
     <row r="76">
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.569214234280331</v>
+        <v>1.557822848424045</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.2092461641359549</v>
+        <v>0.214916028109327</v>
       </c>
     </row>
     <row r="77">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.255987563146873</v>
+        <v>1.181065325519018</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.2618206820393312</v>
+        <v>0.2547636267406239</v>
       </c>
     </row>
     <row r="78">
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.177844254754709</v>
+        <v>1.153993129966209</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.2676011173523023</v>
+        <v>0.266363486227565</v>
       </c>
     </row>
     <row r="79">
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.153029031053011</v>
+        <v>1.076329124027107</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.28575542288676</v>
+        <v>0.282018444243304</v>
       </c>
     </row>
     <row r="80">
@@ -5399,7 +5399,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.9758922138878656</v>
+        <v>0.9545610812784293</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5421,7 +5421,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.3125752262512944</v>
+        <v>0.304375327465304</v>
       </c>
     </row>
     <row r="81">
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8636573770054952</v>
+        <v>0.8586676697711513</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5466,7 +5466,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.3715326972439907</v>
+        <v>0.3628170066006544</v>
       </c>
     </row>
     <row r="82">
@@ -5475,21 +5475,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.8149250602877578</v>
+        <v>0.7880882268144138</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.3933116318798398</v>
+        <v>0.3795046068834751</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -491,12 +491,12 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>213.1</v>
+        <v>209.85</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.001833479278542161</v>
+        <v>-0.02675999046626421</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>-0.03356006302260484</v>
+        <v>-0.07583564832547784</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.01394113317836654</v>
+        <v>0.001622889626244461</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.05375073236228278</v>
+        <v>0.01839274284104642</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.07230921695222103</v>
+        <v>0.009816700682779622</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.4387855938080918</v>
+        <v>0.4171121010951535</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7891279934797888</v>
+        <v>0.6983107200297163</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.9712792475113445</v>
+        <v>0.9073378682442328</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.295753382308867</v>
+        <v>2.212270352203991</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4881666537682929</v>
+        <v>0.4754937123020999</v>
       </c>
     </row>
     <row r="3">
@@ -648,51 +648,51 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>60.97</v>
+        <v>71.69</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.004779184477073928</v>
+        <v>0.008156403122998368</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>-0.05384855818182677</v>
+        <v>0.1263158008292966</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>-0.02432389849474825</v>
+        <v>0.1481422808798802</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.004944833703841578</v>
+        <v>0.3831757651695116</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>-0.05001556667511864</v>
+        <v>0.2441861119462061</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.3453337400583016</v>
+        <v>-0.03795050036228309</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.7042665310042533</v>
+        <v>0.3914325456588812</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.8874913481181854</v>
+        <v>0.7432483011701951</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>2.597907156962665</v>
+        <v>2.640696457329232</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.5323218136313803</v>
+        <v>0.5383724382214043</v>
       </c>
     </row>
     <row r="4">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>30.59</v>
+        <v>30.85</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.03562418616733254</v>
+        <v>-0.007719516562890272</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.04295943512306111</v>
+        <v>0.03488765294060259</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.05192573015280111</v>
+        <v>0.04505419725887116</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.09172018746745358</v>
+        <v>0.08550317729248436</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.2280208887984347</v>
+        <v>0.2310455322792886</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.2352598251978533</v>
+        <v>0.2253443938148396</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.3173226611216025</v>
+        <v>0.2919495801876864</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.6008544693997961</v>
+        <v>0.5917771700818479</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.076329124027107</v>
+        <v>1.065610389630292</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2757494758528483</v>
+        <v>0.2735503995993012</v>
       </c>
     </row>
     <row r="5">
@@ -760,51 +760,51 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>92.48</v>
+        <v>58.78</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.003690079981955696</v>
+        <v>-0.0300329990206426</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.03735279611956077</v>
+        <v>-0.09791289938988268</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.0937906566404425</v>
+        <v>-0.05528772699961992</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.1054267189665317</v>
+        <v>-0.03607741520915686</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.08176401529805633</v>
+        <v>-0.1057356492117627</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.2097381738406576</v>
+        <v>0.2938761399847394</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.5123318937437271</v>
+        <v>0.5564943496256149</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.6215938645180512</v>
+        <v>0.7816732194309011</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.6578226266108977</v>
+        <v>2.396131442742</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.18353022726928</v>
+        <v>0.5031240730379278</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>68.87</v>
+        <v>91.69</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.02729716297827256</v>
+        <v>-0.007576544570478849</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.1220267440229419</v>
+        <v>0.005372867429394246</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.1841472305238747</v>
+        <v>0.04299850553784146</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.4238165033570835</v>
+        <v>0.06085852270806336</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.1829268516416958</v>
+        <v>0.0804855265370048</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>-0.03127045366668679</v>
+        <v>0.1914764860204163</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.4167803707122026</v>
+        <v>0.4955290272571484</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.7338530899927156</v>
+        <v>0.561330933522699</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>2.632850612884869</v>
+        <v>0.6883458680945547</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.5372665590116372</v>
+        <v>0.1907496789932077</v>
       </c>
     </row>
     <row r="7">
@@ -886,37 +886,37 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>30.04</v>
+        <v>30.18</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.01797970690804385</v>
+        <v>-0.007889538807239971</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.0499825331935988</v>
+        <v>0.04682623604031511</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.07400792466893313</v>
+        <v>0.04537580283552112</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.09715127232627219</v>
+        <v>0.08717579453677926</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.2480266429744433</v>
+        <v>0.2389162376437324</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.2064786204040554</v>
+        <v>0.1996937799681542</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.2055841892043744</v>
+        <v>0.1767646752810961</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.3757843583528722</v>
+        <v>0.3610189769235936</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.5070618832077689</v>
+        <v>0.5129753096347567</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1465078392948385</v>
+        <v>0.1480054423622024</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>53.89</v>
+        <v>36.27</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.004433801472953691</v>
+        <v>-0.007117392012631396</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.03526675974181892</v>
+        <v>0.06332453265206328</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-0.008098701022953958</v>
+        <v>0.05130436109459913</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.02199885942504065</v>
+        <v>0.05620268772859438</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.01583412185991273</v>
+        <v>0.1166872219502006</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.3304318049799253</v>
+        <v>0.1131294172520043</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.4137946391265601</v>
+        <v>0.2071055475590073</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.4970897392909994</v>
+        <v>0.5103122338070285</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>1.557822848424045</v>
+        <v>0.7672847881410789</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.3675928476851704</v>
+        <v>0.2090256455308668</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>35.95</v>
+        <v>52.71</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.02995144547273376</v>
+        <v>-0.01953123641821208</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.05425226896189894</v>
+        <v>-0.05858193419657631</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.05828670800958369</v>
+        <v>-0.03655638884058443</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.0718544955762479</v>
+        <v>0.003426619252972829</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.1365792512423245</v>
+        <v>-0.02207796674801388</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.1252063627607496</v>
+        <v>0.306914527760942</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.2322404501981945</v>
+        <v>0.3479846826063997</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.5191869127888411</v>
+        <v>0.4432606453138559</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.760565431307451</v>
+        <v>1.456667521255983</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.2074914290381087</v>
+        <v>0.3493215651502837</v>
       </c>
     </row>
     <row r="10">
@@ -1040,12 +1040,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1054,37 +1054,37 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>37.93</v>
+        <v>17.76</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.01095171279416685</v>
+        <v>0.007945481440426949</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.04313822176594695</v>
+        <v>-0.001686379151297435</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.02443417533027104</v>
+        <v>0.01023892525352377</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-0.01608298169014544</v>
+        <v>0.04225347856046224</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.1042213097549864</v>
+        <v>0.1472868704178349</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.06531467753760722</v>
+        <v>0.1819312688299251</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.2634951713169402</v>
+        <v>0.2064795237029982</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.2696585403600702</v>
+        <v>0.1657450775095146</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.153993129966209</v>
+        <v>1.005313846787673</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2914614228844352</v>
+        <v>0.2610359010229999</v>
       </c>
     </row>
     <row r="11">
@@ -1096,51 +1096,51 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>14.9</v>
+        <v>45.62</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.002677373693205976</v>
+        <v>0.006175535473192939</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.001344052683840191</v>
+        <v>0.02863586249060956</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.01637106232034036</v>
+        <v>0.01989714730061776</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.02971660978343293</v>
+        <v>0.117589399141254</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.002017466926837352</v>
+        <v>0.1830912164718939</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.1899769396860487</v>
+        <v>0.3049929610747049</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.3232219718891018</v>
+        <v>0.09804973512404946</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.2795758209210946</v>
+        <v>0.02492935886041714</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.8586676697711513</v>
+        <v>0.3202776566441634</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.2295152362461075</v>
+        <v>0.09703821888125042</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
       <c r="F12" s="5" t="n">
-        <v>17.41</v>
+        <v>38.05</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.0107954846556515</v>
+        <v>0.001052378776472684</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.02900169821043252</v>
+        <v>-0.03889873477120154</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>-0.007977173546127481</v>
+        <v>-0.02159938713733889</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.02291418208925711</v>
+        <v>-0.01194492611066778</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.1275906943373053</v>
+        <v>0.1022595229573053</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.1183062730658953</v>
+        <v>0.1232916096879459</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.2080303807030734</v>
+        <v>0.2305316738034349</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.1649404244302686</v>
+        <v>0.227278124280597</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.9545610812784293</v>
+        <v>1.201381621141571</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2503062889495984</v>
+        <v>0.3008636511860419</v>
       </c>
     </row>
     <row r="13">
@@ -1208,51 +1208,51 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>53.57</v>
+        <v>23.1</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.004688672194877563</v>
+        <v>-0.008583642151914983</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.0369725097377791</v>
+        <v>-0.007305546753318959</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.08309746636533699</v>
+        <v>-0.03629532569072957</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.1366432947328284</v>
+        <v>0.1803781676899621</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.2634433435604404</v>
+        <v>0.1458333609280764</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.1132267684862671</v>
+        <v>0.3636593742192153</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.02819572296239303</v>
+        <v>0.05132393231104215</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.07298164966225618</v>
+        <v>0.02178387108857849</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.214916028109327</v>
+        <v>0.3750645605370346</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.06704340814234389</v>
+        <v>0.1120074488121563</v>
       </c>
     </row>
     <row r="14">
@@ -1264,51 +1264,51 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>120.98</v>
+        <v>53.66</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.005671034950239906</v>
+        <v>-0.009597645899496188</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.03231477679260419</v>
+        <v>0.0437658044481255</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.01232749231096664</v>
+        <v>0.03610733537029365</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-0.0288191085067474</v>
+        <v>0.1311130143499042</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.05346575422187749</v>
+        <v>0.2593287744374284</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.05092576637544632</v>
+        <v>0.1175256200389043</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.3021928154056812</v>
+        <v>0.001677693800515412</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.2501199105424781</v>
+        <v>0.06224574973988783</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.4720460914787337</v>
+        <v>0.2198085684098507</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.1375586648270697</v>
+        <v>0.06847383915296401</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>22.98</v>
+        <v>121.89</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.009909502426055483</v>
+        <v>-0.0002460529834925618</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.05119734955708477</v>
+        <v>-0.01103448771076321</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.01188905630332138</v>
+        <v>-0.01183623107039566</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.1133721037686402</v>
+        <v>-0.01518944254995491</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.1467065115965649</v>
+        <v>0.06138978819726515</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.3154670755398972</v>
+        <v>0.0741345636024906</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.05643469474884832</v>
+        <v>0.26953191612445</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.0305832865222242</v>
+        <v>0.2219186191473381</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.3795046068834751</v>
+        <v>0.5025708929454991</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.1132030435642668</v>
+        <v>0.1453678554514348</v>
       </c>
     </row>
     <row r="16">
@@ -1376,51 +1376,51 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>44.54</v>
+        <v>115.97</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.006247183873345885</v>
+        <v>0.008347092136695489</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.02452910502907601</v>
+        <v>0.008259473181735588</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.005190691381358636</v>
+        <v>-0.01369280987650345</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.07041577174230729</v>
+        <v>-0.03910846901336862</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.1681090917349128</v>
+        <v>0.08332552932887416</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.2103005430749521</v>
+        <v>0.174617616505518</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.093942356322259</v>
+        <v>0.1282763553434916</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.01775269343861718</v>
+        <v>0.2084423584549633</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.304375327465304</v>
+        <v>0.09509648794249226</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.09261592256211038</v>
+        <v>0.03074395240623562</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>113.8</v>
+        <v>98.94</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.005505525227106678</v>
+        <v>0.01737791713528281</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.0156560639134854</v>
+        <v>0.02933832307786211</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.01446261497610424</v>
+        <v>0.008871242472614727</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.05802495363379212</v>
+        <v>0.01664614418066201</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.06514420584455638</v>
+        <v>0.1335930777404544</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.1350488791844386</v>
+        <v>0.1399199523156087</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.1481868247587237</v>
+        <v>0.156015194765162</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.1963475293119699</v>
+        <v>0.1068651039884059</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.06715716614282985</v>
+        <v>0.6286425268361682</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.02190250018117479</v>
+        <v>0.1765451293135569</v>
       </c>
     </row>
     <row r="18">
@@ -1488,51 +1488,51 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>28.82</v>
+        <v>14.78</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.03321032502027477</v>
+        <v>-0.006720455692246774</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.04821667631154314</v>
+        <v>-0.008718988314643239</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.05539169194950722</v>
+        <v>0.01232872238345406</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.02855100728019022</v>
+        <v>0.02996511080631925</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.07377047432860828</v>
+        <v>-0.04521962725872342</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>-0.00705869828574468</v>
+        <v>0.1657300355714972</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.2228116255792785</v>
+        <v>0.2816436612944095</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.2268858380810603</v>
+        <v>0.2601464743803183</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>1.181065325519018</v>
+        <v>0.8472892217892107</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.296849436924191</v>
+        <v>0.2270011377583219</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>97.05</v>
+        <v>104.82</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.003619504804151852</v>
+        <v>0.001815946156875636</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.004717455382987179</v>
+        <v>0.02936264175591607</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.02058727784363379</v>
+        <v>0.01895593366557957</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.003827086733699803</v>
+        <v>0.06643604352907584</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.1113019697343769</v>
+        <v>0.04454410850694601</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.108494639931813</v>
+        <v>-0.001732204774796298</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.1395264213826315</v>
+        <v>0.2544569669277819</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.08746378266143107</v>
+        <v>0.1789908795538515</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.6016806358705382</v>
+        <v>0.2994642948178405</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.1700164694081565</v>
+        <v>0.09124294840691194</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>102.32</v>
+        <v>18.24</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.0009763569215861523</v>
+        <v>0.007734772745737972</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.01046807758474744</v>
+        <v>0.02876481906651573</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.01598650208507246</v>
+        <v>0.03401362824433085</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.06906280089416406</v>
+        <v>0.1238447495732262</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.03020539679035394</v>
+        <v>0.2135728606238909</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>-0.01517086137183443</v>
+        <v>0.1790562027327856</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.2614619533589808</v>
+        <v>-0.0135208222333516</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.1743790836624082</v>
+        <v>-0.09072780375264677</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.266363486227565</v>
+        <v>0.2908704616694808</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.08189752328212974</v>
+        <v>0.08883202942374413</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>43.53</v>
+        <v>17.55</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.0006887647623569082</v>
+        <v>0.0126947094242944</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.00160549764389939</v>
+        <v>0.01739126011945191</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.006939607685340077</v>
+        <v>0.02094233227565545</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-0.006164394120245054</v>
+        <v>0.08938538622920378</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.0309855988892116</v>
+        <v>0.1530879716920395</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.06384667951360634</v>
+        <v>0.1115397069716235</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.1711196973329436</v>
+        <v>0.1202672495970174</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.1500760325674175</v>
+        <v>-0.03783280043157777</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.3969865290434293</v>
+        <v>0.3963358160948565</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1178857139146836</v>
+        <v>0.1177121174704581</v>
       </c>
     </row>
     <row r="22">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>68.61</v>
+        <v>28.33</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.009098747441579902</v>
+        <v>-0.01734304548467458</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.00809596029229287</v>
+        <v>-0.07236414294597049</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.02189456708469617</v>
+        <v>-0.07175624184830331</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.0502066231037166</v>
+        <v>-0.03508176652701966</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>-0.004759702952392586</v>
+        <v>0.04809468013453766</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.05510638120633304</v>
+        <v>-0.02226129294378287</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.2340972499400129</v>
+        <v>0.1901641028287342</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1558537972866223</v>
+        <v>0.1955694218225474</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.7880882268144138</v>
+        <v>1.164311504741482</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.213751131830372</v>
+        <v>0.2935203215962767</v>
       </c>
     </row>
     <row r="23">
@@ -1768,51 +1768,51 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>17.2</v>
+        <v>97.26000000000001</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.006354633529559228</v>
+        <v>0.01619478702940746</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.018264822286715</v>
+        <v>0.03457078955588577</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.001741078357160641</v>
+        <v>0.03358133595483981</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.06238419984960331</v>
+        <v>0.06167450592987422</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.1293500512091188</v>
+        <v>0.06766990402659823</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.07708858524890649</v>
+        <v>0.02233356346684845</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1235156508766133</v>
+        <v>0.1913837066466695</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>-0.04003068408781374</v>
+        <v>0.1100390906327462</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.3628170066006544</v>
+        <v>0.2041623117383993</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.1086960872195757</v>
+        <v>0.06388579475802758</v>
       </c>
     </row>
     <row r="24">
@@ -1824,51 +1824,51 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>51.51</v>
+        <v>43.73</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.01435132078239987</v>
+        <v>0.005981097635888055</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.03719629305545413</v>
+        <v>0.008068198835945672</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.02847985898139238</v>
+        <v>0.02006066320920596</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.0003883597283853568</v>
+        <v>-0.01486821032860886</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>-0.006365776043274485</v>
+        <v>0.03207208722318478</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.02405790040721034</v>
+        <v>0.06433219440559657</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.1705537068819492</v>
+        <v>0.1547983150011418</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.1899565754724564</v>
+        <v>0.1372671161148564</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.7703397258596525</v>
+        <v>0.3939987397102891</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.2097218871917945</v>
+        <v>0.117088189884752</v>
       </c>
     </row>
     <row r="25">
@@ -1880,51 +1880,51 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>94.70999999999999</v>
+        <v>68.97</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.01158422681994142</v>
+        <v>-0.002891382876051285</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.006712106973154719</v>
+        <v>-0.00217016087844879</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.005520720135768986</v>
+        <v>0.01680671323712857</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.02422404925055854</v>
+        <v>0.0388613022258435</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.03605390392141028</v>
+        <v>-0.02486403433500473</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.01521792892689633</v>
+        <v>0.05063347483899738</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1664140842071615</v>
+        <v>0.2220792338134459</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.08093571974905656</v>
+        <v>0.1581412521865595</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.1618644334302597</v>
+        <v>0.8118292538109142</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.05128020218942697</v>
+        <v>0.2190993204028242</v>
       </c>
     </row>
     <row r="26">
@@ -1936,51 +1936,51 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>13.89</v>
+        <v>185.77</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.003586745951621673</v>
+        <v>0.002915340697390079</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.009272475762932664</v>
+        <v>0.01992975126263663</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.01768033903323463</v>
+        <v>0.0397962636550615</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.002871497557553226</v>
+        <v>0.08024657180787687</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.01091707239470963</v>
+        <v>0.1177497453884624</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>-0.008307363743145224</v>
+        <v>0.1410829967463834</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.2373060921990371</v>
+        <v>0.04794241862270709</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.08287671095381444</v>
+        <v>-0.05682570614179261</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.09394965526969368</v>
+        <v>0.6918350969031164</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.03038401342952657</v>
+        <v>0.1915694042373983</v>
       </c>
     </row>
     <row r="27">
@@ -1992,51 +1992,51 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>17.78</v>
+        <v>13.99</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.005592756085834538</v>
+        <v>-0.001427584399494863</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.02521924836868883</v>
+        <v>0.007199382672692378</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.003386082145375502</v>
+        <v>-0.01200565523487729</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.0583334222672518</v>
+        <v>-0.0007143020629882812</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.1697369019575734</v>
+        <v>0.006474831299125405</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.09079763919374617</v>
+        <v>-0.01156502192508879</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>-0.01167310100858354</v>
+        <v>0.2147173659731565</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>-0.09883420683393462</v>
+        <v>0.07202192220010084</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.2547636267406239</v>
+        <v>0.1003604065284829</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.07858400011413735</v>
+        <v>0.03239284268914311</v>
       </c>
     </row>
     <row r="28">
@@ -2048,51 +2048,51 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>181</v>
+        <v>51.51</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.01119914240688746</v>
+        <v>-0.0101845231489226</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.02964669927350394</v>
+        <v>-0.03485105204377936</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.02098376154285919</v>
+        <v>-0.03067371258631879</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.05514752876367246</v>
+        <v>0.007235020263994363</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.09134756309281333</v>
+        <v>-0.02609190932199801</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.09002378715030757</v>
+        <v>0.02687745316229551</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.04209149642362453</v>
+        <v>0.1427320267312071</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>-0.06788985462103081</v>
+        <v>0.1700310491059032</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.6522926086192531</v>
+        <v>0.7562145934100579</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.1822127895230805</v>
+        <v>0.2064959281948222</v>
       </c>
     </row>
     <row r="29">
@@ -2104,44 +2104,52 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>71.95999999999999</v>
+        <v>17.94</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.019083990106747</v>
+        <v>0.01528016166371748</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.04321233931075763</v>
+        <v>0.007865241741447981</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.04104480001968347</v>
+        <v>-0.02922072627461569</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.003626250310974966</v>
+        <v>0.05096665815976498</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.05358705518565343</v>
+        <v>0.01931819006923785</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.01897474208120853</v>
-      </c>
-      <c r="M29" s="6" t="inlineStr"/>
-      <c r="N29" s="6" t="inlineStr"/>
-      <c r="O29" s="6" t="inlineStr"/>
-      <c r="P29" s="6" t="inlineStr"/>
+        <v>0.0303751491627986</v>
+      </c>
+      <c r="M29" s="6" t="n">
+        <v>0.1238104421102537</v>
+      </c>
+      <c r="N29" s="6" t="n">
+        <v>0.05819058333802096</v>
+      </c>
+      <c r="O29" s="6" t="n">
+        <v>0.5148688874007117</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v>0.1484841748530281</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
@@ -2152,52 +2160,44 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>17.54</v>
+        <v>71.33</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-0.02663704384255594</v>
+        <v>-0.01136520689511145</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.03254265154716696</v>
+        <v>-0.05710508404082981</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.04362045967309669</v>
+        <v>-0.04677268360759934</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.001713345873977978</v>
+        <v>-0.02780429111572269</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.004540290572967676</v>
+        <v>0.04482210837048672</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.003080137010358142</v>
-      </c>
-      <c r="M30" s="6" t="n">
-        <v>0.1209504711435472</v>
-      </c>
-      <c r="N30" s="6" t="n">
-        <v>0.04485033526972004</v>
-      </c>
-      <c r="O30" s="6" t="n">
-        <v>0.44422572734951</v>
-      </c>
-      <c r="P30" s="6" t="n">
-        <v>0.1303467563876686</v>
-      </c>
+        <v>0.009196399590724269</v>
+      </c>
+      <c r="M30" s="6" t="inlineStr"/>
+      <c r="N30" s="6" t="inlineStr"/>
+      <c r="O30" s="6" t="inlineStr"/>
+      <c r="P30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
@@ -2222,37 +2222,37 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>64.76000000000001</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.01982741886854245</v>
+        <v>0.0001526344887530229</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.01982741886854245</v>
+        <v>0.005373019303047677</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.02278549242983741</v>
+        <v>-0.02151505206694126</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.001701478851590332</v>
+        <v>0.05560923432189568</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.007357384170081693</v>
+        <v>-0.008778595939665568</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>-0.01655020948158337</v>
+        <v>0.0003168559683941474</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.0697805520315844</v>
+        <v>0.04205624835204214</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.04461546441924358</v>
+        <v>0.02775354403192631</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.4685913450891375</v>
+        <v>0.5027517344903809</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1366680552304733</v>
+        <v>0.1454138037622641</v>
       </c>
     </row>
     <row r="32">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2278,37 +2278,37 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>54.89</v>
+        <v>120.68</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.002906445951490477</v>
+        <v>-0.003714991814131263</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.0003645062539274768</v>
+        <v>-0.03594823445462114</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.01123803655250311</v>
+        <v>-0.03533172040653265</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.0443302502945031</v>
+        <v>-0.01268103582744351</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.01123803655250311</v>
+        <v>0.003742800762520648</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>-0.04902455034304709</v>
+        <v>-0.09518130387776935</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.03825727344076335</v>
+        <v>0.05703967765766538</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.02101501881689405</v>
+        <v>-0.02550133538084953</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.282018444243304</v>
+        <v>0.3903660413121772</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.08633746572360912</v>
+        <v>0.1161169851287278</v>
       </c>
     </row>
     <row r="33">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -2334,37 +2334,37 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>121.1</v>
+        <v>55</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.01824077849885053</v>
+        <v>-0.01521931060597881</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.02988066412096824</v>
+        <v>0.007326035477244419</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.0352903716104106</v>
+        <v>-0.0003635124972241055</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0.002815471446473428</v>
+        <v>0.04642310812322203</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>0.009418998432276116</v>
+        <v>-0.006682299783677625</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.09354128954230656</v>
+        <v>-0.04727455442426398</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.08845727713612273</v>
+        <v>0.006671171041279234</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.00376265096530326</v>
+        <v>-0.007480422962451216</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.3933463420269316</v>
+        <v>0.2766311625819791</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1169138952583983</v>
+        <v>0.08481366478291519</v>
       </c>
     </row>
     <row r="34">
@@ -2390,37 +2390,37 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>129.96</v>
+        <v>128.05</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>-0.007180956657343529</v>
+        <v>0.007315924206120261</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.01163585607558904</v>
+        <v>-0.02992421930486511</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>0.00440534297014894</v>
+        <v>-0.007595099874528555</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.0369765864929128</v>
+        <v>-0.07738303014564729</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.0415054416162467</v>
+        <v>-0.0728276668833634</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.07003859143869284</v>
+        <v>-0.1016418597809868</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.007287070845783949</v>
+        <v>-0.0387216518085729</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.03798812799400597</v>
+        <v>0.02366695041935607</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.5489648269025156</v>
+        <v>0.5283846890617916</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1570368354445015</v>
+        <v>0.1518896944054777</v>
       </c>
     </row>
   </sheetData>
@@ -2560,17 +2560,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2650,17 +2650,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -2695,17 +2695,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -2717,17 +2717,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -2762,17 +2762,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -2785,17 +2785,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -2807,17 +2807,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -2830,17 +2830,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2852,17 +2852,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2897,17 +2897,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -2920,17 +2920,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -2942,17 +2942,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.4238165033570835</v>
+        <v>0.3831757651695116</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -3048,21 +3048,21 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.05802495363379212</v>
+        <v>-0.07738303014564729</v>
       </c>
     </row>
     <row r="18">
@@ -3071,21 +3071,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.1366432947328284</v>
+        <v>0.1803781676899621</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -3093,21 +3093,21 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.0369765864929128</v>
+        <v>-0.03910846901336862</v>
       </c>
     </row>
     <row r="19">
@@ -3116,21 +3116,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.1133721037686402</v>
+        <v>0.1311130143499042</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -3138,21 +3138,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.0288191085067474</v>
+        <v>-0.03607741520915686</v>
       </c>
     </row>
     <row r="20">
@@ -3161,21 +3161,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.1054267189665317</v>
+        <v>0.1238447495732262</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -3183,21 +3183,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.01608298169014544</v>
+        <v>-0.03508176652701966</v>
       </c>
     </row>
     <row r="21">
@@ -3206,21 +3206,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.09715127232627219</v>
+        <v>0.117589399141254</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -3228,21 +3228,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.006164394120245054</v>
+        <v>-0.02780429111572269</v>
       </c>
     </row>
     <row r="22">
@@ -3251,21 +3251,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.09172018746745358</v>
+        <v>0.08938538622920378</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -3273,21 +3273,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.002871497557553226</v>
+        <v>-0.01518944254995491</v>
       </c>
     </row>
     <row r="23">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.0718544955762479</v>
+        <v>0.08717579453677926</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -3318,21 +3318,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>0.0003883597283853568</v>
+        <v>-0.01486821032860886</v>
       </c>
     </row>
     <row r="24">
@@ -3341,21 +3341,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.07041577174230729</v>
+        <v>0.08550317729248436</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -3363,21 +3363,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
+          <t>Construction &amp; Housing</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
       <c r="K24" s="11" t="n">
-        <v>0.001701478851590332</v>
+        <v>-0.01268103582744351</v>
       </c>
     </row>
     <row r="25">
@@ -3386,21 +3386,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.06906280089416406</v>
+        <v>0.08024657180787687</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -3408,21 +3408,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>0.001713345873977978</v>
+        <v>-0.01194492611066778</v>
       </c>
     </row>
     <row r="26">
@@ -3431,21 +3431,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.06238419984960331</v>
+        <v>0.06643604352907584</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -3453,21 +3453,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>0.002815471446473428</v>
+        <v>-0.0007143020629882812</v>
       </c>
     </row>
     <row r="27"/>
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.2634433435604404</v>
+        <v>0.2593287744374284</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.05001556667511864</v>
+        <v>-0.1057356492117627</v>
       </c>
     </row>
     <row r="32">
@@ -3582,21 +3582,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.2480266429744433</v>
+        <v>0.2441861119462061</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -3618,7 +3618,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.0415054416162467</v>
+        <v>-0.0728276668833634</v>
       </c>
     </row>
     <row r="33">
@@ -3627,12 +3627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3641,7 +3641,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.2280208887984347</v>
+        <v>0.2389162376437324</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -3649,21 +3649,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.007357384170081693</v>
+        <v>-0.04521962725872342</v>
       </c>
     </row>
     <row r="34">
@@ -3672,21 +3672,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.1829268516416958</v>
+        <v>0.2310455322792886</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -3708,7 +3708,7 @@
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.006365776043274485</v>
+        <v>-0.02609190932199801</v>
       </c>
     </row>
     <row r="35">
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.1697369019575734</v>
+        <v>0.2135728606238909</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.004759702952392586</v>
+        <v>-0.02486403433500473</v>
       </c>
     </row>
     <row r="36">
@@ -3776,7 +3776,7 @@
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.1681090917349128</v>
+        <v>0.1830912164718939</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -3784,21 +3784,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.004540290572967676</v>
+        <v>-0.02207796674801388</v>
       </c>
     </row>
     <row r="37">
@@ -3807,21 +3807,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1467065115965649</v>
+        <v>0.1530879716920395</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -3829,21 +3829,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>0.002017466926837352</v>
+        <v>-0.008778595939665568</v>
       </c>
     </row>
     <row r="38">
@@ -3852,21 +3852,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1365792512423245</v>
+        <v>0.1472868704178349</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3888,7 +3888,7 @@
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>0.009418998432276116</v>
+        <v>-0.006682299783677625</v>
       </c>
     </row>
     <row r="39">
@@ -3897,21 +3897,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1293500512091188</v>
+        <v>0.1458333609280764</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -3919,21 +3919,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0.01091707239470963</v>
+        <v>0.003742800762520648</v>
       </c>
     </row>
     <row r="40">
@@ -3942,21 +3942,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
       <c r="E40" s="11" t="n">
-        <v>0.1275906943373053</v>
+        <v>0.1335930777404544</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -3964,21 +3964,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>0.01123803655250311</v>
+        <v>0.006474831299125405</v>
       </c>
     </row>
     <row r="41"/>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.4387855938080918</v>
+        <v>0.4171121010951535</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -4070,21 +4070,21 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.09354128954230656</v>
+        <v>-0.1016418597809868</v>
       </c>
     </row>
     <row r="46">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.3453337400583016</v>
+        <v>0.3636593742192153</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -4115,21 +4115,21 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.07003859143869284</v>
+        <v>-0.09518130387776935</v>
       </c>
     </row>
     <row r="47">
@@ -4152,7 +4152,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.3304318049799253</v>
+        <v>0.306914527760942</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -4174,7 +4174,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.04902455034304709</v>
+        <v>-0.04727455442426398</v>
       </c>
     </row>
     <row r="48">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.3154670755398972</v>
+        <v>0.3049929610747049</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.03127045366668679</v>
+        <v>-0.03795050036228309</v>
       </c>
     </row>
     <row r="49">
@@ -4228,21 +4228,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.2352598251978533</v>
+        <v>0.2938761399847394</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -4250,21 +4250,21 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.01655020948158337</v>
+        <v>-0.02226129294378287</v>
       </c>
     </row>
     <row r="50">
@@ -4273,21 +4273,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.2103005430749521</v>
+        <v>0.2253443938148396</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -4295,21 +4295,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
       <c r="K50" s="11" t="n">
-        <v>-0.01517086137183443</v>
+        <v>-0.01156502192508879</v>
       </c>
     </row>
     <row r="51">
@@ -4318,21 +4318,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.2097381738406576</v>
+        <v>0.1996937799681542</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4354,7 +4354,7 @@
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.008307363743145224</v>
+        <v>-0.001732204774796298</v>
       </c>
     </row>
     <row r="52">
@@ -4363,21 +4363,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.2064786204040554</v>
+        <v>0.1914764860204163</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4385,21 +4385,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-0.00705869828574468</v>
+        <v>0.0003168559683941474</v>
       </c>
     </row>
     <row r="53">
@@ -4408,21 +4408,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.1899769396860487</v>
+        <v>0.1819312688299251</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -4430,21 +4430,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.003080137010358142</v>
+        <v>0.009196399590724269</v>
       </c>
     </row>
     <row r="54">
@@ -4453,21 +4453,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.1350488791844386</v>
+        <v>0.1790562027327856</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -4489,7 +4489,7 @@
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.01521792892689633</v>
+        <v>0.02233356346684845</v>
       </c>
     </row>
     <row r="55"/>
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.9712792475113445</v>
+        <v>0.9073378682442328</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.09883420683393462</v>
+        <v>-0.09072780375264677</v>
       </c>
     </row>
     <row r="60">
@@ -4618,7 +4618,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.8874913481181854</v>
+        <v>0.7816732194309011</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.06788985462103081</v>
+        <v>-0.05682570614179261</v>
       </c>
     </row>
     <row r="61">
@@ -4663,7 +4663,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.7338530899927156</v>
+        <v>0.7432483011701951</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4685,7 +4685,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.04003068408781374</v>
+        <v>-0.03783280043157777</v>
       </c>
     </row>
     <row r="62">
@@ -4694,21 +4694,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.6215938645180512</v>
+        <v>0.5917771700818479</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>0.00376265096530326</v>
+        <v>-0.02550133538084953</v>
       </c>
     </row>
     <row r="63">
@@ -4739,21 +4739,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.6008544693997961</v>
+        <v>0.561330933522699</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4761,21 +4761,21 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>0.01775269343861718</v>
+        <v>-0.007480422962451216</v>
       </c>
     </row>
     <row r="64">
@@ -4798,7 +4798,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.5191869127888411</v>
+        <v>0.5103122338070285</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4806,21 +4806,21 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>0.02101501881689405</v>
+        <v>0.02178387108857849</v>
       </c>
     </row>
     <row r="65">
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.4970897392909994</v>
+        <v>0.4432606453138559</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4851,21 +4851,21 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.0305832865222242</v>
+        <v>0.02366695041935607</v>
       </c>
     </row>
     <row r="66">
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.3757843583528722</v>
+        <v>0.3610189769235936</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4896,21 +4896,21 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>0.03798812799400597</v>
+        <v>0.02492935886041714</v>
       </c>
     </row>
     <row r="67">
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.2795758209210946</v>
+        <v>0.2601464743803183</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4955,7 +4955,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.04461546441924358</v>
+        <v>0.02775354403192631</v>
       </c>
     </row>
     <row r="68">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.2696585403600702</v>
+        <v>0.227278124280597</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -5000,7 +5000,7 @@
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.04485033526972004</v>
+        <v>0.05819058333802096</v>
       </c>
     </row>
     <row r="69"/>
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.632850612884869</v>
+        <v>2.640696457329232</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.06715716614282985</v>
+        <v>0.09509648794249226</v>
       </c>
     </row>
     <row r="74">
@@ -5129,7 +5129,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.597907156962665</v>
+        <v>2.396131442742</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.09394965526969368</v>
+        <v>0.1003604065284829</v>
       </c>
     </row>
     <row r="75">
@@ -5174,7 +5174,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.295753382308867</v>
+        <v>2.212270352203991</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1618644334302597</v>
+        <v>0.2041623117383993</v>
       </c>
     </row>
     <row r="76">
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.557822848424045</v>
+        <v>1.456667521255983</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.214916028109327</v>
+        <v>0.2198085684098507</v>
       </c>
     </row>
     <row r="77">
@@ -5250,21 +5250,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.181065325519018</v>
+        <v>1.201381621141571</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5272,21 +5272,21 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.2547636267406239</v>
+        <v>0.2766311625819791</v>
       </c>
     </row>
     <row r="78">
@@ -5295,21 +5295,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.153993129966209</v>
+        <v>1.164311504741482</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5317,21 +5317,21 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.266363486227565</v>
+        <v>0.2908704616694808</v>
       </c>
     </row>
     <row r="79">
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.076329124027107</v>
+        <v>1.065610389630292</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5362,21 +5362,21 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.282018444243304</v>
+        <v>0.2994642948178405</v>
       </c>
     </row>
     <row r="80">
@@ -5399,7 +5399,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.9545610812784293</v>
+        <v>1.005313846787673</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5421,7 +5421,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.304375327465304</v>
+        <v>0.3202776566441634</v>
       </c>
     </row>
     <row r="81">
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8586676697711513</v>
+        <v>0.8472892217892107</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5452,21 +5452,21 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.3628170066006544</v>
+        <v>0.3750645605370346</v>
       </c>
     </row>
     <row r="82">
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.7880882268144138</v>
+        <v>0.8118292538109142</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5497,21 +5497,21 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.3795046068834751</v>
+        <v>0.3903660413121772</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -627,16 +627,16 @@
         <v>0.4171121010951535</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.6983107200297163</v>
+        <v>0.6983106151683862</v>
       </c>
       <c r="N2" s="6" t="n">
         <v>0.9073378682442328</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.212270352203991</v>
+        <v>2.212270727354308</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4754937123020999</v>
+        <v>0.4754937697414239</v>
       </c>
     </row>
     <row r="3">
@@ -745,10 +745,10 @@
         <v>0.5917771700818479</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.065610389630292</v>
+        <v>1.065610125832187</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2735503995993012</v>
+        <v>0.2735503453844634</v>
       </c>
     </row>
     <row r="5">
@@ -801,10 +801,10 @@
         <v>0.7816732194309011</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>2.396131442742</v>
+        <v>2.396131068485421</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.5031240730379278</v>
+        <v>0.5031240178227412</v>
       </c>
     </row>
     <row r="6">
@@ -854,13 +854,13 @@
         <v>0.4955290272571484</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.561330933522699</v>
+        <v>0.5613310349437368</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.6883458680945547</v>
+        <v>0.6883457495010505</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.1907496789932077</v>
+        <v>0.1907496511128264</v>
       </c>
     </row>
     <row r="7">
@@ -913,10 +913,10 @@
         <v>0.3610189769235936</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.5129753096347567</v>
+        <v>0.5129754543034524</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1480054423622024</v>
+        <v>0.1480054789524545</v>
       </c>
     </row>
     <row r="8">
@@ -969,10 +969,10 @@
         <v>0.5103122338070285</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.7672847881410789</v>
+        <v>0.7672846238947924</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.2090256455308668</v>
+        <v>0.2090256080764281</v>
       </c>
     </row>
     <row r="9">
@@ -1025,10 +1025,10 @@
         <v>0.4432606453138559</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>1.456667521255983</v>
+        <v>1.456667302867464</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.3493215651502837</v>
+        <v>0.3493215251670754</v>
       </c>
     </row>
     <row r="10">
@@ -1078,7 +1078,7 @@
         <v>0.2064795237029982</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.1657450775095146</v>
+        <v>0.1657450045361664</v>
       </c>
       <c r="O10" s="6" t="n">
         <v>1.005313846787673</v>
@@ -1137,10 +1137,10 @@
         <v>0.02492935886041714</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.3202776566441634</v>
+        <v>0.3202778024031709</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.09703821888125042</v>
+        <v>0.09703825925235354</v>
       </c>
     </row>
     <row r="12">
@@ -1187,16 +1187,16 @@
         <v>0.1232916096879459</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.2305316738034349</v>
+        <v>0.2305315979000755</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>0.227278124280597</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.201381621141571</v>
+        <v>1.201381378220015</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.3008636511860419</v>
+        <v>0.3008636033361172</v>
       </c>
     </row>
     <row r="13">
@@ -1361,10 +1361,10 @@
         <v>0.2219186191473381</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.5025708929454991</v>
+        <v>0.5025707516293152</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.1453678554514348</v>
+        <v>0.145367819544306</v>
       </c>
     </row>
     <row r="16">
@@ -1473,10 +1473,10 @@
         <v>0.1068651039884059</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.6286425268361682</v>
+        <v>0.6286424245681888</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.1765451293135569</v>
+        <v>0.1765451046871389</v>
       </c>
     </row>
     <row r="18">
@@ -1523,16 +1523,16 @@
         <v>0.1657300355714972</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.2816436612944095</v>
+        <v>0.2816435553055514</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>0.2601464743803183</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.8472892217892107</v>
+        <v>0.8472890016003212</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.2270011377583219</v>
+        <v>0.2270010890072427</v>
       </c>
     </row>
     <row r="19">
@@ -1585,10 +1585,10 @@
         <v>0.1789908795538515</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.2994642948178405</v>
+        <v>0.2994641719114173</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.09124294840691194</v>
+        <v>0.09124291400279327</v>
       </c>
     </row>
     <row r="20">
@@ -1753,10 +1753,10 @@
         <v>0.1955694218225474</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>1.164311504741482</v>
+        <v>1.164311347055526</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.2935203215962767</v>
+        <v>0.2935202901821305</v>
       </c>
     </row>
     <row r="23">
@@ -1803,10 +1803,10 @@
         <v>0.02233356346684845</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1913837066466695</v>
+        <v>0.1913835953046559</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.1100390906327462</v>
+        <v>0.1100391872895394</v>
       </c>
       <c r="O23" s="6" t="n">
         <v>0.2041623117383993</v>
@@ -1865,10 +1865,10 @@
         <v>0.1372671161148564</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.3939987397102891</v>
+        <v>0.3939991634952182</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.117088189884752</v>
+        <v>0.1170883030854979</v>
       </c>
     </row>
     <row r="25">
@@ -1915,16 +1915,16 @@
         <v>0.05063347483899738</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.2220792338134459</v>
+        <v>0.2220791512099278</v>
       </c>
       <c r="N25" s="6" t="n">
         <v>0.1581412521865595</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.8118292538109142</v>
+        <v>0.8118294353768711</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.2190993204028242</v>
+        <v>0.2190993611253751</v>
       </c>
     </row>
     <row r="26">
@@ -1977,10 +1977,10 @@
         <v>-0.05682570614179261</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.6918350969031164</v>
+        <v>0.6918348617988674</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1915694042373983</v>
+        <v>0.1915693490422943</v>
       </c>
     </row>
     <row r="27">
@@ -2033,10 +2033,10 @@
         <v>0.07202192220010084</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.1003604065284829</v>
+        <v>0.1003602414531355</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.03239284268914311</v>
+        <v>0.03239279106284121</v>
       </c>
     </row>
     <row r="28">
@@ -2089,10 +2089,10 @@
         <v>0.1700310491059032</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.7562145934100579</v>
+        <v>0.7562144792028058</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.2064959281948222</v>
+        <v>0.2064959020418702</v>
       </c>
     </row>
     <row r="29">
@@ -2145,10 +2145,10 @@
         <v>0.05819058333802096</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.5148688874007117</v>
+        <v>0.5148690093917034</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1484841748530281</v>
+        <v>0.1484842056818172</v>
       </c>
     </row>
     <row r="30">
@@ -2243,7 +2243,7 @@
         <v>0.0003168559683941474</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.04205624835204214</v>
+        <v>0.04205631160305034</v>
       </c>
       <c r="N31" s="6" t="n">
         <v>0.02775354403192631</v>
@@ -2302,7 +2302,7 @@
         <v>0.05703967765766538</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.02550133538084953</v>
+        <v>-0.02550139541760876</v>
       </c>
       <c r="O32" s="6" t="n">
         <v>0.3903660413121772</v>
@@ -2361,10 +2361,10 @@
         <v>-0.007480422962451216</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.2766311625819791</v>
+        <v>0.2766312756209799</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.08481366478291519</v>
+        <v>0.08481369680110307</v>
       </c>
     </row>
     <row r="34">
@@ -2411,16 +2411,16 @@
         <v>-0.1016418597809868</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.0387216518085729</v>
+        <v>-0.03872176192161148</v>
       </c>
       <c r="N34" s="6" t="n">
         <v>0.02366695041935607</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.5283846890617916</v>
+        <v>0.5283845498821231</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1518896944054777</v>
+        <v>0.151889659440539</v>
       </c>
     </row>
   </sheetData>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.02550133538084953</v>
+        <v>-0.02550139541760876</v>
       </c>
     </row>
     <row r="63">
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.561330933522699</v>
+        <v>0.5613310349437368</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -5129,7 +5129,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.396131442742</v>
+        <v>2.396131068485421</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.1003604065284829</v>
+        <v>0.1003602414531355</v>
       </c>
     </row>
     <row r="75">
@@ -5174,7 +5174,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.212270352203991</v>
+        <v>2.212270727354308</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.456667521255983</v>
+        <v>1.456667302867464</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.201381621141571</v>
+        <v>1.201381378220015</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.2766311625819791</v>
+        <v>0.2766312756209799</v>
       </c>
     </row>
     <row r="78">
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.164311504741482</v>
+        <v>1.164311347055526</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.065610389630292</v>
+        <v>1.065610125832187</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.2994642948178405</v>
+        <v>0.2994641719114173</v>
       </c>
     </row>
     <row r="80">
@@ -5421,7 +5421,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.3202776566441634</v>
+        <v>0.3202778024031709</v>
       </c>
     </row>
     <row r="81">
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8472892217892107</v>
+        <v>0.8472890016003212</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.8118292538109142</v>
+        <v>0.8118294353768711</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -491,11 +491,11 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
-    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
     <col width="24" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>209.85</v>
+        <v>212.45</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>-0.02675999046626421</v>
+        <v>0.01238975825163435</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>-0.07583564832547784</v>
+        <v>-0.0240709515108507</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.001622889626244461</v>
+        <v>0.009407496156484507</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.01839274284104642</v>
+        <v>0.03101038273006584</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.009816700682779622</v>
+        <v>0.02232808548270238</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.4171121010951535</v>
+        <v>0.4093042817247554</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.6983106151683862</v>
+        <v>0.7066633995642733</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.9073378682442328</v>
+        <v>0.9449358776105117</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.212270727354308</v>
+        <v>2.232448687681074</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4754937697414239</v>
+        <v>0.4785767739564453</v>
       </c>
     </row>
     <row r="3">
@@ -648,51 +648,51 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>71.69</v>
+        <v>31.52</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.008156403122998368</v>
+        <v>0.02171799248003858</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.1263158008292966</v>
+        <v>0.04717608167101983</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.1481422808798802</v>
+        <v>0.07210887301839297</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.3831757651695116</v>
+        <v>0.1090781271339805</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.2441861119462061</v>
+        <v>0.2577813698919151</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>-0.03795050036228309</v>
+        <v>0.2596371757639508</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.3914325456588812</v>
+        <v>0.3081765039009654</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.7432483011701951</v>
+        <v>0.6560339681432914</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>2.640696457329232</v>
+        <v>1.097555304097171</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.5383724382214043</v>
+        <v>0.2800820471693408</v>
       </c>
     </row>
     <row r="4">
@@ -704,51 +704,51 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>30.85</v>
+        <v>73.03</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.007719516562890272</v>
+        <v>0.01869153706593663</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.03488765294060259</v>
+        <v>0.1807599123846972</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.04505419725887116</v>
+        <v>0.171854928384445</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.08550317729248436</v>
+        <v>0.4090294462528825</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.2310455322792886</v>
+        <v>0.267441862774572</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.2253443938148396</v>
+        <v>-0.0235483242788227</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.2919495801876864</v>
+        <v>0.4132501856958326</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.5917771700818479</v>
+        <v>0.7754199127831896</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.065610125832187</v>
+        <v>2.74538018853307</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2735503453844634</v>
+        <v>0.552977998434343</v>
       </c>
     </row>
     <row r="5">
@@ -774,37 +774,37 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>58.78</v>
+        <v>59.77</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.0300329990206426</v>
+        <v>0.0168424923277728</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.09791289938988268</v>
+        <v>-0.03550106050674839</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>-0.05528772699961992</v>
+        <v>-0.04444442547090777</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-0.03607741520915686</v>
+        <v>-0.01984255647025024</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>-0.1057356492117627</v>
+        <v>-0.09067400874461118</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.2938761399847394</v>
+        <v>0.2937838234858181</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.5564943496256149</v>
+        <v>0.5852734915624098</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.7816732194309011</v>
+        <v>0.807856084550592</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>2.396131068485421</v>
+        <v>2.472598869524331</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.5031240178227412</v>
+        <v>0.514321911799311</v>
       </c>
     </row>
     <row r="6">
@@ -830,37 +830,37 @@
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>91.69</v>
+        <v>90.25</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-0.007576544570478849</v>
+        <v>-0.01570511945755992</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.005372867429394246</v>
+        <v>-0.02421881193108977</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.04299850553784146</v>
+        <v>0.01621441820732161</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.06085852270806336</v>
+        <v>0.04419761288136259</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.0804855265370048</v>
+        <v>0.06351637227057649</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.1914764860204163</v>
+        <v>0.1764234136468221</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.4955290272571484</v>
+        <v>0.4816362186515539</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.5613310349437368</v>
+        <v>0.5309346432478741</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.6883457495010505</v>
+        <v>0.6453058408384611</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.1907496511128264</v>
+        <v>0.1805440947761381</v>
       </c>
     </row>
     <row r="7">
@@ -886,37 +886,37 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>30.18</v>
+        <v>30.5</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.007889538807239971</v>
+        <v>0.01060303815733699</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.04682623604031511</v>
+        <v>0.05027544898223502</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.04537580283552112</v>
+        <v>0.06050068697046784</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.08717579453677926</v>
+        <v>0.09870316096998577</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.2389162376437324</v>
+        <v>0.2520525137852132</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.1996937799681542</v>
+        <v>0.218867726635779</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.1767646752810961</v>
+        <v>0.1714525372535143</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.3610189769235936</v>
+        <v>0.3984438068723979</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.5129754543034524</v>
+        <v>0.5195482820158541</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1480054789524545</v>
+        <v>0.1496655062498655</v>
       </c>
     </row>
     <row r="8">
@@ -942,37 +942,37 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>36.27</v>
+        <v>36.81</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.007117392012631396</v>
+        <v>0.01488836252307668</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.06332453265206328</v>
+        <v>0.05775868334186351</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.05130436109459913</v>
+        <v>0.07443091584026962</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.05620268772859438</v>
+        <v>0.0719278162413457</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.1166872219502006</v>
+        <v>0.1333128661354825</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.1131294172520043</v>
+        <v>0.1300405089861418</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.2071055475590073</v>
+        <v>0.1985933653384</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.5103122338070285</v>
+        <v>0.5580271200594566</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.7672846238947924</v>
+        <v>0.7816244106846273</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.2090256080764281</v>
+        <v>0.2122868236264366</v>
       </c>
     </row>
     <row r="9">
@@ -998,37 +998,37 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>52.71</v>
+        <v>53.28</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.01953123641821208</v>
+        <v>0.01081388170602593</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.05858193419657631</v>
+        <v>-0.02274397777064252</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-0.03655638884058443</v>
+        <v>-0.02489020178520018</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.003426619252972829</v>
+        <v>0.01427755601425207</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>-0.02207796674801388</v>
+        <v>-0.01150283356271053</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.306914527760942</v>
+        <v>0.297718187952126</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.3479846826063997</v>
+        <v>0.3645848303886592</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.4432606453138559</v>
+        <v>0.4595909915006999</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>1.456667302867464</v>
+        <v>1.475464432095607</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.3493215251670754</v>
+        <v>0.3527542183888797</v>
       </c>
     </row>
     <row r="10">
@@ -1054,37 +1054,37 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>17.76</v>
+        <v>17.74</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.007945481440426949</v>
+        <v>-0.001126151886594373</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.001686379151297435</v>
+        <v>-0.002249770190244638</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01023892525352377</v>
+        <v>0.004530007044013518</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.04225347856046224</v>
+        <v>0.04107974283927196</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.1472868704178349</v>
+        <v>0.145994851144249</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.1819312688299251</v>
+        <v>0.1578233411311052</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.2064795237029982</v>
+        <v>0.1870214269893371</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.1657450045361664</v>
+        <v>0.1701790986789031</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.005313846787673</v>
+        <v>1.004975971638061</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2610359010229999</v>
+        <v>0.2609650731030881</v>
       </c>
     </row>
     <row r="11">
@@ -1110,37 +1110,37 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>45.62</v>
+        <v>45.68</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.006175535473192939</v>
+        <v>0.001315242759663438</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.02863586249060956</v>
+        <v>0.02444494615065906</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.01989714730061776</v>
+        <v>0.01896048269916162</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.117589399141254</v>
+        <v>0.1190593005067511</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.1830912164718939</v>
+        <v>0.18464726862838</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.3049929610747049</v>
+        <v>0.2810165770916062</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.09804973512404946</v>
+        <v>0.08178481144507299</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.02492935886041714</v>
+        <v>0.03506389141886035</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.3202778024031709</v>
+        <v>0.3055173734094689</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.09703825925235354</v>
+        <v>0.09293470953445437</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>38.05</v>
+        <v>53.92</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.001052378776472684</v>
+        <v>0.004845291134411678</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.03889873477120154</v>
+        <v>0.05518590565618853</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>-0.02159938713733889</v>
+        <v>0.03732202085020497</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-0.01194492611066778</v>
+        <v>0.1365935862103516</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.1022595229573053</v>
+        <v>0.2654305889835198</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.1232916096879459</v>
+        <v>0.1243687617947005</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.2305315979000755</v>
+        <v>-0.009430964685356313</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.227278124280597</v>
+        <v>0.08269192426244754</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.201381378220015</v>
+        <v>0.2141363333811206</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.3008636033361172</v>
+        <v>0.06681509437654221</v>
       </c>
     </row>
     <row r="13">
@@ -1208,51 +1208,51 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>23.1</v>
+        <v>37.94</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.008583642151914983</v>
+        <v>-0.002890949081660543</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.007305546753318959</v>
+        <v>-0.03583227197173611</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-0.03629532569072957</v>
+        <v>-0.0321429110129432</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.1803781676899621</v>
+        <v>-0.01480134301915814</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.1458333609280764</v>
+        <v>0.09907294680166046</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.3636593742192153</v>
+        <v>0.09754825265052713</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.05132393231104215</v>
+        <v>0.1976934713000433</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.02178387108857849</v>
+        <v>0.227697401185303</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.3750645605370346</v>
+        <v>1.207773111598756</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.1120074488121563</v>
+        <v>0.30212141036726</v>
       </c>
     </row>
     <row r="14">
@@ -1264,51 +1264,51 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>53.66</v>
+        <v>122.55</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.009597645899496188</v>
+        <v>0.005414748260023527</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.0437658044481255</v>
+        <v>0.008227066844039399</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.03610733537029365</v>
+        <v>-0.008093888913795366</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.1311130143499042</v>
+        <v>-0.009856941297549437</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.2593287744374284</v>
+        <v>0.06713694670611314</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.1175256200389043</v>
+        <v>0.08449272611796688</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.001677693800515412</v>
+        <v>0.2521894973662733</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.06224574973988783</v>
+        <v>0.2498417746880897</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.2198085684098507</v>
+        <v>0.5066342419951397</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.06847383915296401</v>
+        <v>0.1463993853575347</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>121.89</v>
+        <v>23.06</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.0002460529834925618</v>
+        <v>-0.001731641336224055</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.01103448771076321</v>
+        <v>-0.006462715400562979</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-0.01183623107039566</v>
+        <v>-0.03312372758455528</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-0.01518944254995491</v>
+        <v>0.1783341760624138</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.06138978819726515</v>
+        <v>0.143849188515869</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.0741345636024906</v>
+        <v>0.3186685790323285</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.26953191612445</v>
+        <v>0.03682176209979615</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.2219186191473381</v>
+        <v>0.02853620116910349</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.5025707516293152</v>
+        <v>0.3516069593541307</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.145367819544306</v>
+        <v>0.1056478008111097</v>
       </c>
     </row>
     <row r="16">
@@ -1376,51 +1376,51 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>115.97</v>
+        <v>14.92</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.008347092136695489</v>
+        <v>0.00947228321056337</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.008259473181735588</v>
+        <v>0.01289888255005134</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.01369280987650345</v>
+        <v>0.01704158137013168</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-0.03910846901336862</v>
+        <v>0.03972123203287614</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.08332552932887416</v>
+        <v>-0.03617567716423087</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.174617616505518</v>
+        <v>0.1786023025934405</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.1282763553434916</v>
+        <v>0.2864683114313695</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.2084423584549633</v>
+        <v>0.278208470133203</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.09509648794249226</v>
+        <v>0.8684255421908049</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.03074395240623562</v>
+        <v>0.2316631042724611</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>98.94</v>
+        <v>115.88</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.01737791713528281</v>
+        <v>-0.0007760969762677927</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.02933832307786211</v>
+        <v>0.006864201413370408</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.008871242472614727</v>
+        <v>0.00172888094497381</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.01664614418066201</v>
+        <v>-0.03985421402508871</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.1335930777404544</v>
+        <v>0.08248476366124824</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.1399199523156087</v>
+        <v>0.1583366272783797</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.156015194765162</v>
+        <v>0.1041575190420831</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.1068651039884059</v>
+        <v>0.220506055311535</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.6286424245681888</v>
+        <v>0.09048469079874155</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.1765451046871389</v>
+        <v>0.02929498705045819</v>
       </c>
     </row>
     <row r="18">
@@ -1488,51 +1488,51 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>14.78</v>
+        <v>98.27</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.006720455692246774</v>
+        <v>-0.006771839314807293</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.008718988314643239</v>
+        <v>0.01781453689221069</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.01232872238345406</v>
+        <v>0.006761561608317868</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.02996511080631925</v>
+        <v>0.009761579852252122</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>-0.04521962725872342</v>
+        <v>0.1259165675696183</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.1657300355714972</v>
+        <v>0.1274841105074824</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.2816435553055514</v>
+        <v>0.1365210175888198</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.2601464743803183</v>
+        <v>0.1135250582030158</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.8472890016003212</v>
+        <v>0.6138726355170774</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.2270010890072427</v>
+        <v>0.1729776918639085</v>
       </c>
     </row>
     <row r="19">
@@ -1558,37 +1558,37 @@
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>104.82</v>
+        <v>105.3</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.001815946156875636</v>
+        <v>0.004579310802624414</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.02936264175591607</v>
+        <v>0.04661566855137966</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.01895593366557957</v>
+        <v>0.02262796740247319</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.06643604352907584</v>
+        <v>0.07131958562351648</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.04454410850694601</v>
+        <v>0.04932740062684959</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>-0.001732204774796298</v>
+        <v>0.007118407621416578</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.2544569669277819</v>
+        <v>0.2413969207660533</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1789908795538515</v>
+        <v>0.1897386448897176</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.2994641719114173</v>
+        <v>0.2961107892144479</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.09124291400279327</v>
+        <v>0.09030342230834809</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>18.24</v>
+        <v>28.5</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.007734772745737972</v>
+        <v>0.00600070867461211</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.02876481906651573</v>
+        <v>-0.06801831029743099</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.03401362824433085</v>
+        <v>-0.06771343524660511</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.1238447495732262</v>
+        <v>-0.02929157331312682</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.2135728606238909</v>
+        <v>0.05438399097343583</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.1790562027327856</v>
+        <v>-0.00889100347294558</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>-0.0135208222333516</v>
+        <v>0.1846463033278647</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>-0.09072780375264677</v>
+        <v>0.2072297041270006</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.2908704616694808</v>
+        <v>1.162263911764885</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.08883202942374413</v>
+        <v>0.2931122720749304</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>17.55</v>
+        <v>18.32</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.0126947094242944</v>
+        <v>0.004385960784535126</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.01739126011945191</v>
+        <v>0.03037114664367269</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.02094233227565545</v>
+        <v>0.03854877146848557</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.08938538622920378</v>
+        <v>0.1287738885727603</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.1530879716920395</v>
+        <v>0.2188955435997635</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.1115397069716235</v>
+        <v>0.1543793211677662</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.1202672495970174</v>
+        <v>-0.02397446733962771</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>-0.03783280043157777</v>
+        <v>-0.07893412483669104</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.3963358160948565</v>
+        <v>0.2811188426902231</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1177121174704581</v>
+        <v>0.08608330933169062</v>
       </c>
     </row>
     <row r="22">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>28.33</v>
+        <v>17.48</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.01734304548467458</v>
+        <v>-0.003988586773063796</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.07236414294597049</v>
+        <v>0.01509873630948411</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-0.07175624184830331</v>
+        <v>0.01040464237652561</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.03508176652701966</v>
+        <v>0.08504027808692105</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.04809468013453766</v>
+        <v>0.1484887802599697</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>-0.02226129294378287</v>
+        <v>0.09527255448036076</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.1901641028287342</v>
+        <v>0.0840535473992805</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1955694218225474</v>
+        <v>-0.03583258251212917</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>1.164311347055526</v>
+        <v>0.3866441887740508</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.2935202901821305</v>
+        <v>0.1151201888777345</v>
       </c>
     </row>
     <row r="23">
@@ -1782,37 +1782,37 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>97.26000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.01619478702940746</v>
+        <v>-0.009870440709306205</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.03457078955588577</v>
+        <v>0.01775523416201197</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.03358133595483981</v>
+        <v>0.02457713842420173</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.06167450592987422</v>
+        <v>0.05119531066651151</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.06766990402659823</v>
+        <v>0.05713153154179307</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.02233356346684845</v>
+        <v>0.02626004583204433</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1913835953046559</v>
+        <v>0.1677735268188345</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.1100391872895394</v>
+        <v>0.1285714260168176</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.2041623117383993</v>
+        <v>0.1879635602557039</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.06388579475802758</v>
+        <v>0.05909367178418634</v>
       </c>
     </row>
     <row r="24">
@@ -1838,37 +1838,37 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>43.73</v>
+        <v>43.82</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.005981097635888055</v>
+        <v>0.002058087206265879</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.008068198835945672</v>
+        <v>0.01458673508096942</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.02006066320920596</v>
+        <v>0.02791458120790513</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.01486821032860886</v>
+        <v>-0.01284072319580032</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.03207208722318478</v>
+        <v>0.03419618158184301</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.06433219440559657</v>
+        <v>0.07041320373367776</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.1547983150011418</v>
+        <v>0.1494106233092267</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.1372671161148564</v>
+        <v>0.145301543280407</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.3939991634952182</v>
+        <v>0.3946245434931543</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1170883030854979</v>
+        <v>0.1172553285890447</v>
       </c>
     </row>
     <row r="25">
@@ -1894,37 +1894,37 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>68.97</v>
+        <v>69.45</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.002891382876051285</v>
+        <v>0.006959485559570711</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.00217016087844879</v>
+        <v>0.007543836366809886</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.01680671323712857</v>
+        <v>0.01937472109259475</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.0388613022258435</v>
+        <v>0.04609124245708096</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>-0.02486403433500473</v>
+        <v>-0.01807758966334105</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.05063347483899738</v>
+        <v>0.07223976840530355</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.2220791512099278</v>
+        <v>0.2125089843106895</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.1581412521865595</v>
+        <v>0.1671498404632161</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.8118294353768711</v>
+        <v>0.8275353654026762</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.2190993611253751</v>
+        <v>0.2226118382529212</v>
       </c>
     </row>
     <row r="26">
@@ -1950,37 +1950,37 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>185.77</v>
+        <v>186.62</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.002915340697390079</v>
+        <v>0.004575501023727835</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.01992975126263663</v>
+        <v>0.02538458855597536</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.0397962636550615</v>
+        <v>0.02951393346184927</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.08024657180787687</v>
+        <v>0.08518924110306214</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.1177497453884624</v>
+        <v>0.1228640104927587</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.1410829967463834</v>
+        <v>0.1214079004047779</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.04794241862270709</v>
+        <v>0.03999078234035869</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>-0.05682570614179261</v>
+        <v>-0.04424682496057131</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.6918348617988674</v>
+        <v>0.6923284160957286</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1915693490422943</v>
+        <v>0.1916852088514884</v>
       </c>
     </row>
     <row r="27">
@@ -2006,37 +2006,37 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>13.99</v>
+        <v>14.01</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.001427584399494863</v>
+        <v>0.00142962531028501</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.007199382672692378</v>
+        <v>0.01374822997490921</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.01200565523487729</v>
+        <v>-0.01268494410319088</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.0007143020629882812</v>
+        <v>0.0007143020629882812</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.006474831299125405</v>
+        <v>0.007913713192115424</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>-0.01156502192508879</v>
+        <v>-0.001839698875348517</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.2147173659731565</v>
+        <v>0.1992781089569904</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.07202192220010084</v>
+        <v>0.08566219108284212</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.1003602414531355</v>
+        <v>0.09537862965732868</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.03239279106284121</v>
+        <v>0.03083246542699225</v>
       </c>
     </row>
     <row r="28">
@@ -2062,37 +2062,37 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>51.51</v>
+        <v>51.64</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.0101845231489226</v>
+        <v>0.002523802608257686</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.03485105204377936</v>
+        <v>-0.01205282308394662</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.03067371258631879</v>
+        <v>-0.03512707496329104</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.007235020263994363</v>
+        <v>0.009777082635265</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>-0.02609190932199801</v>
+        <v>-0.02363395754254161</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.02687745316229551</v>
+        <v>0.02644119274826306</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.1427320267312071</v>
+        <v>0.1303345476024413</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.1700310491059032</v>
+        <v>0.1793031586358671</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.7562144792028058</v>
+        <v>0.7403962276267566</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.2064959020418702</v>
+        <v>0.2028626626741645</v>
       </c>
     </row>
     <row r="29">
@@ -2118,37 +2118,37 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>17.94</v>
+        <v>17.75</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.01528016166371748</v>
+        <v>-0.01059088787076212</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.007865241741447981</v>
+        <v>-0.001687327642683423</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.02922072627461569</v>
+        <v>-0.02952437881339354</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.05096665815976498</v>
+        <v>0.03983598812728539</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.01931819006923785</v>
+        <v>0.008522705413586351</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.0303751491627986</v>
+        <v>0.02888152659150234</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.1238104421102537</v>
+        <v>0.08092808627621162</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.05819058333802096</v>
+        <v>0.05631285190140844</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.5148690093917034</v>
+        <v>0.4930254522801132</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1484842056818172</v>
+        <v>0.1429372935841626</v>
       </c>
     </row>
     <row r="30">
@@ -2174,25 +2174,25 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>71.33</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-0.01136520689511145</v>
+        <v>-0.0009813499653344993</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.05710508404082981</v>
+        <v>-0.04065692908853591</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.04677268360759934</v>
+        <v>-0.05540827372616219</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.02780429111572269</v>
+        <v>-0.02875835534093474</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.04482210837048672</v>
+        <v>0.04379677223065648</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.009196399590724269</v>
+        <v>0.01698305189937299</v>
       </c>
       <c r="M30" s="6" t="inlineStr"/>
       <c r="N30" s="6" t="inlineStr"/>
@@ -2222,37 +2222,37 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>65.48999999999999</v>
+        <v>64.84</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.0001526344887530229</v>
+        <v>-0.009925203039875208</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.005373019303047677</v>
+        <v>0.0006171803124896957</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.02151505206694126</v>
+        <v>-0.02905065104624849</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.05560923432189568</v>
+        <v>0.04513209834048371</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.008778595939665568</v>
+        <v>-0.01861666963243458</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.0003168559683941474</v>
+        <v>-0.007447842213938016</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.04205631160305034</v>
+        <v>0.009710375792921333</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.02775354403192631</v>
+        <v>0.0209208881055567</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.5027517344903809</v>
+        <v>0.474864829781666</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1454138037622641</v>
+        <v>0.1382842842527929</v>
       </c>
     </row>
     <row r="32">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2278,37 +2278,37 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>120.68</v>
+        <v>55.01</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.003714991814131263</v>
+        <v>0.0001817876642400407</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.03594823445462114</v>
+        <v>0.01926991064123107</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.03533172040653265</v>
+        <v>-0.002357654507693763</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.01268103582744351</v>
+        <v>0.04661333493585462</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.003742800762520648</v>
+        <v>-0.006501726879106995</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>-0.09518130387776935</v>
+        <v>-0.04896706001373075</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.05703967765766538</v>
+        <v>-0.01058191655854601</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.02550139541760876</v>
+        <v>-0.005572241362974184</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.3903660413121772</v>
+        <v>0.2614885408738008</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1161169851287278</v>
+        <v>0.08050746067392378</v>
       </c>
     </row>
     <row r="33">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -2334,37 +2334,37 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>55</v>
+        <v>119.98</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.01521931060597881</v>
+        <v>-0.005800438734438473</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0.007326035477244419</v>
+        <v>-0.0208911175083023</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.0003635124972241055</v>
+        <v>-0.05034029733503809</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0.04642310812322203</v>
+        <v>-0.01840791899047567</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.006682299783677625</v>
+        <v>-0.002079347858436109</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.04727455442426398</v>
+        <v>-0.07855397015259091</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.006671171041279234</v>
+        <v>0.0208512146530857</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>-0.007480422962451216</v>
+        <v>-0.02065447553389088</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.2766312756209799</v>
+        <v>0.3820177786714296</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.08481369680110307</v>
+        <v>0.1138786419545248</v>
       </c>
     </row>
     <row r="34">
@@ -2390,37 +2390,37 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>128.05</v>
+        <v>128.37</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.007315924206120261</v>
+        <v>0.002498961794638488</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.02992421930486511</v>
+        <v>-0.01835290262951272</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.007595099874528555</v>
+        <v>-0.01602032415392729</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.07738303014564729</v>
+        <v>-0.07507744558689611</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.0728276668833634</v>
+        <v>-0.07051069864585902</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.1016418597809868</v>
+        <v>-0.1040733571264341</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.03872176192161148</v>
+        <v>-0.03236163356898814</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.02366695041935607</v>
+        <v>0.03496858626505639</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.5283845498821231</v>
+        <v>0.5225517702252149</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.151889659440539</v>
+        <v>0.1504224711751172</v>
       </c>
     </row>
   </sheetData>
@@ -2560,17 +2560,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.3831757651695116</v>
+        <v>0.4090294462528825</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.07738303014564729</v>
+        <v>-0.07507744558689611</v>
       </c>
     </row>
     <row r="18">
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.1803781676899621</v>
+        <v>0.1783341760624138</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.03910846901336862</v>
+        <v>-0.03985421402508871</v>
       </c>
     </row>
     <row r="19">
@@ -3130,7 +3130,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.1311130143499042</v>
+        <v>0.1365935862103516</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -3138,21 +3138,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.03607741520915686</v>
+        <v>-0.02929157331312682</v>
       </c>
     </row>
     <row r="20">
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.1238447495732262</v>
+        <v>0.1287738885727603</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.03508176652701966</v>
+        <v>-0.02875835534093474</v>
       </c>
     </row>
     <row r="21">
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.117589399141254</v>
+        <v>0.1190593005067511</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -3228,21 +3228,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.02780429111572269</v>
+        <v>-0.01984255647025024</v>
       </c>
     </row>
     <row r="22">
@@ -3251,21 +3251,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.08938538622920378</v>
+        <v>0.1090781271339805</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -3273,21 +3273,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.01518944254995491</v>
+        <v>-0.01840791899047567</v>
       </c>
     </row>
     <row r="23">
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.08717579453677926</v>
+        <v>0.09870316096998577</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -3318,21 +3318,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.01486821032860886</v>
+        <v>-0.01480134301915814</v>
       </c>
     </row>
     <row r="24">
@@ -3341,21 +3341,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.08550317729248436</v>
+        <v>0.08518924110306214</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -3363,21 +3363,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.01268103582744351</v>
+        <v>-0.01284072319580032</v>
       </c>
     </row>
     <row r="25">
@@ -3386,21 +3386,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.08024657180787687</v>
+        <v>0.08504027808692105</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -3408,21 +3408,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.01194492611066778</v>
+        <v>-0.009856941297549437</v>
       </c>
     </row>
     <row r="26">
@@ -3431,21 +3431,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.06643604352907584</v>
+        <v>0.0719278162413457</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.0007143020629882812</v>
+        <v>0.0007143020629882812</v>
       </c>
     </row>
     <row r="27"/>
@@ -3537,21 +3537,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.2593287744374284</v>
+        <v>0.267441862774572</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.1057356492117627</v>
+        <v>-0.09067400874461118</v>
       </c>
     </row>
     <row r="32">
@@ -3582,21 +3582,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.2441861119462061</v>
+        <v>0.2654305889835198</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -3618,7 +3618,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.0728276668833634</v>
+        <v>-0.07051069864585902</v>
       </c>
     </row>
     <row r="33">
@@ -3627,21 +3627,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>Biotechnology</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
       <c r="E33" s="11" t="n">
-        <v>0.2389162376437324</v>
+        <v>0.2577813698919151</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.04521962725872342</v>
+        <v>-0.03617567716423087</v>
       </c>
     </row>
     <row r="34">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.2310455322792886</v>
+        <v>0.2520525137852132</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -3708,7 +3708,7 @@
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.02609190932199801</v>
+        <v>-0.02363395754254161</v>
       </c>
     </row>
     <row r="35">
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.2135728606238909</v>
+        <v>0.2188955435997635</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -3739,21 +3739,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.02486403433500473</v>
+        <v>-0.01861666963243458</v>
       </c>
     </row>
     <row r="36">
@@ -3776,7 +3776,7 @@
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.1830912164718939</v>
+        <v>0.18464726862838</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -3784,21 +3784,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.02207796674801388</v>
+        <v>-0.01807758966334105</v>
       </c>
     </row>
     <row r="37">
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1530879716920395</v>
+        <v>0.1484887802599697</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -3829,21 +3829,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.008778595939665568</v>
+        <v>-0.01150283356271053</v>
       </c>
     </row>
     <row r="38">
@@ -3866,7 +3866,7 @@
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1472868704178349</v>
+        <v>0.145994851144249</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -3888,7 +3888,7 @@
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.006682299783677625</v>
+        <v>-0.006501726879106995</v>
       </c>
     </row>
     <row r="39">
@@ -3911,7 +3911,7 @@
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1458333609280764</v>
+        <v>0.143849188515869</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0.003742800762520648</v>
+        <v>-0.002079347858436109</v>
       </c>
     </row>
     <row r="40">
@@ -3942,21 +3942,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1335930777404544</v>
+        <v>0.1333128661354825</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -3978,7 +3978,7 @@
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>0.006474831299125405</v>
+        <v>0.007913713192115424</v>
       </c>
     </row>
     <row r="41"/>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.4171121010951535</v>
+        <v>0.4093042817247554</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1016418597809868</v>
+        <v>-0.1040733571264341</v>
       </c>
     </row>
     <row r="46">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.3636593742192153</v>
+        <v>0.3186685790323285</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -4129,7 +4129,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.09518130387776935</v>
+        <v>-0.07855397015259091</v>
       </c>
     </row>
     <row r="47">
@@ -4152,7 +4152,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.306914527760942</v>
+        <v>0.297718187952126</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -4174,7 +4174,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.04727455442426398</v>
+        <v>-0.04896706001373075</v>
       </c>
     </row>
     <row r="48">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.3049929610747049</v>
+        <v>0.2937838234858181</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.03795050036228309</v>
+        <v>-0.0235483242788227</v>
       </c>
     </row>
     <row r="49">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.2938761399847394</v>
+        <v>0.2810165770916062</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -4264,7 +4264,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.02226129294378287</v>
+        <v>-0.00889100347294558</v>
       </c>
     </row>
     <row r="50">
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.2253443938148396</v>
+        <v>0.2596371757639508</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -4295,21 +4295,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.01156502192508879</v>
+        <v>-0.007447842213938016</v>
       </c>
     </row>
     <row r="51">
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.1996937799681542</v>
+        <v>0.218867726635779</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -4340,21 +4340,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
       <c r="K51" s="11" t="n">
-        <v>-0.001732204774796298</v>
+        <v>-0.001839698875348517</v>
       </c>
     </row>
     <row r="52">
@@ -4363,21 +4363,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.1914764860204163</v>
+        <v>0.1786023025934405</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4385,21 +4385,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>0.0003168559683941474</v>
+        <v>0.007118407621416578</v>
       </c>
     </row>
     <row r="53">
@@ -4408,21 +4408,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.1819312688299251</v>
+        <v>0.1764234136468221</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.009196399590724269</v>
+        <v>0.01698305189937299</v>
       </c>
     </row>
     <row r="54">
@@ -4453,21 +4453,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.1790562027327856</v>
+        <v>0.1583366272783797</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -4489,7 +4489,7 @@
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.02233356346684845</v>
+        <v>0.02626004583204433</v>
       </c>
     </row>
     <row r="55"/>
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.9073378682442328</v>
+        <v>0.9449358776105117</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.09072780375264677</v>
+        <v>-0.07893412483669104</v>
       </c>
     </row>
     <row r="60">
@@ -4618,7 +4618,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.7816732194309011</v>
+        <v>0.807856084550592</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.05682570614179261</v>
+        <v>-0.04424682496057131</v>
       </c>
     </row>
     <row r="61">
@@ -4663,7 +4663,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.7432483011701951</v>
+        <v>0.7754199127831896</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4685,7 +4685,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.03783280043157777</v>
+        <v>-0.03583258251212917</v>
       </c>
     </row>
     <row r="62">
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.5917771700818479</v>
+        <v>0.6560339681432914</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.02550139541760876</v>
+        <v>-0.02065447553389088</v>
       </c>
     </row>
     <row r="63">
@@ -4739,21 +4739,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.5613310349437368</v>
+        <v>0.5580271200594566</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.007480422962451216</v>
+        <v>-0.005572241362974184</v>
       </c>
     </row>
     <row r="64">
@@ -4784,21 +4784,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.5103122338070285</v>
+        <v>0.5309346432478741</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4806,21 +4806,21 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>0.02178387108857849</v>
+        <v>0.0209208881055567</v>
       </c>
     </row>
     <row r="65">
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.4432606453138559</v>
+        <v>0.4595909915006999</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4851,21 +4851,21 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.02366695041935607</v>
+        <v>0.02853620116910349</v>
       </c>
     </row>
     <row r="66">
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.3610189769235936</v>
+        <v>0.3984438068723979</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4896,21 +4896,21 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>0.02492935886041714</v>
+        <v>0.03496858626505639</v>
       </c>
     </row>
     <row r="67">
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.2601464743803183</v>
+        <v>0.278208470133203</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4941,21 +4941,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.02775354403192631</v>
+        <v>0.03506389141886035</v>
       </c>
     </row>
     <row r="68">
@@ -4964,21 +4964,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.227278124280597</v>
+        <v>0.2498417746880897</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -5000,7 +5000,7 @@
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.05819058333802096</v>
+        <v>0.05631285190140844</v>
       </c>
     </row>
     <row r="69"/>
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.640696457329232</v>
+        <v>2.74538018853307</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.09509648794249226</v>
+        <v>0.09048469079874155</v>
       </c>
     </row>
     <row r="74">
@@ -5129,7 +5129,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.396131068485421</v>
+        <v>2.472598869524331</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.1003602414531355</v>
+        <v>0.09537862965732868</v>
       </c>
     </row>
     <row r="75">
@@ -5174,7 +5174,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.212270727354308</v>
+        <v>2.232448687681074</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.2041623117383993</v>
+        <v>0.1879635602557039</v>
       </c>
     </row>
     <row r="76">
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.456667302867464</v>
+        <v>1.475464432095607</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.2198085684098507</v>
+        <v>0.2141363333811206</v>
       </c>
     </row>
     <row r="77">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.201381378220015</v>
+        <v>1.207773111598756</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.2766312756209799</v>
+        <v>0.2614885408738008</v>
       </c>
     </row>
     <row r="78">
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.164311347055526</v>
+        <v>1.162263911764885</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.2908704616694808</v>
+        <v>0.2811188426902231</v>
       </c>
     </row>
     <row r="79">
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.065610125832187</v>
+        <v>1.097555304097171</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.2994641719114173</v>
+        <v>0.2961107892144479</v>
       </c>
     </row>
     <row r="80">
@@ -5399,7 +5399,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.005313846787673</v>
+        <v>1.004975971638061</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5421,7 +5421,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.3202778024031709</v>
+        <v>0.3055173734094689</v>
       </c>
     </row>
     <row r="81">
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8472890016003212</v>
+        <v>0.8684255421908049</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5466,7 +5466,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.3750645605370346</v>
+        <v>0.3516069593541307</v>
       </c>
     </row>
     <row r="82">
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.8118294353768711</v>
+        <v>0.8275353654026762</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.3903660413121772</v>
+        <v>0.3820177786714296</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -489,15 +489,15 @@
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>212.45</v>
+        <v>215.53</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.01238975825163435</v>
+        <v>0.0144975376573202</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>-0.0240709515108507</v>
+        <v>0.01325744899826486</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.009407496156484507</v>
+        <v>-0.01219122614393708</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.03101038273006584</v>
+        <v>0.04595749457878306</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.02232808548270238</v>
+        <v>-4.636961653181615e-05</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.4093042817247554</v>
+        <v>0.4344687271531873</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7066633995642733</v>
+        <v>0.7130740597540737</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.9449358776105117</v>
+        <v>0.96915798022432</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.232448687681074</v>
+        <v>2.279311234256085</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4785767739564453</v>
+        <v>0.4856877607575287</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>31.52</v>
+        <v>31.4</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.02171799248003858</v>
+        <v>-0.003807133169118959</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.04717608167101983</v>
+        <v>-0.01008826298080956</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.07210887301839297</v>
+        <v>0.05902192318769228</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.1090781271339805</v>
+        <v>0.1048557190090242</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.2577813698919151</v>
+        <v>0.2465263577933059</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.2596371757639508</v>
+        <v>0.2655168506573173</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.3081765039009654</v>
+        <v>0.294619086856567</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.6560339681432914</v>
+        <v>0.6296301759054801</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1.097555304097171</v>
+        <v>1.089569366500112</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2800820471693408</v>
+        <v>0.2784554462286124</v>
       </c>
     </row>
     <row r="4">
@@ -704,51 +704,51 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>73.03</v>
+        <v>59.79</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.01869153706593663</v>
+        <v>0.000334623684298041</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.1807599123846972</v>
+        <v>-0.01466709599822669</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.171854928384445</v>
+        <v>-0.06651056882523532</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.4090294462528825</v>
+        <v>-0.01951457257530409</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.267441862774572</v>
+        <v>-0.1249817164741547</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>-0.0235483242788227</v>
+        <v>0.3428795023282099</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.4132501856958326</v>
+        <v>0.5492332804652131</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.7754199127831896</v>
+        <v>0.7905037531420884</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>2.74538018853307</v>
+        <v>2.473760498404808</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.552977998434343</v>
+        <v>0.5144907463451043</v>
       </c>
     </row>
     <row r="5">
@@ -760,51 +760,51 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>59.77</v>
+        <v>90.63</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.0168424923277728</v>
+        <v>0.004210495882747578</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.03550106050674839</v>
+        <v>-0.01638812835069448</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>-0.04444442547090777</v>
+        <v>0.01762856206897268</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-0.01984255647025024</v>
+        <v>0.04859420263117453</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>-0.09067400874461118</v>
+        <v>0.09219081208732161</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.2937838234858181</v>
+        <v>0.1763300593173001</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.5852734915624098</v>
+        <v>0.4782395901814684</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.807856084550592</v>
+        <v>0.5376362527878347</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>2.472598869524331</v>
+        <v>0.6522332794043031</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.514321911799311</v>
+        <v>0.182198639366733</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>90.25</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-0.01570511945755992</v>
+        <v>-0.02834451224735657</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>-0.02421881193108977</v>
+        <v>0.05847252558788951</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.01621441820732161</v>
+        <v>0.1299363048813</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.04419761288136259</v>
+        <v>0.3690911938566817</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.06351637227057649</v>
+        <v>0.1826666514078776</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.1764234136468221</v>
+        <v>-0.07299455878713568</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.4816362186515539</v>
+        <v>0.3137203789912799</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.5309346432478741</v>
+        <v>0.6905633030447835</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.6453058408384611</v>
+        <v>2.639219213908187</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.1805440947761381</v>
+        <v>0.5381643408579555</v>
       </c>
     </row>
     <row r="7">
@@ -886,37 +886,37 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>30.5</v>
+        <v>30.29</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.01060303815733699</v>
+        <v>-0.006885215884349427</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.05027544898223502</v>
+        <v>-0.009807101522200101</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.06050068697046784</v>
+        <v>0.04918600744771062</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.09870316096998577</v>
+        <v>0.09113835251389024</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.2520525137852132</v>
+        <v>0.2454770269579263</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.218867726635779</v>
+        <v>0.2113352603514933</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.1714525372535143</v>
+        <v>0.1626467641046663</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.3984438068723979</v>
+        <v>0.3736795987090735</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.5195482820158541</v>
+        <v>0.5090858640474829</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1496655062498655</v>
+        <v>0.1470208622140876</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>36.81</v>
+        <v>53.55</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.01488836252307668</v>
+        <v>0.005067576275331831</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.05775868334186351</v>
+        <v>-0.01071497911712271</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.07443091584026962</v>
+        <v>-0.03426513074367332</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.0719278162413457</v>
+        <v>0.01941748489371142</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.1333128661354825</v>
+        <v>-0.0261866229760479</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.1300405089861418</v>
+        <v>0.325835120672171</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.1985933653384</v>
+        <v>0.3577243737922202</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.5580271200594566</v>
+        <v>0.459388774219599</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.7816244106846273</v>
+        <v>1.488009036922122</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.2122868236264366</v>
+        <v>0.3550354310388013</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>53.28</v>
+        <v>36.08</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.01081388170602593</v>
+        <v>-0.01983155433311146</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.02274397777064252</v>
+        <v>-0.0264435916330702</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-0.02489020178520018</v>
+        <v>0.05497079023905993</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.01427755601425207</v>
+        <v>0.05066982151238197</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>-0.01150283356271053</v>
+        <v>0.1115219608343634</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.297718187952126</v>
+        <v>0.1282418076478455</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.3645848303886592</v>
+        <v>0.1726505407766443</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.4595909915006999</v>
+        <v>0.4994394633496699</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>1.475464432095607</v>
+        <v>0.7462920293829374</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.3527542183888797</v>
+        <v>0.2042194124706305</v>
       </c>
     </row>
     <row r="10">
@@ -1057,34 +1057,34 @@
         <v>17.74</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.001126151886594373</v>
+        <v>0</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.002249770190244638</v>
+        <v>0.007954510603070064</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.004530007044013518</v>
+        <v>-0.003930359175926879</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>0.04107974283927196</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.145994851144249</v>
+        <v>0.1408359841492584</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.1578233411311052</v>
+        <v>0.144574283375775</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.1870214269893371</v>
+        <v>0.182581164373786</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.1701790986789031</v>
+        <v>0.162291827833676</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.004975971638061</v>
+        <v>1.004975755533081</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2609650731030881</v>
+        <v>0.2609650277989972</v>
       </c>
     </row>
     <row r="11">
@@ -1110,37 +1110,37 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>45.68</v>
+        <v>45.6</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.001315242759663438</v>
+        <v>-0.001751353557798097</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.02444494615065906</v>
+        <v>0.01740291799660465</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.01896048269916162</v>
+        <v>0.02265078084944983</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.1190593005067511</v>
+        <v>0.1170994320194214</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.18464726862838</v>
+        <v>0.1871908007100243</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.2810165770916062</v>
+        <v>0.2522568616198702</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.08178481144507299</v>
+        <v>0.083120869920563</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.03506389141886035</v>
+        <v>0.03168092282445834</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.3055173734094689</v>
+        <v>0.3032308088311368</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.09293470953445437</v>
+        <v>0.09229625863570545</v>
       </c>
     </row>
     <row r="12">
@@ -1152,12 +1152,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1166,37 +1166,37 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>53.92</v>
+        <v>116.9</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.004845291134411678</v>
+        <v>0.008802246260243507</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.05518590565618853</v>
+        <v>0.02158525923373089</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.03732202085020497</v>
+        <v>0.003347346858619371</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.1365935862103516</v>
+        <v>-0.03140277437120242</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.2654305889835198</v>
+        <v>0.1082669492368256</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.1243687617947005</v>
+        <v>0.1653873429474912</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>-0.009430964685356313</v>
+        <v>0.1112493354907069</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.08269192426244754</v>
+        <v>0.2346048834453804</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.2141363333811206</v>
+        <v>0.1000834845719392</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.06681509437654221</v>
+        <v>0.03230622978468634</v>
       </c>
     </row>
     <row r="13">
@@ -1208,51 +1208,51 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>37.94</v>
+        <v>53.84</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.002890949081660543</v>
+        <v>-0.001483642786981654</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.03583227197173611</v>
+        <v>0.009752446750560528</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-0.0321429110129432</v>
+        <v>0.03598227608160642</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-0.01480134301915814</v>
+        <v>0.1349072873344408</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.09907294680166046</v>
+        <v>0.2644433498666738</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.09754825265052713</v>
+        <v>0.1056230299442984</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.1976934713000433</v>
+        <v>-0.005745876233973823</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.227697401185303</v>
+        <v>0.07767301422615458</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>1.207773111598756</v>
+        <v>0.2123349887676873</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.30212141036726</v>
+        <v>0.06628724240254846</v>
       </c>
     </row>
     <row r="14">
@@ -1264,51 +1264,51 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>122.55</v>
+        <v>38.06</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.005414748260023527</v>
+        <v>0.003162961279011611</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.008227066844039399</v>
+        <v>-0.007561854299049653</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.008093888913795366</v>
+        <v>-0.03791708665138538</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-0.009856941297549437</v>
+        <v>-0.01168519781499366</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.06713694670611314</v>
+        <v>0.08929601800834153</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.08449272611796688</v>
+        <v>0.09114240319026679</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.2521894973662733</v>
+        <v>0.2028649962246207</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.2498417746880897</v>
+        <v>0.217230671179329</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.5066342419951397</v>
+        <v>1.214755966645919</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.1463993853575347</v>
+        <v>0.3034927704534198</v>
       </c>
     </row>
     <row r="15">
@@ -1334,37 +1334,37 @@
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>23.06</v>
+        <v>23.21</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.001731641336224055</v>
+        <v>0.006504753772948346</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.006462715400562979</v>
+        <v>0</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-0.03312372758455528</v>
+        <v>-0.01610856573366948</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.1783341760624138</v>
+        <v>0.1859989497399495</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.143849188515869</v>
+        <v>0.14957892375093</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.3186685790323285</v>
+        <v>0.2961281752745029</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.03682176209979615</v>
+        <v>0.04242095915868416</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.02853620116910349</v>
+        <v>0.04089806845687405</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.3516069593541307</v>
+        <v>0.3603986777371726</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.1056478008111097</v>
+        <v>0.1080399024609924</v>
       </c>
     </row>
     <row r="16">
@@ -1376,51 +1376,51 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>14.92</v>
+        <v>98.59</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.00947228321056337</v>
+        <v>0.003256331594133632</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.01289888255005134</v>
+        <v>0.01954497879312278</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.01704158137013168</v>
+        <v>0.0159727474004514</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.03972123203287614</v>
+        <v>0.01304969838726744</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>-0.03617567716423087</v>
+        <v>0.1375331535799704</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.1786023025934405</v>
+        <v>0.1145910439666313</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.2864683114313695</v>
+        <v>0.137082524968956</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.278208470133203</v>
+        <v>0.116788626486299</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.8684255421908049</v>
+        <v>0.6191276356628654</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.2316631042724611</v>
+        <v>0.1742494402444239</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>115.88</v>
+        <v>14.96</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.0007760969762677927</v>
+        <v>0.002680962576976365</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.006864201413370408</v>
+        <v>0.00133871876341507</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.00172888094497381</v>
+        <v>0.01492539148201888</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.03985421402508871</v>
+        <v>0.04250868574644384</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.08248476366124824</v>
+        <v>-0.05734088556863592</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.1583366272783797</v>
+        <v>0.191023531653806</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.1041575190420831</v>
+        <v>0.2795814194369781</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.220506055311535</v>
+        <v>0.2806075358029254</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.09048469079874155</v>
+        <v>0.8734351686294406</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.02929498705045819</v>
+        <v>0.2327629011546037</v>
       </c>
     </row>
     <row r="18">
@@ -1488,51 +1488,51 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>98.27</v>
+        <v>122.56</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.006771839314807293</v>
+        <v>8.155452131419771e-05</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.01781453689221069</v>
+        <v>0.007314863179439079</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.006761561608317868</v>
+        <v>-0.006485109012642765</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.009761579852252122</v>
+        <v>-0.009776190654364414</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.1259165675696183</v>
+        <v>0.04582297982178507</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.1274841105074824</v>
+        <v>0.0620714970091234</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.1365210175888198</v>
+        <v>0.2338653446188526</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.1135250582030158</v>
+        <v>0.2426047339263639</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.6138726355170774</v>
+        <v>0.5067569735016786</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.1729776918639085</v>
+        <v>0.1464305133511825</v>
       </c>
     </row>
     <row r="19">
@@ -1558,37 +1558,37 @@
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>105.3</v>
+        <v>105.08</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.004579310802624414</v>
+        <v>-0.002089280288007145</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.04661566855137966</v>
+        <v>0.02597152616349008</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.02262796740247319</v>
+        <v>0.03070137299171805</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.07131958562351648</v>
+        <v>0.06908129873111735</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.04932740062684959</v>
+        <v>0.02888480032283547</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.007118407621416578</v>
+        <v>0.00426905891852547</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.2413969207660533</v>
+        <v>0.2215347349110854</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1897386448897176</v>
+        <v>0.1811565467567657</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.2961107892144479</v>
+        <v>0.293402850491469</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.09030342230834809</v>
+        <v>0.08954357640265309</v>
       </c>
     </row>
     <row r="20">
@@ -1614,37 +1614,37 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>28.5</v>
+        <v>28.74</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.00600070867461211</v>
+        <v>0.008421044600637417</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.06801831029743099</v>
+        <v>-0.03589398570928126</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.06771343524660511</v>
+        <v>-0.05832243315686814</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.02929157331312682</v>
+        <v>-0.02111719435778225</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.05438399097343583</v>
+        <v>0.04319421295869996</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>-0.00889100347294558</v>
+        <v>-0.005716194037690303</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.1846463033278647</v>
+        <v>0.1849843474395774</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.2072297041270006</v>
+        <v>0.18930203817044</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>1.162263911764885</v>
+        <v>1.180472432604205</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.2931122720749304</v>
+        <v>0.2967319159868651</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>18.32</v>
+        <v>96</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.004385960784535126</v>
+        <v>-0.003115296388895961</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.03037114664367269</v>
+        <v>0.001878525420048627</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.03854877146848557</v>
+        <v>0.01824354309475051</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.1287738885727603</v>
+        <v>0.04792052571116767</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.2188955435997635</v>
+        <v>0.06536508842854549</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.1543793211677662</v>
+        <v>0.02198256582850733</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>-0.02397446733962771</v>
+        <v>0.1497316938920066</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>-0.07893412483669104</v>
+        <v>0.1414058739045652</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.2811188426902231</v>
+        <v>0.1842625902073609</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.08608330933169062</v>
+        <v>0.05799269765036508</v>
       </c>
     </row>
     <row r="22">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>17.48</v>
+        <v>18.18</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.003988586773063796</v>
+        <v>-0.007641888208545722</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.01509873630948411</v>
+        <v>0.01677858828245693</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.01040464237652561</v>
+        <v>0.03061229785780095</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.08504027808692105</v>
+        <v>0.1201479247035617</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.1484887802599697</v>
+        <v>0.2120000203450521</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.09527255448036076</v>
+        <v>0.1277915234922746</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.0840535473992805</v>
+        <v>-0.03091683990563709</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>-0.03583258251212917</v>
+        <v>-0.09009005396899405</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.3866441887740508</v>
+        <v>0.2713286757125231</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.1151201888777345</v>
+        <v>0.08330965622664421</v>
       </c>
     </row>
     <row r="23">
@@ -1768,51 +1768,51 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>96.3</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.009870440709306205</v>
+        <v>0.0008640056245503569</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.01775523416201197</v>
+        <v>0.003899541894732295</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.02457713842420173</v>
+        <v>0.01980631457729176</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.05119531066651151</v>
+        <v>0.04699507117435675</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.05713153154179307</v>
+        <v>-0.03305191399325724</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.02626004583204433</v>
+        <v>0.08702840714293947</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1677735268188345</v>
+        <v>0.208602436674765</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.1285714260168176</v>
+        <v>0.1700618863704415</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.1879635602557039</v>
+        <v>0.8291145498466923</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.05909367178418634</v>
+        <v>0.2229638923145449</v>
       </c>
     </row>
     <row r="24">
@@ -1838,37 +1838,37 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>43.82</v>
+        <v>43.56</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.002058087206265879</v>
+        <v>-0.005933325498491793</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.01458673508096942</v>
+        <v>0</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.02791458120790513</v>
+        <v>0.01161170422790869</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.01284072319580032</v>
+        <v>-0.0186978605039354</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.03419618158184301</v>
+        <v>0.02420953336145515</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.07041320373367776</v>
+        <v>0.056865488123792</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.1494106233092267</v>
+        <v>0.1378924393533052</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.145301543280407</v>
+        <v>0.1442227587338851</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.3946245434931543</v>
+        <v>0.3863497821284241</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1172553285890447</v>
+        <v>0.1150412640331273</v>
       </c>
     </row>
     <row r="25">
@@ -1880,51 +1880,51 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>69.45</v>
+        <v>17.38</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.006959485559570711</v>
+        <v>-0.005720845771654548</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.007543836366809886</v>
+        <v>0.004043887751813191</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.01937472109259475</v>
+        <v>-0.004011552957723707</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.04609124245708096</v>
+        <v>0.07883292999995262</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>-0.01807758966334105</v>
+        <v>0.1329855924306858</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.07223976840530355</v>
+        <v>0.06621350094216782</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.2125089843106895</v>
+        <v>0.07332770134571676</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.1671498404632161</v>
+        <v>-0.04537447218428881</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.8275353654026762</v>
+        <v>0.3787115155329877</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.2226118382529212</v>
+        <v>0.1129896720526129</v>
       </c>
     </row>
     <row r="26">
@@ -1950,37 +1950,37 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>186.62</v>
+        <v>186.11</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.004575501023727835</v>
+        <v>-0.002732796700137596</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.02538458855597536</v>
+        <v>0.01671673044293009</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.02951393346184927</v>
+        <v>0.02190866242115064</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.08518924110306214</v>
+        <v>0.08222363952595102</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.1228640104927587</v>
+        <v>0.1220909196037721</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.1214079004047779</v>
+        <v>0.1074639767228271</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.03999078234035869</v>
+        <v>0.02336241231145531</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>-0.04424682496057131</v>
+        <v>-0.05345333520414275</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.6923284160957286</v>
+        <v>0.6877036265846732</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1916852088514884</v>
+        <v>0.1905986740212129</v>
       </c>
     </row>
     <row r="27">
@@ -2006,37 +2006,37 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>14.01</v>
+        <v>14.04</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.00142962531028501</v>
+        <v>0.002141308528271546</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.01374822997490921</v>
+        <v>0.007173628728830872</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.01268494410319088</v>
+        <v>0.0007127747022215303</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.0007143020629882812</v>
+        <v>0.002857140132359159</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.007913713192115424</v>
+        <v>0.002857140132359159</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>-0.001839698875348517</v>
+        <v>0.003809934863525655</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.1992781089569904</v>
+        <v>0.1978665097935834</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.08566219108284212</v>
+        <v>0.08553834587541709</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.09537862965732868</v>
+        <v>0.0977241732587002</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.03083246542699225</v>
+        <v>0.0315677176589706</v>
       </c>
     </row>
     <row r="28">
@@ -2062,37 +2062,37 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>51.64</v>
+        <v>52.06</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.002523802608257686</v>
+        <v>0.008133268563259799</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.01205282308394662</v>
+        <v>-0.003826960479632824</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.03512707496329104</v>
+        <v>-0.02855007977123492</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.009777082635265</v>
+        <v>0.0179898708373627</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>-0.02363395754254161</v>
+        <v>-0.03072049412226951</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.02644119274826306</v>
+        <v>0.03988699876178692</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.1303345476024413</v>
+        <v>0.1257227644711476</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.1793031586358671</v>
+        <v>0.1780528624580626</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.7403962276267566</v>
+        <v>0.7545514503392825</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.2028626626741645</v>
+        <v>0.2061149555627713</v>
       </c>
     </row>
     <row r="29">
@@ -2118,37 +2118,37 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>17.75</v>
+        <v>17.7</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.01059088787076212</v>
+        <v>-0.002816858425946256</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.001687327642683423</v>
+        <v>-0.01775802922837055</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.02952437881339354</v>
+        <v>-0.02263941654302082</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.03983598812728539</v>
+        <v>0.03690691736252671</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.008522705413586351</v>
+        <v>0.00739903644696871</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.02888152659150234</v>
+        <v>0.02431324726431949</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.08092808627621162</v>
+        <v>0.06600284285865587</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.05631285190140844</v>
+        <v>0.05281621790449376</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.4930254522801132</v>
+        <v>0.4888198109547057</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1429372935841626</v>
+        <v>0.1418631201718585</v>
       </c>
     </row>
     <row r="30">
@@ -2174,25 +2174,25 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>71.26000000000001</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-0.0009813499653344993</v>
+        <v>0.01248946622183644</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.04065692908853591</v>
+        <v>-0.01649398956387027</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.05540827372616219</v>
+        <v>-0.04272258330054457</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.02875835534093474</v>
+        <v>-0.01662806562672448</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.04379677223065648</v>
+        <v>0.03574501482726644</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.01698305189937299</v>
+        <v>0.02558639787916928</v>
       </c>
       <c r="M30" s="6" t="inlineStr"/>
       <c r="N30" s="6" t="inlineStr"/>
@@ -2222,37 +2222,37 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>64.84</v>
+        <v>64.48</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.009925203039875208</v>
+        <v>-0.005552020377685651</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.0006171803124896957</v>
+        <v>-0.02406532988095622</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.02905065104624849</v>
+        <v>-0.02125066719567514</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.04513209834048371</v>
+        <v>0.03932950363312404</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.01861666963243458</v>
+        <v>-0.03095878464457669</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>-0.007447842213938016</v>
+        <v>-0.01123039854273433</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.009710375792921333</v>
+        <v>-0.00415504762344665</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.0209208881055567</v>
+        <v>0.01175834418532928</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.474864829781666</v>
+        <v>0.4666762229289729</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1382842842527929</v>
+        <v>0.1361737481923084</v>
       </c>
     </row>
     <row r="32">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2278,37 +2278,37 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>55.01</v>
+        <v>120.15</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.0001817876642400407</v>
+        <v>0.001416887516160426</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.01926991064123107</v>
+        <v>-0.02594241579105938</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.002357654507693763</v>
+        <v>-0.03524971380581632</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.04661333493585462</v>
+        <v>-0.0170171134249314</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.006501726879106995</v>
+        <v>-0.01435602935270253</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>-0.04896706001373075</v>
+        <v>-0.08018073857715302</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>-0.01058191655854601</v>
+        <v>0.009678702245299764</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.005572241362974184</v>
+        <v>-0.02227267218673468</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.2614885408738008</v>
+        <v>0.3839756991588914</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.08050746067392378</v>
+        <v>0.1144044086418896</v>
       </c>
     </row>
     <row r="33">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -2334,37 +2334,37 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>119.98</v>
+        <v>54.58</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.005800438734438473</v>
+        <v>-0.007816697029605191</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.0208911175083023</v>
+        <v>-0.008537646003988542</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.05034029733503809</v>
+        <v>-0.00128087269661048</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.01840791899047567</v>
+        <v>0.03843227558951634</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.002079347858436109</v>
+        <v>-0.01568979116166647</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.07855397015259091</v>
+        <v>-0.05532212316448881</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.0208512146530857</v>
+        <v>-0.02308359336059917</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>-0.02065447553389088</v>
+        <v>-0.02400102266988735</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.3820177786714296</v>
+        <v>0.2516277576528447</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1138786419545248</v>
+        <v>0.07768472853861752</v>
       </c>
     </row>
     <row r="34">
@@ -2390,37 +2390,37 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>128.37</v>
+        <v>129.05</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.002498961794638488</v>
+        <v>0.005297249828120298</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.01835290262951272</v>
+        <v>-0.01413285661563535</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.01602032415392729</v>
+        <v>-0.01638714898242366</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.07507744558689611</v>
+        <v>-0.07017789974450683</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.07051069864585902</v>
+        <v>-0.06861028197777375</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.1040733571264341</v>
+        <v>-0.09443966304596185</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.03236163356898814</v>
+        <v>-0.04227906080302324</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.03496858626505639</v>
+        <v>0.03544397944763755</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.5225517702252149</v>
+        <v>0.5306172458332707</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1504224711751172</v>
+        <v>0.1524502879969964</v>
       </c>
     </row>
   </sheetData>
@@ -2582,12 +2582,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2650,17 +2650,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -2695,17 +2695,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -2785,17 +2785,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -2830,17 +2830,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2942,17 +2942,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.4090294462528825</v>
+        <v>0.3690911938566817</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.07507744558689611</v>
+        <v>-0.07017789974450683</v>
       </c>
     </row>
     <row r="18">
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.1783341760624138</v>
+        <v>0.1859989497399495</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.03985421402508871</v>
+        <v>-0.03140277437120242</v>
       </c>
     </row>
     <row r="19">
@@ -3130,7 +3130,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.1365935862103516</v>
+        <v>0.1349072873344408</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -3152,7 +3152,7 @@
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.02929157331312682</v>
+        <v>-0.02111719435778225</v>
       </c>
     </row>
     <row r="20">
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.1287738885727603</v>
+        <v>0.1201479247035617</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -3183,21 +3183,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.02875835534093474</v>
+        <v>-0.01951457257530409</v>
       </c>
     </row>
     <row r="21">
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.1190593005067511</v>
+        <v>0.1170994320194214</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -3228,21 +3228,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.01984255647025024</v>
+        <v>-0.0186978605039354</v>
       </c>
     </row>
     <row r="22">
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.1090781271339805</v>
+        <v>0.1048557190090242</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.01840791899047567</v>
+        <v>-0.0170171134249314</v>
       </c>
     </row>
     <row r="23">
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.09870316096998577</v>
+        <v>0.09113835251389024</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -3318,21 +3318,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.01480134301915814</v>
+        <v>-0.01662806562672448</v>
       </c>
     </row>
     <row r="24">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.08518924110306214</v>
+        <v>0.08222363952595102</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -3363,21 +3363,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.01284072319580032</v>
+        <v>-0.01168519781499366</v>
       </c>
     </row>
     <row r="25">
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.08504027808692105</v>
+        <v>0.07883292999995262</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -3422,7 +3422,7 @@
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.009856941297549437</v>
+        <v>-0.009776190654364414</v>
       </c>
     </row>
     <row r="26">
@@ -3431,21 +3431,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.0719278162413457</v>
+        <v>0.06908129873111735</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>0.0007143020629882812</v>
+        <v>0.002857140132359159</v>
       </c>
     </row>
     <row r="27"/>
@@ -3537,21 +3537,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.267441862774572</v>
+        <v>0.2644433498666738</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.09067400874461118</v>
+        <v>-0.1249817164741547</v>
       </c>
     </row>
     <row r="32">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3596,7 +3596,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.2654305889835198</v>
+        <v>0.2465263577933059</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -3618,7 +3618,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.07051069864585902</v>
+        <v>-0.06861028197777375</v>
       </c>
     </row>
     <row r="33">
@@ -3627,12 +3627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3641,7 +3641,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.2577813698919151</v>
+        <v>0.2454770269579263</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.03617567716423087</v>
+        <v>-0.05734088556863592</v>
       </c>
     </row>
     <row r="34">
@@ -3672,21 +3672,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.2520525137852132</v>
+        <v>0.2120000203450521</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -3694,21 +3694,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.02363395754254161</v>
+        <v>-0.03305191399325724</v>
       </c>
     </row>
     <row r="35">
@@ -3717,21 +3717,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.2188955435997635</v>
+        <v>0.1871908007100243</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.01861666963243458</v>
+        <v>-0.03095878464457669</v>
       </c>
     </row>
     <row r="36">
@@ -3762,21 +3762,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.18464726862838</v>
+        <v>0.1826666514078776</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -3784,21 +3784,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.01807758966334105</v>
+        <v>-0.03072049412226951</v>
       </c>
     </row>
     <row r="37">
@@ -3807,21 +3807,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1484887802599697</v>
+        <v>0.14957892375093</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.01150283356271053</v>
+        <v>-0.0261866229760479</v>
       </c>
     </row>
     <row r="38">
@@ -3866,7 +3866,7 @@
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.145994851144249</v>
+        <v>0.1408359841492584</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -3888,7 +3888,7 @@
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.006501726879106995</v>
+        <v>-0.01568979116166647</v>
       </c>
     </row>
     <row r="39">
@@ -3897,21 +3897,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.143849188515869</v>
+        <v>0.1375331535799704</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.002079347858436109</v>
+        <v>-0.01435602935270253</v>
       </c>
     </row>
     <row r="40">
@@ -3942,21 +3942,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1333128661354825</v>
+        <v>0.1329855924306858</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -3964,21 +3964,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FDCPX</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>0.007913713192115424</v>
+        <v>-4.636961653181615e-05</v>
       </c>
     </row>
     <row r="41"/>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.4093042817247554</v>
+        <v>0.4344687271531873</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1040733571264341</v>
+        <v>-0.09443966304596185</v>
       </c>
     </row>
     <row r="46">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.3186685790323285</v>
+        <v>0.3428795023282099</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -4129,7 +4129,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.07855397015259091</v>
+        <v>-0.08018073857715302</v>
       </c>
     </row>
     <row r="47">
@@ -4152,7 +4152,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.297718187952126</v>
+        <v>0.325835120672171</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -4160,21 +4160,21 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.04896706001373075</v>
+        <v>-0.07299455878713568</v>
       </c>
     </row>
     <row r="48">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.2937838234858181</v>
+        <v>0.2961281752745029</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -4205,21 +4205,21 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.0235483242788227</v>
+        <v>-0.05532212316448881</v>
       </c>
     </row>
     <row r="49">
@@ -4228,21 +4228,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.2810165770916062</v>
+        <v>0.2655168506573173</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -4250,21 +4250,21 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.00889100347294558</v>
+        <v>-0.01123039854273433</v>
       </c>
     </row>
     <row r="50">
@@ -4273,21 +4273,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.2596371757639508</v>
+        <v>0.2522568616198702</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -4295,21 +4295,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.007447842213938016</v>
+        <v>-0.005716194037690303</v>
       </c>
     </row>
     <row r="51">
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.218867726635779</v>
+        <v>0.2113352603514933</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -4354,7 +4354,7 @@
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.001839698875348517</v>
+        <v>0.003809934863525655</v>
       </c>
     </row>
     <row r="52">
@@ -4377,7 +4377,7 @@
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.1786023025934405</v>
+        <v>0.191023531653806</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>0.007118407621416578</v>
+        <v>0.00426905891852547</v>
       </c>
     </row>
     <row r="53">
@@ -4422,7 +4422,7 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.1764234136468221</v>
+        <v>0.1763300593173001</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -4430,21 +4430,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.01698305189937299</v>
+        <v>0.02198256582850733</v>
       </c>
     </row>
     <row r="54">
@@ -4467,7 +4467,7 @@
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.1583366272783797</v>
+        <v>0.1653873429474912</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -4475,21 +4475,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.02626004583204433</v>
+        <v>0.02431324726431949</v>
       </c>
     </row>
     <row r="55"/>
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.9449358776105117</v>
+        <v>0.96915798022432</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.07893412483669104</v>
+        <v>-0.09009005396899405</v>
       </c>
     </row>
     <row r="60">
@@ -4618,7 +4618,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.807856084550592</v>
+        <v>0.7905037531420884</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.04424682496057131</v>
+        <v>-0.05345333520414275</v>
       </c>
     </row>
     <row r="61">
@@ -4663,7 +4663,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.7754199127831896</v>
+        <v>0.6905633030447835</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4685,7 +4685,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.03583258251212917</v>
+        <v>-0.04537447218428881</v>
       </c>
     </row>
     <row r="62">
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.6560339681432914</v>
+        <v>0.6296301759054801</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4716,12 +4716,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.02065447553389088</v>
+        <v>-0.02400102266988735</v>
       </c>
     </row>
     <row r="63">
@@ -4739,21 +4739,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.5580271200594566</v>
+        <v>0.5376362527878347</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.005572241362974184</v>
+        <v>-0.02227267218673468</v>
       </c>
     </row>
     <row r="64">
@@ -4784,21 +4784,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.5309346432478741</v>
+        <v>0.4994394633496699</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4820,7 +4820,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>0.0209208881055567</v>
+        <v>0.01175834418532928</v>
       </c>
     </row>
     <row r="65">
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.4595909915006999</v>
+        <v>0.459388774219599</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4851,12 +4851,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4865,7 +4865,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.02853620116910349</v>
+        <v>0.03168092282445834</v>
       </c>
     </row>
     <row r="66">
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.3984438068723979</v>
+        <v>0.3736795987090735</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>0.03496858626505639</v>
+        <v>0.03544397944763755</v>
       </c>
     </row>
     <row r="67">
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.278208470133203</v>
+        <v>0.2806075358029254</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4941,12 +4941,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4955,7 +4955,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.03506389141886035</v>
+        <v>0.04089806845687405</v>
       </c>
     </row>
     <row r="68">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.2498417746880897</v>
+        <v>0.2426047339263639</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -5000,7 +5000,7 @@
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.05631285190140844</v>
+        <v>0.05281621790449376</v>
       </c>
     </row>
     <row r="69"/>
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.74538018853307</v>
+        <v>2.639219213908187</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5092,21 +5092,21 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.09048469079874155</v>
+        <v>0.0977241732587002</v>
       </c>
     </row>
     <row r="74">
@@ -5129,7 +5129,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.472598869524331</v>
+        <v>2.473760498404808</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5137,21 +5137,21 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.09537862965732868</v>
+        <v>0.1000834845719392</v>
       </c>
     </row>
     <row r="75">
@@ -5174,7 +5174,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.232448687681074</v>
+        <v>2.279311234256085</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1879635602557039</v>
+        <v>0.1842625902073609</v>
       </c>
     </row>
     <row r="76">
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.475464432095607</v>
+        <v>1.488009036922122</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.2141363333811206</v>
+        <v>0.2123349887676873</v>
       </c>
     </row>
     <row r="77">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.207773111598756</v>
+        <v>1.214755966645919</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.2614885408738008</v>
+        <v>0.2516277576528447</v>
       </c>
     </row>
     <row r="78">
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.162263911764885</v>
+        <v>1.180472432604205</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.2811188426902231</v>
+        <v>0.2713286757125231</v>
       </c>
     </row>
     <row r="79">
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.097555304097171</v>
+        <v>1.089569366500112</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.2961107892144479</v>
+        <v>0.293402850491469</v>
       </c>
     </row>
     <row r="80">
@@ -5399,7 +5399,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.004975971638061</v>
+        <v>1.004975755533081</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5421,7 +5421,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.3055173734094689</v>
+        <v>0.3032308088311368</v>
       </c>
     </row>
     <row r="81">
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8684255421908049</v>
+        <v>0.8734351686294406</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5466,7 +5466,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.3516069593541307</v>
+        <v>0.3603986777371726</v>
       </c>
     </row>
     <row r="82">
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.8275353654026762</v>
+        <v>0.8291145498466923</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.3820177786714296</v>
+        <v>0.3787115155329877</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -489,15 +489,15 @@
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>215.53</v>
+        <v>216.76</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.0144975376573202</v>
+        <v>0.005706842363037312</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.01325744899826486</v>
+        <v>0.01717498028386921</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>-0.01219122614393708</v>
+        <v>-0.01696147615947419</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.04595749457878306</v>
+        <v>0.06536905216794264</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>-4.636961653181615e-05</v>
+        <v>0.0099711091153456</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.4344687271531873</v>
+        <v>0.4267036834460756</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7130740597540737</v>
+        <v>0.7228503033692986</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.96915798022432</v>
+        <v>0.9736036996916693</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.279311234256085</v>
+        <v>2.298025363687851</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4856877607575287</v>
+        <v>0.4885085392085013</v>
       </c>
     </row>
     <row r="3">
@@ -648,51 +648,51 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>31.4</v>
+        <v>61.78</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>-0.003807133169118959</v>
+        <v>0.03328312148014589</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>-0.01008826298080956</v>
+        <v>0.01328518193171213</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.05902192318769228</v>
+        <v>-0.04127876414232068</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.1048557190090242</v>
+        <v>0.03779606998383644</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.2465263577933059</v>
+        <v>-0.08161138899559306</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.2655168506573173</v>
+        <v>0.4095859555758101</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.294619086856567</v>
+        <v>0.6007964417116183</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.6296301759054801</v>
+        <v>0.8423947499575954</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1.089569366500112</v>
+        <v>2.589377693306653</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2784554462286124</v>
+        <v>0.5311099771928893</v>
       </c>
     </row>
     <row r="4">
@@ -704,51 +704,51 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>59.79</v>
+        <v>31.21</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.000334623684298041</v>
+        <v>-0.006050972495728613</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>-0.01466709599822669</v>
+        <v>0.02026802643975523</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>-0.06651056882523532</v>
+        <v>0.06409816452972739</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>-0.01951457257530409</v>
+        <v>0.08973462812827826</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>-0.1249817164741547</v>
+        <v>0.2316495223574528</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.3428795023282099</v>
+        <v>0.2453384935806155</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.5492332804652131</v>
+        <v>0.2867853823695528</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.7905037531420884</v>
+        <v>0.6181919951898354</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>2.473760498404808</v>
+        <v>1.076925307925577</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.5144907463451043</v>
+        <v>0.2758715676899339</v>
       </c>
     </row>
     <row r="5">
@@ -760,51 +760,51 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>90.63</v>
+        <v>71.62</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.004210495882747578</v>
+        <v>0.009301066384227008</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.01638812835069448</v>
+        <v>0.03993030187785895</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.01762856206897268</v>
+        <v>0.1668296106268092</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.04859420263117453</v>
+        <v>0.373346129453924</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.09219081208732161</v>
+        <v>0.2322781153268592</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.1763300593173001</v>
+        <v>-0.0805464588454059</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.4782395901814684</v>
+        <v>0.3259393794465897</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.5376362527878347</v>
+        <v>0.7074525665280891</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.6522332794043031</v>
+        <v>2.673068192700584</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.182198639366733</v>
+        <v>0.5429185381605379</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>70.95999999999999</v>
+        <v>90.62</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-0.02834451224735657</v>
+        <v>-0.0001102781323935043</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.05847252558788951</v>
+        <v>-0.02011246261716437</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.1299363048813</v>
+        <v>0.01648907678679512</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.3690911938566817</v>
+        <v>0.07115844422033213</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.1826666514078776</v>
+        <v>0.1142260015538337</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>-0.07299455878713568</v>
+        <v>0.1601312408328082</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.3137203789912799</v>
+        <v>0.478076572680233</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.6905633030447835</v>
+        <v>0.5187817415959493</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>2.639219213908187</v>
+        <v>0.6520511890941696</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.5381643408579555</v>
+        <v>0.1821552082870872</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>30.29</v>
+        <v>55.61</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.006885215884349427</v>
+        <v>0.03846874701475889</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.009807101522200101</v>
+        <v>0.03191689070669224</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.04918600744771062</v>
+        <v>-0.0044754743513854</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.09113835251389024</v>
+        <v>0.07045235406470129</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.2454770269579263</v>
+        <v>0.02036698367617551</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.2113352603514933</v>
+        <v>0.4071502959075652</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.1626467641046663</v>
+        <v>0.4099543292434051</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.3736795987090735</v>
+        <v>0.5047651803675064</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.5090858640474829</v>
+        <v>1.583719627133914</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1470208622140876</v>
+        <v>0.3721927743698297</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>53.55</v>
+        <v>30.16</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.005067576275331831</v>
+        <v>-0.00429188062680419</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.01071497911712271</v>
+        <v>0.003994638090131897</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-0.03426513074367332</v>
+        <v>0.05417683341466728</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.01941748489371142</v>
+        <v>0.08684684134818421</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>-0.0261866229760479</v>
+        <v>0.2401315882347959</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.325835120672171</v>
+        <v>0.1967864944729936</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.3577243737922202</v>
+        <v>0.1576568229819888</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.459388774219599</v>
+        <v>0.3662436883965514</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>1.488009036922122</v>
+        <v>0.5026090476633933</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.3550354310388013</v>
+        <v>0.1453775501282315</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>36.08</v>
+        <v>24.75</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.01983155433311146</v>
+        <v>0.06635075296308801</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.0264435916330702</v>
+        <v>0.07702352014892266</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.05497079023905993</v>
+        <v>0.02188277050665621</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.05066982151238197</v>
+        <v>0.2325697257986856</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.1115219608343634</v>
+        <v>0.2399800167953714</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.1282418076478455</v>
+        <v>0.4072308786961814</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.1726505407766443</v>
+        <v>0.1115863747033672</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.4994394633496699</v>
+        <v>0.08693747080287406</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.7462920293829374</v>
+        <v>0.4506621543350233</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.2042194124706305</v>
+        <v>0.1320234594394043</v>
       </c>
     </row>
     <row r="10">
@@ -1040,51 +1040,51 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>17.74</v>
+        <v>35.7</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0</v>
+        <v>-0.01053217984562738</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.007954510603070064</v>
+        <v>-0.006954102773141568</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.003930359175926879</v>
+        <v>0.04692089033472002</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.04107974283927196</v>
+        <v>0.04142362993607152</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.1408359841492584</v>
+        <v>0.09140940880937354</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.144574283375775</v>
+        <v>0.09925635929674215</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.182581164373786</v>
+        <v>0.160299902456382</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.162291827833676</v>
+        <v>0.478402558161541</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.004975755533081</v>
+        <v>0.7278996081524525</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2609650277989972</v>
+        <v>0.1999767606963496</v>
       </c>
     </row>
     <row r="11">
@@ -1110,37 +1110,37 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>45.6</v>
+        <v>46.31</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.001751353557798097</v>
+        <v>0.0155702395378996</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.01740291799660465</v>
+        <v>0.03973956940684809</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.02265078084944983</v>
+        <v>0.0142356883059811</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.1170994320194214</v>
+        <v>0.1129536335976453</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.1871908007100243</v>
+        <v>0.2078769219870533</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.2522568616198702</v>
+        <v>0.2771140955130174</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.083120869920563</v>
+        <v>0.09998532131372428</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.03168092282445834</v>
+        <v>0.04298906904814004</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.3032308088311368</v>
+        <v>0.3235224246978083</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.09229625863570545</v>
+        <v>0.09793619222861794</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>116.9</v>
+        <v>17.67</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.008802246260243507</v>
+        <v>-0.003945867853853202</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.02158525923373089</v>
+        <v>0.01493395928550134</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.003347346858619371</v>
+        <v>-0.01450084910521632</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-0.03140277437120242</v>
+        <v>0.02792318367211988</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.1082669492368256</v>
+        <v>0.1481481274924346</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.1653873429474912</v>
+        <v>0.1736329370325238</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.1112493354907069</v>
+        <v>0.1779148553727112</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.2346048834453804</v>
+        <v>0.15346486668504</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.1000834845719392</v>
+        <v>0.9970643861515682</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.03230622978468634</v>
+        <v>0.2593043077632513</v>
       </c>
     </row>
     <row r="13">
@@ -1208,51 +1208,51 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>53.84</v>
+        <v>37.91</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.001483642786981654</v>
+        <v>-0.003941185508841594</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.009752446750560528</v>
+        <v>-0.000527299172231821</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.03598227608160642</v>
+        <v>-0.04364277418955009</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.1349072873344408</v>
+        <v>-0.01404423679616229</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.2644433498666738</v>
+        <v>0.09661556789333581</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.1056230299442984</v>
+        <v>0.1429143336290135</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>-0.005745876233973823</v>
+        <v>0.1981242821324074</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.07767301422615458</v>
+        <v>0.202277337957645</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2123349887676873</v>
+        <v>1.206027447373407</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.06628724240254846</v>
+        <v>0.3017781283950942</v>
       </c>
     </row>
     <row r="14">
@@ -1264,51 +1264,51 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>38.06</v>
+        <v>53.79</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.003162961279011611</v>
+        <v>-0.0009286633900230656</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.007561854299049653</v>
+        <v>0.004106798991159621</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.03791708665138538</v>
+        <v>0.04123114739463052</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-0.01168519781499366</v>
+        <v>0.1262563401572701</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.08929601800834153</v>
+        <v>0.2752489456223861</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.09114240319026679</v>
+        <v>0.1038061346542838</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.2028649962246207</v>
+        <v>-0.006669203639094845</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.217230671179329</v>
+        <v>0.07774654342059284</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>1.214755966645919</v>
+        <v>0.2112091376471747</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.3034927704534198</v>
+        <v>0.06595706619883912</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>23.21</v>
+        <v>14.97</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.006504753772948346</v>
+        <v>0.0006684644957444252</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0</v>
+        <v>0.00469803022085169</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-0.01610856573366948</v>
+        <v>0.006048397304818875</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.1859989497399495</v>
+        <v>0.03455424953510855</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.14957892375093</v>
+        <v>-0.04588905880244154</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.2961281752745029</v>
+        <v>0.1853172043875482</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.04242095915868416</v>
+        <v>0.2804368786319544</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.04089806845687405</v>
+        <v>0.2773662166329907</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.3603986777371726</v>
+        <v>0.8746871576887671</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.1080399024609924</v>
+        <v>0.2330374524186274</v>
       </c>
     </row>
     <row r="16">
@@ -1376,51 +1376,51 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>98.59</v>
+        <v>115.67</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.003256331594133632</v>
+        <v>-0.01052184209476936</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.01954497879312278</v>
+        <v>0.01643229408646851</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.0159727474004514</v>
+        <v>0.0005189651265202766</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.01304969838726744</v>
+        <v>-0.03712643957748663</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.1375331535799704</v>
+        <v>0.0848808402666581</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.1145910439666313</v>
+        <v>0.1437753516307538</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.137082524968956</v>
+        <v>0.09955694545475646</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.116788626486299</v>
+        <v>0.2133475531209263</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.6191276356628654</v>
+        <v>0.08850865800694852</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.1742494402444239</v>
+        <v>0.02867289351820035</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>14.96</v>
+        <v>97.38</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.002680962576976365</v>
+        <v>-0.01227304117474259</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.00133871876341507</v>
+        <v>0.00340024926618665</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.01492539148201888</v>
+        <v>-0.001333246641004759</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.04250868574644384</v>
+        <v>-0.005616287654894858</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>-0.05734088556863592</v>
+        <v>0.1406816694440927</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.191023531653806</v>
+        <v>0.1042190874367415</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.2795814194369781</v>
+        <v>0.1231271631485067</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.2806075358029254</v>
+        <v>0.1003446435166364</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.8734351686294406</v>
+        <v>0.5992562159041268</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.2327629011546037</v>
+        <v>0.1694258307035761</v>
       </c>
     </row>
     <row r="18">
@@ -1502,37 +1502,37 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>122.56</v>
+        <v>121.43</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>8.155452131419771e-05</v>
+        <v>-0.009219951663900217</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.007314863179439079</v>
+        <v>0.003719597749675563</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.006485109012642765</v>
+        <v>-0.02871537701396765</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-0.009776190654364414</v>
+        <v>-0.01372646526726273</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.04582297982178507</v>
+        <v>0.01640578441823104</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.0620714970091234</v>
+        <v>0.06119180173753036</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.2338653446188526</v>
+        <v>0.2224891657817052</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.2426047339263639</v>
+        <v>0.2361015325849036</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.5067569735016786</v>
+        <v>0.4928647470367484</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.1464305133511825</v>
+        <v>0.1428962845475206</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>105.08</v>
+        <v>18.22</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.002089280288007145</v>
+        <v>0.002200165429443013</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.02597152616349008</v>
+        <v>0.02474682844300813</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.03070137299171805</v>
+        <v>-0.001096516338522147</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.06908129873111735</v>
+        <v>0.08194769288968984</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.02888480032283547</v>
+        <v>0.2010546619460312</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.00426905891852547</v>
+        <v>0.1553581981276779</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.2215347349110854</v>
+        <v>-0.02878469663854211</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1811565467567657</v>
+        <v>-0.08991014501756156</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.293402850491469</v>
+        <v>0.2741258091142853</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.08954357640265309</v>
+        <v>0.08410356108866379</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>28.74</v>
+        <v>104.82</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.008421044600637417</v>
+        <v>-0.002474325577653591</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.03589398570928126</v>
+        <v>0.02443315097201326</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.05832243315686814</v>
+        <v>0.03515699667677574</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.02111719435778225</v>
+        <v>0.06405438454734358</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.04319421295869996</v>
+        <v>0.02483379884475978</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>-0.005716194037690303</v>
+        <v>-0.007599011540526557</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.1849843474395774</v>
+        <v>0.2185122602725025</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.18930203817044</v>
+        <v>0.1769750101879386</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>1.180472432604205</v>
+        <v>0.2902025507362878</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.2967319159868651</v>
+        <v>0.088644205702618</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>96</v>
+        <v>28.44</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.003115296388895961</v>
+        <v>-0.01043838689804122</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.001878525420048627</v>
+        <v>-0.01318525901424095</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.01824354309475051</v>
+        <v>-0.06076618595981054</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.04792052571116767</v>
+        <v>-0.04435482811398539</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.06536508842854549</v>
+        <v>0.0274566553649831</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.02198256582850733</v>
+        <v>-0.0198141395634166</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.1497316938920066</v>
+        <v>0.1726149301358026</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.1414058739045652</v>
+        <v>0.1802325360502908</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.1842625902073609</v>
+        <v>1.157711973851758</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.05799269765036508</v>
+        <v>0.2922042265695393</v>
       </c>
     </row>
     <row r="22">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1726,37 +1726,37 @@
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>18.18</v>
+        <v>186.35</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.007641888208545722</v>
+        <v>0.001289589449126716</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.01677858828245693</v>
+        <v>0.02955804477080459</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.03061229785780095</v>
+        <v>-0.000964952967132171</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.1201479247035617</v>
+        <v>0.06760242248898085</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.2120000203450521</v>
+        <v>0.1322761212192012</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.1277915234922746</v>
+        <v>0.1431932470104362</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>-0.03091683990563709</v>
+        <v>0.02468212968100492</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>-0.09009005396899405</v>
+        <v>-0.04772964473785268</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.2713286757125231</v>
+        <v>0.6898801882903691</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.08330965622664421</v>
+        <v>0.1911102761424348</v>
       </c>
     </row>
     <row r="23">
@@ -1768,51 +1768,51 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>69.51000000000001</v>
+        <v>43.14</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.0008640056245503569</v>
+        <v>-0.009641918512429237</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.003899541894732295</v>
+        <v>-0.0089593246171632</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.01980631457729176</v>
+        <v>-0.0105504380864988</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.04699507117435675</v>
+        <v>-0.02486442692324242</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>-0.03305191399325724</v>
+        <v>0.01719159255101754</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.08702840714293947</v>
+        <v>0.0423949744081249</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.208602436674765</v>
+        <v>0.1269209731771512</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.1700618863704415</v>
+        <v>0.1280923207092655</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.8291145498466923</v>
+        <v>0.3729827104994177</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.2229638923145449</v>
+        <v>0.1114459716470249</v>
       </c>
     </row>
     <row r="24">
@@ -1824,51 +1824,51 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>43.56</v>
+        <v>94.64</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.005933325498491793</v>
+        <v>-0.01416667302449548</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0</v>
+        <v>-0.0007390950850055811</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.01161170422790869</v>
+        <v>-0.007446241172886392</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.0186978605039354</v>
+        <v>0.01708754740186524</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.02420953336145515</v>
+        <v>0.03652990357287322</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.056865488123792</v>
+        <v>-0.003647931003766924</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.1378924393533052</v>
+        <v>0.1334438209187392</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.1442227587338851</v>
+        <v>0.1177584375995411</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.3863497821284241</v>
+        <v>0.1674856391966872</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1150412640331273</v>
+        <v>0.05297287175454857</v>
       </c>
     </row>
     <row r="25">
@@ -1880,51 +1880,51 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>17.38</v>
+        <v>69.08</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.005720845771654548</v>
+        <v>-0.006186164464979216</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.004043887751813191</v>
+        <v>0.00685033109637101</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.004011552957723707</v>
+        <v>-0.001301089204467143</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.07883292999995262</v>
+        <v>0.03258595299631639</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.1329855924306858</v>
+        <v>-0.04859098388139238</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.06621350094216782</v>
+        <v>0.06345990972436821</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.07332770134571676</v>
+        <v>0.2011259028968779</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>-0.04537447218428881</v>
+        <v>0.1493394929628382</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.3787115155329877</v>
+        <v>0.8177989814692777</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.1129896720526129</v>
+        <v>0.2204367739770308</v>
       </c>
     </row>
     <row r="26">
@@ -1936,51 +1936,51 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>186.11</v>
+        <v>52.16</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.002732796700137596</v>
+        <v>0.00192083118484887</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.01671673044293009</v>
+        <v>0.01261893898387445</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.02190866242115064</v>
+        <v>-0.02504673182407269</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.08222363952595102</v>
+        <v>0.02094342712132513</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.1220909196037721</v>
+        <v>-0.02559310598031661</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.1074639767228271</v>
+        <v>0.0437354337353848</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.02336241231145531</v>
+        <v>0.1278850878626381</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>-0.05345333520414275</v>
+        <v>0.1797909127469746</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.6877036265846732</v>
+        <v>0.7579215344771184</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1905986740212129</v>
+        <v>0.2068866835164269</v>
       </c>
     </row>
     <row r="27">
@@ -2006,37 +2006,37 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>14.04</v>
+        <v>13.95</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.002141308528271546</v>
+        <v>-0.006410267295756666</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.007173628728830872</v>
+        <v>0.004319615871804183</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.0007127747022215303</v>
+        <v>-0.00499291342460495</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.002857140132359159</v>
+        <v>-0.002859182452283227</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.002857140132359159</v>
+        <v>-0.004282685127513952</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.003809934863525655</v>
+        <v>-0.01370670379271199</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.1978665097935834</v>
+        <v>0.1901878652811715</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.08553834587541709</v>
+        <v>0.07535296835113425</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.0977241732587002</v>
+        <v>0.09068738656564412</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.0315677176589706</v>
+        <v>0.02935875710706481</v>
       </c>
     </row>
     <row r="28">
@@ -2048,51 +2048,51 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>52.06</v>
+        <v>17</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.008133268563259799</v>
+        <v>-0.02186416450608397</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.003826960479632824</v>
+        <v>-0.01162795081790879</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.02855007977123492</v>
+        <v>-0.029680390649376</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.0179898708373627</v>
+        <v>0.02347979381803178</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>-0.03072049412226951</v>
+        <v>0.08142491801707341</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.03988699876178692</v>
+        <v>0.05269413947362089</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.1257227644711476</v>
+        <v>0.04986041157882459</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.1780528624580626</v>
+        <v>-0.06798614793542357</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.7545514503392825</v>
+        <v>0.3485669361058084</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.2061149555627713</v>
+        <v>0.104818240575433</v>
       </c>
     </row>
     <row r="29">
@@ -2104,52 +2104,44 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>17.7</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.002816858425946256</v>
+        <v>-0.01150383663896359</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.01775802922837055</v>
+        <v>-0.008893821536839597</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.02263941654302082</v>
+        <v>-0.05172183801357788</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.03690691736252671</v>
+        <v>-0.03163614097463363</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.00739903644696871</v>
+        <v>0.02663017765385844</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.02431324726431949</v>
-      </c>
-      <c r="M29" s="6" t="n">
-        <v>0.06600284285865587</v>
-      </c>
-      <c r="N29" s="6" t="n">
-        <v>0.05281621790449376</v>
-      </c>
-      <c r="O29" s="6" t="n">
-        <v>0.4888198109547057</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v>0.1418631201718585</v>
-      </c>
+        <v>0.01234922333951549</v>
+      </c>
+      <c r="M29" s="6" t="inlineStr"/>
+      <c r="N29" s="6" t="inlineStr"/>
+      <c r="O29" s="6" t="inlineStr"/>
+      <c r="P29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
@@ -2160,44 +2152,52 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>72.15000000000001</v>
+        <v>17.37</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.01248946622183644</v>
+        <v>-0.01864406268258556</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.01649398956387027</v>
+        <v>-0.009692136112915084</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.04272258330054457</v>
+        <v>-0.04191937985181171</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.01662806562672448</v>
+        <v>-0.0005752774462597365</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.03574501482726644</v>
+        <v>-0.02305960807527185</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.02558639787916928</v>
-      </c>
-      <c r="M30" s="6" t="inlineStr"/>
-      <c r="N30" s="6" t="inlineStr"/>
-      <c r="O30" s="6" t="inlineStr"/>
-      <c r="P30" s="6" t="inlineStr"/>
+        <v>0.002496089917800148</v>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>0.04612821903658482</v>
+      </c>
+      <c r="N30" s="6" t="n">
+        <v>0.02962118114114975</v>
+      </c>
+      <c r="O30" s="6" t="n">
+        <v>0.4610621610761911</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v>0.1347222336646121</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
@@ -2222,37 +2222,37 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>64.48</v>
+        <v>63.77</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.005552020377685651</v>
+        <v>-0.01101121064215294</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.02406532988095622</v>
+        <v>-0.01528723974381918</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.02125066719567514</v>
+        <v>-0.03481155210661702</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.03932950363312404</v>
+        <v>0.01431527821169509</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.03095878464457669</v>
+        <v>-0.05818931738270416</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>-0.01123039854273433</v>
+        <v>-0.01565508376421076</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>-0.00415504762344665</v>
+        <v>-0.01512050616098959</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.01175834418532928</v>
+        <v>-0.001387323540229413</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.4666762229289729</v>
+        <v>0.4505262162323975</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1361737481923084</v>
+        <v>0.1319880985922375</v>
       </c>
     </row>
     <row r="32">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2278,37 +2278,37 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>120.15</v>
+        <v>54.55</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.001416887516160426</v>
+        <v>-0.0005496993951559226</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.02594241579105938</v>
+        <v>-0.006194209443770027</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.03524971380581632</v>
+        <v>-0.005831961017922827</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.0170171134249314</v>
+        <v>0.009998165752803878</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.01435602935270253</v>
+        <v>-0.03536693239580602</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>-0.08018073857715302</v>
+        <v>-0.04978807217141457</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.009678702245299764</v>
+        <v>-0.02362060371844676</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.02227267218673468</v>
+        <v>-0.02039764582317483</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.3839756991588914</v>
+        <v>0.2509398480619425</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1144044086418896</v>
+        <v>0.07748725621616992</v>
       </c>
     </row>
     <row r="33">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -2334,37 +2334,37 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>54.58</v>
+        <v>118.66</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.007816697029605191</v>
+        <v>-0.01240114727296615</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.008537646003988542</v>
+        <v>-0.02014859490302257</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.00128087269661048</v>
+        <v>-0.04942720562718417</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0.03843227558951634</v>
+        <v>-0.03645958431292429</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.01568979116166647</v>
+        <v>-0.03465664310359706</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.05532212316448881</v>
+        <v>-0.09037749119708116</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>-0.02308359336059917</v>
+        <v>-0.002842472039621624</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>-0.02400102266988735</v>
+        <v>-0.03580137451428966</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.2516277576528447</v>
+        <v>0.3668129328082388</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.07768472853861752</v>
+        <v>0.1097786352951109</v>
       </c>
     </row>
     <row r="34">
@@ -2390,37 +2390,37 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>129.05</v>
+        <v>128.2</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.005297249828120298</v>
+        <v>-0.006586641483260713</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.01413285661563535</v>
+        <v>-0.01354270294476068</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.01638714898242366</v>
+        <v>-0.02502097807801007</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.07017789974450683</v>
+        <v>-0.0630025574808657</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.06861028197777375</v>
+        <v>-0.06831401699358841</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.09443966304596185</v>
+        <v>-0.1083060679272645</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.04227906080302324</v>
+        <v>-0.04858722527052539</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.03544397944763755</v>
+        <v>0.02933155377000274</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.5306172458332707</v>
+        <v>0.520535618786871</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1524502879969964</v>
+        <v>0.1499144533181065</v>
       </c>
     </row>
   </sheetData>
@@ -2560,17 +2560,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2650,17 +2650,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -2695,17 +2695,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -2717,17 +2717,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -2740,17 +2740,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2762,17 +2762,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -2785,17 +2785,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -2807,17 +2807,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -2830,17 +2830,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2875,17 +2875,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -2897,17 +2897,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -2942,17 +2942,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.3690911938566817</v>
+        <v>0.373346129453924</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.07017789974450683</v>
+        <v>-0.0630025574808657</v>
       </c>
     </row>
     <row r="18">
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.1859989497399495</v>
+        <v>0.2325697257986856</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -3093,21 +3093,21 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.03140277437120242</v>
+        <v>-0.04435482811398539</v>
       </c>
     </row>
     <row r="19">
@@ -3130,7 +3130,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.1349072873344408</v>
+        <v>0.1262563401572701</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -3138,21 +3138,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.02111719435778225</v>
+        <v>-0.03712643957748663</v>
       </c>
     </row>
     <row r="20">
@@ -3161,21 +3161,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.1201479247035617</v>
+        <v>0.1129536335976453</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -3183,21 +3183,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.01951457257530409</v>
+        <v>-0.03645958431292429</v>
       </c>
     </row>
     <row r="21">
@@ -3206,21 +3206,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.1170994320194214</v>
+        <v>0.08973462812827826</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -3228,21 +3228,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.0186978605039354</v>
+        <v>-0.03163614097463363</v>
       </c>
     </row>
     <row r="22">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.1048557190090242</v>
+        <v>0.08684684134818421</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -3273,21 +3273,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.0170171134249314</v>
+        <v>-0.02486442692324242</v>
       </c>
     </row>
     <row r="23">
@@ -3296,21 +3296,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.09113835251389024</v>
+        <v>0.08194769288968984</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -3318,21 +3318,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.01662806562672448</v>
+        <v>-0.01404423679616229</v>
       </c>
     </row>
     <row r="24">
@@ -3341,21 +3341,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.08222363952595102</v>
+        <v>0.07115844422033213</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -3363,21 +3363,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.01168519781499366</v>
+        <v>-0.01372646526726273</v>
       </c>
     </row>
     <row r="25">
@@ -3386,21 +3386,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.07883292999995262</v>
+        <v>0.07045235406470129</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -3408,21 +3408,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.009776190654364414</v>
+        <v>-0.005616287654894858</v>
       </c>
     </row>
     <row r="26">
@@ -3431,21 +3431,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.06908129873111735</v>
+        <v>0.06760242248898085</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>0.002857140132359159</v>
+        <v>-0.002859182452283227</v>
       </c>
     </row>
     <row r="27"/>
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.2644433498666738</v>
+        <v>0.2752489456223861</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.1249817164741547</v>
+        <v>-0.08161138899559306</v>
       </c>
     </row>
     <row r="32">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3596,7 +3596,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.2465263577933059</v>
+        <v>0.2401315882347959</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -3618,7 +3618,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.06861028197777375</v>
+        <v>-0.06831401699358841</v>
       </c>
     </row>
     <row r="33">
@@ -3627,21 +3627,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.2454770269579263</v>
+        <v>0.2399800167953714</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -3649,21 +3649,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.05734088556863592</v>
+        <v>-0.05818931738270416</v>
       </c>
     </row>
     <row r="34">
@@ -3672,21 +3672,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.2120000203450521</v>
+        <v>0.2322781153268592</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -3708,7 +3708,7 @@
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.03305191399325724</v>
+        <v>-0.04859098388139238</v>
       </c>
     </row>
     <row r="35">
@@ -3717,21 +3717,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.1871908007100243</v>
+        <v>0.2316495223574528</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -3739,21 +3739,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.03095878464457669</v>
+        <v>-0.04588905880244154</v>
       </c>
     </row>
     <row r="36">
@@ -3762,21 +3762,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.1826666514078776</v>
+        <v>0.2078769219870533</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -3784,21 +3784,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.03072049412226951</v>
+        <v>-0.03536693239580602</v>
       </c>
     </row>
     <row r="37">
@@ -3807,21 +3807,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.14957892375093</v>
+        <v>0.2010546619460312</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -3829,21 +3829,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.0261866229760479</v>
+        <v>-0.03465664310359706</v>
       </c>
     </row>
     <row r="38">
@@ -3866,7 +3866,7 @@
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1408359841492584</v>
+        <v>0.1481481274924346</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -3874,21 +3874,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.01568979116166647</v>
+        <v>-0.02559310598031661</v>
       </c>
     </row>
     <row r="39">
@@ -3911,7 +3911,7 @@
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1375331535799704</v>
+        <v>0.1406816694440927</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.01435602935270253</v>
+        <v>-0.02305960807527185</v>
       </c>
     </row>
     <row r="40">
@@ -3942,21 +3942,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1329855924306858</v>
+        <v>0.1322761212192012</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -3964,21 +3964,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FDCPX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Tech Hardware</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-4.636961653181615e-05</v>
+        <v>-0.004282685127513952</v>
       </c>
     </row>
     <row r="41"/>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.4344687271531873</v>
+        <v>0.4267036834460756</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.09443966304596185</v>
+        <v>-0.1083060679272645</v>
       </c>
     </row>
     <row r="46">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.3428795023282099</v>
+        <v>0.4095859555758101</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -4129,7 +4129,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.08018073857715302</v>
+        <v>-0.09037749119708116</v>
       </c>
     </row>
     <row r="47">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4152,7 +4152,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.325835120672171</v>
+        <v>0.4072308786961814</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -4174,7 +4174,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.07299455878713568</v>
+        <v>-0.0805464588454059</v>
       </c>
     </row>
     <row r="48">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.2961281752745029</v>
+        <v>0.4071502959075652</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.05532212316448881</v>
+        <v>-0.04978807217141457</v>
       </c>
     </row>
     <row r="49">
@@ -4228,21 +4228,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.2655168506573173</v>
+        <v>0.2771140955130174</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -4250,21 +4250,21 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.01123039854273433</v>
+        <v>-0.0198141395634166</v>
       </c>
     </row>
     <row r="50">
@@ -4273,21 +4273,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.2522568616198702</v>
+        <v>0.2453384935806155</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -4295,21 +4295,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.005716194037690303</v>
+        <v>-0.01565508376421076</v>
       </c>
     </row>
     <row r="51">
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.2113352603514933</v>
+        <v>0.1967864944729936</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -4354,7 +4354,7 @@
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0.003809934863525655</v>
+        <v>-0.01370670379271199</v>
       </c>
     </row>
     <row r="52">
@@ -4377,7 +4377,7 @@
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.191023531653806</v>
+        <v>0.1853172043875482</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>0.00426905891852547</v>
+        <v>-0.007599011540526557</v>
       </c>
     </row>
     <row r="53">
@@ -4408,21 +4408,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.1763300593173001</v>
+        <v>0.1736329370325238</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.02198256582850733</v>
+        <v>-0.003647931003766924</v>
       </c>
     </row>
     <row r="54">
@@ -4453,21 +4453,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.1653873429474912</v>
+        <v>0.1601312408328082</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -4489,7 +4489,7 @@
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.02431324726431949</v>
+        <v>0.002496089917800148</v>
       </c>
     </row>
     <row r="55"/>
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.96915798022432</v>
+        <v>0.9736036996916693</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.09009005396899405</v>
+        <v>-0.08991014501756156</v>
       </c>
     </row>
     <row r="60">
@@ -4618,7 +4618,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.7905037531420884</v>
+        <v>0.8423947499575954</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4626,21 +4626,21 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.05345333520414275</v>
+        <v>-0.06798614793542357</v>
       </c>
     </row>
     <row r="61">
@@ -4663,7 +4663,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.6905633030447835</v>
+        <v>0.7074525665280891</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4671,21 +4671,21 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.04537447218428881</v>
+        <v>-0.04772964473785268</v>
       </c>
     </row>
     <row r="62">
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.6296301759054801</v>
+        <v>0.6181919951898354</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4716,12 +4716,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.02400102266988735</v>
+        <v>-0.03580137451428966</v>
       </c>
     </row>
     <row r="63">
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.5376362527878347</v>
+        <v>0.5187817415959493</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.02227267218673468</v>
+        <v>-0.02039764582317483</v>
       </c>
     </row>
     <row r="64">
@@ -4784,21 +4784,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.4994394633496699</v>
+        <v>0.5047651803675064</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4820,7 +4820,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>0.01175834418532928</v>
+        <v>-0.001387323540229413</v>
       </c>
     </row>
     <row r="65">
@@ -4829,21 +4829,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.459388774219599</v>
+        <v>0.478402558161541</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4851,21 +4851,21 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.03168092282445834</v>
+        <v>0.02933155377000274</v>
       </c>
     </row>
     <row r="66">
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.3736795987090735</v>
+        <v>0.3662436883965514</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4896,21 +4896,21 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>0.03544397944763755</v>
+        <v>0.02962118114114975</v>
       </c>
     </row>
     <row r="67">
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.2806075358029254</v>
+        <v>0.2773662166329907</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4941,12 +4941,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4955,7 +4955,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.04089806845687405</v>
+        <v>0.04298906904814004</v>
       </c>
     </row>
     <row r="68">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.2426047339263639</v>
+        <v>0.2361015325849036</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -4986,21 +4986,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.05281621790449376</v>
+        <v>0.07535296835113425</v>
       </c>
     </row>
     <row r="69"/>
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.639219213908187</v>
+        <v>2.673068192700584</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5092,21 +5092,21 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.0977241732587002</v>
+        <v>0.08850865800694852</v>
       </c>
     </row>
     <row r="74">
@@ -5129,7 +5129,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.473760498404808</v>
+        <v>2.589377693306653</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5137,21 +5137,21 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.1000834845719392</v>
+        <v>0.09068738656564412</v>
       </c>
     </row>
     <row r="75">
@@ -5174,7 +5174,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.279311234256085</v>
+        <v>2.298025363687851</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1842625902073609</v>
+        <v>0.1674856391966872</v>
       </c>
     </row>
     <row r="76">
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.488009036922122</v>
+        <v>1.583719627133914</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.2123349887676873</v>
+        <v>0.2112091376471747</v>
       </c>
     </row>
     <row r="77">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.214755966645919</v>
+        <v>1.206027447373407</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.2516277576528447</v>
+        <v>0.2509398480619425</v>
       </c>
     </row>
     <row r="78">
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.180472432604205</v>
+        <v>1.157711973851758</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.2713286757125231</v>
+        <v>0.2741258091142853</v>
       </c>
     </row>
     <row r="79">
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.089569366500112</v>
+        <v>1.076925307925577</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.293402850491469</v>
+        <v>0.2902025507362878</v>
       </c>
     </row>
     <row r="80">
@@ -5399,7 +5399,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.004975755533081</v>
+        <v>0.9970643861515682</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5421,7 +5421,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.3032308088311368</v>
+        <v>0.3235224246978083</v>
       </c>
     </row>
     <row r="81">
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8734351686294406</v>
+        <v>0.8746871576887671</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5452,21 +5452,21 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.3603986777371726</v>
+        <v>0.3485669361058084</v>
       </c>
     </row>
     <row r="82">
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.8291145498466923</v>
+        <v>0.8177989814692777</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.3787115155329877</v>
+        <v>0.3668129328082388</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -630,13 +630,13 @@
         <v>0.7228503033692986</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.9736036996916693</v>
+        <v>0.9736038367895916</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.298025363687851</v>
+        <v>2.298025746529321</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4885085392085013</v>
+        <v>0.4885085968048619</v>
       </c>
     </row>
     <row r="3">
@@ -683,16 +683,16 @@
         <v>0.4095859555758101</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.6007964417116183</v>
+        <v>0.6007965999400218</v>
       </c>
       <c r="N3" s="6" t="n">
         <v>0.8423947499575954</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>2.589377693306653</v>
+        <v>2.589378488825729</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.5311099771928893</v>
+        <v>0.5311100903069357</v>
       </c>
     </row>
     <row r="4">
@@ -745,10 +745,10 @@
         <v>0.6181919951898354</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.076925307925577</v>
+        <v>1.076925571545445</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2758715676899339</v>
+        <v>0.2758716216711852</v>
       </c>
     </row>
     <row r="5">
@@ -801,10 +801,10 @@
         <v>0.7074525665280891</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>2.673068192700584</v>
+        <v>2.673067833403502</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.5429185381605379</v>
+        <v>0.5429184878514486</v>
       </c>
     </row>
     <row r="6">
@@ -857,10 +857,10 @@
         <v>0.5187817415959493</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.6520511890941696</v>
+        <v>0.652051074203972</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.1821552082870872</v>
+        <v>0.1821551808831645</v>
       </c>
     </row>
     <row r="7">
@@ -910,13 +910,13 @@
         <v>0.4099543292434051</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.5047651803675064</v>
+        <v>0.5047653356936965</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>1.583719627133914</v>
+        <v>1.583719169205206</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.3721927743698297</v>
+        <v>0.3721926933024033</v>
       </c>
     </row>
     <row r="8">
@@ -1075,7 +1075,7 @@
         <v>0.09925635929674215</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.160299902456382</v>
+        <v>0.1602999743851126</v>
       </c>
       <c r="N10" s="6" t="n">
         <v>0.478402558161541</v>
@@ -1305,10 +1305,10 @@
         <v>0.07774654342059284</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.2112091376471747</v>
+        <v>0.2112092416863356</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.06595706619883912</v>
+        <v>0.06595709671965566</v>
       </c>
     </row>
     <row r="15">
@@ -1417,10 +1417,10 @@
         <v>0.2133475531209263</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.08850865800694852</v>
+        <v>0.08850857985620952</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.02867289351820035</v>
+        <v>0.02867286889994625</v>
       </c>
     </row>
     <row r="17">
@@ -1473,10 +1473,10 @@
         <v>0.1003446435166364</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.5992562159041268</v>
+        <v>0.5992563160946032</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.1694258307035761</v>
+        <v>0.1694258551243719</v>
       </c>
     </row>
     <row r="18">
@@ -1803,16 +1803,16 @@
         <v>0.0423949744081249</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1269209731771512</v>
+        <v>0.1269210854738296</v>
       </c>
       <c r="N23" s="6" t="n">
         <v>0.1280923207092655</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.3729827104994177</v>
+        <v>0.3729825438092331</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.1114459716470249</v>
+        <v>0.1114459266677883</v>
       </c>
     </row>
     <row r="24">
@@ -1915,16 +1915,16 @@
         <v>0.06345990972436821</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.2011259028968779</v>
+        <v>0.2011258232287201</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.1493394929628382</v>
+        <v>0.1493394200163531</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.8177989814692777</v>
+        <v>0.8177993464160542</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.2204367739770308</v>
+        <v>0.2204368556498746</v>
       </c>
     </row>
     <row r="26">
@@ -1971,7 +1971,7 @@
         <v>0.0437354337353848</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.1278850878626381</v>
+        <v>0.1278851808988977</v>
       </c>
       <c r="N26" s="6" t="n">
         <v>0.1797909127469746</v>
@@ -2033,10 +2033,10 @@
         <v>0.07535296835113425</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.09068738656564412</v>
+        <v>0.09068746789109849</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.02935875710706481</v>
+        <v>0.02935878269125669</v>
       </c>
     </row>
     <row r="28">
@@ -2089,10 +2089,10 @@
         <v>-0.06798614793542357</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.3485669361058084</v>
+        <v>0.3485670381283674</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.104818240575433</v>
+        <v>0.1048182684362131</v>
       </c>
     </row>
     <row r="29">
@@ -2193,10 +2193,10 @@
         <v>0.02962118114114975</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.4610621610761911</v>
+        <v>0.4610620438734958</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1347222336646121</v>
+        <v>0.1347222033230997</v>
       </c>
     </row>
     <row r="31">
@@ -2249,10 +2249,10 @@
         <v>-0.001387323540229413</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.4505262162323975</v>
+        <v>0.450526342094465</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1319880985922375</v>
+        <v>0.1319881313330815</v>
       </c>
     </row>
     <row r="32">
@@ -2305,10 +2305,10 @@
         <v>-0.02039764582317483</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.2509398480619425</v>
+        <v>0.2509397386315027</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.07748725621616992</v>
+        <v>0.07748722479715098</v>
       </c>
     </row>
     <row r="33">
@@ -2361,10 +2361,10 @@
         <v>-0.03580137451428966</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.3668129328082388</v>
+        <v>0.3668128126914156</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1097786352951109</v>
+        <v>0.109778602785642</v>
       </c>
     </row>
     <row r="34">
@@ -2414,13 +2414,13 @@
         <v>-0.04858722527052539</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.02933155377000274</v>
+        <v>0.02933149071600805</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.520535618786871</v>
+        <v>0.5205357563795399</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1499144533181065</v>
+        <v>0.1499144880032073</v>
       </c>
     </row>
   </sheetData>
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.9736036996916693</v>
+        <v>0.9736038367895916</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4798,7 +4798,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.5047651803675064</v>
+        <v>0.5047653356936965</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4865,7 +4865,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.02933155377000274</v>
+        <v>0.02933149071600805</v>
       </c>
     </row>
     <row r="66">
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.673068192700584</v>
+        <v>2.673067833403502</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.08850865800694852</v>
+        <v>0.08850857985620952</v>
       </c>
     </row>
     <row r="74">
@@ -5129,7 +5129,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.589377693306653</v>
+        <v>2.589378488825729</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.09068738656564412</v>
+        <v>0.09068746789109849</v>
       </c>
     </row>
     <row r="75">
@@ -5174,7 +5174,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.298025363687851</v>
+        <v>2.298025746529321</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.583719627133914</v>
+        <v>1.583719169205206</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.2112091376471747</v>
+        <v>0.2112092416863356</v>
       </c>
     </row>
     <row r="77">
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.2509398480619425</v>
+        <v>0.2509397386315027</v>
       </c>
     </row>
     <row r="78">
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.076925307925577</v>
+        <v>1.076925571545445</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5466,7 +5466,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.3485669361058084</v>
+        <v>0.3485670381283674</v>
       </c>
     </row>
     <row r="82">
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.8177989814692777</v>
+        <v>0.8177993464160542</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.3668129328082388</v>
+        <v>0.3668128126914156</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -683,16 +683,16 @@
         <v>0.4095859555758101</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.6007965999400218</v>
+        <v>0.6007964417116183</v>
       </c>
       <c r="N3" s="6" t="n">
         <v>0.8423947499575954</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>2.589378488825729</v>
+        <v>2.589377693306653</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.5311100903069357</v>
+        <v>0.5311099771928893</v>
       </c>
     </row>
     <row r="4">
@@ -857,10 +857,10 @@
         <v>0.5187817415959493</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.652051074203972</v>
+        <v>0.6520511890941696</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.1821551808831645</v>
+        <v>0.1821552082870872</v>
       </c>
     </row>
     <row r="7">
@@ -910,13 +910,13 @@
         <v>0.4099543292434051</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.5047653356936965</v>
+        <v>0.5047651803675064</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>1.583719169205206</v>
+        <v>1.583719627133914</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.3721926933024033</v>
+        <v>0.3721927743698297</v>
       </c>
     </row>
     <row r="8">
@@ -1025,10 +1025,10 @@
         <v>0.08693747080287406</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.4506621543350233</v>
+        <v>0.4506623165113615</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1320234594394043</v>
+        <v>0.1320235016241431</v>
       </c>
     </row>
     <row r="10">
@@ -1193,10 +1193,10 @@
         <v>0.15346486668504</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.9970643861515682</v>
+        <v>0.9970646014038262</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2593043077632513</v>
+        <v>0.2593043530076757</v>
       </c>
     </row>
     <row r="13">
@@ -1305,10 +1305,10 @@
         <v>0.07774654342059284</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.2112092416863356</v>
+        <v>0.2112091376471747</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.06595709671965566</v>
+        <v>0.06595706619883912</v>
       </c>
     </row>
     <row r="15">
@@ -1355,16 +1355,16 @@
         <v>0.1853172043875482</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.2804368786319544</v>
+        <v>0.280436774185286</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>0.2773662166329907</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.8746871576887671</v>
+        <v>0.8746873815794078</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.2330374524186274</v>
+        <v>0.2330375015051347</v>
       </c>
     </row>
     <row r="16">
@@ -1417,10 +1417,10 @@
         <v>0.2133475531209263</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.08850857985620952</v>
+        <v>0.08850850170548163</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.02867286889994625</v>
+        <v>0.02867284428169414</v>
       </c>
     </row>
     <row r="17">
@@ -1467,16 +1467,16 @@
         <v>0.1042190874367415</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.1231271631485067</v>
+        <v>0.1231270643209317</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.1003446435166364</v>
+        <v>0.1003447383754787</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.5992563160946032</v>
+        <v>0.5992560155232114</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.1694258551243719</v>
+        <v>0.1694257818619904</v>
       </c>
     </row>
     <row r="18">
@@ -1526,13 +1526,13 @@
         <v>0.2224891657817052</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.2361015325849036</v>
+        <v>0.2361016285851618</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.4928647470367484</v>
+        <v>0.492864607011948</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.1428962845475206</v>
+        <v>0.1428962488144712</v>
       </c>
     </row>
     <row r="19">
@@ -1641,10 +1641,10 @@
         <v>0.1769750101879386</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.2902025507362878</v>
+        <v>0.2902026718969819</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.088644205702618</v>
+        <v>0.08864423978018277</v>
       </c>
     </row>
     <row r="21">
@@ -1697,10 +1697,10 @@
         <v>0.1802325360502908</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>1.157711973851758</v>
+        <v>1.157711817732169</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.2922042265695393</v>
+        <v>0.292204195404058</v>
       </c>
     </row>
     <row r="22">
@@ -1750,7 +1750,7 @@
         <v>0.02468212968100492</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>-0.04772964473785268</v>
+        <v>-0.04772971899036516</v>
       </c>
       <c r="O22" s="6" t="n">
         <v>0.6898801882903691</v>
@@ -1803,16 +1803,16 @@
         <v>0.0423949744081249</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1269210854738296</v>
+        <v>0.1269209731771512</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.1280923207092655</v>
+        <v>0.1280924332395126</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.3729825438092331</v>
+        <v>0.3729824604641561</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.1114459266677883</v>
+        <v>0.111445904178173</v>
       </c>
     </row>
     <row r="24">
@@ -1859,7 +1859,7 @@
         <v>-0.003647931003766924</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.1334438209187392</v>
+        <v>0.1334439244843051</v>
       </c>
       <c r="N24" s="6" t="n">
         <v>0.1177584375995411</v>
@@ -1915,7 +1915,7 @@
         <v>0.06345990972436821</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.2011258232287201</v>
+        <v>0.2011259028968779</v>
       </c>
       <c r="N25" s="6" t="n">
         <v>0.1493394200163531</v>
@@ -1977,10 +1977,10 @@
         <v>0.1797909127469746</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.7579215344771184</v>
+        <v>0.7579216474805159</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2068866835164269</v>
+        <v>0.2068867093769464</v>
       </c>
     </row>
     <row r="27">
@@ -2033,10 +2033,10 @@
         <v>0.07535296835113425</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.09068746789109849</v>
+        <v>0.09068754921656508</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.02935878269125669</v>
+        <v>0.02935880827545123</v>
       </c>
     </row>
     <row r="28">
@@ -2083,16 +2083,16 @@
         <v>0.05269413947362089</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.04986041157882459</v>
+        <v>0.0498602879145571</v>
       </c>
       <c r="N28" s="6" t="n">
         <v>-0.06798614793542357</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.3485670381283674</v>
+        <v>0.348567140150942</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.1048182684362131</v>
+        <v>0.1048182962969963</v>
       </c>
     </row>
     <row r="29">
@@ -2193,10 +2193,10 @@
         <v>0.02962118114114975</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.4610620438734958</v>
+        <v>0.4610621610761911</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1347222033230997</v>
+        <v>0.1347222336646121</v>
       </c>
     </row>
     <row r="31">
@@ -2246,7 +2246,7 @@
         <v>-0.01512050616098959</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-0.001387323540229413</v>
+        <v>-0.001387263886467927</v>
       </c>
       <c r="O31" s="6" t="n">
         <v>0.450526342094465</v>
@@ -2361,10 +2361,10 @@
         <v>-0.03580137451428966</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.3668128126914156</v>
+        <v>0.3668129328082388</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.109778602785642</v>
+        <v>0.1097786352951109</v>
       </c>
     </row>
     <row r="34">
@@ -2417,10 +2417,10 @@
         <v>0.02933149071600805</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.5205357563795399</v>
+        <v>0.5205354811942273</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1499144880032073</v>
+        <v>0.1499144186330097</v>
       </c>
     </row>
   </sheetData>
@@ -4685,7 +4685,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.04772964473785268</v>
+        <v>-0.04772971899036516</v>
       </c>
     </row>
     <row r="62">
@@ -4798,7 +4798,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.5047653356936965</v>
+        <v>0.5047651803675064</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4820,7 +4820,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.001387323540229413</v>
+        <v>-0.001387263886467927</v>
       </c>
     </row>
     <row r="65">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.2361015325849036</v>
+        <v>0.2361016285851618</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.08850857985620952</v>
+        <v>0.08850850170548163</v>
       </c>
     </row>
     <row r="74">
@@ -5129,7 +5129,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.589378488825729</v>
+        <v>2.589377693306653</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.09068746789109849</v>
+        <v>0.09068754921656508</v>
       </c>
     </row>
     <row r="75">
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.583719169205206</v>
+        <v>1.583719627133914</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.2112092416863356</v>
+        <v>0.2112091376471747</v>
       </c>
     </row>
     <row r="77">
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.157711973851758</v>
+        <v>1.157711817732169</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.2902025507362878</v>
+        <v>0.2902026718969819</v>
       </c>
     </row>
     <row r="80">
@@ -5399,7 +5399,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.9970643861515682</v>
+        <v>0.9970646014038262</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8746871576887671</v>
+        <v>0.8746873815794078</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5466,7 +5466,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.3485670381283674</v>
+        <v>0.348567140150942</v>
       </c>
     </row>
     <row r="82">
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.3668128126914156</v>
+        <v>0.3668129328082388</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -490,12 +490,12 @@
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
     <col width="24" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>216.76</v>
+        <v>213.96</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.005706842363037312</v>
+        <v>-0.01291745646764375</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.01717498028386921</v>
+        <v>0.01958542049469458</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>-0.01696147615947419</v>
+        <v>-0.05773550089172552</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.06536905216794264</v>
+        <v>0.03657769932564459</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.0099711091153456</v>
+        <v>-0.02855842581672108</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.4267036834460756</v>
+        <v>0.4082743007229339</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7228503033692986</v>
+        <v>0.6881454474007416</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.9736038367895916</v>
+        <v>0.939834632220764</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.298025746529321</v>
+        <v>2.149964916355807</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4885085968048619</v>
+        <v>0.4658917666341071</v>
       </c>
     </row>
     <row r="3">
@@ -648,51 +648,51 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>61.78</v>
+        <v>92.79000000000001</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.03328312148014589</v>
+        <v>0.02394612782140038</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.01328518193171213</v>
+        <v>0.01199692927071339</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>-0.04127876414232068</v>
+        <v>0.01743425461063897</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.03779606998383644</v>
+        <v>0.07970675214713219</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>-0.08161138899559306</v>
+        <v>0.1535305581711912</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.4095859555758101</v>
+        <v>0.1879118918153904</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.6007964417116183</v>
+        <v>0.4948367280718573</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.8423947499575954</v>
+        <v>0.5414800205477082</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>2.589377693306653</v>
+        <v>0.6519621868699921</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.5311099771928893</v>
+        <v>0.182133978853632</v>
       </c>
     </row>
     <row r="4">
@@ -704,51 +704,51 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>31.21</v>
+        <v>59.97</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.006050972495728613</v>
+        <v>-0.0292974683450512</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.02026802643975523</v>
+        <v>0.02024502324122857</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.06409816452972739</v>
+        <v>-0.07965012507241831</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.08973462812827826</v>
+        <v>0.0131779458031982</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.2316495223574528</v>
+        <v>-0.1124759287915646</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.2453384935806155</v>
+        <v>0.368288655662699</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.2867853823695528</v>
+        <v>0.5416973740560633</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.6181919951898354</v>
+        <v>0.8416097029766065</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.076925571545445</v>
+        <v>2.296073536551117</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2758716216711852</v>
+        <v>0.4882148397605377</v>
       </c>
     </row>
     <row r="5">
@@ -760,51 +760,51 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>71.62</v>
+        <v>30.37</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.009301066384227008</v>
+        <v>-0.02691439506184312</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.03993030187785895</v>
+        <v>-0.01555914218155552</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.1668296106268092</v>
+        <v>0.01878568880656339</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.373346129453924</v>
+        <v>0.08193805377323438</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.2322781153268592</v>
+        <v>0.1872557048402588</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>-0.0805464588454059</v>
+        <v>0.2118209613786664</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.3259393794465897</v>
+        <v>0.2492504949103009</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.7074525665280891</v>
+        <v>0.5784819214331203</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>2.673067833403502</v>
+        <v>1.013632394404492</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.5429184878514486</v>
+        <v>0.2627771937894383</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>90.62</v>
+        <v>54.79</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-0.0001102781323935043</v>
+        <v>-0.01474554371199877</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>-0.02011246261716437</v>
+        <v>0.03946123823150316</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.01648907678679512</v>
+        <v>-0.02143241162646659</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.07115844422033213</v>
+        <v>0.04881315381181639</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.1142260015538337</v>
+        <v>-0.01686701299892501</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.1601312408328082</v>
+        <v>0.3864010997099081</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.478076572680233</v>
+        <v>0.3837401593199061</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.5187817415959493</v>
+        <v>0.5005851217043742</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.6520511890941696</v>
+        <v>1.428788446688389</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.1821552082870872</v>
+        <v>0.3441979522241667</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>55.61</v>
+        <v>29.52</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.03846874701475889</v>
+        <v>-0.02122013902143149</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.03191689070669224</v>
+        <v>-0.02186878199928055</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-0.0044754743513854</v>
+        <v>0.02393342129322207</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.07045235406470129</v>
+        <v>0.07894736108283862</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.02036698367617551</v>
+        <v>0.1936919128262218</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.4071502959075652</v>
+        <v>0.1713905186813049</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.4099543292434051</v>
+        <v>0.1341733715392723</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.5047651803675064</v>
+        <v>0.3392627167153628</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>1.583719627133914</v>
+        <v>0.4516850568560895</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.3721927743698297</v>
+        <v>0.1322894707423801</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>30.16</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.00429188062680419</v>
+        <v>-0.04761244807788156</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.003994638090131897</v>
+        <v>-0.04854238022627877</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.05417683341466728</v>
+        <v>0.07164175097057512</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.08684684134818421</v>
+        <v>0.3314464121405516</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.2401315882347959</v>
+        <v>0.1149068117723129</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.1967864944729936</v>
+        <v>-0.1243238928336534</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.1576568229819888</v>
+        <v>0.2419516225667264</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.3662436883965514</v>
+        <v>0.5832681933564661</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.5026090476633933</v>
+        <v>2.389762640584165</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1453775501282315</v>
+        <v>0.5021838767760864</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>24.75</v>
+        <v>35.04</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.06635075296308801</v>
+        <v>-0.01848739028872126</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.07702352014892266</v>
+        <v>-0.03391231118589755</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.02188277050665621</v>
+        <v>0.02726474020916747</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.2325697257986856</v>
+        <v>0.03883787106639724</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.2399800167953714</v>
+        <v>0.06504557113667997</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.4072308786961814</v>
+        <v>0.0789339779550644</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.1115863747033672</v>
+        <v>0.1459137477635846</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.08693747080287406</v>
+        <v>0.4567925944299629</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.4506623165113615</v>
+        <v>0.693129899035515</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1320235016241431</v>
+        <v>0.1918733056406818</v>
       </c>
     </row>
     <row r="10">
@@ -1040,51 +1040,51 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>35.7</v>
+        <v>17.64</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.01053217984562738</v>
+        <v>-0.001697831721334087</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.006954102773141568</v>
+        <v>-0.006756803923811283</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.04692089033472002</v>
+        <v>-0.008431788541842233</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.04142362993607152</v>
+        <v>0.01965318887757705</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.09140940880937354</v>
+        <v>0.1484374859331483</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.09925635929674215</v>
+        <v>0.1716403058028275</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.1602999743851126</v>
+        <v>0.1700790556514515</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.478402558161541</v>
+        <v>0.1522097878853794</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.7278996081524525</v>
+        <v>0.9561633399053882</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.1999767606963496</v>
+        <v>0.2506478433609944</v>
       </c>
     </row>
     <row r="11">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1110,37 +1110,37 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>46.31</v>
+        <v>24.54</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.0155702395378996</v>
+        <v>-0.008484811493844724</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.03973956940684809</v>
+        <v>0.06233768442760512</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.0142356883059811</v>
+        <v>0.05457672680620673</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.1129536335976453</v>
+        <v>0.1387471825671691</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.2078769219870533</v>
+        <v>0.1169777734408337</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.2771140955130174</v>
+        <v>0.3952907899621267</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.09998532131372428</v>
+        <v>0.0901921474306695</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.04298906904814004</v>
+        <v>0.05952568005984582</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.3235224246978083</v>
+        <v>0.3891324430063932</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.09793619222861794</v>
+        <v>0.1157867969190642</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
       <c r="F12" s="5" t="n">
-        <v>17.67</v>
+        <v>37.6</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.003945867853853202</v>
+        <v>-0.008177298194111615</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.01493395928550134</v>
+        <v>-0.01182656430913021</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>-0.01450084910521632</v>
+        <v>-0.05026526069201631</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.02792318367211988</v>
+        <v>-0.02363022298298245</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.1481481274924346</v>
+        <v>0.08764821539036705</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.1736329370325238</v>
+        <v>0.1335683823126046</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.1779148553727112</v>
+        <v>0.1890114250052368</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.15346486668504</v>
+        <v>0.1934801249080289</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.9970646014038262</v>
+        <v>1.142340019433309</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2593043530076757</v>
+        <v>0.2891282733919374</v>
       </c>
     </row>
     <row r="13">
@@ -1208,51 +1208,51 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>37.91</v>
+        <v>45.95</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.003941185508841594</v>
+        <v>-0.007773711934268901</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.000527299172231821</v>
+        <v>0.007233709749695727</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-0.04364277418955009</v>
+        <v>0.03607671575799465</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-0.01404423679616229</v>
+        <v>0.06390373290087736</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.09661556789333581</v>
+        <v>0.1320522441537815</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.1429143336290135</v>
+        <v>0.2671861784273049</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.1981242821324074</v>
+        <v>0.08087137195678684</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.202277337957645</v>
+        <v>0.02097991896250861</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>1.206027447373407</v>
+        <v>0.2836121993018388</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.3017781283950942</v>
+        <v>0.08678744335664335</v>
       </c>
     </row>
     <row r="14">
@@ -1264,51 +1264,51 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>53.79</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.0009286633900230656</v>
+        <v>-0.004929099826219363</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.004106798991159621</v>
+        <v>-0.02061856544561402</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.04123114739463052</v>
+        <v>0.008114843497802671</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.1262563401572701</v>
+        <v>-0.00513347014545118</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.2752489456223861</v>
+        <v>0.1593682627783228</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.1038061346542838</v>
+        <v>0.09877628132474903</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>-0.006669203639094845</v>
+        <v>0.1196874718444494</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.07774654342059284</v>
+        <v>0.09433055289171954</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.2112091376471747</v>
+        <v>0.5801953484251889</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.06595706619883912</v>
+        <v>0.1647612835686416</v>
       </c>
     </row>
     <row r="15">
@@ -1334,37 +1334,37 @@
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>14.97</v>
+        <v>14.81</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.0006684644957444252</v>
+        <v>-0.01068803236861038</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.00469803022085169</v>
+        <v>0.002029816453824607</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.006048397304818875</v>
+        <v>-0.006706869806760385</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.03455424953510855</v>
+        <v>0.04812457888664978</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>-0.04588905880244154</v>
+        <v>-0.05788803002254062</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.1853172043875482</v>
+        <v>0.1726484957399832</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.280436774185286</v>
+        <v>0.2606904803055712</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.2773662166329907</v>
+        <v>0.2738968069996928</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.8746873815794078</v>
+        <v>0.7766513530977373</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.2330375015051347</v>
+        <v>0.2111578183124225</v>
       </c>
     </row>
     <row r="16">
@@ -1390,37 +1390,37 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>115.67</v>
+        <v>114.46</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.01052184209476936</v>
+        <v>-0.01046078588767119</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.01643229408646851</v>
+        <v>-0.01302062706162066</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.0005189651265202766</v>
+        <v>-0.004868697399909916</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-0.03712643957748663</v>
+        <v>-0.02545762402264817</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.0848808402666581</v>
+        <v>0.08093304130911161</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.1437753516307538</v>
+        <v>0.1318105625737487</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.09955694545475646</v>
+        <v>0.08959668910789031</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.2133475531209263</v>
+        <v>0.189018643795241</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.08850850170548163</v>
+        <v>0.08940260585231186</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.02867284428169414</v>
+        <v>0.02895441885317029</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>97.38</v>
+        <v>53.03</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.01227304117474259</v>
+        <v>-0.01412905973777523</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.00340024926618665</v>
+        <v>-0.01174060883165695</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.001333246641004759</v>
+        <v>0.03151135842624031</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.005616287654894858</v>
+        <v>0.09317667726566947</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.1406816694440927</v>
+        <v>0.2008604837530263</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.1042190874367415</v>
+        <v>0.08821039183883062</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.1231270643209317</v>
+        <v>-0.01905004444495251</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.1003447383754787</v>
+        <v>0.0625189981264227</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.5992560155232114</v>
+        <v>0.1567024149097707</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.1694257818619904</v>
+        <v>0.04972098857513507</v>
       </c>
     </row>
     <row r="18">
@@ -1502,37 +1502,37 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>121.43</v>
+        <v>119.59</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.009219951663900217</v>
+        <v>-0.01515279554196569</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.003719597749675563</v>
+        <v>-0.01886949760665224</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.02871537701396765</v>
+        <v>-0.02969577007796653</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-0.01372646526726273</v>
+        <v>-0.008045796618664447</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.01640578441823104</v>
+        <v>0.002514841311600957</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.06119180173753036</v>
+        <v>0.04511177933499133</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.2224891657817052</v>
+        <v>0.1970965850415967</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.2361016285851618</v>
+        <v>0.2182831463538515</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.492864607011948</v>
+        <v>0.4515466919016697</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.1428962488144712</v>
+        <v>0.1322534955014953</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>18.22</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.002200165429443013</v>
+        <v>0.006224671305415042</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.02474682844300813</v>
+        <v>0.007829504218788585</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.001096516338522147</v>
+        <v>0.005642352056586475</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.08194769288968984</v>
+        <v>0.05976529985069234</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.2010546619460312</v>
+        <v>-0.03530867360984635</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.1553581981276779</v>
+        <v>0.07007972379144078</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>-0.02878469663854211</v>
+        <v>0.2022629817281612</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>-0.08991014501756156</v>
+        <v>0.1566800741529377</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.2741258091142853</v>
+        <v>0.7380800740649665</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.08410356108866379</v>
+        <v>0.2023288280210374</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>104.82</v>
+        <v>94.55</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.002474325577653591</v>
+        <v>-0.0009509334157969951</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.02443315097201326</v>
+        <v>-0.02786344874511526</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.03515699667677574</v>
+        <v>0.005744079387902001</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.06405438454734358</v>
+        <v>0.008103231995007398</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.02483379884475978</v>
+        <v>0.05768751679726547</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>-0.007599011540526557</v>
+        <v>-0.004595395480073927</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.2185122602725025</v>
+        <v>0.1264490597501133</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.1769750101879386</v>
+        <v>0.1186180138828288</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.2902026718969819</v>
+        <v>0.1603786587505707</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.08864423978018277</v>
+        <v>0.05083189062510329</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>28.44</v>
+        <v>186.43</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.01043838689804122</v>
+        <v>0.0004292276342678925</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.01318525901424095</v>
+        <v>0.003552717813110062</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-0.06076618595981054</v>
+        <v>0.02355327385806838</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-0.04435482811398539</v>
+        <v>0.06842791453224506</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.0274566553649831</v>
+        <v>0.1184233604010767</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>-0.0198141395634166</v>
+        <v>0.1436839371433616</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.1726149301358026</v>
+        <v>0.01544956788932694</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.1802325360502908</v>
+        <v>-0.04349391154757565</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>1.157711817732169</v>
+        <v>0.6505308013950086</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.292204195404058</v>
+        <v>0.1817924499788774</v>
       </c>
     </row>
     <row r="22">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>186.35</v>
+        <v>103.49</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.001289589449126716</v>
+        <v>-0.01268843574629741</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.02955804477080459</v>
+        <v>-0.01268843574629741</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-0.000964952967132171</v>
+        <v>0.01630164001635714</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.06760242248898085</v>
+        <v>0.07187979899173458</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.1322761212192012</v>
+        <v>0.007986750846872503</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.1431932470104362</v>
+        <v>-0.02019102771715664</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.02468212968100492</v>
+        <v>0.1913213477876539</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>-0.04772971899036516</v>
+        <v>0.1599339405909979</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.6898801882903691</v>
+        <v>0.2351730690360279</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.1911102761424348</v>
+        <v>0.07294123918867146</v>
       </c>
     </row>
     <row r="23">
@@ -1768,51 +1768,51 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>43.14</v>
+        <v>14</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.009641918512429237</v>
+        <v>0.003584243112437546</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.0089593246171632</v>
+        <v>0.0007148126551423939</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.0105504380864988</v>
+        <v>0.007919341537678593</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.02486442692324242</v>
+        <v>0.01818181818181808</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.01719159255101754</v>
+        <v>0.01596518659593427</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.0423949744081249</v>
+        <v>-0.01017158883893765</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1269209731771512</v>
+        <v>0.1875721600646141</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.1280924332395126</v>
+        <v>0.08407216196794565</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.3729824604641561</v>
+        <v>0.0691574333283469</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.111445904178173</v>
+        <v>0.02254058246146418</v>
       </c>
     </row>
     <row r="24">
@@ -1824,51 +1824,51 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>94.64</v>
+        <v>42.61</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.01416667302449548</v>
+        <v>-0.01228555370411177</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.0007390950850055811</v>
+        <v>-0.02561168405234082</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.007446241172886392</v>
+        <v>-0.01775012537585274</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.01708754740186524</v>
+        <v>-0.02135967582959153</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.03652990357287322</v>
+        <v>0.01759378297854974</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>-0.003647931003766924</v>
+        <v>0.02958857496913758</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.1334439244843051</v>
+        <v>0.1093696818698584</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.1177584375995411</v>
+        <v>0.1114551074349475</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.1674856391966872</v>
+        <v>0.335031630932219</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.05297287175454857</v>
+        <v>0.1011095226261269</v>
       </c>
     </row>
     <row r="25">
@@ -1880,51 +1880,51 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>69.08</v>
+        <v>17.86</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.006186164464979216</v>
+        <v>-0.01975843669429045</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.00685033109637101</v>
+        <v>-0.0208332875841537</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.001301089204467143</v>
+        <v>0.007332265734443233</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.03258595299631639</v>
+        <v>0.05617982090548868</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>-0.04859098388139238</v>
+        <v>0.1441384371018783</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.06345990972436821</v>
+        <v>0.1325301263107428</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.2011259028968779</v>
+        <v>-0.05552613672835338</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.1493394200163531</v>
+        <v>-0.1149652953290186</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.8177993464160542</v>
+        <v>0.209207857604613</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.2204368556498746</v>
+        <v>0.0653696491694562</v>
       </c>
     </row>
     <row r="26">
@@ -1950,37 +1950,37 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>52.16</v>
+        <v>51.33</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.00192083118484887</v>
+        <v>-0.01591253870370946</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.01261893898387445</v>
+        <v>-0.003494399074815524</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.02504673182407269</v>
+        <v>-0.03822366763457674</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.02094342712132513</v>
+        <v>0.0007798969548318269</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>-0.02559310598031661</v>
+        <v>-0.0482106148601591</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.0437354337353848</v>
+        <v>0.02712695324963765</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.1278851808988977</v>
+        <v>0.1003490800993596</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.1797909127469746</v>
+        <v>0.1698603585553631</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.7579216474805159</v>
+        <v>0.6926794456816388</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2068867093769464</v>
+        <v>0.1917675978727857</v>
       </c>
     </row>
     <row r="27">
@@ -1992,51 +1992,51 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>13.95</v>
+        <v>27.65</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.006410267295756666</v>
+        <v>-0.02777780944769315</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.004319615871804183</v>
+        <v>-0.02400283469844877</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.00499291342460495</v>
+        <v>-0.09463003308319218</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.002859182452283227</v>
+        <v>-0.05437757062359538</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>-0.004282685127513952</v>
+        <v>-0.02434723113417514</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>-0.01370670379271199</v>
+        <v>-0.0470415556179471</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.1901878652811715</v>
+        <v>0.1322776337534974</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.07535296835113425</v>
+        <v>0.1521259856787782</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.09068754921656508</v>
+        <v>1.067918410549169</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.02935880827545123</v>
+        <v>0.2740245591793817</v>
       </c>
     </row>
     <row r="28">
@@ -2062,37 +2062,37 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>17</v>
+        <v>16.7</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.02186416450608397</v>
+        <v>-0.017647013944738</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.01162795081790879</v>
+        <v>-0.04843296359387539</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.029680390649376</v>
+        <v>-0.03188401374264038</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.02347979381803178</v>
+        <v>-0.01007706389074903</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.08142491801707341</v>
+        <v>0.07051284324174434</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.05269413947362089</v>
+        <v>0.03411723131478572</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.0498602879145571</v>
+        <v>0.02809697185183246</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>-0.06798614793542357</v>
+        <v>-0.08443340937949617</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.348567140150942</v>
+        <v>0.3061864392683151</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.1048182962969963</v>
+        <v>0.09312138403650061</v>
       </c>
     </row>
     <row r="29">
@@ -2104,44 +2104,52 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>71.31999999999999</v>
+        <v>17.39</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.01150383663896359</v>
+        <v>0.001151326968843236</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.008893821536839597</v>
+        <v>-0.03065781092732123</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.05172183801357788</v>
+        <v>-0.02303370028008023</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.03163614097463363</v>
+        <v>-0.03763145083895902</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.02663017765385844</v>
+        <v>-0.01528881427500339</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.01234922333951549</v>
-      </c>
-      <c r="M29" s="6" t="inlineStr"/>
-      <c r="N29" s="6" t="inlineStr"/>
-      <c r="O29" s="6" t="inlineStr"/>
-      <c r="P29" s="6" t="inlineStr"/>
+        <v>0.003650290702282399</v>
+      </c>
+      <c r="M29" s="6" t="n">
+        <v>0.04055548834629463</v>
+      </c>
+      <c r="N29" s="6" t="n">
+        <v>0.03848788052574958</v>
+      </c>
+      <c r="O29" s="6" t="n">
+        <v>0.4188227872074253</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v>0.1236801739473259</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
@@ -2152,52 +2160,44 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>17.37</v>
+        <v>69.45</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-0.01864406268258556</v>
+        <v>-0.02621989280122983</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.009692136112915084</v>
+        <v>-0.02635643957034095</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.04191937985181171</v>
+        <v>-0.08195643691448939</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.0005752774462597365</v>
+        <v>-0.04246521277943061</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.02305960807527185</v>
+        <v>0.0001439301049042108</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.002496089917800148</v>
-      </c>
-      <c r="M30" s="6" t="n">
-        <v>0.04612821903658482</v>
-      </c>
-      <c r="N30" s="6" t="n">
-        <v>0.02962118114114975</v>
-      </c>
-      <c r="O30" s="6" t="n">
-        <v>0.4610621610761911</v>
-      </c>
-      <c r="P30" s="6" t="n">
-        <v>0.1347222336646121</v>
-      </c>
+        <v>-0.01419446477385478</v>
+      </c>
+      <c r="M30" s="6" t="inlineStr"/>
+      <c r="N30" s="6" t="inlineStr"/>
+      <c r="O30" s="6" t="inlineStr"/>
+      <c r="P30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
@@ -2222,37 +2222,37 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>63.77</v>
+        <v>64.12</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.01101121064215294</v>
+        <v>0.005488510056545604</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.01528723974381918</v>
+        <v>-0.02091915043328185</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.03481155210661702</v>
+        <v>-0.01565853012931551</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.01431527821169509</v>
+        <v>-0.01580965088523811</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.05818931738270416</v>
+        <v>-0.05218032076387324</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>-0.01565508376421076</v>
+        <v>-0.01025249679234097</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>-0.01512050616098959</v>
+        <v>-0.01535557254882991</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-0.001387263886467927</v>
+        <v>0.01498865822225293</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.450526342094465</v>
+        <v>0.4059895530331996</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1319881313330815</v>
+        <v>0.1202820168415746</v>
       </c>
     </row>
     <row r="32">
@@ -2278,37 +2278,37 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>54.55</v>
+        <v>54.83</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.0005496993951559226</v>
+        <v>0.005132953215587044</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.006194209443770027</v>
+        <v>-0.003090875799005688</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.005831961017922827</v>
+        <v>0.0042125158124795</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.009998165752803878</v>
+        <v>0.01181035653376572</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.03536693239580602</v>
+        <v>-0.02955748971584626</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>-0.04978807217141457</v>
+        <v>-0.04491067880097765</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>-0.02362060371844676</v>
+        <v>-0.0260852666876763</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.02039764582317483</v>
+        <v>-0.006940466474240958</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.2509397386315027</v>
+        <v>0.2107564534382467</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.07748722479715098</v>
+        <v>0.06582425069386444</v>
       </c>
     </row>
     <row r="33">
@@ -2334,37 +2334,37 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>118.66</v>
+        <v>116.59</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.01240114727296615</v>
+        <v>-0.01744486145570334</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.02014859490302257</v>
+        <v>-0.03389131551990676</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.04942720562718417</v>
+        <v>-0.06862121701824275</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.03645958431292429</v>
+        <v>-0.03787757019083871</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.03465664310359706</v>
+        <v>-0.04426593671974055</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.09037749119708116</v>
+        <v>-0.1062457298401374</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>-0.002842472039621624</v>
+        <v>-0.02217204509824011</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>-0.03580137451428966</v>
+        <v>-0.04664047046851338</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.3668129328082388</v>
+        <v>0.303521021097227</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1097786352951109</v>
+        <v>0.09237733259508363</v>
       </c>
     </row>
     <row r="34">
@@ -2390,37 +2390,37 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>128.2</v>
+        <v>125.4</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>-0.006586641483260713</v>
+        <v>-0.02184083844786455</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.01354270294476068</v>
+        <v>-0.02069505242266789</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.02502097807801007</v>
+        <v>-0.04999998844031128</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.0630025574808657</v>
+        <v>-0.05494009180342352</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.06831401699358841</v>
+        <v>-0.07547636248930434</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.1083060679272645</v>
+        <v>-0.1277814110426062</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.04858722527052539</v>
+        <v>-0.07748150492986716</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.02933149071600805</v>
+        <v>0.01750589418053949</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.5205354811942273</v>
+        <v>0.4979799307279833</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1499144186330097</v>
+        <v>0.1442001445775207</v>
       </c>
     </row>
   </sheetData>
@@ -2560,17 +2560,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -2650,17 +2650,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -2695,17 +2695,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -2717,17 +2717,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -2740,17 +2740,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2762,17 +2762,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -2785,17 +2785,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -2830,17 +2830,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2852,17 +2852,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -2875,17 +2875,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2942,17 +2942,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.373346129453924</v>
+        <v>0.3314464121405516</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.0630025574808657</v>
+        <v>-0.05494009180342352</v>
       </c>
     </row>
     <row r="18">
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.2325697257986856</v>
+        <v>0.1387471825671691</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.04435482811398539</v>
+        <v>-0.05437757062359538</v>
       </c>
     </row>
     <row r="19">
@@ -3130,7 +3130,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.1262563401572701</v>
+        <v>0.09317667726566947</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -3138,21 +3138,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.03712643957748663</v>
+        <v>-0.04246521277943061</v>
       </c>
     </row>
     <row r="20">
@@ -3161,21 +3161,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.1129536335976453</v>
+        <v>0.08193805377323438</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.03645958431292429</v>
+        <v>-0.03787757019083871</v>
       </c>
     </row>
     <row r="21">
@@ -3206,21 +3206,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.08973462812827826</v>
+        <v>0.07970675214713219</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -3228,21 +3228,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.03163614097463363</v>
+        <v>-0.03763145083895902</v>
       </c>
     </row>
     <row r="22">
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.08684684134818421</v>
+        <v>0.07894736108283862</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -3273,21 +3273,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.02486442692324242</v>
+        <v>-0.02545762402264817</v>
       </c>
     </row>
     <row r="23">
@@ -3296,21 +3296,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.08194769288968984</v>
+        <v>0.07187979899173458</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.01404423679616229</v>
+        <v>-0.02363022298298245</v>
       </c>
     </row>
     <row r="24">
@@ -3341,21 +3341,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.07115844422033213</v>
+        <v>0.06842791453224506</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -3363,21 +3363,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.01372646526726273</v>
+        <v>-0.02135967582959153</v>
       </c>
     </row>
     <row r="25">
@@ -3386,12 +3386,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.07045235406470129</v>
+        <v>0.06390373290087736</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -3408,21 +3408,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.005616287654894858</v>
+        <v>-0.01580965088523811</v>
       </c>
     </row>
     <row r="26">
@@ -3431,21 +3431,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.06760242248898085</v>
+        <v>0.05976529985069234</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -3453,21 +3453,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.002859182452283227</v>
+        <v>-0.01007706389074903</v>
       </c>
     </row>
     <row r="27"/>
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.2752489456223861</v>
+        <v>0.2008604837530263</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.08161138899559306</v>
+        <v>-0.1124759287915646</v>
       </c>
     </row>
     <row r="32">
@@ -3596,7 +3596,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.2401315882347959</v>
+        <v>0.1936919128262218</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -3618,7 +3618,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.06831401699358841</v>
+        <v>-0.07547636248930434</v>
       </c>
     </row>
     <row r="33">
@@ -3627,21 +3627,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.2399800167953714</v>
+        <v>0.1872557048402588</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -3649,21 +3649,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.05818931738270416</v>
+        <v>-0.05788803002254062</v>
       </c>
     </row>
     <row r="34">
@@ -3672,21 +3672,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.2322781153268592</v>
+        <v>0.1593682627783228</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -3694,21 +3694,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.04859098388139238</v>
+        <v>-0.05218032076387324</v>
       </c>
     </row>
     <row r="35">
@@ -3717,21 +3717,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.2316495223574528</v>
+        <v>0.1535305581711912</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -3739,21 +3739,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.04588905880244154</v>
+        <v>-0.0482106148601591</v>
       </c>
     </row>
     <row r="36">
@@ -3762,21 +3762,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.2078769219870533</v>
+        <v>0.1484374859331483</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.03536693239580602</v>
+        <v>-0.04426593671974055</v>
       </c>
     </row>
     <row r="37">
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.2010546619460312</v>
+        <v>0.1441384371018783</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -3829,21 +3829,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.03465664310359706</v>
+        <v>-0.03530867360984635</v>
       </c>
     </row>
     <row r="38">
@@ -3852,21 +3852,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1481481274924346</v>
+        <v>0.1320522441537815</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -3874,21 +3874,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.02559310598031661</v>
+        <v>-0.02955748971584626</v>
       </c>
     </row>
     <row r="39">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3911,7 +3911,7 @@
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1406816694440927</v>
+        <v>0.1184233604010767</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -3919,21 +3919,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FDCPX</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.02305960807527185</v>
+        <v>-0.02855842581672108</v>
       </c>
     </row>
     <row r="40">
@@ -3942,21 +3942,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1322761212192012</v>
+        <v>0.1169777734408337</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -3964,21 +3964,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.004282685127513952</v>
+        <v>-0.02434723113417514</v>
       </c>
     </row>
     <row r="41"/>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.4267036834460756</v>
+        <v>0.4082743007229339</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1083060679272645</v>
+        <v>-0.1277814110426062</v>
       </c>
     </row>
     <row r="46">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.4095859555758101</v>
+        <v>0.3952907899621267</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -4115,21 +4115,21 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.09037749119708116</v>
+        <v>-0.1243238928336534</v>
       </c>
     </row>
     <row r="47">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4152,7 +4152,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.4072308786961814</v>
+        <v>0.3864010997099081</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -4160,21 +4160,21 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.0805464588454059</v>
+        <v>-0.1062457298401374</v>
       </c>
     </row>
     <row r="48">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.4071502959075652</v>
+        <v>0.368288655662699</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -4205,21 +4205,21 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.04978807217141457</v>
+        <v>-0.0470415556179471</v>
       </c>
     </row>
     <row r="49">
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.2771140955130174</v>
+        <v>0.2671861784273049</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -4250,21 +4250,21 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.0198141395634166</v>
+        <v>-0.04491067880097765</v>
       </c>
     </row>
     <row r="50">
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.2453384935806155</v>
+        <v>0.2118209613786664</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -4295,21 +4295,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.01565508376421076</v>
+        <v>-0.02019102771715664</v>
       </c>
     </row>
     <row r="51">
@@ -4318,21 +4318,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.1967864944729936</v>
+        <v>0.1879118918153904</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -4340,21 +4340,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.01370670379271199</v>
+        <v>-0.01419446477385478</v>
       </c>
     </row>
     <row r="52">
@@ -4377,7 +4377,7 @@
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.1853172043875482</v>
+        <v>0.1726484957399832</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4385,21 +4385,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-0.007599011540526557</v>
+        <v>-0.01025249679234097</v>
       </c>
     </row>
     <row r="53">
@@ -4422,7 +4422,7 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.1736329370325238</v>
+        <v>0.1716403058028275</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -4430,21 +4430,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>-0.003647931003766924</v>
+        <v>-0.01017158883893765</v>
       </c>
     </row>
     <row r="54">
@@ -4453,21 +4453,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.1601312408328082</v>
+        <v>0.1713905186813049</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -4475,21 +4475,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.002496089917800148</v>
+        <v>-0.004595395480073927</v>
       </c>
     </row>
     <row r="55"/>
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.9736038367895916</v>
+        <v>0.939834632220764</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.08991014501756156</v>
+        <v>-0.1149652953290186</v>
       </c>
     </row>
     <row r="60">
@@ -4618,7 +4618,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.8423947499575954</v>
+        <v>0.8416097029766065</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.06798614793542357</v>
+        <v>-0.08443340937949617</v>
       </c>
     </row>
     <row r="61">
@@ -4663,7 +4663,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.7074525665280891</v>
+        <v>0.5832681933564661</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4671,21 +4671,21 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.04772971899036516</v>
+        <v>-0.04664047046851338</v>
       </c>
     </row>
     <row r="62">
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.6181919951898354</v>
+        <v>0.5784819214331203</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4716,21 +4716,21 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.03580137451428966</v>
+        <v>-0.04349391154757565</v>
       </c>
     </row>
     <row r="63">
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.5187817415959493</v>
+        <v>0.5414800205477082</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.02039764582317483</v>
+        <v>-0.006940466474240958</v>
       </c>
     </row>
     <row r="64">
@@ -4798,7 +4798,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.5047651803675064</v>
+        <v>0.5005851217043742</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4820,7 +4820,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.001387263886467927</v>
+        <v>0.01498865822225293</v>
       </c>
     </row>
     <row r="65">
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.478402558161541</v>
+        <v>0.4567925944299629</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4865,7 +4865,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.02933149071600805</v>
+        <v>0.01750589418053949</v>
       </c>
     </row>
     <row r="66">
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.3662436883965514</v>
+        <v>0.3392627167153628</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4896,21 +4896,21 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>0.02962118114114975</v>
+        <v>0.02097991896250861</v>
       </c>
     </row>
     <row r="67">
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.2773662166329907</v>
+        <v>0.2738968069996928</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4941,21 +4941,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.04298906904814004</v>
+        <v>0.03848788052574958</v>
       </c>
     </row>
     <row r="68">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.2361016285851618</v>
+        <v>0.2182831463538515</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -4986,21 +4986,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.07535296835113425</v>
+        <v>0.05952568005984582</v>
       </c>
     </row>
     <row r="69"/>
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.673067833403502</v>
+        <v>2.389762640584165</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5092,21 +5092,21 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.08850850170548163</v>
+        <v>0.0691574333283469</v>
       </c>
     </row>
     <row r="74">
@@ -5129,7 +5129,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.589377693306653</v>
+        <v>2.296073536551117</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5137,21 +5137,21 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.09068754921656508</v>
+        <v>0.08940260585231186</v>
       </c>
     </row>
     <row r="75">
@@ -5174,7 +5174,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.298025746529321</v>
+        <v>2.149964916355807</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5182,21 +5182,21 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1674856391966872</v>
+        <v>0.1567024149097707</v>
       </c>
     </row>
     <row r="76">
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.583719627133914</v>
+        <v>1.428788446688389</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5227,21 +5227,21 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.2112091376471747</v>
+        <v>0.1603786587505707</v>
       </c>
     </row>
     <row r="77">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.206027447373407</v>
+        <v>1.142340019433309</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5272,21 +5272,21 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.2509397386315027</v>
+        <v>0.209207857604613</v>
       </c>
     </row>
     <row r="78">
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.157711817732169</v>
+        <v>1.067918410549169</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5317,21 +5317,21 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.2741258091142853</v>
+        <v>0.2107564534382467</v>
       </c>
     </row>
     <row r="79">
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.076925571545445</v>
+        <v>1.013632394404492</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.2902026718969819</v>
+        <v>0.2351730690360279</v>
       </c>
     </row>
     <row r="80">
@@ -5399,7 +5399,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.9970646014038262</v>
+        <v>0.9561633399053882</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5421,7 +5421,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.3235224246978083</v>
+        <v>0.2836121993018388</v>
       </c>
     </row>
     <row r="81">
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.8746873815794078</v>
+        <v>0.7766513530977373</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5452,12 +5452,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5466,7 +5466,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.348567140150942</v>
+        <v>0.303521021097227</v>
       </c>
     </row>
     <row r="82">
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.8177993464160542</v>
+        <v>0.7380800740649665</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.3668129328082388</v>
+        <v>0.3061864392683151</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -627,7 +627,7 @@
         <v>0.4082743007229339</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.6881454474007416</v>
+        <v>0.6881453457812148</v>
       </c>
       <c r="N2" s="6" t="n">
         <v>0.939834632220764</v>
@@ -686,13 +686,13 @@
         <v>0.4948367280718573</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.5414800205477082</v>
+        <v>0.5414801182342481</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.6519621868699921</v>
+        <v>0.6519620746787196</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.182133978853632</v>
+        <v>0.1821339520925034</v>
       </c>
     </row>
     <row r="4">
@@ -739,16 +739,16 @@
         <v>0.368288655662699</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.5416973740560633</v>
+        <v>0.5416975252465026</v>
       </c>
       <c r="N4" s="6" t="n">
         <v>0.8416097029766065</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>2.296073536551117</v>
+        <v>2.296073191017931</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.4882148397605377</v>
+        <v>0.4882147877564764</v>
       </c>
     </row>
     <row r="5">
@@ -801,10 +801,10 @@
         <v>0.5784819214331203</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1.013632394404492</v>
+        <v>1.01363252173008</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2627771937894383</v>
+        <v>0.2627772204053265</v>
       </c>
     </row>
     <row r="6">
@@ -913,10 +913,10 @@
         <v>0.3392627167153628</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.4516850568560895</v>
+        <v>0.4516849206932829</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1322894707423801</v>
+        <v>0.1322894353408268</v>
       </c>
     </row>
     <row r="8">
@@ -969,10 +969,10 @@
         <v>0.5832681933564661</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>2.389762640584165</v>
+        <v>2.389762961891512</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.5021838767760864</v>
+        <v>0.502183924238869</v>
       </c>
     </row>
     <row r="9">
@@ -1081,10 +1081,10 @@
         <v>0.1522097878853794</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.9561633399053882</v>
+        <v>0.9561635467821921</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2506478433609944</v>
+        <v>0.2506478874489997</v>
       </c>
     </row>
     <row r="11">
@@ -1134,7 +1134,7 @@
         <v>0.0901921474306695</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.05952568005984582</v>
+        <v>0.0595255928072318</v>
       </c>
       <c r="O11" s="6" t="n">
         <v>0.3891324430063932</v>
@@ -1249,10 +1249,10 @@
         <v>0.02097991896250861</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2836121993018388</v>
+        <v>0.2836120625156715</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.08678744335664335</v>
+        <v>0.08678740475269575</v>
       </c>
     </row>
     <row r="14">
@@ -1299,16 +1299,16 @@
         <v>0.09877628132474903</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.1196874718444494</v>
+        <v>0.1196875705541798</v>
       </c>
       <c r="N14" s="6" t="n">
         <v>0.09433055289171954</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.5801953484251889</v>
+        <v>0.580195250124214</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.1647612835686416</v>
+        <v>0.1647612594161063</v>
       </c>
     </row>
     <row r="15">
@@ -1361,10 +1361,10 @@
         <v>0.2738968069996928</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.7766513530977373</v>
+        <v>0.7766511498389226</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.2111578183124225</v>
+        <v>0.2111577721246864</v>
       </c>
     </row>
     <row r="16">
@@ -1473,10 +1473,10 @@
         <v>0.0625189981264227</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.1567024149097707</v>
+        <v>0.1567025111555695</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.04972098857513507</v>
+        <v>0.04972101768986414</v>
       </c>
     </row>
     <row r="18">
@@ -1529,10 +1529,10 @@
         <v>0.2182831463538515</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.4515466919016697</v>
+        <v>0.4515468263196243</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.1322534955014953</v>
+        <v>0.1322535304516155</v>
       </c>
     </row>
     <row r="19">
@@ -1576,19 +1576,19 @@
         <v>-0.03530867360984635</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.07007972379144078</v>
+        <v>0.07007959810888864</v>
       </c>
       <c r="M19" s="6" t="n">
         <v>0.2022629817281612</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1566800741529377</v>
+        <v>0.1566799273045356</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.7380800740649665</v>
+        <v>0.7380805714282443</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.2023288280210374</v>
+        <v>0.2023289427058477</v>
       </c>
     </row>
     <row r="20">
@@ -1641,10 +1641,10 @@
         <v>0.1186180138828288</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.1603786587505707</v>
+        <v>0.1603788760497415</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.05083189062510329</v>
+        <v>0.05083195622003722</v>
       </c>
     </row>
     <row r="21">
@@ -1747,16 +1747,16 @@
         <v>-0.02019102771715664</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.1913213477876539</v>
+        <v>0.1913212431592726</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1599339405909979</v>
+        <v>0.1599338414032176</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.2351730690360279</v>
+        <v>0.2351729565632854</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.07294123918867146</v>
+        <v>0.07294120662194037</v>
       </c>
     </row>
     <row r="23">
@@ -1809,10 +1809,10 @@
         <v>0.08407216196794565</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.0691574333283469</v>
+        <v>0.06915735546100699</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.02254058246146418</v>
+        <v>0.02254055763739404</v>
       </c>
     </row>
     <row r="24">
@@ -1865,10 +1865,10 @@
         <v>0.1114551074349475</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.335031630932219</v>
+        <v>0.3350313915880621</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1011095226261269</v>
+        <v>0.1011094568239042</v>
       </c>
     </row>
     <row r="25">
@@ -1977,10 +1977,10 @@
         <v>0.1698603585553631</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.6926794456816388</v>
+        <v>0.6926796586123447</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1917675978727857</v>
+        <v>0.1917676478456076</v>
       </c>
     </row>
     <row r="27">
@@ -2249,10 +2249,10 @@
         <v>0.01498865822225293</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.4059895530331996</v>
+        <v>0.4059894354268698</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1202820168415746</v>
+        <v>0.1202819856056241</v>
       </c>
     </row>
     <row r="32">
@@ -2414,7 +2414,7 @@
         <v>-0.07748150492986716</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.01750589418053949</v>
+        <v>0.01750583119129878</v>
       </c>
       <c r="O34" s="6" t="n">
         <v>0.4979799307279833</v>
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.5414800205477082</v>
+        <v>0.5414801182342481</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4865,7 +4865,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.01750589418053949</v>
+        <v>0.01750583119129878</v>
       </c>
     </row>
     <row r="66">
@@ -5000,7 +5000,7 @@
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.05952568005984582</v>
+        <v>0.0595255928072318</v>
       </c>
     </row>
     <row r="69"/>
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.389762640584165</v>
+        <v>2.389762961891512</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.0691574333283469</v>
+        <v>0.06915735546100699</v>
       </c>
     </row>
     <row r="74">
@@ -5129,7 +5129,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.296073536551117</v>
+        <v>2.296073191017931</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1567024149097707</v>
+        <v>0.1567025111555695</v>
       </c>
     </row>
     <row r="76">
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1603786587505707</v>
+        <v>0.1603788760497415</v>
       </c>
     </row>
     <row r="77">
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.013632394404492</v>
+        <v>1.01363252173008</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.2351730690360279</v>
+        <v>0.2351729565632854</v>
       </c>
     </row>
     <row r="80">
@@ -5399,7 +5399,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.9561633399053882</v>
+        <v>0.9561635467821921</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5421,7 +5421,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.2836121993018388</v>
+        <v>0.2836120625156715</v>
       </c>
     </row>
     <row r="81">
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.7766513530977373</v>
+        <v>0.7766511498389226</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.7380800740649665</v>
+        <v>0.7380805714282443</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -683,10 +683,10 @@
         <v>0.1879118918153904</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.4948367280718573</v>
+        <v>0.4948368199360886</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.5414801182342481</v>
+        <v>0.5414800205477082</v>
       </c>
       <c r="O3" s="6" t="n">
         <v>0.6519620746787196</v>
@@ -739,7 +739,7 @@
         <v>0.368288655662699</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.5416975252465026</v>
+        <v>0.5416973740560633</v>
       </c>
       <c r="N4" s="6" t="n">
         <v>0.8416097029766065</v>
@@ -801,10 +801,10 @@
         <v>0.5784819214331203</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1.01363252173008</v>
+        <v>1.013632776381304</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2627772204053265</v>
+        <v>0.2627772736371099</v>
       </c>
     </row>
     <row r="6">
@@ -851,16 +851,16 @@
         <v>0.3864010997099081</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.3837401593199061</v>
+        <v>0.3837400260083434</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>0.5005851217043742</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>1.428788446688389</v>
+        <v>1.428788652044763</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.3441979522241667</v>
+        <v>0.344197990108571</v>
       </c>
     </row>
     <row r="7">
@@ -969,10 +969,10 @@
         <v>0.5832681933564661</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>2.389762961891512</v>
+        <v>2.389762640584165</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.502183924238869</v>
+        <v>0.5021838767760864</v>
       </c>
     </row>
     <row r="9">
@@ -1025,10 +1025,10 @@
         <v>0.4567925944299629</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.693129899035515</v>
+        <v>0.6931300550793342</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1918733056406818</v>
+        <v>0.1918733422561942</v>
       </c>
     </row>
     <row r="10">
@@ -1075,7 +1075,7 @@
         <v>0.1716403058028275</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.1700790556514515</v>
+        <v>0.1700791296685333</v>
       </c>
       <c r="N10" s="6" t="n">
         <v>0.1522097878853794</v>
@@ -1134,13 +1134,13 @@
         <v>0.0901921474306695</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.0595255928072318</v>
+        <v>0.05952568005984582</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.3891324430063932</v>
+        <v>0.3891325929896787</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.1157867969190642</v>
+        <v>0.1157868370758697</v>
       </c>
     </row>
     <row r="12">
@@ -1299,16 +1299,16 @@
         <v>0.09877628132474903</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.1196875705541798</v>
+        <v>0.1196874718444494</v>
       </c>
       <c r="N14" s="6" t="n">
         <v>0.09433055289171954</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.580195250124214</v>
+        <v>0.5801954467261763</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.1647612594161063</v>
+        <v>0.1647613077211791</v>
       </c>
     </row>
     <row r="15">
@@ -1355,16 +1355,16 @@
         <v>0.1726484957399832</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.2606904803055712</v>
+        <v>0.2606903779616794</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.2738968069996928</v>
+        <v>0.2738967025003693</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.7766511498389226</v>
+        <v>0.7766513530977373</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.2111577721246864</v>
+        <v>0.2111578183124225</v>
       </c>
     </row>
     <row r="16">
@@ -1473,10 +1473,10 @@
         <v>0.0625189981264227</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.1567025111555695</v>
+        <v>0.1567024149097707</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.04972101768986414</v>
+        <v>0.04972098857513507</v>
       </c>
     </row>
     <row r="18">
@@ -1529,10 +1529,10 @@
         <v>0.2182831463538515</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.4515468263196243</v>
+        <v>0.4515466919016697</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.1322535304516155</v>
+        <v>0.1322534955014953</v>
       </c>
     </row>
     <row r="19">
@@ -1576,19 +1576,19 @@
         <v>-0.03530867360984635</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.07007959810888864</v>
+        <v>0.07007972379144078</v>
       </c>
       <c r="M19" s="6" t="n">
         <v>0.2022629817281612</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1566799273045356</v>
+        <v>0.1566800007287321</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.7380805714282443</v>
+        <v>0.7380804056404535</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.2023289427058477</v>
+        <v>0.2023289044775727</v>
       </c>
     </row>
     <row r="20">
@@ -1641,10 +1641,10 @@
         <v>0.1186180138828288</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.1603788760497415</v>
+        <v>0.1603785501010158</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.05083195622003722</v>
+        <v>0.05083185782764255</v>
       </c>
     </row>
     <row r="21">
@@ -1697,10 +1697,10 @@
         <v>-0.04349391154757565</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.6505308013950086</v>
+        <v>0.6505309128813304</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1817924499788774</v>
+        <v>0.1817924765872247</v>
       </c>
     </row>
     <row r="22">
@@ -1747,10 +1747,10 @@
         <v>-0.02019102771715664</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.1913212431592726</v>
+        <v>0.1913213477876539</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1599338414032176</v>
+        <v>0.1599339405909979</v>
       </c>
       <c r="O22" s="6" t="n">
         <v>0.2351729565632854</v>
@@ -1809,10 +1809,10 @@
         <v>0.08407216196794565</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.06915735546100699</v>
+        <v>0.0691574333283469</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.02254055763739404</v>
+        <v>0.02254058246146418</v>
       </c>
     </row>
     <row r="24">
@@ -1977,10 +1977,10 @@
         <v>0.1698603585553631</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.6926796586123447</v>
+        <v>0.6926795521469851</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1917676478456076</v>
+        <v>0.1917676228591956</v>
       </c>
     </row>
     <row r="27">
@@ -2089,10 +2089,10 @@
         <v>-0.08443340937949617</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.3061864392683151</v>
+        <v>0.3061865366985992</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.09312138403650061</v>
+        <v>0.09312141121565376</v>
       </c>
     </row>
     <row r="29">
@@ -2249,10 +2249,10 @@
         <v>0.01498865822225293</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.4059894354268698</v>
+        <v>0.4059893178205598</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1202819856056241</v>
+        <v>0.1202819543696771</v>
       </c>
     </row>
     <row r="32">
@@ -2358,13 +2358,13 @@
         <v>-0.02217204509824011</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>-0.04664047046851338</v>
+        <v>-0.04664041099244709</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.303521021097227</v>
+        <v>0.3035211322870146</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.09237733259508363</v>
+        <v>0.09237736365485638</v>
       </c>
     </row>
     <row r="34">
@@ -4685,7 +4685,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.04664047046851338</v>
+        <v>-0.04664041099244709</v>
       </c>
     </row>
     <row r="62">
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.5414801182342481</v>
+        <v>0.5414800205477082</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.2738968069996928</v>
+        <v>0.2738967025003693</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -5000,7 +5000,7 @@
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.0595255928072318</v>
+        <v>0.05952568005984582</v>
       </c>
     </row>
     <row r="69"/>
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.389762961891512</v>
+        <v>2.389762640584165</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.06915735546100699</v>
+        <v>0.0691574333283469</v>
       </c>
     </row>
     <row r="74">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1567025111555695</v>
+        <v>0.1567024149097707</v>
       </c>
     </row>
     <row r="76">
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.428788446688389</v>
+        <v>1.428788652044763</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1603788760497415</v>
+        <v>0.1603785501010158</v>
       </c>
     </row>
     <row r="77">
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.01363252173008</v>
+        <v>1.013632776381304</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.7766511498389226</v>
+        <v>0.7766513530977373</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5466,7 +5466,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.303521021097227</v>
+        <v>0.3035211322870146</v>
       </c>
     </row>
     <row r="82">
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.7380805714282443</v>
+        <v>0.7380804056404535</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.3061864392683151</v>
+        <v>0.3061865366985992</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -490,8 +490,8 @@
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>213.96</v>
+        <v>211.76</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>-0.01291745646764375</v>
+        <v>-0.01028235248643161</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.01958542049469458</v>
+        <v>-0.003247834555508811</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>-0.05773550089172552</v>
+        <v>-0.02724060759825864</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.03657769932564459</v>
+        <v>0.0259192420416039</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>-0.02855842581672108</v>
+        <v>-0.07350368932101059</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.4082743007229339</v>
+        <v>0.3937939279653178</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.6881453457812148</v>
+        <v>0.6838470702366788</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.939834632220764</v>
+        <v>0.9198885687668827</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.149964916355807</v>
+        <v>2.047118468042688</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4658917666341071</v>
+        <v>0.4497611129313885</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>92.79000000000001</v>
+        <v>94.06</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.02394612782140038</v>
+        <v>0.01368678338760398</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.01199692927071339</v>
+        <v>0.04221603943040164</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.01743425461063897</v>
+        <v>0.01697480517987149</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.07970675214713219</v>
+        <v>0.09448446458590332</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.1535305581711912</v>
+        <v>0.1502996382545341</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.1879118918153904</v>
+        <v>0.2041705845622266</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.4948368199360886</v>
+        <v>0.5054270071702542</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.5414800205477082</v>
+        <v>0.5625780227088186</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.6519620746787196</v>
+        <v>0.638365120877719</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.1821339520925034</v>
+        <v>0.1788817138945482</v>
       </c>
     </row>
     <row r="4">
@@ -704,51 +704,51 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>59.97</v>
+        <v>30.56</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.0292974683450512</v>
+        <v>0.006256128464228849</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.02024502324122857</v>
+        <v>-0.03045688381596556</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>-0.07965012507241831</v>
+        <v>0.01528236141670747</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.0131779458031982</v>
+        <v>0.08870679722797759</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>-0.1124759287915646</v>
+        <v>0.2204472183941526</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.368288655662699</v>
+        <v>0.2194022689886967</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.5416973740560633</v>
+        <v>0.2818211186413124</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.8416097029766065</v>
+        <v>0.5883571071120688</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>2.296073191017931</v>
+        <v>0.994608215142561</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.4882147877564764</v>
+        <v>0.2587878270619526</v>
       </c>
     </row>
     <row r="5">
@@ -760,51 +760,51 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>30.37</v>
+        <v>58.93</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.02691439506184312</v>
+        <v>-0.01734201924892254</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.01555914218155552</v>
+        <v>-0.01405387562580784</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.01878568880656339</v>
+        <v>-0.04905600864361015</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.08193805377323438</v>
+        <v>-0.004392605635504809</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.1872557048402588</v>
+        <v>-0.1461894643384374</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.2118209613786664</v>
+        <v>0.344559767458114</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.2492504949103009</v>
+        <v>0.5122475919828533</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.5784819214331203</v>
+        <v>0.8096724720585837</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1.013632776381304</v>
+        <v>2.245501211221454</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2627772736371099</v>
+        <v>0.4805642496720317</v>
       </c>
     </row>
     <row r="6">
@@ -830,37 +830,37 @@
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>54.79</v>
+        <v>54.18</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-0.01474554371199877</v>
+        <v>-0.01113342946082507</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.03946123823150316</v>
+        <v>0.0168919209177727</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-0.02143241162646659</v>
+        <v>-0.006236246326727146</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.04881315381181639</v>
+        <v>0.03713626654626712</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>-0.01686701299892501</v>
+        <v>-0.05527459901111864</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.3864010997099081</v>
+        <v>0.3709657008618776</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.3837400260083434</v>
+        <v>0.3606975128666878</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.5005851217043742</v>
+        <v>0.4838784631019151</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>1.428788652044763</v>
+        <v>1.394599853504655</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.344197990108571</v>
+        <v>0.3378609694020667</v>
       </c>
     </row>
     <row r="7">
@@ -886,37 +886,37 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>29.52</v>
+        <v>29.41</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.02122013902143149</v>
+        <v>-0.003726307880955071</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.02186878199928055</v>
+        <v>-0.03573770992091441</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.02393342129322207</v>
+        <v>0.0127410096494498</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.07894736108283862</v>
+        <v>0.07492687102809992</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.1936919128262218</v>
+        <v>0.209292772058346</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.1713905186813049</v>
+        <v>0.1670255569598669</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.1341733715392723</v>
+        <v>0.1485967013835996</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.3392627167153628</v>
+        <v>0.334272211499397</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.4516849206932829</v>
+        <v>0.4380023965913902</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1322894353408268</v>
+        <v>0.1287208216871976</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>68.20999999999999</v>
+        <v>35.3</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.04761244807788156</v>
+        <v>0.007420043228879791</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.04854238022627877</v>
+        <v>-0.04102151806291732</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.07164175097057512</v>
+        <v>0.01436781640694762</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.3314464121405516</v>
+        <v>0.04654609297750745</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.1149068117723129</v>
+        <v>0.09661387831719592</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>-0.1243238928336534</v>
+        <v>0.08693971471259831</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.2419516225667264</v>
+        <v>0.1763081839799363</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.5832681933564661</v>
+        <v>0.4676020584561451</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>2.389762640584165</v>
+        <v>0.6909039080879833</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.5021838767760864</v>
+        <v>0.1913507501978058</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>35.04</v>
+        <v>65.42</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.01848739028872126</v>
+        <v>-0.04090310735926195</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.03391231118589755</v>
+        <v>-0.104203761982109</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.02726474020916747</v>
+        <v>0.05772028751654634</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.03883787106639724</v>
+        <v>0.2769861166016625</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.06504557113667997</v>
+        <v>0.1009761054340756</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.0789339779550644</v>
+        <v>-0.160141766657019</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.1459137477635846</v>
+        <v>0.1942663937200362</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.4567925944299629</v>
+        <v>0.518507604465102</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.6931300550793342</v>
+        <v>2.276498777913448</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1918733422561942</v>
+        <v>0.4852629126962746</v>
       </c>
     </row>
     <row r="10">
@@ -1054,37 +1054,37 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>17.64</v>
+        <v>17.48</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.001697831721334087</v>
+        <v>-0.009070286448309095</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.006756803923811283</v>
+        <v>-0.01465615739776571</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.008431788541842233</v>
+        <v>-0.01687295460199334</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.01965318887757705</v>
+        <v>0.01040464237652561</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.1484374859331483</v>
+        <v>0.1387621568620874</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.1716403058028275</v>
+        <v>0.1610131926148113</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.1700791296685333</v>
+        <v>0.1637980368635252</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.1522097878853794</v>
+        <v>0.1417589150607137</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.9561635467821921</v>
+        <v>0.9185671489311815</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2506478874489997</v>
+        <v>0.2425837447842376</v>
       </c>
     </row>
     <row r="11">
@@ -1096,51 +1096,51 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>24.54</v>
+        <v>116.44</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.008484811493844724</v>
+        <v>0.01729864907191137</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.06233768442760512</v>
+        <v>0.00483263031810055</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.05457672680620673</v>
+        <v>0.01173000387933087</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.1387471825671691</v>
+        <v>-0.008599357454909251</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.1169777734408337</v>
+        <v>0.1048486869318945</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.3952907899621267</v>
+        <v>0.1513893563115947</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.0901921474306695</v>
+        <v>0.1270808629399602</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.05952568005984582</v>
+        <v>0.2095870600542149</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.3891325929896787</v>
+        <v>0.1074417837519781</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.1157868370758697</v>
+        <v>0.03460276594911504</v>
       </c>
     </row>
     <row r="12">
@@ -1166,37 +1166,37 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>37.6</v>
+        <v>37.27</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.008177298194111615</v>
+        <v>-0.008776543344398036</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.01182656430913021</v>
+        <v>-0.01765941468626331</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>-0.05026526069201631</v>
+        <v>-0.05285890970809959</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-0.02363022298298245</v>
+        <v>-0.03219937465113254</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.08764821539036705</v>
+        <v>0.09328249606752714</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.1335683823126046</v>
+        <v>0.1236195702713989</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.1890114250052368</v>
+        <v>0.1721615988828955</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.1934801249080289</v>
+        <v>0.1830054948610962</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.142340019433309</v>
+        <v>1.088871642167592</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2891282733919374</v>
+        <v>0.2783131348049144</v>
       </c>
     </row>
     <row r="13">
@@ -1208,51 +1208,51 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>45.95</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.007773711934268901</v>
+        <v>0.000309584920789252</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.007233709749695727</v>
+        <v>-0.01363586428885022</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.03607671575799465</v>
+        <v>0.003935755995929435</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.06390373290087736</v>
+        <v>-0.004825474469610236</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.1320522441537815</v>
+        <v>0.1575113778109249</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.2671861784273049</v>
+        <v>0.09911644589276802</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.08087137195678684</v>
+        <v>0.124750070226006</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.02097991896250861</v>
+        <v>0.09466934112925385</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2836120625156715</v>
+        <v>0.5681864314717839</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.08678740475269575</v>
+        <v>0.1618031882755273</v>
       </c>
     </row>
     <row r="14">
@@ -1264,51 +1264,51 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>96.90000000000001</v>
+        <v>14.8</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.004929099826219363</v>
+        <v>-0.0006752348817350429</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.02061856544561402</v>
+        <v>-0.008042887730928872</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.008114843497802671</v>
+        <v>0.004752250554918014</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-0.00513347014545118</v>
+        <v>0.04741684861058149</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.1593682627783228</v>
+        <v>-0.05852417688716949</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.09877628132474903</v>
+        <v>0.1718566825716454</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.1196874718444494</v>
+        <v>0.2669112116183805</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.09433055289171954</v>
+        <v>0.2730366274398757</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.5801954467261763</v>
+        <v>0.7721390846427458</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.1647613077211791</v>
+        <v>0.2101315988833097</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>14.81</v>
+        <v>23.77</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.01068803236861038</v>
+        <v>-0.03137736059644824</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.002029816453824607</v>
+        <v>0.03078928917018842</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-0.006706869806760385</v>
+        <v>0.0241275913563328</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.04812457888664978</v>
+        <v>0.1030163015915697</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>-0.05788803002254062</v>
+        <v>0.01581200193441012</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.1726484957399832</v>
+        <v>0.3515102477085821</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.2606903779616794</v>
+        <v>0.05828202911396807</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.2738967025003693</v>
+        <v>0.02628056073541107</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.7766513530977373</v>
+        <v>0.3369035369195423</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.2111578183124225</v>
+        <v>0.1016239201520925</v>
       </c>
     </row>
     <row r="16">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1390,37 +1390,37 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>114.46</v>
+        <v>52.07</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.01046078588767119</v>
+        <v>-0.01810294374073118</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.01302062706162066</v>
+        <v>-0.03431006188695651</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.004868697399909916</v>
+        <v>0.01898241193088035</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-0.02545762402264817</v>
+        <v>0.07338696137844969</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.08093304130911161</v>
+        <v>0.1839472541335212</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.1318105625737487</v>
+        <v>0.06851058033729318</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.08959668910789031</v>
+        <v>-0.02709858395191111</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.189018643795241</v>
+        <v>0.04328427647988198</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.08940260585231186</v>
+        <v>0.1323078898656993</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.02895441885317029</v>
+        <v>0.04228905626306578</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>53.03</v>
+        <v>44.95</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.01412905973777523</v>
+        <v>-0.02176278527521902</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.01174060883165695</v>
+        <v>-0.01598072542380469</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.03151135842624031</v>
+        <v>0.008073572754420999</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.09317667726566947</v>
+        <v>0.0407502244082516</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.2008604837530263</v>
+        <v>0.06164384980976512</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.08821039183883062</v>
+        <v>0.239608677722466</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>-0.01905004444495251</v>
+        <v>0.06428558332031953</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.0625189981264227</v>
+        <v>-0.001239447784183056</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.1567024149097707</v>
+        <v>0.2425970901813472</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.04972098857513507</v>
+        <v>0.07508658835438875</v>
       </c>
     </row>
     <row r="18">
@@ -1488,51 +1488,51 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>119.59</v>
+        <v>69.44</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.01515279554196569</v>
+        <v>-0.00100704492408199</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.01886949760665224</v>
+        <v>-0.0001439093920102552</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.02969577007796653</v>
+        <v>0.007398841345894747</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-0.008045796618664447</v>
+        <v>0.05869806858475934</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.002514841311600957</v>
+        <v>-0.02327324362516248</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.04511177933499133</v>
+        <v>0.06900197988124934</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.1970965850415967</v>
+        <v>0.2119205126059298</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.2182831463538515</v>
+        <v>0.1555152453554753</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.4515466919016697</v>
+        <v>0.7435612641683127</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.1322534955014953</v>
+        <v>0.2035913853865894</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>69.51000000000001</v>
+        <v>94.55</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.006224671305415042</v>
+        <v>0</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.007829504218788585</v>
+        <v>-0.01817237740957744</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.005642352056586475</v>
+        <v>-0.0007397980637529056</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.05976529985069234</v>
+        <v>0.008103231995007398</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>-0.03530867360984635</v>
+        <v>0.06731581938118913</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.07007972379144078</v>
+        <v>-0.004595395480073927</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.2022629817281612</v>
+        <v>0.1292025531769105</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1566800007287321</v>
+        <v>0.1186180138828288</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.7380804056404535</v>
+        <v>0.1680659018023558</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.2023289044775727</v>
+        <v>0.05314729205385116</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>94.55</v>
+        <v>42.56</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.0009509334157969951</v>
+        <v>-0.001173415544340584</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.02786344874511526</v>
+        <v>-0.02875395550680548</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.005744079387902001</v>
+        <v>-0.01458664675734378</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.008103231995007398</v>
+        <v>-0.02250802759829151</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.05768751679726547</v>
+        <v>0.03335205809523334</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>-0.004595395480073927</v>
+        <v>0.02838043973099325</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.1264490597501133</v>
+        <v>0.1218611946208656</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.1186180138828288</v>
+        <v>0.1101509087350467</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.1603785501010158</v>
+        <v>0.3359291125368771</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.05083185782764255</v>
+        <v>0.1013562094597438</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>186.43</v>
+        <v>116.66</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.0004292276342678925</v>
+        <v>-0.02450031579148826</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.003552717813110062</v>
+        <v>-0.04806200932659999</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.02355327385806838</v>
+        <v>-0.04023035184594936</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.06842791453224506</v>
+        <v>-0.03234898785220142</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.1184233604010767</v>
+        <v>-0.03154570356337572</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.1436839371433616</v>
+        <v>0.0195062107038797</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.01544956788932694</v>
+        <v>0.1700282107089284</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>-0.04349391154757565</v>
+        <v>0.1884348245447343</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.6505309128813304</v>
+        <v>0.4129190457705505</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1817924765872247</v>
+        <v>0.1221194575872064</v>
       </c>
     </row>
     <row r="22">
@@ -1726,37 +1726,37 @@
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>103.49</v>
+        <v>101.98</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.01268843574629741</v>
+        <v>-0.01459072894004343</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.01268843574629741</v>
+        <v>-0.03152896105038427</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.01630164001635714</v>
+        <v>0.01361696390290135</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.07187979899173458</v>
+        <v>0.05624029138833797</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.007986750846872503</v>
+        <v>-0.003225434557079021</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>-0.02019102771715664</v>
+        <v>-0.03448715484475806</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.1913213477876539</v>
+        <v>0.1762585157751002</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1599339405909979</v>
+        <v>0.1430096588754781</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.2351729565632854</v>
+        <v>0.2036484441663757</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.07294120662194037</v>
+        <v>0.06373443803210477</v>
       </c>
     </row>
     <row r="23">
@@ -1782,37 +1782,37 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>14</v>
+        <v>13.86</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.003584243112437546</v>
+        <v>-0.01000002452305382</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.0007148126551423939</v>
+        <v>-0.01070667878329945</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.007919341537678593</v>
+        <v>0.002894353309429443</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.01818181818181808</v>
+        <v>0.007999975031072415</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.01596518659593427</v>
+        <v>0.0153846186092117</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>-0.01017158883893765</v>
+        <v>-0.02006989722416375</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1875721600646141</v>
+        <v>0.1815310358676347</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.08407216196794565</v>
+        <v>0.07323141376350617</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.0691574333283469</v>
+        <v>0.05100230308020626</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.02254058246146418</v>
+        <v>0.01671966259817736</v>
       </c>
     </row>
     <row r="24">
@@ -1824,51 +1824,51 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>42.61</v>
+        <v>182.38</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.01228555370411177</v>
+        <v>-0.02172390683945391</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.02561168405234082</v>
+        <v>-0.02271991397123607</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.01775012537585274</v>
+        <v>0.002087938916552234</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.02135967582959153</v>
+        <v>0.04521748605227449</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.01759378297854974</v>
+        <v>0.09656082762963636</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.02958857496913758</v>
+        <v>0.1188386538390793</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.1093696818698584</v>
+        <v>0.001504881312122341</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.1114551074349475</v>
+        <v>-0.06427296070448663</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.3350313915880621</v>
+        <v>0.6092061606333612</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1011094568239042</v>
+        <v>0.1718460546304907</v>
       </c>
     </row>
     <row r="25">
@@ -1880,51 +1880,51 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>17.86</v>
+        <v>27.33</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.01975843669429045</v>
+        <v>-0.01157322601226241</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.0208332875841537</v>
+        <v>-0.04105263425592787</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.007332265734443233</v>
+        <v>-0.1062786137380123</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.05617982090548868</v>
+        <v>-0.06532147272103306</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.1441384371018783</v>
+        <v>-0.01584445541248114</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.1325301263107428</v>
+        <v>-0.05807035907507463</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>-0.05552613672835338</v>
+        <v>0.1500440512865007</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>-0.1149652953290186</v>
+        <v>0.1387921712519171</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.209207857604613</v>
+        <v>1.040198287555399</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.0653696491694562</v>
+        <v>0.2683062314441382</v>
       </c>
     </row>
     <row r="26">
@@ -1936,52 +1936,46 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>51.33</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.01591253870370946</v>
+        <v>-0.0146867773633822</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.003494399074815524</v>
+        <v>-0.03971374889442836</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.03822366763457674</v>
+        <v>-0.07875603891032357</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.0007798969548318269</v>
+        <v>-0.05652831301703265</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>-0.0482106148601591</v>
+        <v>-0.005233327599364901</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.02712695324963765</v>
+        <v>-0.02867277119331102</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.1003490800993596</v>
-      </c>
-      <c r="N26" s="6" t="n">
-        <v>0.1698603585553631</v>
-      </c>
-      <c r="O26" s="6" t="n">
-        <v>0.6926795521469851</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v>0.1917676228591956</v>
-      </c>
+        <v>0.1479554269704841</v>
+      </c>
+      <c r="N26" s="6" t="inlineStr"/>
+      <c r="O26" s="6" t="inlineStr"/>
+      <c r="P26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
@@ -1992,51 +1986,51 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>27.65</v>
+        <v>50.57</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.02777780944769315</v>
+        <v>-0.01480619733332378</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.02400283469844877</v>
+        <v>-0.0207203661400257</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.09463003308319218</v>
+        <v>-0.03252345031665194</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.05437757062359538</v>
+        <v>-0.0140378476867048</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>-0.02434723113417514</v>
+        <v>-0.05846210097136639</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>-0.0470415556179471</v>
+        <v>0.01191910889344783</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.1322776337534974</v>
+        <v>0.09420131055328951</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.1521259856787782</v>
+        <v>0.1525391752341594</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>1.067918410549169</v>
+        <v>0.6617398650501398</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.2740245591793817</v>
+        <v>0.1844616745862382</v>
       </c>
     </row>
     <row r="28">
@@ -2048,51 +2042,51 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>16.7</v>
+        <v>17.44</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.017647013944738</v>
+        <v>-0.02351624087014392</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.04843296359387539</v>
+        <v>-0.0480348894883017</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.03188401374264038</v>
+        <v>-0.01912261751729083</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.01007706389074903</v>
+        <v>0.03134244183488977</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.07051284324174434</v>
+        <v>0.1037974888306934</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.03411723131478572</v>
+        <v>0.1058972750677247</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.02809697185183246</v>
+        <v>-0.06837600567558511</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>-0.08443340937949617</v>
+        <v>-0.1357779846224981</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.3061865366985992</v>
+        <v>0.1696848231078039</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.09312141121565376</v>
+        <v>0.05363361607268713</v>
       </c>
     </row>
     <row r="29">
@@ -2118,37 +2112,37 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>17.39</v>
+        <v>17.26</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.001151326968843236</v>
+        <v>-0.007475512669884554</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.03065781092732123</v>
+        <v>-0.02760562090806562</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.02303370028008023</v>
+        <v>-0.0292463688234974</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.03763145083895902</v>
+        <v>-0.04482564912131071</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>-0.01528881427500339</v>
+        <v>-0.00403922072316143</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.003650290702282399</v>
+        <v>-0.003852509761995804</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.04055548834629463</v>
+        <v>0.02664448467426506</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.03848788052574958</v>
+        <v>0.03072465121735779</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.4188227872074253</v>
+        <v>0.4052025912021058</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1236801739473259</v>
+        <v>0.1200729627217687</v>
       </c>
     </row>
     <row r="30">
@@ -2160,44 +2154,52 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>69.45</v>
+        <v>16.47</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-0.02621989280122983</v>
+        <v>-0.01377254126211647</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.02635643957034095</v>
+        <v>-0.05778033497320223</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.08195643691448939</v>
+        <v>-0.0435540087053522</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.04246521277943061</v>
+        <v>-0.02371081837462929</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.0001439301049042108</v>
+        <v>0.05172410433172758</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>-0.01419446477385478</v>
-      </c>
-      <c r="M30" s="6" t="inlineStr"/>
-      <c r="N30" s="6" t="inlineStr"/>
-      <c r="O30" s="6" t="inlineStr"/>
-      <c r="P30" s="6" t="inlineStr"/>
+        <v>0.01987480907663719</v>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>0.01659595839726036</v>
+      </c>
+      <c r="N30" s="6" t="n">
+        <v>-0.09704308802703243</v>
+      </c>
+      <c r="O30" s="6" t="n">
+        <v>0.2829482443564915</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v>0.08660002892649188</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
@@ -2222,37 +2224,37 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>64.12</v>
+        <v>62.99</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.005488510056545604</v>
+        <v>-0.01762322239101077</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.02091915043328185</v>
+        <v>-0.02853168975801967</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.01565853012931551</v>
+        <v>-0.02793211864273082</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.01580965088523811</v>
+        <v>-0.03315425628277402</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.05218032076387324</v>
+        <v>-0.04690565639578559</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>-0.01025249679234097</v>
+        <v>-0.02769503715231714</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>-0.01535557254882991</v>
+        <v>-0.0345411646558168</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.01498865822225293</v>
+        <v>-0.00289865241617171</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.4059893178205598</v>
+        <v>0.3837395932208332</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1202819543696771</v>
+        <v>0.1143410326586138</v>
       </c>
     </row>
     <row r="32">
@@ -2278,37 +2280,37 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>54.83</v>
+        <v>54.23</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.005132953215587044</v>
+        <v>-0.01094295584134974</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.003090875799005688</v>
+        <v>-0.01417921838022584</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.0042125158124795</v>
+        <v>0.004817459989855832</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.01181035653376572</v>
+        <v>0.0007381604823961663</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.02955748971584626</v>
+        <v>-0.03143422188728651</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>-0.04491067880097765</v>
+        <v>-0.05536217906740326</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>-0.0260852666876763</v>
+        <v>-0.03056316191992026</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.006940466474240958</v>
+        <v>-0.01780747309744479</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.2107564534382467</v>
+        <v>0.1981904007681328</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.06582425069386444</v>
+        <v>0.06212413763767333</v>
       </c>
     </row>
     <row r="33">
@@ -2320,51 +2322,51 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>116.59</v>
+        <v>126.37</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.01744486145570334</v>
+        <v>0.007735256849282779</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.03389131551990676</v>
+        <v>-0.01557990532584896</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.06862121701824275</v>
+        <v>-0.03364687146993928</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.03787757019083871</v>
+        <v>-0.04762981067556338</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.04426593671974055</v>
+        <v>-0.03764848016664146</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.1062457298401374</v>
+        <v>-0.1210345762283017</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>-0.02217204509824011</v>
+        <v>-0.04675055142461093</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>-0.04664041099244709</v>
+        <v>0.02537643666473577</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.3035211322870146</v>
+        <v>0.5101851711712335</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.09237736365485638</v>
+        <v>0.1472993138208196</v>
       </c>
     </row>
     <row r="34">
@@ -2376,51 +2378,51 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>125.4</v>
+        <v>114.69</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>-0.02184083844786455</v>
+        <v>-0.01629637152554653</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.02069505242266789</v>
+        <v>-0.04409068817734485</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.04999998844031128</v>
+        <v>-0.06406070193791225</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.05494009180342352</v>
+        <v>-0.05355667476007042</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.07547636248930434</v>
+        <v>-0.04734609998454986</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.1277814110426062</v>
+        <v>-0.1208106814792062</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.07748150492986716</v>
+        <v>-0.03467674141927102</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.01750583119129878</v>
+        <v>-0.06217677155917867</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.4979799307279833</v>
+        <v>0.2691359888301936</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1442001445775207</v>
+        <v>0.08268649563402342</v>
       </c>
     </row>
   </sheetData>
@@ -2537,17 +2539,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -2582,17 +2584,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -2605,17 +2607,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -2650,17 +2652,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -2717,17 +2719,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -2785,17 +2787,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -2807,17 +2809,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -2830,17 +2832,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2852,17 +2854,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -2897,17 +2899,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -2920,17 +2922,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -2942,17 +2944,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3040,7 +3042,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.3314464121405516</v>
+        <v>0.2769861166016625</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -3048,21 +3050,21 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.05494009180342352</v>
+        <v>-0.06532147272103306</v>
       </c>
     </row>
     <row r="18">
@@ -3085,7 +3087,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.1387471825671691</v>
+        <v>0.1030163015915697</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -3093,12 +3095,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -3107,7 +3109,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.05437757062359538</v>
+        <v>-0.05652831301703265</v>
       </c>
     </row>
     <row r="19">
@@ -3116,21 +3118,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.09317667726566947</v>
+        <v>0.09448446458590332</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -3138,21 +3140,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.04246521277943061</v>
+        <v>-0.05355667476007042</v>
       </c>
     </row>
     <row r="20">
@@ -3175,7 +3177,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.08193805377323438</v>
+        <v>0.08870679722797759</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -3183,21 +3185,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.03787757019083871</v>
+        <v>-0.04762981067556338</v>
       </c>
     </row>
     <row r="21">
@@ -3206,21 +3208,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.07970675214713219</v>
+        <v>0.07492687102809992</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -3242,7 +3244,7 @@
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.03763145083895902</v>
+        <v>-0.04482564912131071</v>
       </c>
     </row>
     <row r="22">
@@ -3251,21 +3253,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>Medical Tech &amp; Devices</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
       <c r="E22" s="11" t="n">
-        <v>0.07894736108283862</v>
+        <v>0.07338696137844969</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -3273,21 +3275,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.02545762402264817</v>
+        <v>-0.03315425628277402</v>
       </c>
     </row>
     <row r="23">
@@ -3296,21 +3298,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.07187979899173458</v>
+        <v>0.05869806858475934</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -3318,21 +3320,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.02363022298298245</v>
+        <v>-0.03234898785220142</v>
       </c>
     </row>
     <row r="24">
@@ -3341,21 +3343,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.06842791453224506</v>
+        <v>0.05624029138833797</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -3363,21 +3365,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.02135967582959153</v>
+        <v>-0.03219937465113254</v>
       </c>
     </row>
     <row r="25">
@@ -3386,21 +3388,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.06390373290087736</v>
+        <v>0.04741684861058149</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -3408,21 +3410,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t>Leisure</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
       <c r="K25" s="11" t="n">
-        <v>-0.01580965088523811</v>
+        <v>-0.02371081837462929</v>
       </c>
     </row>
     <row r="26">
@@ -3431,21 +3433,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.05976529985069234</v>
+        <v>0.04654609297750745</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -3453,21 +3455,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.01007706389074903</v>
+        <v>-0.02250802759829151</v>
       </c>
     </row>
     <row r="27"/>
@@ -3537,12 +3539,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3551,7 +3553,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.2008604837530263</v>
+        <v>0.2204472183941526</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -3573,7 +3575,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.1124759287915646</v>
+        <v>-0.1461894643384374</v>
       </c>
     </row>
     <row r="32">
@@ -3596,7 +3598,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.1936919128262218</v>
+        <v>0.209292772058346</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -3604,21 +3606,21 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FDCPX</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.07547636248930434</v>
+        <v>-0.07350368932101059</v>
       </c>
     </row>
     <row r="33">
@@ -3627,12 +3629,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3641,7 +3643,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.1872557048402588</v>
+        <v>0.1839472541335212</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -3663,7 +3665,7 @@
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.05788803002254062</v>
+        <v>-0.05852417688716949</v>
       </c>
     </row>
     <row r="34">
@@ -3686,7 +3688,7 @@
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.1593682627783228</v>
+        <v>0.1575113778109249</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -3694,21 +3696,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.05218032076387324</v>
+        <v>-0.05846210097136639</v>
       </c>
     </row>
     <row r="35">
@@ -3731,7 +3733,7 @@
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.1535305581711912</v>
+        <v>0.1502996382545341</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -3739,21 +3741,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.0482106148601591</v>
+        <v>-0.05527459901111864</v>
       </c>
     </row>
     <row r="36">
@@ -3776,7 +3778,7 @@
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.1484374859331483</v>
+        <v>0.1387621568620874</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -3798,7 +3800,7 @@
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.04426593671974055</v>
+        <v>-0.04734609998454986</v>
       </c>
     </row>
     <row r="37">
@@ -3807,21 +3809,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1441384371018783</v>
+        <v>0.1048486869318945</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -3829,21 +3831,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.03530867360984635</v>
+        <v>-0.04690565639578559</v>
       </c>
     </row>
     <row r="38">
@@ -3852,21 +3854,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1320522441537815</v>
+        <v>0.1037974888306934</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -3874,21 +3876,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.02955748971584626</v>
+        <v>-0.03764848016664146</v>
       </c>
     </row>
     <row r="39">
@@ -3897,21 +3899,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1184233604010767</v>
+        <v>0.1009761054340756</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -3919,21 +3921,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>FDCPX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Tech Hardware</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.02855842581672108</v>
+        <v>-0.03154570356337572</v>
       </c>
     </row>
     <row r="40">
@@ -3942,21 +3944,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1169777734408337</v>
+        <v>0.09661387831719592</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -3964,21 +3966,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.02434723113417514</v>
+        <v>-0.03143422188728651</v>
       </c>
     </row>
     <row r="41"/>
@@ -4062,7 +4064,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.4082743007229339</v>
+        <v>0.3937939279653178</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -4070,21 +4072,21 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1277814110426062</v>
+        <v>-0.160141766657019</v>
       </c>
     </row>
     <row r="46">
@@ -4093,12 +4095,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4107,7 +4109,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.3952907899621267</v>
+        <v>0.3709657008618776</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -4115,21 +4117,21 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.1243238928336534</v>
+        <v>-0.1210345762283017</v>
       </c>
     </row>
     <row r="47">
@@ -4138,12 +4140,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4152,7 +4154,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.3864010997099081</v>
+        <v>0.3515102477085821</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -4174,7 +4176,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.1062457298401374</v>
+        <v>-0.1208106814792062</v>
       </c>
     </row>
     <row r="48">
@@ -4197,7 +4199,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.368288655662699</v>
+        <v>0.344559767458114</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -4219,7 +4221,7 @@
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.0470415556179471</v>
+        <v>-0.05807035907507463</v>
       </c>
     </row>
     <row r="49">
@@ -4242,7 +4244,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.2671861784273049</v>
+        <v>0.239608677722466</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -4264,7 +4266,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.04491067880097765</v>
+        <v>-0.05536217906740326</v>
       </c>
     </row>
     <row r="50">
@@ -4287,7 +4289,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.2118209613786664</v>
+        <v>0.2194022689886967</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -4309,7 +4311,7 @@
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.02019102771715664</v>
+        <v>-0.03448715484475806</v>
       </c>
     </row>
     <row r="51">
@@ -4332,7 +4334,7 @@
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.1879118918153904</v>
+        <v>0.2041705845622266</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -4354,7 +4356,7 @@
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.01419446477385478</v>
+        <v>-0.02867277119331102</v>
       </c>
     </row>
     <row r="52">
@@ -4377,7 +4379,7 @@
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.1726484957399832</v>
+        <v>0.1718566825716454</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4399,7 +4401,7 @@
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-0.01025249679234097</v>
+        <v>-0.02769503715231714</v>
       </c>
     </row>
     <row r="53">
@@ -4408,21 +4410,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.1716403058028275</v>
+        <v>0.1670255569598669</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -4444,7 +4446,7 @@
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>-0.01017158883893765</v>
+        <v>-0.02006989722416375</v>
       </c>
     </row>
     <row r="54">
@@ -4453,21 +4455,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.1713905186813049</v>
+        <v>0.1610131926148113</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -4573,7 +4575,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.939834632220764</v>
+        <v>0.9198885687668827</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4595,7 +4597,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.1149652953290186</v>
+        <v>-0.1357779846224981</v>
       </c>
     </row>
     <row r="60">
@@ -4618,7 +4620,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.8416097029766065</v>
+        <v>0.8096724720585837</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4640,7 +4642,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.08443340937949617</v>
+        <v>-0.09704308802703243</v>
       </c>
     </row>
     <row r="61">
@@ -4649,21 +4651,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.5832681933564661</v>
+        <v>0.5883571071120688</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4671,21 +4673,21 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.04664041099244709</v>
+        <v>-0.06427296070448663</v>
       </c>
     </row>
     <row r="62">
@@ -4694,21 +4696,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.5784819214331203</v>
+        <v>0.5625780227088186</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4716,21 +4718,21 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.04349391154757565</v>
+        <v>-0.06217677155917867</v>
       </c>
     </row>
     <row r="63">
@@ -4739,21 +4741,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.5414800205477082</v>
+        <v>0.518507604465102</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4775,7 +4777,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.006940466474240958</v>
+        <v>-0.01780747309744479</v>
       </c>
     </row>
     <row r="64">
@@ -4798,7 +4800,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.5005851217043742</v>
+        <v>0.4838784631019151</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4820,7 +4822,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>0.01498865822225293</v>
+        <v>-0.00289865241617171</v>
       </c>
     </row>
     <row r="65">
@@ -4843,7 +4845,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.4567925944299629</v>
+        <v>0.4676020584561451</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4851,21 +4853,21 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.01750583119129878</v>
+        <v>-0.001239447784183056</v>
       </c>
     </row>
     <row r="66">
@@ -4888,7 +4890,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.3392627167153628</v>
+        <v>0.334272211499397</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4896,21 +4898,21 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>0.02097991896250861</v>
+        <v>0.02537643666473577</v>
       </c>
     </row>
     <row r="67">
@@ -4933,7 +4935,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.2738967025003693</v>
+        <v>0.2730366274398757</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4941,21 +4943,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.03848788052574958</v>
+        <v>0.02628056073541107</v>
       </c>
     </row>
     <row r="68">
@@ -4964,21 +4966,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.2182831463538515</v>
+        <v>0.2095870600542149</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -4986,21 +4988,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.05952568005984582</v>
+        <v>0.03072465121735779</v>
       </c>
     </row>
     <row r="69"/>
@@ -5084,7 +5086,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.389762640584165</v>
+        <v>2.276498777913448</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5106,7 +5108,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.0691574333283469</v>
+        <v>0.05100230308020626</v>
       </c>
     </row>
     <row r="74">
@@ -5129,7 +5131,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.296073191017931</v>
+        <v>2.245501211221454</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5151,7 +5153,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.08940260585231186</v>
+        <v>0.1074417837519781</v>
       </c>
     </row>
     <row r="75">
@@ -5174,7 +5176,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.149964916355807</v>
+        <v>2.047118468042688</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5196,7 +5198,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1567024149097707</v>
+        <v>0.1323078898656993</v>
       </c>
     </row>
     <row r="76">
@@ -5219,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.428788652044763</v>
+        <v>1.394599853504655</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5241,7 +5243,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1603785501010158</v>
+        <v>0.1680659018023558</v>
       </c>
     </row>
     <row r="77">
@@ -5264,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.142340019433309</v>
+        <v>1.088871642167592</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5286,7 +5288,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.209207857604613</v>
+        <v>0.1696848231078039</v>
       </c>
     </row>
     <row r="78">
@@ -5309,7 +5311,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.067918410549169</v>
+        <v>1.040198287555399</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5331,7 +5333,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.2107564534382467</v>
+        <v>0.1981904007681328</v>
       </c>
     </row>
     <row r="79">
@@ -5354,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.013632776381304</v>
+        <v>0.994608215142561</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5376,7 +5378,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.2351729565632854</v>
+        <v>0.2036484441663757</v>
       </c>
     </row>
     <row r="80">
@@ -5399,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.9561635467821921</v>
+        <v>0.9185671489311815</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5421,7 +5423,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.2836120625156715</v>
+        <v>0.2425970901813472</v>
       </c>
     </row>
     <row r="81">
@@ -5444,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.7766513530977373</v>
+        <v>0.7721390846427458</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5466,7 +5468,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.3035211322870146</v>
+        <v>0.2691359888301936</v>
       </c>
     </row>
     <row r="82">
@@ -5489,7 +5491,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.7380804056404535</v>
+        <v>0.7435612641683127</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5511,7 +5513,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.3061865366985992</v>
+        <v>0.2829482443564915</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -627,16 +627,16 @@
         <v>0.3937939279653178</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.6838470702366788</v>
+        <v>0.683846968083609</v>
       </c>
       <c r="N2" s="6" t="n">
         <v>0.9198885687668827</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.047118468042688</v>
+        <v>2.047118133520609</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4497611129313885</v>
+        <v>0.4497610598783019</v>
       </c>
     </row>
     <row r="3">
@@ -745,10 +745,10 @@
         <v>0.5883571071120688</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.994608215142561</v>
+        <v>0.9946083392969218</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2587878270619526</v>
+        <v>0.2587878531796957</v>
       </c>
     </row>
     <row r="5">
@@ -851,16 +851,16 @@
         <v>0.3709657008618776</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.3606975128666878</v>
+        <v>0.3606973825067288</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>0.4838784631019151</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>1.394599853504655</v>
+        <v>1.394599651641552</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.3378609694020667</v>
+        <v>0.3378609318084824</v>
       </c>
     </row>
     <row r="7">
@@ -1137,10 +1137,10 @@
         <v>0.2095870600542149</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.1074417837519781</v>
+        <v>0.1074418641100874</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.03460276594911504</v>
+        <v>0.03460279097337104</v>
       </c>
     </row>
     <row r="12">
@@ -1187,16 +1187,16 @@
         <v>0.1236195702713989</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.1721615988828955</v>
+        <v>0.1721615285682749</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>0.1830054948610962</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.088871642167592</v>
+        <v>1.088871418864804</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2783131348049144</v>
+        <v>0.2783130892538632</v>
       </c>
     </row>
     <row r="13">
@@ -1249,10 +1249,10 @@
         <v>0.09466934112925385</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.5681864314717839</v>
+        <v>0.5681861411240625</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.1618031882755273</v>
+        <v>0.1618031165733957</v>
       </c>
     </row>
     <row r="14">
@@ -1302,13 +1302,13 @@
         <v>0.2669112116183805</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.2730366274398757</v>
+        <v>0.2730365230111138</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7721390846427458</v>
+        <v>0.772139287007104</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.2101315988833097</v>
+        <v>0.2101316449458144</v>
       </c>
     </row>
     <row r="15">
@@ -1361,10 +1361,10 @@
         <v>0.02628056073541107</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.3369035369195423</v>
+        <v>0.3369033935024246</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.1016239201520925</v>
+        <v>0.1016238807596386</v>
       </c>
     </row>
     <row r="16">
@@ -1417,10 +1417,10 @@
         <v>0.04328427647988198</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.1323078898656993</v>
+        <v>0.1323077959363024</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.04228905626306578</v>
+        <v>0.04228902744240481</v>
       </c>
     </row>
     <row r="17">
@@ -1467,16 +1467,16 @@
         <v>0.239608677722466</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.06428558332031953</v>
+        <v>0.06428548719303073</v>
       </c>
       <c r="N17" s="6" t="n">
         <v>-0.001239447784183056</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.2425970901813472</v>
+        <v>0.2425969591452368</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.07508658835438875</v>
+        <v>0.07508655056386893</v>
       </c>
     </row>
     <row r="18">
@@ -1520,7 +1520,7 @@
         <v>-0.02327324362516248</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.06900197988124934</v>
+        <v>0.06900210543723362</v>
       </c>
       <c r="M18" s="6" t="n">
         <v>0.2119205126059298</v>
@@ -1529,10 +1529,10 @@
         <v>0.1555152453554753</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.7435612641683127</v>
+        <v>0.7435610971651356</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.2035913853865894</v>
+        <v>0.2035913469588044</v>
       </c>
     </row>
     <row r="19">
@@ -1585,10 +1585,10 @@
         <v>0.1186180138828288</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.1680659018023558</v>
+        <v>0.1680656816146164</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.05314729205385116</v>
+        <v>0.0531472258788932</v>
       </c>
     </row>
     <row r="20">
@@ -1691,7 +1691,7 @@
         <v>0.0195062107038797</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.1700282107089284</v>
+        <v>0.1700281211805494</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>0.1884348245447343</v>
@@ -1750,7 +1750,7 @@
         <v>0.1762585157751002</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1430096588754781</v>
+        <v>0.1430095611349198</v>
       </c>
       <c r="O22" s="6" t="n">
         <v>0.2036484441663757</v>
@@ -1862,13 +1862,13 @@
         <v>0.001504881312122341</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>-0.06427296070448663</v>
+        <v>-0.06427303396014417</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.6092061606333612</v>
+        <v>0.6092059439796358</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1718460546304907</v>
+        <v>0.1718460020404144</v>
       </c>
     </row>
     <row r="25">
@@ -2027,10 +2027,10 @@
         <v>0.1525391752341594</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.6617398650501398</v>
+        <v>0.6617399692010899</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.1844616745862382</v>
+        <v>0.1844616993319497</v>
       </c>
     </row>
     <row r="28">
@@ -2307,10 +2307,10 @@
         <v>-0.01780747309744479</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.1981904007681328</v>
+        <v>0.1981902997795884</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.06212413763767333</v>
+        <v>0.06212410779757072</v>
       </c>
     </row>
     <row r="33">
@@ -2363,10 +2363,10 @@
         <v>0.02537643666473577</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.5101851711712335</v>
+        <v>0.5101853088625403</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1472993138208196</v>
+        <v>0.1472993486892009</v>
       </c>
     </row>
     <row r="34">
@@ -2413,10 +2413,10 @@
         <v>-0.1208106814792062</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.03467674141927102</v>
+        <v>-0.03467667943092045</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.06217677155917867</v>
+        <v>-0.06217671305235661</v>
       </c>
       <c r="O34" s="6" t="n">
         <v>0.2691359888301936</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.06427296070448663</v>
+        <v>-0.06427303396014417</v>
       </c>
     </row>
     <row r="62">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.06217677155917867</v>
+        <v>-0.06217671305235661</v>
       </c>
     </row>
     <row r="63">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.2730366274398757</v>
+        <v>0.2730365230111138</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.1074417837519781</v>
+        <v>0.1074418641100874</v>
       </c>
     </row>
     <row r="75">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.047118468042688</v>
+        <v>2.047118133520609</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1323078898656993</v>
+        <v>0.1323077959363024</v>
       </c>
     </row>
     <row r="76">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.394599853504655</v>
+        <v>1.394599651641552</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1680659018023558</v>
+        <v>0.1680656816146164</v>
       </c>
     </row>
     <row r="77">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.088871642167592</v>
+        <v>1.088871418864804</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.1981904007681328</v>
+        <v>0.1981902997795884</v>
       </c>
     </row>
     <row r="79">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>0.994608215142561</v>
+        <v>0.9946083392969218</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.2425970901813472</v>
+        <v>0.2425969591452368</v>
       </c>
     </row>
     <row r="81">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.7721390846427458</v>
+        <v>0.772139287007104</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.7435612641683127</v>
+        <v>0.7435610971651356</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -489,14 +489,14 @@
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="23" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>211.76</v>
+        <v>213.79</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>-0.01028235248643161</v>
+        <v>0.00958631862465098</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>-0.003247834555508811</v>
+        <v>-0.00807314760366995</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>-0.02724060759825864</v>
+        <v>0.005077272051983828</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.0259192420416039</v>
+        <v>0.03575403077897521</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>-0.07350368932101059</v>
+        <v>-0.08472475550041192</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.3937939279653178</v>
+        <v>0.4170465009848368</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.683846968083609</v>
+        <v>0.689620955198808</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.9198885687668827</v>
+        <v>0.9486809491260837</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.047118133520609</v>
+        <v>2.076329116564404</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4497610598783019</v>
+        <v>0.4543790119855118</v>
       </c>
     </row>
     <row r="3">
@@ -648,51 +648,51 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>94.06</v>
+        <v>30.9</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.01368678338760398</v>
+        <v>0.01112565963774981</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.04221603943040164</v>
+        <v>-0.01592356707243181</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.01697480517987149</v>
+        <v>-0.02585118892102212</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.09448446458590332</v>
+        <v>0.1008193784992408</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.1502996382545341</v>
+        <v>0.2810944669731763</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.2041705845622266</v>
+        <v>0.2424825601469582</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.5054270071702542</v>
+        <v>0.30793026169183</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.5625780227088186</v>
+        <v>0.5836153450337398</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.638365120877719</v>
+        <v>1.016799672790557</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.1788817138945482</v>
+        <v>0.263438928565719</v>
       </c>
     </row>
     <row r="4">
@@ -704,51 +704,51 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>30.56</v>
+        <v>94.42</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.006256128464228849</v>
+        <v>0.003827350836653975</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>-0.03045688381596556</v>
+        <v>0.04181839380321084</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.01528236141670747</v>
+        <v>0.02474494024744933</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.08870679722797759</v>
+        <v>0.09867344061714123</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.2204472183941526</v>
+        <v>0.1389625624973023</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.2194022689886967</v>
+        <v>0.187849396602793</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.2818211186413124</v>
+        <v>0.5308873370462681</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.5883571071120688</v>
+        <v>0.5624542381089783</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.9946083392969218</v>
+        <v>0.6446357189938552</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2587878531796957</v>
+        <v>0.1803837971594375</v>
       </c>
     </row>
     <row r="5">
@@ -774,37 +774,37 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>58.93</v>
+        <v>59.39</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.01734201924892254</v>
+        <v>0.007805855796546801</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.01405387562580784</v>
+        <v>-0.006690107371699838</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>-0.04905600864361015</v>
+        <v>-0.02125907892286727</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-0.004392605635504809</v>
+        <v>0.003378962114880091</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>-0.1461894643384374</v>
+        <v>-0.1908719597409124</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.344559767458114</v>
+        <v>0.3413366332155268</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.5122475919828533</v>
+        <v>0.5115291396455997</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.8096724720585837</v>
+        <v>0.8440574937963792</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>2.245501211221454</v>
+        <v>2.270834782078904</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.4805642496720317</v>
+        <v>0.4844065743014196</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>54.18</v>
+        <v>29.81</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-0.01113342946082507</v>
+        <v>0.01360080314877909</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.0168919209177727</v>
+        <v>-0.01584686150798043</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-0.006236246326727146</v>
+        <v>-0.02549855125056355</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.03713626654626712</v>
+        <v>0.08954673980028605</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>-0.05527459901111864</v>
+        <v>0.2483249796305862</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.3709657008618776</v>
+        <v>0.1904484431687647</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.3606973825067288</v>
+        <v>0.1783279531226922</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.4838784631019151</v>
+        <v>0.3453386401918264</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>1.394599651641552</v>
+        <v>0.4575602481830654</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.3378609318084824</v>
+        <v>0.1338149308553074</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>29.41</v>
+        <v>54.23</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.003726307880955071</v>
+        <v>0.0009228356732913223</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.03573770992091441</v>
+        <v>0.01269841857822418</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.0127410096494498</v>
+        <v>0.00184737617121522</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.07492687102809992</v>
+        <v>0.03809337289110015</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.209292772058346</v>
+        <v>-0.08022387407875642</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.1670255569598669</v>
+        <v>0.3602520511087157</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.1485967013835996</v>
+        <v>0.3436937580264661</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.334272211499397</v>
+        <v>0.501626472439225</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.4380023965913902</v>
+        <v>1.396809473623338</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1287208216871976</v>
+        <v>0.3382723472094129</v>
       </c>
     </row>
     <row r="8">
@@ -942,37 +942,37 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>35.3</v>
+        <v>35.54</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.007420043228879791</v>
+        <v>0.006798914551103596</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.04102151806291732</v>
+        <v>-0.01496676519186191</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.01436781640694762</v>
+        <v>-0.04101458179813045</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.04654609297750745</v>
+        <v>0.05366147043745295</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.09661387831719592</v>
+        <v>0.1016739852650512</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.08693971471259831</v>
+        <v>0.1116947651081028</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.1763081839799363</v>
+        <v>0.1925981988647618</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.4676020584561451</v>
+        <v>0.4729336952824486</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.6909039080879833</v>
+        <v>0.7024002192732006</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1913507501978058</v>
+        <v>0.1940446182480682</v>
       </c>
     </row>
     <row r="9">
@@ -998,37 +998,37 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>65.42</v>
+        <v>67.2</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.04090310735926195</v>
+        <v>0.02720878674897054</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.104203761982109</v>
+        <v>-0.05298762943548607</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.05772028751654634</v>
+        <v>0.002386575634395482</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.2769861166016625</v>
+        <v>0.3117313595296731</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.1009761054340756</v>
+        <v>0.1177644401554128</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>-0.160141766657019</v>
+        <v>-0.1370739565968099</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.1942663937200362</v>
+        <v>0.2489667142164356</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.518507604465102</v>
+        <v>0.5197422867760992</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>2.276498777913448</v>
+        <v>2.365648012932164</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.4852629126962746</v>
+        <v>0.4986132387583284</v>
       </c>
     </row>
     <row r="10">
@@ -1054,37 +1054,37 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>17.48</v>
+        <v>17.68</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.009070286448309095</v>
+        <v>0.0114416915433091</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.01465615739776571</v>
+        <v>-0.003382157086612048</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.01687295460199334</v>
+        <v>0.004545450112051208</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.01040464237652561</v>
+        <v>0.02196538062852538</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.1387621568620874</v>
+        <v>0.1487979149296503</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.1610131926148113</v>
+        <v>0.1651467785261769</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.1637980368635252</v>
+        <v>0.1793166794009988</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.1417589150607137</v>
+        <v>0.1626351272789941</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.9185671489311815</v>
+        <v>0.9405190055747927</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2425837447842376</v>
+        <v>0.247304914577092</v>
       </c>
     </row>
     <row r="11">
@@ -1110,37 +1110,37 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>116.44</v>
+        <v>117.09</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.01729864907191137</v>
+        <v>0.005582221597869363</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.00483263031810055</v>
+        <v>0.00162527638607135</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.01173000387933087</v>
+        <v>0.02324561763192201</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>-0.008599357454909251</v>
+        <v>-0.003065139375952541</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.1048486869318945</v>
+        <v>0.1212294933995839</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.1513893563115947</v>
+        <v>0.1520070547129075</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.1270808629399602</v>
+        <v>0.1442554643622134</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.2095870600542149</v>
+        <v>0.2110947217639132</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.1074418641100874</v>
+        <v>0.1136238500023075</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.03460279097337104</v>
+        <v>0.03652434722716369</v>
       </c>
     </row>
     <row r="12">
@@ -1166,37 +1166,37 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>37.27</v>
+        <v>38.06</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.008776543344398036</v>
+        <v>0.02119669723166795</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.01765941468626331</v>
+        <v>0</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>-0.05285890970809959</v>
+        <v>-0.007561854299049653</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-0.03219937465113254</v>
+        <v>-0.01168519781499366</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.09328249606752714</v>
+        <v>0.0952518380803169</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.1236195702713989</v>
+        <v>0.1340631868590902</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.1721615285682749</v>
+        <v>0.2001014237881484</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.1830054948610962</v>
+        <v>0.2161679426197756</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.088871418864804</v>
+        <v>1.133148593886366</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2783130892538632</v>
+        <v>0.2872820192400511</v>
       </c>
     </row>
     <row r="13">
@@ -1222,37 +1222,37 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>96.93000000000001</v>
+        <v>97.63</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.000309584920789252</v>
+        <v>0.007221674879173801</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.01363586428885022</v>
+        <v>-0.00973728694727316</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.003935755995929435</v>
+        <v>0.009617376778962683</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-0.004825474469610236</v>
+        <v>0.002361352401806238</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.1575113778109249</v>
+        <v>0.1614323113127061</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.09911644589276802</v>
+        <v>0.1006852489933547</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.124750070226006</v>
+        <v>0.1391839273475257</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.09466934112925385</v>
+        <v>0.1023369539046703</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.5681861411240625</v>
+        <v>0.5795112665482867</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.1618031165733957</v>
+        <v>0.1645931804934673</v>
       </c>
     </row>
     <row r="14">
@@ -1264,51 +1264,51 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>14.8</v>
+        <v>52.75</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.0006752348817350429</v>
+        <v>0.01305934912927165</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.008042887730928872</v>
+        <v>-0.02024517365339384</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.004752250554918014</v>
+        <v>-0.0106901668808439</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.04741684861058149</v>
+        <v>0.08740469645789894</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>-0.05852417688716949</v>
+        <v>0.2193712909540968</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.1718566825716454</v>
+        <v>0.09638512567429447</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.2669112116183805</v>
+        <v>-0.007156208684149346</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.2730365230111138</v>
+        <v>0.06220843337557413</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.772139287007104</v>
+        <v>0.1470949987652306</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.2101316449458144</v>
+        <v>0.04680662395491542</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>23.77</v>
+        <v>14.84</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.03137736059644824</v>
+        <v>0.002702700090373433</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.03078928917018842</v>
+        <v>-0.008021382704083591</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.0241275913563328</v>
+        <v>-0.006693402316203079</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.1030163015915697</v>
+        <v>0.05024770222198005</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.01581200193441012</v>
+        <v>-0.106562335504105</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.3515102477085821</v>
+        <v>0.1695543502401924</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.05828202911396807</v>
+        <v>0.2592274536410035</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.02628056073541107</v>
+        <v>0.2847592622590653</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.3369033935024246</v>
+        <v>0.7769288480182526</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.1016238807596386</v>
+        <v>0.2112208718851827</v>
       </c>
     </row>
     <row r="16">
@@ -1376,51 +1376,51 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>52.07</v>
+        <v>45.07</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.01810294374073118</v>
+        <v>0.002669609117864624</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.03431006188695651</v>
+        <v>-0.011622780636663</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.01898241193088035</v>
+        <v>0.005577867061629327</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.07338696137844969</v>
+        <v>0.04352862069675156</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.1839472541335212</v>
+        <v>0.08602408903190883</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.06851058033729318</v>
+        <v>0.2364811886800113</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>-0.02709858395191111</v>
+        <v>0.06564379024689648</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.04328427647988198</v>
+        <v>0.01506187928588454</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.1323077959363024</v>
+        <v>0.2459140759313039</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.04228902744240481</v>
+        <v>0.07604234962601852</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>44.95</v>
+        <v>94.98</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.02176278527521902</v>
+        <v>0.004547861356920313</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.01598072542380469</v>
+        <v>-0.01062496503194177</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.008073572754420999</v>
+        <v>-0.008766398878792714</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.0407502244082516</v>
+        <v>0.01268794572758392</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.06164384980976512</v>
+        <v>0.07410124224797521</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.239608677722466</v>
+        <v>0.01552074072243204</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.06428548719303073</v>
+        <v>0.1407114105877671</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>-0.001239447784183056</v>
+        <v>0.1282373380266117</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.2425969591452368</v>
+        <v>0.1733779929849273</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.07508655056386893</v>
+        <v>0.0547413673825079</v>
       </c>
     </row>
     <row r="18">
@@ -1502,37 +1502,37 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>69.44</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.00100704492408199</v>
+        <v>0.01022464083395969</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.0001439093920102552</v>
+        <v>0.009207299237225186</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.007398841345894747</v>
+        <v>0.01314274538107041</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.05869806858475934</v>
+        <v>0.0695228760876454</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>-0.02327324362516248</v>
+        <v>-0.0256239044535681</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.06900210543723362</v>
+        <v>0.07246419579365737</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.2119205126059298</v>
+        <v>0.2145656452469278</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.1555152453554753</v>
+        <v>0.1779557658421946</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.7435610971651356</v>
+        <v>0.761388720577195</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.2035913469588044</v>
+        <v>0.2076796185445129</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>94.55</v>
+        <v>23.25</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0</v>
+        <v>-0.02187633351911999</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.01817237740957744</v>
+        <v>0.001723434601688778</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.0007397980637529056</v>
+        <v>0.001723434601688778</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.008103231995007398</v>
+        <v>0.07888634910092618</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.06731581938118913</v>
+        <v>0.02649008351324023</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>-0.004595395480073927</v>
+        <v>0.3063520083814377</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.1292025531769105</v>
+        <v>0.01923978034040608</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1186180138828288</v>
+        <v>0.01381053978399049</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.1680656816146164</v>
+        <v>0.3076569892629994</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.0531472258788932</v>
+        <v>0.09353145483965264</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>42.56</v>
+        <v>117.26</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.001173415544340584</v>
+        <v>0.005143137796042918</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.02875395550680548</v>
+        <v>-0.04324408883762787</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.01458664675734378</v>
+        <v>-0.03624555025135556</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.02250802759829151</v>
+        <v>-0.02737222535824491</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.03335205809523334</v>
+        <v>-0.01701734230628749</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.02838043973099325</v>
+        <v>0.02466625434238856</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.1218611946208656</v>
+        <v>0.167115189033592</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.1101509087350467</v>
+        <v>0.2081228253380711</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.3359291125368771</v>
+        <v>0.420185883117602</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.1013562094597438</v>
+        <v>0.1240399072926608</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>116.66</v>
+        <v>103.86</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.02450031579148826</v>
+        <v>0.01843495971301268</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.04806200932659999</v>
+        <v>-0.01161021316562805</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-0.04023035184594936</v>
+        <v>0.01405977804286729</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-0.03234898785220142</v>
+        <v>0.07571203860734288</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>-0.03154570356337572</v>
+        <v>-0.0005773437225836675</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.0195062107038797</v>
+        <v>-0.01632665861411053</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.1700281211805494</v>
+        <v>0.2069518944156099</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.1884348245447343</v>
+        <v>0.1701971942371832</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.4129190457705505</v>
+        <v>0.2258376547432133</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1221194575872064</v>
+        <v>0.07023131073482136</v>
       </c>
     </row>
     <row r="22">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
       <c r="F22" s="5" t="n">
-        <v>101.98</v>
+        <v>14</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.01459072894004343</v>
+        <v>0.01010103512198191</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.03152896105038427</v>
+        <v>-0.002849000139722779</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.01361696390290135</v>
+        <v>0.00430419091985712</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.05624029138833797</v>
+        <v>0.01818181818181808</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>-0.003225434557079021</v>
+        <v>0.02264429723291639</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>-0.03448715484475806</v>
+        <v>-0.006030080459076714</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.1762585157751002</v>
+        <v>0.2004160224748299</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1430095611349198</v>
+        <v>0.09476483204121067</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.2036484441663757</v>
+        <v>0.06161843748381912</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.06373443803210477</v>
+        <v>0.02013148294918055</v>
       </c>
     </row>
     <row r="23">
@@ -1768,51 +1768,51 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>13.86</v>
+        <v>42.19</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.01000002452305382</v>
+        <v>-0.00869367327638837</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.01070667878329945</v>
+        <v>-0.03145093442127511</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.002894353309429443</v>
+        <v>-0.03145093442127511</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.007999975031072415</v>
+        <v>-0.03100602343664438</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.0153846186092117</v>
+        <v>0.01944003618414358</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>-0.02006989722416375</v>
+        <v>0.01748187414154589</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1815310358676347</v>
+        <v>0.1155800461872334</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.07323141376350617</v>
+        <v>0.1211846149962741</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.05100230308020626</v>
+        <v>0.324314981312066</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.01671966259817736</v>
+        <v>0.09815530524062899</v>
       </c>
     </row>
     <row r="24">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1838,37 +1838,37 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>182.38</v>
+        <v>17.77</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.02172390683945391</v>
+        <v>0.01892201339453026</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.02271991397123607</v>
+        <v>-0.0225522464537794</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.002087938916552234</v>
+        <v>-0.006152053029414906</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.04521748605227449</v>
+        <v>0.05085751733363719</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.09656082762963636</v>
+        <v>0.1576547241793773</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.1188386538390793</v>
+        <v>0.1261090467976698</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.001504881312122341</v>
+        <v>-0.05327650376195803</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>-0.06427303396014417</v>
+        <v>-0.1079317073441636</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.6092059439796358</v>
+        <v>0.1918176149980286</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1718460020404144</v>
+        <v>0.06023775816498844</v>
       </c>
     </row>
     <row r="25">
@@ -1880,51 +1880,51 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>27.33</v>
+        <v>181.57</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.01157322601226241</v>
+        <v>-0.004441262950476421</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.04105263425592787</v>
+        <v>-0.02439413933288814</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.1062786137380123</v>
+        <v>-0.008085199141573352</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.06532147272103306</v>
+        <v>0.04057540035628038</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>-0.01584445541248114</v>
+        <v>0.1100446242832371</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>-0.05807035907507463</v>
+        <v>0.1031395339351044</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1500440512865007</v>
+        <v>-0.002567810946616511</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.1387921712519171</v>
+        <v>-0.06045583088196749</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>1.040198287555399</v>
+        <v>0.6020590372409527</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.2683062314441382</v>
+        <v>0.1701086020019349</v>
       </c>
     </row>
     <row r="26">
@@ -1950,28 +1950,28 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>68.43000000000001</v>
+        <v>68.55</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.0146867773633822</v>
+        <v>0.001753656964004868</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.03971374889442836</v>
+        <v>-0.04989602769211088</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.07875603891032357</v>
+        <v>-0.06556703269594888</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.05652831301703265</v>
+        <v>-0.05487378732281356</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>-0.005233327599364901</v>
+        <v>-0.01324309993924599</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>-0.02867277119331102</v>
+        <v>-0.03314525280035896</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.1479554269704841</v>
+        <v>0.1405518083296209</v>
       </c>
       <c r="N26" s="6" t="inlineStr"/>
       <c r="O26" s="6" t="inlineStr"/>
@@ -1986,51 +1986,51 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>50.57</v>
+        <v>27.11</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.01480619733332378</v>
+        <v>-0.008049737064348306</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.0207203661400257</v>
+        <v>-0.05671535051314247</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.03252345031665194</v>
+        <v>-0.09057359624160821</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.0140378476867048</v>
+        <v>-0.07284538910532101</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>-0.05846210097136639</v>
+        <v>-0.01454015322436553</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.01191910889344783</v>
+        <v>-0.08606697626112414</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.09420131055328951</v>
+        <v>0.1232145635710475</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.1525391752341594</v>
+        <v>0.1282453793247316</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.6617399692010899</v>
+        <v>1.023775227781444</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.1844616993319497</v>
+        <v>0.2648938815992976</v>
       </c>
     </row>
     <row r="28">
@@ -2042,51 +2042,51 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>17.44</v>
+        <v>50.7</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.02351624087014392</v>
+        <v>0.002570715224436526</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.0480348894883017</v>
+        <v>-0.02612371445401651</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.01912261751729083</v>
+        <v>-0.0298507005108527</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.03134244183488977</v>
+        <v>-0.01150321977103486</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.1037974888306934</v>
+        <v>-0.07244784294781048</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.1058972750677247</v>
+        <v>0.01472069052949054</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>-0.06837600567558511</v>
+        <v>0.09190531700266513</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>-0.1357779846224981</v>
+        <v>0.167268889436923</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.1696848231078039</v>
+        <v>0.6660117250202773</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.05363361607268713</v>
+        <v>0.1854757773121303</v>
       </c>
     </row>
     <row r="29">
@@ -2098,12 +2098,12 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -2112,37 +2112,37 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>17.26</v>
+        <v>16.56</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.007475512669884554</v>
+        <v>0.005464490366730912</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.02760562090806562</v>
+        <v>-0.04718065215303779</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.0292463688234974</v>
+        <v>-0.04332755766258878</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.04482564912131071</v>
+        <v>-0.01837589554649377</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>-0.00403922072316143</v>
+        <v>0.06701024339586703</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>-0.003852509761995804</v>
+        <v>0.04695217875850033</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.02664448467426506</v>
+        <v>0.01523030977693995</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.03072465121735779</v>
+        <v>-0.08614992611591599</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.4052025912021058</v>
+        <v>0.2899589026787919</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1200729627217687</v>
+        <v>0.08857567311848902</v>
       </c>
     </row>
     <row r="30">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -2168,37 +2168,37 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>16.47</v>
+        <v>17.26</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-0.01377254126211647</v>
+        <v>0</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.05778033497320223</v>
+        <v>-0.02485878616338244</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.0435540087053522</v>
+        <v>-0.04217537234048185</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.02371081837462929</v>
+        <v>-0.04482564912131071</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.05172410433172758</v>
+        <v>0.002905354274788552</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.01987480907663719</v>
+        <v>0.008701674378984059</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.01659595839726036</v>
+        <v>0.02919073533843997</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>-0.09704308802703243</v>
+        <v>0.03380600475455142</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.2829482443564915</v>
+        <v>0.4052024820989935</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.08660002892649188</v>
+        <v>0.1200729337334339</v>
       </c>
     </row>
     <row r="31">
@@ -2224,37 +2224,37 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>62.99</v>
+        <v>63.35</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.01762322239101077</v>
+        <v>0.005715141864766071</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.02853168975801967</v>
+        <v>-0.01752488870940772</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.02793211864273082</v>
+        <v>-0.04116847636244514</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.03315425628277402</v>
+        <v>-0.02762859569608478</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.04690565639578559</v>
+        <v>-0.03898664693887899</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>-0.02769503715231714</v>
+        <v>-0.009776822041803968</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>-0.0345411646558168</v>
+        <v>-0.02732196204857429</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-0.00289865241617171</v>
+        <v>0.009665337374226812</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.3837395932208332</v>
+        <v>0.3916479779197644</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1143410326586138</v>
+        <v>0.1164599048270423</v>
       </c>
     </row>
     <row r="32">
@@ -2280,37 +2280,37 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>54.23</v>
+        <v>54.45</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.01094295584134974</v>
+        <v>0.004056817675828661</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.01417921838022584</v>
+        <v>-0.002381844334077399</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.004817459989855832</v>
+        <v>-0.01089915499430494</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.0007381604823961663</v>
+        <v>0.004797972740717471</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.03143422188728651</v>
+        <v>-0.03062128292816635</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>-0.05536217906740326</v>
+        <v>-0.0439862064678983</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>-0.03056316191992026</v>
+        <v>-0.02157831179370484</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.01780747309744479</v>
+        <v>-0.01444777831756816</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.1981902997795884</v>
+        <v>0.2030511393667407</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.06212410779757072</v>
+        <v>0.06355845120421622</v>
       </c>
     </row>
     <row r="33">
@@ -2336,37 +2336,37 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>126.37</v>
+        <v>126.7</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.007735256849282779</v>
+        <v>0.002611333342469768</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.01557990532584896</v>
+        <v>-0.01821004299064688</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.03364687146993928</v>
+        <v>-0.03208553967973093</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.04762981067556338</v>
+        <v>-0.04514285464580614</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.03764848016664146</v>
+        <v>-0.05520544879274702</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.1210345762283017</v>
+        <v>-0.1124541752191471</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>-0.04675055142461093</v>
+        <v>-0.03780933599731351</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.02537643666473577</v>
+        <v>0.03188026605857974</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.5101853088625403</v>
+        <v>0.5141291822146858</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1472993486892009</v>
+        <v>0.1482972108148524</v>
       </c>
     </row>
     <row r="34">
@@ -2392,37 +2392,37 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>114.69</v>
+        <v>115.02</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>-0.01629637152554653</v>
+        <v>0.002877270857403191</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.04409068817734485</v>
+        <v>-0.04269666931054972</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.06406070193791225</v>
+        <v>-0.06753143035346143</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.05355667476007042</v>
+        <v>-0.05083350096217376</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.04734609998454986</v>
+        <v>-0.05550995404821513</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.1208106814792062</v>
+        <v>-0.1079163769663869</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.03467667943092045</v>
+        <v>-0.02673130118796885</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.06217671305235661</v>
+        <v>-0.0526217526662941</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2691359888301936</v>
+        <v>0.2727876368249362</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.08268649563402342</v>
+        <v>0.08372389540976388</v>
       </c>
     </row>
   </sheetData>
@@ -2562,17 +2562,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -2607,17 +2607,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -2697,17 +2697,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2742,17 +2742,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2809,17 +2809,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -2854,17 +2854,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -2944,17 +2944,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.2769861166016625</v>
+        <v>0.3117313595296731</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.06532147272103306</v>
+        <v>-0.07284538910532101</v>
       </c>
     </row>
     <row r="18">
@@ -3073,21 +3073,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.1030163015915697</v>
+        <v>0.1008193784992408</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -3109,7 +3109,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.05652831301703265</v>
+        <v>-0.05487378732281356</v>
       </c>
     </row>
     <row r="19">
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.09448446458590332</v>
+        <v>0.09867344061714123</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.05355667476007042</v>
+        <v>-0.05083350096217376</v>
       </c>
     </row>
     <row r="20">
@@ -3163,12 +3163,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.08870679722797759</v>
+        <v>0.08954673980028605</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.04762981067556338</v>
+        <v>-0.04514285464580614</v>
       </c>
     </row>
     <row r="21">
@@ -3208,21 +3208,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>Medical Tech &amp; Devices</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
       <c r="E21" s="11" t="n">
-        <v>0.07492687102809992</v>
+        <v>0.08740469645789894</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -3253,21 +3253,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.07338696137844969</v>
+        <v>0.07888634910092618</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -3275,21 +3275,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.03315425628277402</v>
+        <v>-0.03100602343664438</v>
       </c>
     </row>
     <row r="23">
@@ -3298,21 +3298,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.05869806858475934</v>
+        <v>0.07571203860734288</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -3320,21 +3320,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.03234898785220142</v>
+        <v>-0.02762859569608478</v>
       </c>
     </row>
     <row r="24">
@@ -3343,21 +3343,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.05624029138833797</v>
+        <v>0.0695228760876454</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -3365,21 +3365,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.03219937465113254</v>
+        <v>-0.02737222535824491</v>
       </c>
     </row>
     <row r="25">
@@ -3388,21 +3388,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.04741684861058149</v>
+        <v>0.05366147043745295</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.02371081837462929</v>
+        <v>-0.01837589554649377</v>
       </c>
     </row>
     <row r="26">
@@ -3433,21 +3433,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.04654609297750745</v>
+        <v>0.05085751733363719</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -3455,21 +3455,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.02250802759829151</v>
+        <v>-0.01168519781499366</v>
       </c>
     </row>
     <row r="27"/>
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.2204472183941526</v>
+        <v>0.2810944669731763</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.1461894643384374</v>
+        <v>-0.1908719597409124</v>
       </c>
     </row>
     <row r="32">
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.209292772058346</v>
+        <v>0.2483249796305862</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -3606,21 +3606,21 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>FDCPX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Tech Hardware</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.07350368932101059</v>
+        <v>-0.106562335504105</v>
       </c>
     </row>
     <row r="33">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.1839472541335212</v>
+        <v>0.2193712909540968</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -3651,21 +3651,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FDCPX</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.05852417688716949</v>
+        <v>-0.08472475550041192</v>
       </c>
     </row>
     <row r="34">
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.1575113778109249</v>
+        <v>0.1614323113127061</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -3696,21 +3696,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.05846210097136639</v>
+        <v>-0.08022387407875642</v>
       </c>
     </row>
     <row r="35">
@@ -3719,21 +3719,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.1502996382545341</v>
+        <v>0.1576547241793773</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -3741,21 +3741,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.05527459901111864</v>
+        <v>-0.07244784294781048</v>
       </c>
     </row>
     <row r="36">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.1387621568620874</v>
+        <v>0.1487979149296503</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.04734609998454986</v>
+        <v>-0.05550995404821513</v>
       </c>
     </row>
     <row r="37">
@@ -3809,21 +3809,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1048486869318945</v>
+        <v>0.1389625624973023</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -3831,21 +3831,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.04690565639578559</v>
+        <v>-0.05520544879274702</v>
       </c>
     </row>
     <row r="38">
@@ -3854,21 +3854,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1037974888306934</v>
+        <v>0.1212294933995839</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -3876,21 +3876,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.03764848016664146</v>
+        <v>-0.03898664693887899</v>
       </c>
     </row>
     <row r="39">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1009761054340756</v>
+        <v>0.1177644401554128</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -3921,21 +3921,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.03154570356337572</v>
+        <v>-0.03062128292816635</v>
       </c>
     </row>
     <row r="40">
@@ -3944,21 +3944,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.09661387831719592</v>
+        <v>0.1100446242832371</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -3966,21 +3966,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.03143422188728651</v>
+        <v>-0.0256239044535681</v>
       </c>
     </row>
     <row r="41"/>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.3937939279653178</v>
+        <v>0.4170465009848368</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.160141766657019</v>
+        <v>-0.1370739565968099</v>
       </c>
     </row>
     <row r="46">
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.3709657008618776</v>
+        <v>0.3602520511087157</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -4131,7 +4131,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.1210345762283017</v>
+        <v>-0.1124541752191471</v>
       </c>
     </row>
     <row r="47">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.3515102477085821</v>
+        <v>0.3413366332155268</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.1208106814792062</v>
+        <v>-0.1079163769663869</v>
       </c>
     </row>
     <row r="48">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.344559767458114</v>
+        <v>0.3063520083814377</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.05807035907507463</v>
+        <v>-0.08606697626112414</v>
       </c>
     </row>
     <row r="49">
@@ -4230,21 +4230,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.239608677722466</v>
+        <v>0.2424825601469582</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.05536217906740326</v>
+        <v>-0.0439862064678983</v>
       </c>
     </row>
     <row r="50">
@@ -4275,21 +4275,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.2194022689886967</v>
+        <v>0.2364811886800113</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -4297,21 +4297,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.03448715484475806</v>
+        <v>-0.03314525280035896</v>
       </c>
     </row>
     <row r="51">
@@ -4320,21 +4320,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.2041705845622266</v>
+        <v>0.1904484431687647</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -4342,21 +4342,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.02867277119331102</v>
+        <v>-0.01632665861411053</v>
       </c>
     </row>
     <row r="52">
@@ -4365,21 +4365,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.1718566825716454</v>
+        <v>0.187849396602793</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-0.02769503715231714</v>
+        <v>-0.009776822041803968</v>
       </c>
     </row>
     <row r="53">
@@ -4410,21 +4410,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.1670255569598669</v>
+        <v>0.1695543502401924</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -4446,7 +4446,7 @@
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>-0.02006989722416375</v>
+        <v>-0.006030080459076714</v>
       </c>
     </row>
     <row r="54">
@@ -4469,7 +4469,7 @@
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.1610131926148113</v>
+        <v>0.1651467785261769</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -4477,21 +4477,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>-0.004595395480073927</v>
+        <v>0.008701674378984059</v>
       </c>
     </row>
     <row r="55"/>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.9198885687668827</v>
+        <v>0.9486809491260837</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.1357779846224981</v>
+        <v>-0.1079317073441636</v>
       </c>
     </row>
     <row r="60">
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.8096724720585837</v>
+        <v>0.8440574937963792</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.09704308802703243</v>
+        <v>-0.08614992611591599</v>
       </c>
     </row>
     <row r="61">
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.5883571071120688</v>
+        <v>0.5836153450337398</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.06427303396014417</v>
+        <v>-0.06045583088196749</v>
       </c>
     </row>
     <row r="62">
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.5625780227088186</v>
+        <v>0.5624542381089783</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.06217671305235661</v>
+        <v>-0.0526217526662941</v>
       </c>
     </row>
     <row r="63">
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.518507604465102</v>
+        <v>0.5197422867760992</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.01780747309744479</v>
+        <v>-0.01444777831756816</v>
       </c>
     </row>
     <row r="64">
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.4838784631019151</v>
+        <v>0.501626472439225</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.00289865241617171</v>
+        <v>0.009665337374226812</v>
       </c>
     </row>
     <row r="65">
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.4676020584561451</v>
+        <v>0.4729336952824486</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.001239447784183056</v>
+        <v>0.01381053978399049</v>
       </c>
     </row>
     <row r="66">
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.334272211499397</v>
+        <v>0.3453386401918264</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4898,21 +4898,21 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>0.02537643666473577</v>
+        <v>0.01506187928588454</v>
       </c>
     </row>
     <row r="67">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.2730365230111138</v>
+        <v>0.2847592622590653</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4943,21 +4943,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.02628056073541107</v>
+        <v>0.03188026605857974</v>
       </c>
     </row>
     <row r="68">
@@ -4966,21 +4966,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.2095870600542149</v>
+        <v>0.2161679426197756</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -5002,7 +5002,7 @@
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.03072465121735779</v>
+        <v>0.03380600475455142</v>
       </c>
     </row>
     <row r="69"/>
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.276498777913448</v>
+        <v>2.365648012932164</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.05100230308020626</v>
+        <v>0.06161843748381912</v>
       </c>
     </row>
     <row r="74">
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.245501211221454</v>
+        <v>2.270834782078904</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.1074418641100874</v>
+        <v>0.1136238500023075</v>
       </c>
     </row>
     <row r="75">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.047118133520609</v>
+        <v>2.076329116564404</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1323077959363024</v>
+        <v>0.1470949987652306</v>
       </c>
     </row>
     <row r="76">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.394599651641552</v>
+        <v>1.396809473623338</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1680656816146164</v>
+        <v>0.1733779929849273</v>
       </c>
     </row>
     <row r="77">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.088871418864804</v>
+        <v>1.133148593886366</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1696848231078039</v>
+        <v>0.1918176149980286</v>
       </c>
     </row>
     <row r="78">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.040198287555399</v>
+        <v>1.023775227781444</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.1981902997795884</v>
+        <v>0.2030511393667407</v>
       </c>
     </row>
     <row r="79">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>0.9946083392969218</v>
+        <v>1.016799672790557</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.2036484441663757</v>
+        <v>0.2258376547432133</v>
       </c>
     </row>
     <row r="80">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.9185671489311815</v>
+        <v>0.9405190055747927</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.2425969591452368</v>
+        <v>0.2459140759313039</v>
       </c>
     </row>
     <row r="81">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.772139287007104</v>
+        <v>0.7769288480182526</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.2691359888301936</v>
+        <v>0.2727876368249362</v>
       </c>
     </row>
     <row r="82">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.7435610971651356</v>
+        <v>0.761388720577195</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.2829482443564915</v>
+        <v>0.2899589026787919</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -489,15 +489,15 @@
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="25" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="24" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>213.79</v>
+        <v>215.15</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.00958631862465098</v>
+        <v>0.006361385719916957</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>-0.00807314760366995</v>
+        <v>-0.007427572666324211</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.005077272051983828</v>
+        <v>0.009619839203443892</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.03575403077897521</v>
+        <v>0.02898272353881892</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>-0.08472475550041192</v>
+        <v>-0.07878402446946553</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.4170465009848368</v>
+        <v>0.4938975646941843</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.689620955198808</v>
+        <v>0.72035447422934</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.9486809491260837</v>
+        <v>0.9386741294708902</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.076329116564404</v>
+        <v>2.095898492798943</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4543790119855118</v>
+        <v>0.4574563975472217</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>30.9</v>
+        <v>30.89</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.01112565963774981</v>
+        <v>-0.0003236320066437592</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>-0.01592356707243181</v>
+        <v>-0.01025311452134658</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>-0.02585118892102212</v>
+        <v>0.009807101522200101</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.1008193784992408</v>
+        <v>0.1171790168469589</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.2810944669731763</v>
+        <v>0.2577361588498377</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.2424825601469582</v>
+        <v>0.2610546688730686</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.30793026169183</v>
+        <v>0.2780450095163329</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.5836153450337398</v>
+        <v>0.5777877495461556</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1.016799672790557</v>
+        <v>1.01614684637042</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.263438928565719</v>
+        <v>0.2633025912231215</v>
       </c>
     </row>
     <row r="4">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>94.42</v>
+        <v>93.92</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.003827350836653975</v>
+        <v>-0.005295488346709676</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.04181839380321084</v>
+        <v>0.03641575063280111</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.02474494024744933</v>
+        <v>0.01557087759235842</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.09867344061714123</v>
+        <v>0.1028651259996782</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.1389625624973023</v>
+        <v>0.121700637805694</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.187849396602793</v>
+        <v>0.1965726511943291</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.5308873370462681</v>
+        <v>0.4953473715013119</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.5624542381089783</v>
+        <v>0.5821441070209217</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.6446357189938552</v>
+        <v>0.6359265697093406</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1803837971594375</v>
+        <v>0.1782965389141948</v>
       </c>
     </row>
     <row r="5">
@@ -774,37 +774,37 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>59.39</v>
+        <v>59.57</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.007805855796546801</v>
+        <v>0.003030818437879113</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.006690107371699838</v>
+        <v>-0.0357720804166356</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>-0.02125907892286727</v>
+        <v>-0.02296213708133432</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.003378962114880091</v>
+        <v>-0.005343124028809543</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>-0.1908719597409124</v>
+        <v>-0.1921616297728077</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.3413366332155268</v>
+        <v>0.3991717461873354</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.5115291396455997</v>
+        <v>0.4873734985340017</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.8440574937963792</v>
+        <v>0.8476440521545707</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>2.270834782078904</v>
+        <v>2.280748088443685</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.4844065743014196</v>
+        <v>0.4859047173909332</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>29.81</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.01360080314877909</v>
+        <v>0.03779763438804418</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>-0.01584686150798043</v>
+        <v>-0.02624971810549426</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-0.02549855125056355</v>
+        <v>0.01263242460420377</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.08954673980028605</v>
+        <v>0.3554907061149115</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.2483249796305862</v>
+        <v>0.2026210699294706</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.1904484431687647</v>
+        <v>-0.02717773275784641</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.1783279531226922</v>
+        <v>0.3024151490577824</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.3453386401918264</v>
+        <v>0.5677063463050824</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.4575602481830654</v>
+        <v>2.492861879669038</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.1338149308553074</v>
+        <v>0.5172616150006557</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>54.23</v>
+        <v>29.88</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.0009228356732913223</v>
+        <v>0.002348195104940887</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.01269841857822418</v>
+        <v>-0.009283842442377677</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.00184737617121522</v>
+        <v>-0.005326289942888751</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.03809337289110015</v>
+        <v>0.09330403381555352</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>-0.08022387407875642</v>
+        <v>0.2418952545307658</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.3602520511087157</v>
+        <v>0.2125937181650828</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.3436937580264661</v>
+        <v>0.1707412530469439</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.501626472439225</v>
+        <v>0.3459809014449917</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>1.396809473623338</v>
+        <v>0.4609830202740366</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.3382723472094129</v>
+        <v>0.134701745271151</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>35.54</v>
+        <v>55.09</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.006798914551103596</v>
+        <v>0.01585839235867526</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.01496676519186191</v>
+        <v>-0.009350844309591211</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-0.04101458179813045</v>
+        <v>0.02226759652125665</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.05366147043745295</v>
+        <v>0.04159577969989603</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.1016739852650512</v>
+        <v>-0.05441123000811454</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.1116947651081028</v>
+        <v>0.4105544324177868</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.1925981988647618</v>
+        <v>0.3539814180831902</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.4729336952824486</v>
+        <v>0.5216264313801517</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.7024002192732006</v>
+        <v>1.434819223918615</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1940446182480682</v>
+        <v>0.34530959810399</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>67.2</v>
+        <v>35.63</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.02720878674897054</v>
+        <v>0.002532362134762156</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.05298762943548607</v>
+        <v>-0.001960775723480856</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.002386575634395482</v>
+        <v>-0.00890124306072626</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.3117313595296731</v>
+        <v>0.06836589800036652</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.1177644401554128</v>
+        <v>0.0932801749399792</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>-0.1370739565968099</v>
+        <v>0.1338867696390422</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.2489667142164356</v>
+        <v>0.1910693052350443</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.5197422867760992</v>
+        <v>0.4645741038173641</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>2.365648012932164</v>
+        <v>0.7067113131266989</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.4986132387583284</v>
+        <v>0.1950516864315586</v>
       </c>
     </row>
     <row r="10">
@@ -1054,37 +1054,37 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>17.68</v>
+        <v>17.94</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.0114416915433091</v>
+        <v>0.01470589504490682</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.003382157086612048</v>
+        <v>0.01528016166371748</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.004545450112051208</v>
+        <v>0.03044231426138055</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.02196538062852538</v>
+        <v>0.02572903195130705</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.1487979149296503</v>
+        <v>0.1825972606349773</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.1651467785261769</v>
+        <v>0.1915662380442442</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.1793166794009988</v>
+        <v>0.1790075905047148</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.1626351272789941</v>
+        <v>0.1819133855764432</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.9405190055747927</v>
+        <v>0.9690558682959405</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.247304914577092</v>
+        <v>0.2533893865767978</v>
       </c>
     </row>
     <row r="11">
@@ -1096,51 +1096,51 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>117.09</v>
+        <v>38.48</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.005582221597869363</v>
+        <v>0.01103515905913888</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.00162527638607135</v>
+        <v>0.01503560266732973</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.02324561763192201</v>
+        <v>0.0145003752342574</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>-0.003065139375952541</v>
+        <v>-0.01181302261672768</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.1212294933995839</v>
+        <v>0.1271236154123605</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.1520070547129075</v>
+        <v>0.1529606327184165</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.1442554643622134</v>
+        <v>0.1857608791225325</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.2110947217639132</v>
+        <v>0.2313804281907024</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.1136238500023075</v>
+        <v>1.156688458469165</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.03652434722716369</v>
+        <v>0.2919998742897276</v>
       </c>
     </row>
     <row r="12">
@@ -1152,12 +1152,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1166,37 +1166,37 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>38.06</v>
+        <v>99.22</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.02119669723166795</v>
+        <v>0.01628601876488833</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0</v>
+        <v>0.01889509159151848</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>-0.007561854299049653</v>
+        <v>0.02235958887902378</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-0.01168519781499366</v>
+        <v>0.01743236911562773</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.0952518380803169</v>
+        <v>0.1934087316466444</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.1340631868590902</v>
+        <v>0.1291038545741465</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.2001014237881484</v>
+        <v>0.1613599084411854</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.2161679426197756</v>
+        <v>0.1128506409113266</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.133148593886366</v>
+        <v>0.6052353157437484</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2872820192400511</v>
+        <v>0.1708813861118326</v>
       </c>
     </row>
     <row r="13">
@@ -1208,51 +1208,51 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FSHCX</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>97.63</v>
+        <v>117.58</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.007221674879173801</v>
+        <v>0.004184862144414492</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.00973728694727316</v>
+        <v>0.01651252435674522</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.009617376778962683</v>
+        <v>0.03321615709955372</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.002361352401806238</v>
+        <v>-0.001613270080898066</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.1614323113127061</v>
+        <v>0.1191700415324901</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.1006852489933547</v>
+        <v>0.1689035302883712</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.1391839273475257</v>
+        <v>0.1496014852561591</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.1023369539046703</v>
+        <v>0.2167875984263936</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.5795112665482867</v>
+        <v>0.1182841311504481</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.1645931804934673</v>
+        <v>0.03796821366251502</v>
       </c>
     </row>
     <row r="14">
@@ -1264,51 +1264,51 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>52.75</v>
+        <v>24.08</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.01305934912927165</v>
+        <v>0.03569892144972275</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.02024517365339384</v>
+        <v>-0.02707071015329077</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.0106901668808439</v>
+        <v>0.04786772860669419</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.08740469645789894</v>
+        <v>0.08030502174326015</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.2193712909540968</v>
+        <v>0.1101889963486014</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.09638512567429447</v>
+        <v>0.3385720786667437</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>-0.007156208684149346</v>
+        <v>0.04925731675268885</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.06220843337557413</v>
+        <v>0.04962981105947573</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.1470949987652306</v>
+        <v>0.3543389334058802</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.04680662395491542</v>
+        <v>0.1063922401628281</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>14.84</v>
+        <v>45.94</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.002702700090373433</v>
+        <v>0.01930328240016999</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.008021382704083591</v>
+        <v>-0.007989694139707515</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-0.006693402316203079</v>
+        <v>0.03143236826233609</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.05024770222198005</v>
+        <v>0.05077761537103087</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>-0.106562335504105</v>
+        <v>0.1450648018387373</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.1695543502401924</v>
+        <v>0.2600385181951754</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.2592274536410035</v>
+        <v>0.07279622323976764</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.2847592622590653</v>
+        <v>0.03231341455961201</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.7769288480182526</v>
+        <v>0.269964575029535</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.2112208718851827</v>
+        <v>0.08292206375181044</v>
       </c>
     </row>
     <row r="16">
@@ -1376,51 +1376,51 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>45.07</v>
+        <v>52.95</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.002669609117864624</v>
+        <v>0.003791483657620054</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.011622780636663</v>
+        <v>-0.01561628812587379</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.005577867061629327</v>
+        <v>-0.01157362209103519</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.04352862069675156</v>
+        <v>0.07556370618105723</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.08602408903190883</v>
+        <v>0.2189227080311937</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.2364811886800113</v>
+        <v>0.1114126633636754</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.06564379024689648</v>
+        <v>-0.004791090033746892</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.01506187928588454</v>
+        <v>0.07485909076090569</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.2459140759313039</v>
+        <v>0.1514441907067867</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.07604234962601852</v>
+        <v>0.04812793884710875</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>94.98</v>
+        <v>14.98</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.004547861356920313</v>
+        <v>0.009433921038338067</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.01062496503194177</v>
+        <v>0.0006679542437646457</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.008766398878792714</v>
+        <v>0.005369122533839699</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.01268794572758392</v>
+        <v>0.04975466444966914</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.07410124224797521</v>
+        <v>-0.09101942000396746</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.01552074072243204</v>
+        <v>0.1888888165643838</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.1407114105877671</v>
+        <v>0.2600886637274673</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.1282373380266117</v>
+        <v>0.2968795796924908</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.1733779929849273</v>
+        <v>0.7936920496356643</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.0547413673825079</v>
+        <v>0.2150177645651059</v>
       </c>
     </row>
     <row r="18">
@@ -1502,37 +1502,37 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>70.15000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.01022464083395969</v>
+        <v>0.01069137539110843</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.009207299237225186</v>
+        <v>0.02634626008371121</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.01314274538107041</v>
+        <v>0.03337707178480676</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.0695228760876454</v>
+        <v>0.05931572094130289</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>-0.0256239044535681</v>
+        <v>0.01765258894599708</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.07246419579365737</v>
+        <v>0.07200481634789746</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.2145656452469278</v>
+        <v>0.2190850661962966</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.1779557658421946</v>
+        <v>0.1959931612342185</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.761388720577195</v>
+        <v>0.7802202180840432</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.2076796185445129</v>
+        <v>0.2119682507567646</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>23.25</v>
+        <v>186.82</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.02187633351911999</v>
+        <v>0.02891446708280077</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.001723434601688778</v>
+        <v>0.002522142234017588</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.001723434601688778</v>
+        <v>0.03215473659789359</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.07888634910092618</v>
+        <v>0.04902022104467152</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.02649008351324023</v>
+        <v>0.1688669535378804</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.3063520083814377</v>
+        <v>0.1451772665293714</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.01923978034040608</v>
+        <v>0.003715821549403975</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.01381053978399049</v>
+        <v>-0.02554155412270065</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.3076569892629994</v>
+        <v>0.6483819424660735</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.09353145483965264</v>
+        <v>0.1812793608701202</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>117.26</v>
+        <v>94.89</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.005143137796042918</v>
+        <v>-0.0009476096452315508</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.04324408883762787</v>
+        <v>0.002641589197086791</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.03624555025135556</v>
+        <v>0.001900541726489013</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.02737222535824491</v>
+        <v>0.01270013319278518</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>-0.01701734230628749</v>
+        <v>0.06971120497584171</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.02466625434238856</v>
+        <v>0.02587353834271244</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.167115189033592</v>
+        <v>0.13141930403108</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.2081228253380711</v>
+        <v>0.1270384912677189</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.420185883117602</v>
+        <v>0.1722659781915219</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.1240399072926608</v>
+        <v>0.05440806793346109</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>103.86</v>
+        <v>17.99</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.01843495971301268</v>
+        <v>0.0123803774725495</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.01161021316562805</v>
+        <v>-0.01262346602108533</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.01405977804286729</v>
+        <v>0.01181097167394296</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.07571203860734288</v>
+        <v>0.05020435799677392</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>-0.0005773437225836675</v>
+        <v>0.2122641230553464</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>-0.01632665861411053</v>
+        <v>0.1414974308280543</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.2069518944156099</v>
+        <v>-0.05116030380765557</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.1701971942371832</v>
+        <v>-0.09643395735854343</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.2258376547432133</v>
+        <v>0.206572766950138</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.07023131073482136</v>
+        <v>0.06459520626867654</v>
       </c>
     </row>
     <row r="22">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1726,37 +1726,37 @@
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>14</v>
+        <v>103.57</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.01010103512198191</v>
+        <v>-0.002792229095157972</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.002849000139722779</v>
+        <v>-0.01192520514824735</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.00430419091985712</v>
+        <v>0.01221657548600663</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.01818181818181808</v>
+        <v>0.0614943119685003</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.02264429723291639</v>
+        <v>-0.0002895635109914085</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>-0.006030080459076714</v>
+        <v>0.01168814928159256</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.2004160224748299</v>
+        <v>0.1934189123171899</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.09476483204121067</v>
+        <v>0.171956377903921</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.06161843748381912</v>
+        <v>0.2224148351776991</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.02013148294918055</v>
+        <v>0.06923427183640318</v>
       </c>
     </row>
     <row r="23">
@@ -1768,51 +1768,51 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>42.19</v>
+        <v>117.85</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.00869367327638837</v>
+        <v>0.005031522489699292</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.03145093442127511</v>
+        <v>-0.02948202109904874</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.03145093442127511</v>
+        <v>-0.02587208460870916</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.03100602343664438</v>
+        <v>-0.03591295374972825</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.01944003618414358</v>
+        <v>-0.006909915795707877</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.01748187414154589</v>
+        <v>0.03234391354015664</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1155800461872334</v>
+        <v>0.1424660044873722</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.1211846149962741</v>
+        <v>0.2138565956958591</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.324314981312066</v>
+        <v>0.4273317122175799</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.09815530524062899</v>
+        <v>0.125921999645106</v>
       </c>
     </row>
     <row r="24">
@@ -1824,51 +1824,51 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>17.77</v>
+        <v>42.66</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.01892201339453026</v>
+        <v>0.01114010988389991</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.0225522464537794</v>
+        <v>-0.01112655421945841</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.006152053029414906</v>
+        <v>-0.01998619242549904</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.05085751733363719</v>
+        <v>-0.02335165866843658</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.1576547241793773</v>
+        <v>0.0317896065243648</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.1261090467976698</v>
+        <v>0.03452976895138615</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>-0.05327650376195803</v>
+        <v>0.1233319749226063</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>-0.1079317073441636</v>
+        <v>0.134539173033851</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.1918176149980286</v>
+        <v>0.3390683164067814</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.06023775816498844</v>
+        <v>0.1022182005858534</v>
       </c>
     </row>
     <row r="25">
@@ -1880,51 +1880,51 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>181.57</v>
+        <v>13.91</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.004441262950476421</v>
+        <v>-0.006428582327706489</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.02439413933288814</v>
+        <v>-0.002867380817199727</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.008085199141573352</v>
+        <v>0.001439849070915988</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.04057540035628038</v>
+        <v>0.0007194409464950091</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.1100446242832371</v>
+        <v>0.01016698511215397</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.1031395339351044</v>
+        <v>0.006531551938669944</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>-0.002567810946616511</v>
+        <v>0.1897296737783052</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>-0.06045583088196749</v>
+        <v>0.09604308518672422</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.6020590372409527</v>
+        <v>0.0547937359578432</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.1701086020019349</v>
+        <v>0.01794078211331973</v>
       </c>
     </row>
     <row r="26">
@@ -1936,46 +1936,52 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
+          <t>Defense and Aerospace</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
       <c r="F26" s="5" t="n">
-        <v>68.55</v>
+        <v>27.45</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.001753656964004868</v>
+        <v>0.01254150294847522</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.04989602769211088</v>
+        <v>-0.03481011788071575</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.06556703269594888</v>
+        <v>-0.04753639647438312</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.05487378732281356</v>
+        <v>-0.08712999529347287</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>-0.01324309993924599</v>
+        <v>0.01142230583134252</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>-0.03314525280035896</v>
+        <v>-0.05230616904524543</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.1405518083296209</v>
-      </c>
-      <c r="N26" s="6" t="inlineStr"/>
-      <c r="O26" s="6" t="inlineStr"/>
-      <c r="P26" s="6" t="inlineStr"/>
+        <v>0.1363801714664681</v>
+      </c>
+      <c r="N26" s="6" t="n">
+        <v>0.1503578475719136</v>
+      </c>
+      <c r="O26" s="6" t="n">
+        <v>1.049156410767717</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v>0.2701598184324046</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
@@ -1986,12 +1992,12 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -2000,38 +2006,32 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>27.11</v>
+        <v>69.31</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.008049737064348306</v>
+        <v>0.01108671733044431</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.05671535051314247</v>
+        <v>-0.028182867986977</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.09057359624160821</v>
+        <v>-0.03682603612554403</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.07284538910532101</v>
+        <v>-0.06565115565579516</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>-0.01454015322436553</v>
+        <v>-0.003164119438595958</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>-0.08606697626112414</v>
+        <v>0.0007218512968703017</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.1232145635710475</v>
-      </c>
-      <c r="N27" s="6" t="n">
-        <v>0.1282453793247316</v>
-      </c>
-      <c r="O27" s="6" t="n">
-        <v>1.023775227781444</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v>0.2648938815992976</v>
-      </c>
+        <v>0.1458778744385456</v>
+      </c>
+      <c r="N27" s="6" t="inlineStr"/>
+      <c r="O27" s="6" t="inlineStr"/>
+      <c r="P27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
@@ -2056,37 +2056,37 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>50.7</v>
+        <v>51.47</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.002570715224436526</v>
+        <v>0.01518738552616594</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.02612371445401651</v>
+        <v>-0.01322850131762832</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.0298507005108527</v>
+        <v>-0.0007764919847290663</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.01150321977103486</v>
+        <v>-0.01643417886985821</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>-0.07244784294781048</v>
+        <v>-0.0576711419403344</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.01472069052949054</v>
+        <v>0.05087950701343025</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.09190531700266513</v>
+        <v>0.09941205210080795</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.167268889436923</v>
+        <v>0.1852648060679702</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.6660117250202773</v>
+        <v>0.6913141933838125</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.1854757773121303</v>
+        <v>0.1914470998807409</v>
       </c>
     </row>
     <row r="29">
@@ -2098,12 +2098,12 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -2112,37 +2112,37 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>16.56</v>
+        <v>17.38</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.005464490366730912</v>
+        <v>0.006952429333341836</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.04718065215303779</v>
+        <v>0.0005756085808943379</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.04332755766258878</v>
+        <v>-0.009122106408734565</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.01837589554649377</v>
+        <v>-0.05697238887805678</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.06701024339586703</v>
+        <v>0.01046502266528893</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.04695217875850033</v>
+        <v>0.01794573949972977</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.01523030977693995</v>
+        <v>0.02869212373804331</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>-0.08614992611591599</v>
+        <v>0.03892281417891286</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.2899589026787919</v>
+        <v>0.4149720530548233</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.08857567311848902</v>
+        <v>0.1226626839287659</v>
       </c>
     </row>
     <row r="30">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -2168,37 +2168,37 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>17.26</v>
+        <v>16.49</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0</v>
+        <v>-0.004227034847928635</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.02485878616338244</v>
+        <v>-0.03000001346363745</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.04217537234048185</v>
+        <v>-0.04127912560045444</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.04482564912131071</v>
+        <v>-0.01961949641459271</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.002905354274788552</v>
+        <v>0.06800519554863849</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.008701674378984059</v>
+        <v>0.04252667541477329</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.02919073533843997</v>
+        <v>0.005180122439891743</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.03380600475455142</v>
+        <v>-0.0895859929388888</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.4052024820989935</v>
+        <v>0.2845062968675121</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1200729337334339</v>
+        <v>0.08703971801425459</v>
       </c>
     </row>
     <row r="31">
@@ -2224,37 +2224,37 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>63.35</v>
+        <v>64.28</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.005715141864766071</v>
+        <v>0.01468035244792776</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.01752488870940772</v>
+        <v>0.007997464605178806</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.04116847636244514</v>
+        <v>-0.007412034297402448</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.02762859569608478</v>
+        <v>-0.03526937672206709</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.03898664693887899</v>
+        <v>-0.01997252068509381</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>-0.009776822041803968</v>
+        <v>0.01319827403023033</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>-0.02732196204857429</v>
+        <v>-0.02387587630729238</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.009665337374226812</v>
+        <v>0.02121504269310681</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.3916479779197644</v>
+        <v>0.4120777423872728</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1164599048270423</v>
+        <v>0.121896696456993</v>
       </c>
     </row>
     <row r="32">
@@ -2280,37 +2280,37 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>54.45</v>
+        <v>55.43</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.004056817675828661</v>
+        <v>0.01799815479347711</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.002381844334077399</v>
+        <v>0.0161320088070207</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.01089915499430494</v>
+        <v>0.009837874321951379</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.004797972740717471</v>
+        <v>0.02081033303853141</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.03062128292816635</v>
+        <v>-0.01282281747350056</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>-0.0439862064678983</v>
+        <v>-0.001294960102706022</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>-0.02157831179370484</v>
+        <v>-0.01081405453352891</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.01444777831756816</v>
+        <v>0.005041864057943268</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.2030511393667407</v>
+        <v>0.2247039432207498</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.06355845120421622</v>
+        <v>0.06990127578406868</v>
       </c>
     </row>
     <row r="33">
@@ -2336,37 +2336,37 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>126.7</v>
+        <v>127.85</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.002611333342469768</v>
+        <v>0.009076571062181626</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.01821004299064688</v>
+        <v>-0.002730097367025675</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.03208553967973093</v>
+        <v>-0.01623582741413443</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.04514285464580614</v>
+        <v>-0.04196327165367431</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.05520544879274702</v>
+        <v>-0.04171783301933008</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.1124541752191471</v>
+        <v>-0.09288988230856621</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>-0.03780933599731351</v>
+        <v>-0.0266028862995743</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.03188026605857974</v>
+        <v>0.04229686831170421</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.5141291822146858</v>
+        <v>0.527872004726518</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1482972108148524</v>
+        <v>0.1517608826276542</v>
       </c>
     </row>
     <row r="34">
@@ -2392,37 +2392,37 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>115.02</v>
+        <v>115.99</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.002877270857403191</v>
+        <v>0.00843332680414921</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.04269666931054972</v>
+        <v>-0.02250131228668106</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.06753143035346143</v>
+        <v>-0.04219653736365292</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.05083350096217376</v>
+        <v>-0.06263132482459144</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.05550995404821513</v>
+        <v>-0.05345195856717055</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.1079163769663869</v>
+        <v>-0.08483892865464948</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.02673130118796885</v>
+        <v>-0.02758813853892617</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.0526217526662941</v>
+        <v>-0.04589009622407458</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2727876368249362</v>
+        <v>0.2835213625568711</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.08372389540976388</v>
+        <v>0.08676180670338551</v>
       </c>
     </row>
   </sheetData>
@@ -2697,17 +2697,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2742,17 +2742,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2787,17 +2787,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -2832,17 +2832,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2854,12 +2854,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2899,12 +2899,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2922,17 +2922,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -2944,17 +2944,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.3117313595296731</v>
+        <v>0.3554907061149115</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.07284538910532101</v>
+        <v>-0.08712999529347287</v>
       </c>
     </row>
     <row r="18">
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.1008193784992408</v>
+        <v>0.1171790168469589</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -3109,7 +3109,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.05487378732281356</v>
+        <v>-0.06565115565579516</v>
       </c>
     </row>
     <row r="19">
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.09867344061714123</v>
+        <v>0.1028651259996782</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.05083350096217376</v>
+        <v>-0.06263132482459144</v>
       </c>
     </row>
     <row r="20">
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.08954673980028605</v>
+        <v>0.09330403381555352</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -3185,21 +3185,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.04514285464580614</v>
+        <v>-0.05697238887805678</v>
       </c>
     </row>
     <row r="21">
@@ -3208,21 +3208,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.08740469645789894</v>
+        <v>0.08030502174326015</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -3230,21 +3230,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.04482564912131071</v>
+        <v>-0.04196327165367431</v>
       </c>
     </row>
     <row r="22">
@@ -3253,21 +3253,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.07888634910092618</v>
+        <v>0.07556370618105723</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -3275,21 +3275,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.03100602343664438</v>
+        <v>-0.03591295374972825</v>
       </c>
     </row>
     <row r="23">
@@ -3298,21 +3298,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.07571203860734288</v>
+        <v>0.06836589800036652</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.02762859569608478</v>
+        <v>-0.03526937672206709</v>
       </c>
     </row>
     <row r="24">
@@ -3343,21 +3343,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.0695228760876454</v>
+        <v>0.0614943119685003</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -3365,21 +3365,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.02737222535824491</v>
+        <v>-0.02335165866843658</v>
       </c>
     </row>
     <row r="25">
@@ -3388,21 +3388,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.05366147043745295</v>
+        <v>0.05931572094130289</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.01837589554649377</v>
+        <v>-0.01961949641459271</v>
       </c>
     </row>
     <row r="26">
@@ -3433,21 +3433,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.05085751733363719</v>
+        <v>0.05077761537103087</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -3455,21 +3455,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.01168519781499366</v>
+        <v>-0.01643417886985821</v>
       </c>
     </row>
     <row r="27"/>
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.2810944669731763</v>
+        <v>0.2577361588498377</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.1908719597409124</v>
+        <v>-0.1921616297728077</v>
       </c>
     </row>
     <row r="32">
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.2483249796305862</v>
+        <v>0.2418952545307658</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.106562335504105</v>
+        <v>-0.09101942000396746</v>
       </c>
     </row>
     <row r="33">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.2193712909540968</v>
+        <v>0.2189227080311937</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.08472475550041192</v>
+        <v>-0.07878402446946553</v>
       </c>
     </row>
     <row r="34">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FSPCX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.1614323113127061</v>
+        <v>0.2122641230553464</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -3696,21 +3696,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.08022387407875642</v>
+        <v>-0.0576711419403344</v>
       </c>
     </row>
     <row r="35">
@@ -3719,21 +3719,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.1576547241793773</v>
+        <v>0.2026210699294706</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -3741,21 +3741,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.07244784294781048</v>
+        <v>-0.05441123000811454</v>
       </c>
     </row>
     <row r="36">
@@ -3764,21 +3764,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FSPCX</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
       <c r="E36" s="11" t="n">
-        <v>0.1487979149296503</v>
+        <v>0.1934087316466444</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.05550995404821513</v>
+        <v>-0.05345195856717055</v>
       </c>
     </row>
     <row r="37">
@@ -3809,21 +3809,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1389625624973023</v>
+        <v>0.1825972606349773</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.05520544879274702</v>
+        <v>-0.04171783301933008</v>
       </c>
     </row>
     <row r="38">
@@ -3854,21 +3854,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FSHCX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1212294933995839</v>
+        <v>0.1688669535378804</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.03898664693887899</v>
+        <v>-0.01997252068509381</v>
       </c>
     </row>
     <row r="39">
@@ -3899,21 +3899,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1177644401554128</v>
+        <v>0.1450648018387373</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.03062128292816635</v>
+        <v>-0.01282281747350056</v>
       </c>
     </row>
     <row r="40">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSRBX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1100446242832371</v>
+        <v>0.1271236154123605</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -3966,21 +3966,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.0256239044535681</v>
+        <v>-0.006909915795707877</v>
       </c>
     </row>
     <row r="41"/>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.4170465009848368</v>
+        <v>0.4938975646941843</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -4072,21 +4072,21 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1370739565968099</v>
+        <v>-0.09288988230856621</v>
       </c>
     </row>
     <row r="46">
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.3602520511087157</v>
+        <v>0.4105544324177868</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -4117,21 +4117,21 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.1124541752191471</v>
+        <v>-0.08483892865464948</v>
       </c>
     </row>
     <row r="47">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.3413366332155268</v>
+        <v>0.3991717461873354</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -4162,21 +4162,21 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.1079163769663869</v>
+        <v>-0.05230616904524543</v>
       </c>
     </row>
     <row r="48">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.3063520083814377</v>
+        <v>0.3385720786667437</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -4207,21 +4207,21 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.08606697626112414</v>
+        <v>-0.02717773275784641</v>
       </c>
     </row>
     <row r="49">
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.2424825601469582</v>
+        <v>0.2610546688730686</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.0439862064678983</v>
+        <v>-0.001294960102706022</v>
       </c>
     </row>
     <row r="50">
@@ -4289,7 +4289,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.2364811886800113</v>
+        <v>0.2600385181951754</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.03314525280035896</v>
+        <v>0.0007218512968703017</v>
       </c>
     </row>
     <row r="51">
@@ -4334,7 +4334,7 @@
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.1904484431687647</v>
+        <v>0.2125937181650828</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -4342,21 +4342,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
       <c r="K51" s="11" t="n">
-        <v>-0.01632665861411053</v>
+        <v>0.006531551938669944</v>
       </c>
     </row>
     <row r="52">
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.187849396602793</v>
+        <v>0.1965726511943291</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4387,21 +4387,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-0.009776822041803968</v>
+        <v>0.01168814928159256</v>
       </c>
     </row>
     <row r="53">
@@ -4410,21 +4410,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FIDSX</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.1695543502401924</v>
+        <v>0.1915662380442442</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -4432,21 +4432,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>-0.006030080459076714</v>
+        <v>0.01319827403023033</v>
       </c>
     </row>
     <row r="54">
@@ -4455,21 +4455,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FIDSX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.1651467785261769</v>
+        <v>0.1888888165643838</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.008701674378984059</v>
+        <v>0.01794573949972977</v>
       </c>
     </row>
     <row r="55"/>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.9486809491260837</v>
+        <v>0.9386741294708902</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.1079317073441636</v>
+        <v>-0.09643395735854343</v>
       </c>
     </row>
     <row r="60">
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.8440574937963792</v>
+        <v>0.8476440521545707</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.08614992611591599</v>
+        <v>-0.0895859929388888</v>
       </c>
     </row>
     <row r="61">
@@ -4651,21 +4651,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.5836153450337398</v>
+        <v>0.5821441070209217</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4673,21 +4673,21 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.06045583088196749</v>
+        <v>-0.04589009622407458</v>
       </c>
     </row>
     <row r="62">
@@ -4696,21 +4696,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.5624542381089783</v>
+        <v>0.5777877495461556</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4718,21 +4718,21 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.0526217526662941</v>
+        <v>-0.02554155412270065</v>
       </c>
     </row>
     <row r="63">
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.5197422867760992</v>
+        <v>0.5677063463050824</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.01444777831756816</v>
+        <v>0.005041864057943268</v>
       </c>
     </row>
     <row r="64">
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.501626472439225</v>
+        <v>0.5216264313801517</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>0.009665337374226812</v>
+        <v>0.02121504269310681</v>
       </c>
     </row>
     <row r="65">
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.4729336952824486</v>
+        <v>0.4645741038173641</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.01381053978399049</v>
+        <v>0.03231341455961201</v>
       </c>
     </row>
     <row r="66">
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.3453386401918264</v>
+        <v>0.3459809014449917</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4898,21 +4898,21 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSRPX</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Retailing</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>0.01506187928588454</v>
+        <v>0.03892281417891286</v>
       </c>
     </row>
     <row r="67">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.2847592622590653</v>
+        <v>0.2968795796924908</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.03188026605857974</v>
+        <v>0.04229686831170421</v>
       </c>
     </row>
     <row r="68">
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.2161679426197756</v>
+        <v>0.2313804281907024</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -4988,21 +4988,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.03380600475455142</v>
+        <v>0.04962981105947573</v>
       </c>
     </row>
     <row r="69"/>
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.365648012932164</v>
+        <v>2.492861879669038</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.06161843748381912</v>
+        <v>0.0547937359578432</v>
       </c>
     </row>
     <row r="74">
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.270834782078904</v>
+        <v>2.280748088443685</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.1136238500023075</v>
+        <v>0.1182841311504481</v>
       </c>
     </row>
     <row r="75">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.076329116564404</v>
+        <v>2.095898492798943</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1470949987652306</v>
+        <v>0.1514441907067867</v>
       </c>
     </row>
     <row r="76">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.396809473623338</v>
+        <v>1.434819223918615</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1733779929849273</v>
+        <v>0.1722659781915219</v>
       </c>
     </row>
     <row r="77">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.133148593886366</v>
+        <v>1.156688458469165</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1918176149980286</v>
+        <v>0.206572766950138</v>
       </c>
     </row>
     <row r="78">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.023775227781444</v>
+        <v>1.049156410767717</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5319,21 +5319,21 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.2030511393667407</v>
+        <v>0.2224148351776991</v>
       </c>
     </row>
     <row r="79">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.016799672790557</v>
+        <v>1.01614684637042</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5364,21 +5364,21 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.2258376547432133</v>
+        <v>0.2247039432207498</v>
       </c>
     </row>
     <row r="80">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.9405190055747927</v>
+        <v>0.9690558682959405</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.2459140759313039</v>
+        <v>0.269964575029535</v>
       </c>
     </row>
     <row r="81">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.7769288480182526</v>
+        <v>0.7936920496356643</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.2727876368249362</v>
+        <v>0.2835213625568711</v>
       </c>
     </row>
     <row r="82">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.761388720577195</v>
+        <v>0.7802202180840432</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.2899589026787919</v>
+        <v>0.2845062968675121</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -633,10 +633,10 @@
         <v>0.9386741294708902</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.095898492798943</v>
+        <v>2.095898832676281</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4574563975472217</v>
+        <v>0.4574564508819141</v>
       </c>
     </row>
     <row r="3">
@@ -689,10 +689,10 @@
         <v>0.5777877495461556</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1.01614684637042</v>
+        <v>1.016146595380402</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2633025912231215</v>
+        <v>0.2633025388002943</v>
       </c>
     </row>
     <row r="4">
@@ -742,7 +742,7 @@
         <v>0.4953473715013119</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.5821441070209217</v>
+        <v>0.5821442086912221</v>
       </c>
       <c r="O4" s="6" t="n">
         <v>0.6359265697093406</v>
@@ -795,16 +795,16 @@
         <v>0.3991717461873354</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.4873734985340017</v>
+        <v>0.4873736402022748</v>
       </c>
       <c r="N5" s="6" t="n">
         <v>0.8476440521545707</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>2.280748088443685</v>
+        <v>2.280748433069891</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.4859047173909332</v>
+        <v>0.4859047694198886</v>
       </c>
     </row>
     <row r="6">
@@ -969,10 +969,10 @@
         <v>0.5216264313801517</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>1.434819223918615</v>
+        <v>1.434819018665046</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.34530959810399</v>
+        <v>0.3453095603011007</v>
       </c>
     </row>
     <row r="9">
@@ -1025,10 +1025,10 @@
         <v>0.4645741038173641</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.7067113131266989</v>
+        <v>0.7067111571950246</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1950516864315586</v>
+        <v>0.1950516500367263</v>
       </c>
     </row>
     <row r="10">
@@ -1134,7 +1134,7 @@
         <v>0.1857608791225325</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.2313804281907024</v>
+        <v>0.2313803530319625</v>
       </c>
       <c r="O11" s="6" t="n">
         <v>1.156688458469165</v>
@@ -1358,7 +1358,7 @@
         <v>0.07279622323976764</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.03231341455961201</v>
+        <v>0.03231332607001747</v>
       </c>
       <c r="O15" s="6" t="n">
         <v>0.269964575029535</v>
@@ -1414,13 +1414,13 @@
         <v>-0.004791090033746892</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.07485909076090569</v>
+        <v>0.07485917399422393</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.1514441907067867</v>
+        <v>0.1514442862236229</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.04812793884710875</v>
+        <v>0.04812796782922302</v>
       </c>
     </row>
     <row r="17">
@@ -1523,16 +1523,16 @@
         <v>0.07200481634789746</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.2190850661962966</v>
+        <v>0.2190851461579719</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.1959931612342185</v>
+        <v>0.1959930842731306</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.7802202180840432</v>
+        <v>0.7802203885985499</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.2119682507567646</v>
+        <v>0.2119682894520076</v>
       </c>
     </row>
     <row r="19">
@@ -1582,7 +1582,7 @@
         <v>0.003715821549403975</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>-0.02554155412270065</v>
+        <v>-0.02554147656527817</v>
       </c>
       <c r="O19" s="6" t="n">
         <v>0.6483819424660735</v>
@@ -1632,19 +1632,19 @@
         <v>0.06971120497584171</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.02587353834271244</v>
+        <v>0.02587362295965345</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.13141930403108</v>
+        <v>0.1314194069551231</v>
       </c>
       <c r="N20" s="6" t="n">
         <v>0.1270384912677189</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.1722659781915219</v>
+        <v>0.1722660886812724</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.05440806793346109</v>
+        <v>0.05440810106055083</v>
       </c>
     </row>
     <row r="21">
@@ -1747,16 +1747,16 @@
         <v>0.01168814928159256</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.1934189123171899</v>
+        <v>0.1934188074011494</v>
       </c>
       <c r="N22" s="6" t="n">
         <v>0.171956377903921</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.2224148351776991</v>
+        <v>0.222414725101536</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.06923427183640318</v>
+        <v>0.06923423974222209</v>
       </c>
     </row>
     <row r="23">
@@ -1809,10 +1809,10 @@
         <v>0.2138565956958591</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.4273317122175799</v>
+        <v>0.4273315803280615</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.125921999645106</v>
+        <v>0.1259219649656378</v>
       </c>
     </row>
     <row r="24">
@@ -1865,10 +1865,10 @@
         <v>0.134539173033851</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.3390683164067814</v>
+        <v>0.339068075895264</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1022182005858534</v>
+        <v>0.1022181345956459</v>
       </c>
     </row>
     <row r="25">
@@ -1971,7 +1971,7 @@
         <v>-0.05230616904524543</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.1363801714664681</v>
+        <v>0.1363800817370231</v>
       </c>
       <c r="N26" s="6" t="n">
         <v>0.1503578475719136</v>
@@ -2083,10 +2083,10 @@
         <v>0.1852648060679702</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.6913141933838125</v>
+        <v>0.6913140873792729</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.1914470998807409</v>
+        <v>0.1914470749890909</v>
       </c>
     </row>
     <row r="29">
@@ -2133,16 +2133,16 @@
         <v>0.01794573949972977</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.02869212373804331</v>
+        <v>0.02869223986985725</v>
       </c>
       <c r="N29" s="6" t="n">
         <v>0.03892281417891286</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.4149720530548233</v>
+        <v>0.4149722727781284</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1226626839287659</v>
+        <v>0.1226627420394877</v>
       </c>
     </row>
     <row r="30">
@@ -2248,7 +2248,7 @@
         <v>-0.02387587630729238</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.02121504269310681</v>
+        <v>0.02121491891365124</v>
       </c>
       <c r="O31" s="6" t="n">
         <v>0.4120777423872728</v>
@@ -2304,7 +2304,7 @@
         <v>-0.01081405453352891</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.005041864057943268</v>
+        <v>0.005041794542151701</v>
       </c>
       <c r="O32" s="6" t="n">
         <v>0.2247039432207498</v>
@@ -2354,19 +2354,19 @@
         <v>-0.04171783301933008</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.09288988230856621</v>
+        <v>-0.09288978410225213</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>-0.0266028862995743</v>
+        <v>-0.02660277321600679</v>
       </c>
       <c r="N33" s="6" t="n">
         <v>0.04229686831170421</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.527872004726518</v>
+        <v>0.5278722833343803</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1517608826276542</v>
+        <v>0.1517609526356167</v>
       </c>
     </row>
     <row r="34">
@@ -2413,16 +2413,16 @@
         <v>-0.08483892865464948</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.02758813853892617</v>
+        <v>-0.02758820073600687</v>
       </c>
       <c r="N34" s="6" t="n">
         <v>-0.04589009622407458</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2835213625568711</v>
+        <v>0.2835212541951986</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.08676180670338551</v>
+        <v>0.08676177611998837</v>
       </c>
     </row>
   </sheetData>
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.09288988230856621</v>
+        <v>-0.09288978410225213</v>
       </c>
     </row>
     <row r="46">
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.5821441070209217</v>
+        <v>0.5821442086912221</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.02554155412270065</v>
+        <v>-0.02554147656527817</v>
       </c>
     </row>
     <row r="63">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>0.005041864057943268</v>
+        <v>0.005041794542151701</v>
       </c>
     </row>
     <row r="64">
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>0.02121504269310681</v>
+        <v>0.02121491891365124</v>
       </c>
     </row>
     <row r="65">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.03231341455961201</v>
+        <v>0.03231332607001747</v>
       </c>
     </row>
     <row r="66">
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.2313804281907024</v>
+        <v>0.2313803530319625</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.280748088443685</v>
+        <v>2.280748433069891</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.095898492798943</v>
+        <v>2.095898832676281</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1514441907067867</v>
+        <v>0.1514442862236229</v>
       </c>
     </row>
     <row r="76">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.434819223918615</v>
+        <v>1.434819018665046</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1722659781915219</v>
+        <v>0.1722660886812724</v>
       </c>
     </row>
     <row r="77">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.2224148351776991</v>
+        <v>0.222414725101536</v>
       </c>
     </row>
     <row r="79">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.01614684637042</v>
+        <v>1.016146595380402</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.2835213625568711</v>
+        <v>0.2835212541951986</v>
       </c>
     </row>
     <row r="82">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.7802202180840432</v>
+        <v>0.7802203885985499</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -633,10 +633,10 @@
         <v>0.9386741294708902</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.095898832676281</v>
+        <v>2.095899172553695</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4574564508819141</v>
+        <v>0.4574565042166145</v>
       </c>
     </row>
     <row r="3">
@@ -683,16 +683,16 @@
         <v>0.2610546688730686</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.2780450095163329</v>
+        <v>0.2780449086597045</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.5777877495461556</v>
+        <v>0.5777879032587259</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1.016146595380402</v>
+        <v>1.01614684637042</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2633025388002943</v>
+        <v>0.2633025912231215</v>
       </c>
     </row>
     <row r="4">
@@ -742,13 +742,13 @@
         <v>0.4953473715013119</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.5821442086912221</v>
+        <v>0.5821441070209217</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.6359265697093406</v>
+        <v>0.6359264610093303</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1782965389141948</v>
+        <v>0.1782965128166809</v>
       </c>
     </row>
     <row r="5">
@@ -857,10 +857,10 @@
         <v>0.5677063463050824</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>2.492861879669038</v>
+        <v>2.492861212338668</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.5172616150006557</v>
+        <v>0.5172615183736053</v>
       </c>
     </row>
     <row r="7">
@@ -913,10 +913,10 @@
         <v>0.3459809014449917</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.4609830202740366</v>
+        <v>0.4609828840230052</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.134701745271151</v>
+        <v>0.1347017099971184</v>
       </c>
     </row>
     <row r="8">
@@ -969,10 +969,10 @@
         <v>0.5216264313801517</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>1.434819018665046</v>
+        <v>1.434819223918615</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.3453095603011007</v>
+        <v>0.34530959810399</v>
       </c>
     </row>
     <row r="9">
@@ -1025,10 +1025,10 @@
         <v>0.4645741038173641</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.7067111571950246</v>
+        <v>0.7067113131266989</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1950516500367263</v>
+        <v>0.1950516864315586</v>
       </c>
     </row>
     <row r="10">
@@ -1081,10 +1081,10 @@
         <v>0.1819133855764432</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.9690558682959405</v>
+        <v>0.9690560744034227</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2533893865767978</v>
+        <v>0.253389430308911</v>
       </c>
     </row>
     <row r="11">
@@ -1137,10 +1137,10 @@
         <v>0.2313803530319625</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>1.156688458469165</v>
+        <v>1.156688689021698</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.2919998742897276</v>
+        <v>0.2919999203284949</v>
       </c>
     </row>
     <row r="12">
@@ -1193,10 +1193,10 @@
         <v>0.1128506409113266</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.6052353157437484</v>
+        <v>0.6052350185364734</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.1708813861118326</v>
+        <v>0.1708813138494287</v>
       </c>
     </row>
     <row r="13">
@@ -1358,13 +1358,13 @@
         <v>0.07279622323976764</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.03231332607001747</v>
+        <v>0.03231341455961201</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.269964575029535</v>
+        <v>0.2699644411074296</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.08292206375181044</v>
+        <v>0.08292202568586471</v>
       </c>
     </row>
     <row r="16">
@@ -1417,10 +1417,10 @@
         <v>0.07485917399422393</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.1514442862236229</v>
+        <v>0.1514441907067867</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.04812796782922302</v>
+        <v>0.04812793884710875</v>
       </c>
     </row>
     <row r="17">
@@ -1473,10 +1473,10 @@
         <v>0.2968795796924908</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.7936920496356643</v>
+        <v>0.7936922544612015</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.2150177645651059</v>
+        <v>0.2150178108135978</v>
       </c>
     </row>
     <row r="18">
@@ -1523,16 +1523,16 @@
         <v>0.07200481634789746</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.2190851461579719</v>
+        <v>0.2190850661962966</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.1959930842731306</v>
+        <v>0.1959931612342185</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.7802203885985499</v>
+        <v>0.7802202180840432</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.2119682894520076</v>
+        <v>0.2119682507567646</v>
       </c>
     </row>
     <row r="19">
@@ -1632,19 +1632,19 @@
         <v>0.06971120497584171</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.02587362295965345</v>
+        <v>0.02587353834271244</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.1314194069551231</v>
+        <v>0.13141930403108</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.1270384912677189</v>
+        <v>0.1270383891391873</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.1722660886812724</v>
+        <v>0.1722659781915219</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.05440810106055083</v>
+        <v>0.05440806793346109</v>
       </c>
     </row>
     <row r="21">
@@ -1753,10 +1753,10 @@
         <v>0.171956377903921</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.222414725101536</v>
+        <v>0.2224148351776991</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.06923423974222209</v>
+        <v>0.06923427183640318</v>
       </c>
     </row>
     <row r="23">
@@ -1862,7 +1862,7 @@
         <v>0.1233319749226063</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.134539173033851</v>
+        <v>0.1345392881346303</v>
       </c>
       <c r="O24" s="6" t="n">
         <v>0.339068075895264</v>
@@ -1971,7 +1971,7 @@
         <v>-0.05230616904524543</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.1363800817370231</v>
+        <v>0.1363801714664681</v>
       </c>
       <c r="N26" s="6" t="n">
         <v>0.1503578475719136</v>
@@ -2139,10 +2139,10 @@
         <v>0.03892281417891286</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.4149722727781284</v>
+        <v>0.4149720530548233</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1226627420394877</v>
+        <v>0.1226626839287659</v>
       </c>
     </row>
     <row r="30">
@@ -2195,10 +2195,10 @@
         <v>-0.0895859929388888</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.2845062968675121</v>
+        <v>0.2845062014447728</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.08703971801425459</v>
+        <v>0.08703969109643928</v>
       </c>
     </row>
     <row r="31">
@@ -2248,13 +2248,13 @@
         <v>-0.02387587630729238</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.02121491891365124</v>
+        <v>0.02121504269310681</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.4120777423872728</v>
+        <v>0.4120778607190725</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.121896696456993</v>
+        <v>0.121896727795223</v>
       </c>
     </row>
     <row r="32">
@@ -2307,10 +2307,10 @@
         <v>0.005041794542151701</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.2247039432207498</v>
+        <v>0.2247038399975321</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.06990127578406868</v>
+        <v>0.0699012457254693</v>
       </c>
     </row>
     <row r="33">
@@ -2363,10 +2363,10 @@
         <v>0.04229686831170421</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.5278722833343803</v>
+        <v>0.5278721440304364</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1517609526356167</v>
+        <v>0.1517609176316332</v>
       </c>
     </row>
     <row r="34">
@@ -2419,10 +2419,10 @@
         <v>-0.04589009622407458</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2835212541951986</v>
+        <v>0.2835213625568711</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.08676177611998837</v>
+        <v>0.08676180670338551</v>
       </c>
     </row>
   </sheetData>
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.5821442086912221</v>
+        <v>0.5821441070209217</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.5777877495461556</v>
+        <v>0.5777879032587259</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>0.02121491891365124</v>
+        <v>0.02121504269310681</v>
       </c>
     </row>
     <row r="65">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.03231332607001747</v>
+        <v>0.03231341455961201</v>
       </c>
     </row>
     <row r="66">
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.492861879669038</v>
+        <v>2.492861212338668</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.095898832676281</v>
+        <v>2.095899172553695</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1514442862236229</v>
+        <v>0.1514441907067867</v>
       </c>
     </row>
     <row r="76">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.434819018665046</v>
+        <v>1.434819223918615</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1722660886812724</v>
+        <v>0.1722659781915219</v>
       </c>
     </row>
     <row r="77">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.156688458469165</v>
+        <v>1.156688689021698</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.222414725101536</v>
+        <v>0.2224148351776991</v>
       </c>
     </row>
     <row r="79">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.016146595380402</v>
+        <v>1.01614684637042</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.2247039432207498</v>
+        <v>0.2247038399975321</v>
       </c>
     </row>
     <row r="80">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.9690558682959405</v>
+        <v>0.9690560744034227</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.269964575029535</v>
+        <v>0.2699644411074296</v>
       </c>
     </row>
     <row r="81">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.7936920496356643</v>
+        <v>0.7936922544612015</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.2835212541951986</v>
+        <v>0.2835213625568711</v>
       </c>
     </row>
     <row r="82">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.7802203885985499</v>
+        <v>0.7802202180840432</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.2845062968675121</v>
+        <v>0.2845062014447728</v>
       </c>
     </row>
   </sheetData>

--- a/Fidelity_RS_Leaderboard.xlsx
+++ b/Fidelity_RS_Leaderboard.xlsx
@@ -489,14 +489,14 @@
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
     <col width="21" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>215.15</v>
+        <v>219.46</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.006361385719916957</v>
+        <v>0.02003259558285886</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>-0.007427572666324211</v>
+        <v>0.03304464409614738</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.009619839203443892</v>
+        <v>0.01780916280325795</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.02898272353881892</v>
+        <v>0.008594192782064525</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>-0.07878402446946553</v>
+        <v>-0.04648938468019193</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.4938975646941843</v>
+        <v>0.4881384780615803</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.72035447422934</v>
+        <v>0.7453300462667705</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.9386741294708902</v>
+        <v>0.944512198213405</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.095899172553695</v>
+        <v>2.15791772195673</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4574565042166145</v>
+        <v>0.4671243893505963</v>
       </c>
     </row>
     <row r="3">
@@ -648,51 +648,51 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>30.89</v>
+        <v>61.35</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>-0.0003236320066437592</v>
+        <v>0.02988079215067607</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>-0.01025311452134658</v>
+        <v>0.03057281592717209</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.009807101522200101</v>
+        <v>0.01237623793539</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.1171790168469589</v>
+        <v>-0.02881114053473155</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.2577361588498377</v>
+        <v>-0.1528583260800356</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.2610546688730686</v>
+        <v>0.4196277453949253</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.2780449086597045</v>
+        <v>0.5354973879175204</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.5777879032587259</v>
+        <v>0.8744448065313644</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1.01614684637042</v>
+        <v>2.378779795097108</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2633025912231215</v>
+        <v>0.5005597607299823</v>
       </c>
     </row>
     <row r="4">
@@ -704,51 +704,51 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>93.92</v>
+        <v>30.6</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.005295488346709676</v>
+        <v>-0.009388119582672827</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.03641575063280111</v>
+        <v>0.009901028117592858</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.01557087759235842</v>
+        <v>-0.01576068731789237</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.1028651259996782</v>
+        <v>0.07670655521898428</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.121700637805694</v>
+        <v>0.2171838156077872</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.1965726511943291</v>
+        <v>0.2271056958961459</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.4953473715013119</v>
+        <v>0.2596844761162502</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.5821441070209217</v>
+        <v>0.5637254242607663</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.6359264610093303</v>
+        <v>0.9972191429973363</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1782965128166809</v>
+        <v>0.259336835662711</v>
       </c>
     </row>
     <row r="5">
@@ -760,51 +760,51 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>59.57</v>
+        <v>93.22</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.003030818437879113</v>
+        <v>-0.007453119270541486</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.0357720804166356</v>
+        <v>0.02642591426936192</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>-0.02296213708133432</v>
+        <v>0.008983676117955364</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-0.005343124028809543</v>
+        <v>0.100460420590305</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>-0.1921616297728077</v>
+        <v>0.1102906412244469</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.3991717461873354</v>
+        <v>0.1928076187977046</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.4873736402022748</v>
+        <v>0.4802257094488755</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.8476440521545707</v>
+        <v>0.5590290012319978</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>2.280748433069891</v>
+        <v>0.6237337059775929</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.4859047694198886</v>
+        <v>0.1753618818292768</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>69.73999999999999</v>
+        <v>55.47</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.03779763438804418</v>
+        <v>0.006897822963563449</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>-0.02624971810549426</v>
+        <v>0.01481890551687148</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.01263242460420377</v>
+        <v>0.03180809063539325</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.3554907061149115</v>
+        <v>0.01167243057223377</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.2026210699294706</v>
+        <v>-0.04870519783401617</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>-0.02717773275784641</v>
+        <v>0.4008664274395921</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.3024151490577824</v>
+        <v>0.366891456181085</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.5677063463050824</v>
+        <v>0.5203395510118518</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>2.492861212338668</v>
+        <v>1.451613969204115</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.5172615183736053</v>
+        <v>0.348395710959795</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>29.88</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.002348195104940887</v>
+        <v>-0.01634642134453912</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.009283842442377677</v>
+        <v>-0.009529362427843746</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-0.005326289942888751</v>
+        <v>-0.03529745626053449</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.09330403381555352</v>
+        <v>0.2724911643162278</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.2418952545307658</v>
+        <v>0.1633033246408868</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.2125937181650828</v>
+        <v>-0.04606616324414392</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.1707412530469439</v>
+        <v>0.2720522705606589</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.3459809014449917</v>
+        <v>0.5517388278611113</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.4609828840230052</v>
+        <v>2.435765431263782</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1347017099971184</v>
+        <v>0.5089487926857919</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>55.09</v>
+        <v>29.68</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.01585839235867526</v>
+        <v>-0.006693402316203079</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.009350844309591211</v>
+        <v>0.005420048947527345</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.02226759652125665</v>
+        <v>-0.02432609366411009</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.04159577969989603</v>
+        <v>0.07536231503469604</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>-0.05441123000811454</v>
+        <v>0.2001617814220076</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.4105544324177868</v>
+        <v>0.193723085193934</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.3539814180831902</v>
+        <v>0.1583917862990591</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.5216264313801517</v>
+        <v>0.3280487452047611</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>1.434819223918615</v>
+        <v>0.4512040731422011</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.34530959810399</v>
+        <v>0.1321644039101491</v>
       </c>
     </row>
     <row r="9">
@@ -998,37 +998,37 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>35.63</v>
+        <v>35.29</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.002532362134762156</v>
+        <v>-0.009542524344523629</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.001960775723480856</v>
+        <v>0.004268683223799252</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-0.00890124306072626</v>
+        <v>-0.03394464563936128</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.06836589800036652</v>
+        <v>0.05029769399269157</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.0932801749399792</v>
+        <v>0.05406216840020051</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.1338867696390422</v>
+        <v>0.1182064142505757</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.1910693052350443</v>
+        <v>0.1902701886213711</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.4645741038173641</v>
+        <v>0.4483397004692005</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.7067113131266989</v>
+        <v>0.6904249788721135</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1950516864315586</v>
+        <v>0.1912382607465002</v>
       </c>
     </row>
     <row r="10">
@@ -1054,37 +1054,37 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>17.94</v>
+        <v>17.85</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.01470589504490682</v>
+        <v>-0.005016730764139776</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.01528016166371748</v>
+        <v>0.004501965202319491</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.03044231426138055</v>
+        <v>0.01305332186614905</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.02572903195130705</v>
+        <v>0.01305332186614905</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.1825972606349773</v>
+        <v>0.1464354997645521</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.1915662380442442</v>
+        <v>0.180951189962268</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.1790075905047148</v>
+        <v>0.1673529052596574</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.1819133855764432</v>
+        <v>0.1623763819965536</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.9690560744034227</v>
+        <v>0.9591776451451504</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.253389430308911</v>
+        <v>0.2512898994340056</v>
       </c>
     </row>
     <row r="11">
@@ -1110,37 +1110,37 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>38.48</v>
+        <v>38.59</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.01103515905913888</v>
+        <v>0.002858643754161783</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.01503560266732973</v>
+        <v>0.01552631980494446</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.0145003752342574</v>
+        <v>0.01525919117776198</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>-0.01181302261672768</v>
+        <v>-0.01981200915566128</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.1271236154123605</v>
+        <v>0.09351088556103071</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.1529606327184165</v>
+        <v>0.1498554118457829</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.1857608791225325</v>
+        <v>0.1841654316169528</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.2313803530319625</v>
+        <v>0.2168132542319201</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>1.156688689021698</v>
+        <v>1.16285366246064</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.2919999203284949</v>
+        <v>0.2932298254927455</v>
       </c>
     </row>
     <row r="12">
@@ -1166,37 +1166,37 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>99.22</v>
+        <v>97.73999999999999</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.01628601876488833</v>
+        <v>-0.01491638116030158</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.01889509159151848</v>
+        <v>-0.003771305109369183</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.02235958887902378</v>
+        <v>0.005038538444930962</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.01743236911562773</v>
+        <v>0.003284743387792721</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.1934087316466444</v>
+        <v>0.1583313705288181</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.1291038545741465</v>
+        <v>0.1122617111097528</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.1613599084411854</v>
+        <v>0.1428870032344536</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.1128506409113266</v>
+        <v>0.08878792045808215</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.6052350185364734</v>
+        <v>0.5812911115135011</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.1708813138494287</v>
+        <v>0.1650304501888928</v>
       </c>
     </row>
     <row r="13">
@@ -1222,37 +1222,37 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>117.58</v>
+        <v>116.7</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.004184862144414492</v>
+        <v>-0.007484307442663041</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.01651252435674522</v>
+        <v>0.0139009426180039</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.03321615709955372</v>
+        <v>0.0146943290202699</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-0.001613270080898066</v>
+        <v>0.002921934823884698</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.1191700415324901</v>
+        <v>0.07736334266088796</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.1689035302883712</v>
+        <v>0.1560178353256925</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.1496014852561591</v>
+        <v>0.1422167624120596</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.2167875984263936</v>
+        <v>0.2037243436122176</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.1182841311504481</v>
+        <v>0.1099146294422049</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.03796821366251502</v>
+        <v>0.03537226045148101</v>
       </c>
     </row>
     <row r="14">
@@ -1264,12 +1264,12 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1278,37 +1278,37 @@
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>24.08</v>
+        <v>45.23</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.03569892144972275</v>
+        <v>-0.01545492176092211</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.02707071015329077</v>
+        <v>-0.02014732036936784</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.04786772860669419</v>
+        <v>-0.002426127260285904</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.08030502174326015</v>
+        <v>0.0141255849701607</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.1101889963486014</v>
+        <v>0.1123954675842205</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.3385720786667437</v>
+        <v>0.231456447130798</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.04925731675268885</v>
+        <v>0.06393494770628649</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.04962981105947573</v>
+        <v>0.01368141307688586</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.3543389334058802</v>
+        <v>0.2503372400309611</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.1063922401628281</v>
+        <v>0.07731421118809978</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FWRLX</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Wireless</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>45.94</v>
+        <v>14.98</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.01930328240016999</v>
+        <v>0</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.007989694139707515</v>
+        <v>0.01079621124877539</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.03143236826233609</v>
+        <v>0.006720391601231279</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.05077761537103087</v>
+        <v>0.01697216617578001</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.1450648018387373</v>
+        <v>-0.09486403427188717</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.2600385181951754</v>
+        <v>0.1751179743733882</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.07279622323976764</v>
+        <v>0.2551433157371434</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.03231341455961201</v>
+        <v>0.2885194493603942</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.2699644411074296</v>
+        <v>0.7936922544612015</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.08292202568586471</v>
+        <v>0.2150178108135978</v>
       </c>
     </row>
     <row r="16">
@@ -1376,51 +1376,51 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>52.95</v>
+        <v>23.61</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.003791483657620054</v>
+        <v>-0.01951824397191093</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.01561628812587379</v>
+        <v>-0.03828915095402396</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.01157362209103519</v>
+        <v>0.01330478040522554</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.07556370618105723</v>
+        <v>0.02163565498895048</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.2189227080311937</v>
+        <v>0.08751734712130044</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.1114126633636754</v>
+        <v>0.2953580258851012</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>-0.004791090033746892</v>
+        <v>0.02622849975170105</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.07485917399422393</v>
+        <v>0.02987410656729828</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.1514441907067867</v>
+        <v>0.3279046156830066</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.04812793884710875</v>
+        <v>0.09914661515915468</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>FWRLX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Wireless</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>14.98</v>
+        <v>52.47</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.009433921038338067</v>
+        <v>-0.009065147031542375</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.0006679542437646457</v>
+        <v>-0.01316526184593758</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.005369122533839699</v>
+        <v>-0.03156144471836231</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.04975466444966914</v>
+        <v>0.07125360782123535</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>-0.09101942000396746</v>
+        <v>0.1772493062591676</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.1888888165643838</v>
+        <v>0.09952737264145961</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.2600886637274673</v>
+        <v>-0.01611525103707179</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.2968795796924908</v>
+        <v>0.05427946128539696</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.7936922544612015</v>
+        <v>0.1410062744703764</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.2150178108135978</v>
+        <v>0.04495120441565881</v>
       </c>
     </row>
     <row r="18">
@@ -1502,37 +1502,37 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>70.90000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.01069137539110843</v>
+        <v>-0.01128354068463322</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.02634626008371121</v>
+        <v>0.009213927412669687</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.03337707178480676</v>
+        <v>0.01344513994209295</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.05931572094130289</v>
+        <v>0.03377084497825833</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.01765258894599708</v>
+        <v>0.007314092787185089</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.07200481634789746</v>
+        <v>0.04026642984416395</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.2190850661962966</v>
+        <v>0.1952767031705027</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.1959931612342185</v>
+        <v>0.1755873764560663</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.7802202180840432</v>
+        <v>0.7601331994161846</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.2119682507567646</v>
+        <v>0.2073926049118651</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>FSLBX</t>
+          <t>FDFAX</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Brokerage &amp; Inv Mgmt</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>186.82</v>
+        <v>94.31</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.02891446708280077</v>
+        <v>-0.006112359940830148</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.002522142234017588</v>
+        <v>-0.00788975404231107</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.03215473659789359</v>
+        <v>-0.0146275367179064</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.04902022104467152</v>
+        <v>0.0007427811588600619</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.1688669535378804</v>
+        <v>0.06712509865041238</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.1451772665293714</v>
+        <v>0.02842610555348757</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.003715821549403975</v>
+        <v>0.1330625779350605</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>-0.02554147656527817</v>
+        <v>0.1197624198477694</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.6483819424660735</v>
+        <v>0.1651006665864259</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.1812793608701202</v>
+        <v>0.05225536872158654</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>FDFAX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>94.89</v>
+        <v>118.89</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.0009476096452315508</v>
+        <v>0.008824785142069524</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.002641589197086791</v>
+        <v>-0.01865457786022151</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.001900541726489013</v>
+        <v>-0.02485235256564056</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.01270013319278518</v>
+        <v>-0.04918427287947347</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.06971120497584171</v>
+        <v>-0.007844466552971774</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.02587353834271244</v>
+        <v>0.04162412389746684</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.13141930403108</v>
+        <v>0.152548021509092</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.1270383891391873</v>
+        <v>0.2254968845405563</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.1722659781915219</v>
+        <v>0.4399273417975569</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.05440806793346109</v>
+        <v>0.129224241563815</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>FSVLX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>17.99</v>
+        <v>103.01</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.0123803774725495</v>
+        <v>-0.005406947574044807</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.01262346602108533</v>
+        <v>-0.01284136423080973</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.01181097167394296</v>
+        <v>-0.01548308477217875</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.05020435799677392</v>
+        <v>0.03071842725463347</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.2122641230553464</v>
+        <v>-0.003675377267252533</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.1414974308280543</v>
+        <v>0.003271360890588992</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>-0.05116030380765557</v>
+        <v>0.1944321281314889</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>-0.09643395735854343</v>
+        <v>0.1626148979427879</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.206572766950138</v>
+        <v>0.2158053022501587</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.06459520626867654</v>
+        <v>0.06730369024238247</v>
       </c>
     </row>
     <row r="22">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
       <c r="F22" s="5" t="n">
-        <v>103.57</v>
+        <v>13.91</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.002792229095157972</v>
+        <v>0</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.01192520514824735</v>
+        <v>-0.008553092504847037</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.01221657548600663</v>
+        <v>-0.00713778585553293</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.0614943119685003</v>
+        <v>-0.0134752148168249</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>-0.0002895635109914085</v>
+        <v>0.01237264040217023</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.01168814928159256</v>
+        <v>0.007247417674119516</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.1934188074011494</v>
+        <v>0.1986825882951999</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.171956377903921</v>
+        <v>0.08690246673796587</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.2224148351776991</v>
+        <v>0.0547937359578432</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.06923427183640318</v>
+        <v>0.01794078211331973</v>
       </c>
     </row>
     <row r="23">
@@ -1768,51 +1768,51 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>117.85</v>
+        <v>185.16</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.005031522489699292</v>
+        <v>-0.008885577545388434</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.02948202109904874</v>
+        <v>-0.008460971321501476</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.02587208460870916</v>
+        <v>-0.0003778657185342649</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.03591295374972825</v>
+        <v>0.03187695688184644</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>-0.006909915795707877</v>
+        <v>0.1257296234906689</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.03234391354015664</v>
+        <v>0.1161354666506746</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1424660044873722</v>
+        <v>-0.01447869274886115</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.2138565956958591</v>
+        <v>-0.04449221291586569</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.4273315803280615</v>
+        <v>0.6337350069137886</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.1259219649656378</v>
+        <v>0.1777701369571916</v>
       </c>
     </row>
     <row r="24">
@@ -1824,51 +1824,51 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSVLX</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>42.66</v>
+        <v>17.73</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.01114010988389991</v>
+        <v>-0.0144524865030432</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.01112655421945841</v>
+        <v>-0.02044203488593266</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.01998619242549904</v>
+        <v>-0.02044203488593266</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.02335165866843658</v>
+        <v>0.01430205987110766</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.0317896065243648</v>
+        <v>0.1695250475390295</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.03452976895138615</v>
+        <v>0.09647492013493686</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.1233319749226063</v>
+        <v>-0.06635072375293893</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.1345392881346303</v>
+        <v>-0.1148278115608177</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.339068075895264</v>
+        <v>0.1891347903208516</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1022181345956459</v>
+        <v>0.05944161593507835</v>
       </c>
     </row>
     <row r="25">
@@ -1880,52 +1880,46 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>13.91</v>
+        <v>69.8</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.006428582327706489</v>
+        <v>0.00706976641789403</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.002867380817199727</v>
+        <v>-0.008522705413586351</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.001439849070915988</v>
+        <v>-0.03257101073349511</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.0007194409464950091</v>
+        <v>-0.075986203259228</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.01016698511215397</v>
+        <v>-0.01035014518890565</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.006531551938669944</v>
+        <v>0.001434807860750453</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1897296737783052</v>
-      </c>
-      <c r="N25" s="6" t="n">
-        <v>0.09604308518672422</v>
-      </c>
-      <c r="O25" s="6" t="n">
-        <v>0.0547937359578432</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v>0.01794078211331973</v>
-      </c>
+        <v>0.14448049429888</v>
+      </c>
+      <c r="N25" s="6" t="inlineStr"/>
+      <c r="O25" s="6" t="inlineStr"/>
+      <c r="P25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -1936,51 +1930,51 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>27.45</v>
+        <v>51.41</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.01254150294847522</v>
+        <v>-0.001165754262055119</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.03481011788071575</v>
+        <v>-0.0001944442218833053</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.04753639647438312</v>
+        <v>-0.0121060925640234</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.08712999529347287</v>
+        <v>-0.03816652734160142</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.01142230583134252</v>
+        <v>-0.06048978982914732</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>-0.05230616904524543</v>
+        <v>0.0406418567450455</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.1363801714664681</v>
+        <v>0.09194054327125434</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.1503578475719136</v>
+        <v>0.1693260499886728</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>1.049156410767717</v>
+        <v>0.6893424307734368</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2701598184324046</v>
+        <v>0.1909839167976672</v>
       </c>
     </row>
     <row r="27">
@@ -1992,46 +1986,52 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
+          <t>Defense and Aerospace</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
       <c r="F27" s="5" t="n">
-        <v>69.31</v>
+        <v>27.48</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.01108671733044431</v>
+        <v>0.00109285167442974</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.028182867986977</v>
+        <v>-0.02760087333079153</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.03682603612554403</v>
+        <v>-0.04682623604031511</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.06565115565579516</v>
+        <v>-0.1034257786540864</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>-0.003164119438595958</v>
+        <v>-0.01575933140599128</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.0007218512968703017</v>
+        <v>-0.06224587527861825</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.1458778744385456</v>
-      </c>
-      <c r="N27" s="6" t="inlineStr"/>
-      <c r="O27" s="6" t="inlineStr"/>
-      <c r="P27" s="6" t="inlineStr"/>
+        <v>0.1221689492968916</v>
+      </c>
+      <c r="N27" s="6" t="n">
+        <v>0.1450423868300328</v>
+      </c>
+      <c r="O27" s="6" t="n">
+        <v>1.051395980825927</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v>0.2706223788952469</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
@@ -2042,51 +2042,51 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>51.47</v>
+        <v>41.51</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.01518738552616594</v>
+        <v>-0.02695737294871714</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.01322850131762832</v>
+        <v>-0.03330229042639765</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.0007764919847290663</v>
+        <v>-0.0450886322551205</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.01643417886985821</v>
+        <v>-0.04837232145847725</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>-0.0576711419403344</v>
+        <v>-0.01546417263401134</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.05087950701343025</v>
+        <v>0.006398478637610339</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.09941205210080795</v>
+        <v>0.09531991582171817</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.1852648060679702</v>
+        <v>0.09642996155702854</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.6913140873792729</v>
+        <v>0.3029702403603334</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.1914470749890909</v>
+        <v>0.09222345573826241</v>
       </c>
     </row>
     <row r="29">
@@ -2112,37 +2112,37 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>17.38</v>
+        <v>17.44</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.006952429333341836</v>
+        <v>0.003452323140870073</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.0005756085808943379</v>
+        <v>-0.008527550723653965</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.009122106408734565</v>
+        <v>-0.013016386035272</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.05697238887805678</v>
+        <v>-0.05525452876500925</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.01046502266528893</v>
+        <v>0.01218810199655018</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.01794573949972977</v>
+        <v>0.008719466889954175</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.02869223986985725</v>
+        <v>0.03940837869111102</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.03892281417891286</v>
+        <v>0.01820616497162053</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.4149720530548233</v>
+        <v>0.4198569938172687</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1226626839287659</v>
+        <v>0.1239531315064422</v>
       </c>
     </row>
     <row r="30">
@@ -2168,37 +2168,37 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>16.49</v>
+        <v>16.31</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-0.004227034847928635</v>
+        <v>-0.01091572514700989</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.03000001346363745</v>
+        <v>-0.04842473472941466</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.04127912560045444</v>
+        <v>-0.05885749926452066</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.01961949641459271</v>
+        <v>-0.0354819862143021</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.06800519554863849</v>
+        <v>0.0475272823135735</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.04252667541477329</v>
+        <v>0.02868141840275684</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.005180122439891743</v>
+        <v>0.004087442861224089</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>-0.0895859929388888</v>
+        <v>-0.1012101463350646</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.2845062014447728</v>
+        <v>0.2704849791813029</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.08703969109643928</v>
+        <v>0.08306996293701974</v>
       </c>
     </row>
     <row r="31">
@@ -2210,51 +2210,51 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
       <c r="F31" s="5" t="n">
-        <v>64.28</v>
+        <v>55.33</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.01468035244792776</v>
+        <v>-0.001804049676538688</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.007997464605178806</v>
+        <v>0.01374129671745949</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.007412034297402448</v>
+        <v>-0.009310593684391133</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.03526937672206709</v>
+        <v>0.01040912211455169</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.01997252068509381</v>
+        <v>-0.01653033270928062</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.01319827403023033</v>
+        <v>-0.01299858296256096</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>-0.02387587630729238</v>
+        <v>-0.01888197378021861</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.02121504269310681</v>
+        <v>-0.007482528813908207</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.4120778607190725</v>
+        <v>0.2224945164681267</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.121896727795223</v>
+        <v>0.06925750347948578</v>
       </c>
     </row>
     <row r="32">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2280,37 +2280,37 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>55.43</v>
+        <v>63.89</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.01799815479347711</v>
+        <v>-0.006067196593881219</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.0161320088070207</v>
+        <v>-0.009457373803900215</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.009837874321951379</v>
+        <v>-0.02428228292258927</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.02081033303853141</v>
+        <v>-0.04513531769795942</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.01282281747350056</v>
+        <v>-0.02562147800815673</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>-0.001294960102706022</v>
+        <v>-0.01002273089448691</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>-0.01081405453352891</v>
+        <v>-0.02543494245029465</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.005041794542151701</v>
+        <v>-0.006193290426003917</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.2247038399975321</v>
+        <v>0.4035103891183653</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.0699012457254693</v>
+        <v>0.1196231696556525</v>
       </c>
     </row>
     <row r="33">
@@ -2336,37 +2336,37 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>127.85</v>
+        <v>128.33</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.009076571062181626</v>
+        <v>0.003754425988755417</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.002730097367025675</v>
+        <v>0.01366511356860123</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.01623582741413443</v>
+        <v>0.009518557727573596</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.04196327165367431</v>
+        <v>-0.02469980205786071</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.04171783301933008</v>
+        <v>-0.04354794448729971</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.09288978410225213</v>
+        <v>-0.09326310074223132</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>-0.02660277321600679</v>
+        <v>-0.02401358497993078</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.04229686831170421</v>
+        <v>0.04710404761015452</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.5278721440304364</v>
+        <v>0.5336082870885552</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1517609176316332</v>
+        <v>0.1532004828340117</v>
       </c>
     </row>
     <row r="34">
@@ -2392,37 +2392,37 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>115.99</v>
+        <v>117.34</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.00843332680414921</v>
+        <v>0.01163892144999146</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.02250131228668106</v>
+        <v>-0.00390498049193666</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.04219653736365292</v>
+        <v>-0.03128870636064018</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.06263132482459144</v>
+        <v>-0.07343653740192613</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.05345195856717055</v>
+        <v>-0.04841457577570973</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.08483892865464948</v>
+        <v>-0.07573626107622489</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.02758820073600687</v>
+        <v>-0.01276347617420259</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.04589009622407458</v>
+        <v>-0.05247213785370597</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2835213625568711</v>
+        <v>0.2984601668750564</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.08676180670338551</v>
+        <v>0.09096179924427661</v>
       </c>
     </row>
   </sheetData>
@@ -2562,17 +2562,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -2607,17 +2607,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FSAVX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FSAVX</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2697,17 +2697,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FSAGX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -2742,17 +2742,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FSPHX</t>
+          <t>FSAGX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2787,17 +2787,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSPHX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -2809,17 +2809,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -2854,12 +2854,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2899,17 +2899,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>FSDAX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Defense and Aerospace</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -2944,17 +2944,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.3554907061149115</v>
+        <v>0.2724911643162278</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.08712999529347287</v>
+        <v>-0.1034257786540864</v>
       </c>
     </row>
     <row r="18">
@@ -3073,21 +3073,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.1171790168469589</v>
+        <v>0.100460420590305</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -3109,7 +3109,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.06565115565579516</v>
+        <v>-0.075986203259228</v>
       </c>
     </row>
     <row r="19">
@@ -3118,21 +3118,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.1028651259996782</v>
+        <v>0.07670655521898428</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.06263132482459144</v>
+        <v>-0.07343653740192613</v>
       </c>
     </row>
     <row r="20">
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.09330403381555352</v>
+        <v>0.07536231503469604</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.05697238887805678</v>
+        <v>-0.05525452876500925</v>
       </c>
     </row>
     <row r="21">
@@ -3208,21 +3208,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSMEX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Medical Tech &amp; Devices</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.08030502174326015</v>
+        <v>0.07125360782123535</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -3230,21 +3230,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.04196327165367431</v>
+        <v>-0.04918427287947347</v>
       </c>
     </row>
     <row r="22">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FSMEX</t>
+          <t>FPHAX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Medical Tech &amp; Devices</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.07556370618105723</v>
+        <v>0.05029769399269157</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -3275,21 +3275,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.03591295374972825</v>
+        <v>-0.04837232145847725</v>
       </c>
     </row>
     <row r="23">
@@ -3298,21 +3298,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FPHAX</t>
+          <t>FSTCX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.06836589800036652</v>
+        <v>0.03377084497825833</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.03526937672206709</v>
+        <v>-0.04513531769795942</v>
       </c>
     </row>
     <row r="24">
@@ -3343,21 +3343,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FSDPX</t>
+          <t>FSLBX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Brokerage &amp; Inv Mgmt</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.0614943119685003</v>
+        <v>0.03187695688184644</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -3365,21 +3365,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>FRESX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Real Estate Investment</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.02335165866843658</v>
+        <v>-0.03816652734160142</v>
       </c>
     </row>
     <row r="25">
@@ -3388,21 +3388,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FSTCX</t>
+          <t>FSDPX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.05931572094130289</v>
+        <v>0.03071842725463347</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.01961949641459271</v>
+        <v>-0.0354819862143021</v>
       </c>
     </row>
     <row r="26">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.05077761537103087</v>
+        <v>0.02163565498895048</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -3455,21 +3455,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.01643417886985821</v>
+        <v>-0.02881114053473155</v>
       </c>
     </row>
     <row r="27"/>
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.2577361588498377</v>
+        <v>0.2171838156077872</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.1921616297728077</v>
+        <v>-0.1528583260800356</v>
       </c>
     </row>
     <row r="32">
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.2418952545307658</v>
+        <v>0.2001617814220076</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.09101942000396746</v>
+        <v>-0.09486403427188717</v>
       </c>
     </row>
     <row r="33">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.2189227080311937</v>
+        <v>0.1772493062591676</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -3651,21 +3651,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>FDCPX</t>
+          <t>FSLEX</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Tech Hardware</t>
+          <t>Environment &amp; Alt Energy</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.07878402446946553</v>
+        <v>-0.06048978982914732</v>
       </c>
     </row>
     <row r="34">
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.2122641230553464</v>
+        <v>0.1695250475390295</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -3696,21 +3696,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>FSLEX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Environment &amp; Alt Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.0576711419403344</v>
+        <v>-0.04870519783401617</v>
       </c>
     </row>
     <row r="35">
@@ -3733,7 +3733,7 @@
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.2026210699294706</v>
+        <v>0.1633033246408868</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -3741,21 +3741,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.05441123000811454</v>
+        <v>-0.04841457577570973</v>
       </c>
     </row>
     <row r="36">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.1934087316466444</v>
+        <v>0.1583313705288181</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -3786,21 +3786,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FDCPX</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Tech Hardware</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.05345195856717055</v>
+        <v>-0.04648938468019193</v>
       </c>
     </row>
     <row r="37">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1825972606349773</v>
+        <v>0.1464354997645521</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.04171783301933008</v>
+        <v>-0.04354794448729971</v>
       </c>
     </row>
     <row r="38">
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1688669535378804</v>
+        <v>0.1257296234906689</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.01997252068509381</v>
+        <v>-0.02562147800815673</v>
       </c>
     </row>
     <row r="39">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1450648018387373</v>
+        <v>0.1123954675842205</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.01282281747350056</v>
+        <v>-0.01653033270928062</v>
       </c>
     </row>
     <row r="40">
@@ -3944,21 +3944,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1271236154123605</v>
+        <v>0.1102906412244469</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FSRFX</t>
+          <t>FSDAX</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Defense and Aerospace</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.006909915795707877</v>
+        <v>-0.01575933140599128</v>
       </c>
     </row>
     <row r="41"/>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.4938975646941843</v>
+        <v>0.4881384780615803</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.09288978410225213</v>
+        <v>-0.09326310074223132</v>
       </c>
     </row>
     <row r="46">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FSPTX</t>
+          <t>FSELX</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.4105544324177868</v>
+        <v>0.4196277453949253</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -4131,7 +4131,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.08483892865464948</v>
+        <v>-0.07573626107622489</v>
       </c>
     </row>
     <row r="47">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FSELX</t>
+          <t>FSPTX</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.3991717461873354</v>
+        <v>0.4008664274395921</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.05230616904524543</v>
+        <v>-0.06224587527861825</v>
       </c>
     </row>
     <row r="48">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.3385720786667437</v>
+        <v>0.2953580258851012</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.02717773275784641</v>
+        <v>-0.04606616324414392</v>
       </c>
     </row>
     <row r="49">
@@ -4230,21 +4230,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FBSOX</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Enterprise Tech Services</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.2610546688730686</v>
+        <v>0.231456447130798</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.001294960102706022</v>
+        <v>-0.01299858296256096</v>
       </c>
     </row>
     <row r="50">
@@ -4275,21 +4275,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FBSOX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Enterprise Tech Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.2600385181951754</v>
+        <v>0.2271056958961459</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -4297,21 +4297,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>FIDRX</t>
+          <t>FSCPX</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>0.0007218512968703017</v>
+        <v>-0.01002273089448691</v>
       </c>
     </row>
     <row r="51">
@@ -4334,7 +4334,7 @@
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.2125937181650828</v>
+        <v>0.193723085193934</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -4342,21 +4342,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>FSCHX</t>
+          <t>FIDRX</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0.006531551938669944</v>
+        <v>0.001434807860750453</v>
       </c>
     </row>
     <row r="52">
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.1965726511943291</v>
+        <v>0.1928076187977046</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>0.01168814928159256</v>
+        <v>0.003271360890588992</v>
       </c>
     </row>
     <row r="53">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.1915662380442442</v>
+        <v>0.180951189962268</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -4432,21 +4432,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>FSCPX</t>
+          <t>FRESX</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate Investment</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.01319827403023033</v>
+        <v>0.006398478637610339</v>
       </c>
     </row>
     <row r="54">
@@ -4469,7 +4469,7 @@
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.1888888165643838</v>
+        <v>0.1751179743733882</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -4477,21 +4477,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>FSRPX</t>
+          <t>FSCHX</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.01794573949972977</v>
+        <v>0.007247417674119516</v>
       </c>
     </row>
     <row r="55"/>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.9386741294708902</v>
+        <v>0.944512198213405</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.09643395735854343</v>
+        <v>-0.1148278115608177</v>
       </c>
     </row>
     <row r="60">
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.8476440521545707</v>
+        <v>0.8744448065313644</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.0895859929388888</v>
+        <v>-0.1012101463350646</v>
       </c>
     </row>
     <row r="61">
@@ -4651,21 +4651,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FSENX</t>
+          <t>FBIOX</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.5821441070209217</v>
+        <v>0.5637254242607663</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.04589009622407458</v>
+        <v>-0.05247213785370597</v>
       </c>
     </row>
     <row r="62">
@@ -4696,21 +4696,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FBIOX</t>
+          <t>FSENX</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.5777879032587259</v>
+        <v>0.5590290012319978</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.02554147656527817</v>
+        <v>-0.04449221291586569</v>
       </c>
     </row>
     <row r="63">
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.5677063463050824</v>
+        <v>0.5517388278611113</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>0.005041794542151701</v>
+        <v>-0.007482528813908207</v>
       </c>
     </row>
     <row r="64">
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.5216264313801517</v>
+        <v>0.5203395510118518</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>0.02121504269310681</v>
+        <v>-0.006193290426003917</v>
       </c>
     </row>
     <row r="65">
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.4645741038173641</v>
+        <v>0.4483397004692005</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.03231341455961201</v>
+        <v>0.01368141307688586</v>
       </c>
     </row>
     <row r="66">
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.3459809014449917</v>
+        <v>0.3280487452047611</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>0.03892281417891286</v>
+        <v>0.01820616497162053</v>
       </c>
     </row>
     <row r="67">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.2968795796924908</v>
+        <v>0.2885194493603942</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -4943,21 +4943,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>FSUTX</t>
+          <t>FSCSX</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Software &amp; IT Services</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.04229686831170421</v>
+        <v>0.02987410656729828</v>
       </c>
     </row>
     <row r="68">
@@ -4966,21 +4966,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FSRBX</t>
+          <t>FSRFX</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.2313803530319625</v>
+        <v>0.2254968845405563</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -4988,21 +4988,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>FSCSX</t>
+          <t>FSUTX</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Software &amp; IT Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.04962981105947573</v>
+        <v>0.04710404761015452</v>
       </c>
     </row>
     <row r="69"/>
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.492861212338668</v>
+        <v>2.435765431263782</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.280748433069891</v>
+        <v>2.378779795097108</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.1182841311504481</v>
+        <v>0.1099146294422049</v>
       </c>
     </row>
     <row r="75">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.095899172553695</v>
+        <v>2.15791772195673</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1514441907067867</v>
+        <v>0.1410062744703764</v>
       </c>
     </row>
     <row r="76">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.434819223918615</v>
+        <v>1.451613969204115</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1722659781915219</v>
+        <v>0.1651006665864259</v>
       </c>
     </row>
     <row r="77">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.156688689021698</v>
+        <v>1.16285366246064</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.206572766950138</v>
+        <v>0.1891347903208516</v>
       </c>
     </row>
     <row r="78">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.049156410767717</v>
+        <v>1.051395980825927</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.2224148351776991</v>
+        <v>0.2158053022501587</v>
       </c>
     </row>
     <row r="79">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.01614684637042</v>
+        <v>0.9972191429973363</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.2247038399975321</v>
+        <v>0.2224945164681267</v>
       </c>
     </row>
     <row r="80">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.9690560744034227</v>
+        <v>0.9591776451451504</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.2699644411074296</v>
+        <v>0.2503372400309611</v>
       </c>
     </row>
     <row r="81">
@@ -5454,12 +5454,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>FSHOX</t>
+          <t>FDLSX</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Construction &amp; Housing</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.2835213625568711</v>
+        <v>0.2704849791813029</v>
       </c>
     </row>
     <row r="82">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.7802202180840432</v>
+        <v>0.7601331994161846</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -5499,12 +5499,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>FDLSX</t>
+          <t>FSHOX</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Construction &amp; Housing</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.2845062014447728</v>
+        <v>0.2984601668750564</v>
       </c>
     </row>
   </sheetData>
